--- a/vs-x64/Running insertion.xlsx
+++ b/vs-x64/Running insertion.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>23.9636</v>
+        <v>24.7831</v>
       </c>
       <c r="C2" t="n">
-        <v>53.6061</v>
+        <v>31.6017</v>
       </c>
       <c r="D2" t="n">
-        <v>57.8235</v>
+        <v>59.6592</v>
       </c>
       <c r="E2" t="n">
-        <v>16.4245</v>
+        <v>16.5562</v>
       </c>
       <c r="F2" t="n">
-        <v>46.52</v>
+        <v>46.9936</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>22.7295</v>
+        <v>23.1199</v>
       </c>
       <c r="C3" t="n">
-        <v>52.9646</v>
+        <v>30.9836</v>
       </c>
       <c r="D3" t="n">
-        <v>57.7677</v>
+        <v>59.2992</v>
       </c>
       <c r="E3" t="n">
-        <v>15.9942</v>
+        <v>16.1141</v>
       </c>
       <c r="F3" t="n">
-        <v>45.851</v>
+        <v>46.2719</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>22.6705</v>
+        <v>22.6208</v>
       </c>
       <c r="C4" t="n">
-        <v>52.7386</v>
+        <v>30.516</v>
       </c>
       <c r="D4" t="n">
-        <v>57.5732</v>
+        <v>58.842</v>
       </c>
       <c r="E4" t="n">
-        <v>15.6808</v>
+        <v>15.7516</v>
       </c>
       <c r="F4" t="n">
-        <v>45.5118</v>
+        <v>46.0073</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>22.4282</v>
+        <v>22.5089</v>
       </c>
       <c r="C5" t="n">
-        <v>51.9053</v>
+        <v>30.1138</v>
       </c>
       <c r="D5" t="n">
-        <v>56.6137</v>
+        <v>58.1588</v>
       </c>
       <c r="E5" t="n">
-        <v>15.2712</v>
+        <v>15.3508</v>
       </c>
       <c r="F5" t="n">
-        <v>44.9903</v>
+        <v>45.3195</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>21.6119</v>
+        <v>21.9019</v>
       </c>
       <c r="C6" t="n">
-        <v>51.1934</v>
+        <v>29.618</v>
       </c>
       <c r="D6" t="n">
-        <v>56.1013</v>
+        <v>57.6472</v>
       </c>
       <c r="E6" t="n">
-        <v>14.9756</v>
+        <v>15.0763</v>
       </c>
       <c r="F6" t="n">
-        <v>44.5837</v>
+        <v>44.9726</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>21.3438</v>
+        <v>21.8809</v>
       </c>
       <c r="C7" t="n">
-        <v>50.8778</v>
+        <v>29.262</v>
       </c>
       <c r="D7" t="n">
-        <v>67.25230000000001</v>
+        <v>68.54089999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>14.7076</v>
+        <v>14.8818</v>
       </c>
       <c r="F7" t="n">
-        <v>44.0606</v>
+        <v>44.6755</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>21.4496</v>
+        <v>21.3633</v>
       </c>
       <c r="C8" t="n">
-        <v>50.7129</v>
+        <v>36.9839</v>
       </c>
       <c r="D8" t="n">
-        <v>66.072</v>
+        <v>67.64570000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>14.621</v>
+        <v>14.7358</v>
       </c>
       <c r="F8" t="n">
-        <v>44.4003</v>
+        <v>45.1065</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>21.0818</v>
+        <v>20.9668</v>
       </c>
       <c r="C9" t="n">
-        <v>50.551</v>
+        <v>36.2231</v>
       </c>
       <c r="D9" t="n">
-        <v>65.0646</v>
+        <v>66.5303</v>
       </c>
       <c r="E9" t="n">
-        <v>21.6689</v>
+        <v>21.7557</v>
       </c>
       <c r="F9" t="n">
-        <v>51.0439</v>
+        <v>52.0044</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>27.6754</v>
+        <v>27.8499</v>
       </c>
       <c r="C10" t="n">
-        <v>58.0405</v>
+        <v>35.5128</v>
       </c>
       <c r="D10" t="n">
-        <v>64.2535</v>
+        <v>65.57899999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>20.8635</v>
+        <v>21.0219</v>
       </c>
       <c r="F10" t="n">
-        <v>50.0488</v>
+        <v>51.0247</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>27.0194</v>
+        <v>27.4962</v>
       </c>
       <c r="C11" t="n">
-        <v>57.6389</v>
+        <v>34.9169</v>
       </c>
       <c r="D11" t="n">
-        <v>63.2234</v>
+        <v>64.6557</v>
       </c>
       <c r="E11" t="n">
-        <v>20.1477</v>
+        <v>20.3813</v>
       </c>
       <c r="F11" t="n">
-        <v>49.5956</v>
+        <v>50.629</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>26.4079</v>
+        <v>26.514</v>
       </c>
       <c r="C12" t="n">
-        <v>56.6147</v>
+        <v>34.1684</v>
       </c>
       <c r="D12" t="n">
-        <v>62.3442</v>
+        <v>63.6275</v>
       </c>
       <c r="E12" t="n">
-        <v>19.5099</v>
+        <v>19.7047</v>
       </c>
       <c r="F12" t="n">
-        <v>48.8179</v>
+        <v>49.8396</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>25.8387</v>
+        <v>26.0082</v>
       </c>
       <c r="C13" t="n">
-        <v>55.9833</v>
+        <v>33.5736</v>
       </c>
       <c r="D13" t="n">
-        <v>61.7642</v>
+        <v>63.0913</v>
       </c>
       <c r="E13" t="n">
-        <v>18.9049</v>
+        <v>19.0733</v>
       </c>
       <c r="F13" t="n">
-        <v>48.1475</v>
+        <v>48.9767</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>25.3196</v>
+        <v>25.0854</v>
       </c>
       <c r="C14" t="n">
-        <v>55.2575</v>
+        <v>32.9639</v>
       </c>
       <c r="D14" t="n">
-        <v>60.9722</v>
+        <v>62.4336</v>
       </c>
       <c r="E14" t="n">
-        <v>18.3261</v>
+        <v>18.5031</v>
       </c>
       <c r="F14" t="n">
-        <v>47.5227</v>
+        <v>48.1559</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>24.6222</v>
+        <v>24.5733</v>
       </c>
       <c r="C15" t="n">
-        <v>54.5408</v>
+        <v>32.4908</v>
       </c>
       <c r="D15" t="n">
-        <v>60.1992</v>
+        <v>61.5797</v>
       </c>
       <c r="E15" t="n">
-        <v>17.7925</v>
+        <v>17.9872</v>
       </c>
       <c r="F15" t="n">
-        <v>46.8245</v>
+        <v>47.6527</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>24.3824</v>
+        <v>24.6765</v>
       </c>
       <c r="C16" t="n">
-        <v>53.9254</v>
+        <v>31.9401</v>
       </c>
       <c r="D16" t="n">
-        <v>59.8211</v>
+        <v>61.4671</v>
       </c>
       <c r="E16" t="n">
-        <v>17.312</v>
+        <v>17.4883</v>
       </c>
       <c r="F16" t="n">
-        <v>46.2591</v>
+        <v>47.2185</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>23.5877</v>
+        <v>23.8969</v>
       </c>
       <c r="C17" t="n">
-        <v>53.3502</v>
+        <v>31.3886</v>
       </c>
       <c r="D17" t="n">
-        <v>59.3653</v>
+        <v>60.5789</v>
       </c>
       <c r="E17" t="n">
-        <v>16.8281</v>
+        <v>16.9739</v>
       </c>
       <c r="F17" t="n">
-        <v>45.5927</v>
+        <v>46.5981</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>23.3214</v>
+        <v>23.5466</v>
       </c>
       <c r="C18" t="n">
-        <v>53.0795</v>
+        <v>30.9553</v>
       </c>
       <c r="D18" t="n">
-        <v>59.0644</v>
+        <v>60.3421</v>
       </c>
       <c r="E18" t="n">
-        <v>16.4052</v>
+        <v>16.5666</v>
       </c>
       <c r="F18" t="n">
-        <v>45.3821</v>
+        <v>45.8912</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>23.1033</v>
+        <v>23.0593</v>
       </c>
       <c r="C19" t="n">
-        <v>52.3312</v>
+        <v>30.4334</v>
       </c>
       <c r="D19" t="n">
-        <v>58.2832</v>
+        <v>59.7606</v>
       </c>
       <c r="E19" t="n">
-        <v>16.0911</v>
+        <v>16.1819</v>
       </c>
       <c r="F19" t="n">
-        <v>44.7477</v>
+        <v>45.2668</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>22.7173</v>
+        <v>22.3934</v>
       </c>
       <c r="C20" t="n">
-        <v>52.1245</v>
+        <v>30.0455</v>
       </c>
       <c r="D20" t="n">
-        <v>58.2853</v>
+        <v>59.7877</v>
       </c>
       <c r="E20" t="n">
-        <v>15.7844</v>
+        <v>15.909</v>
       </c>
       <c r="F20" t="n">
-        <v>44.4323</v>
+        <v>45.1991</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>22.61</v>
+        <v>22.3772</v>
       </c>
       <c r="C21" t="n">
-        <v>51.6084</v>
+        <v>29.602</v>
       </c>
       <c r="D21" t="n">
-        <v>70.4277</v>
+        <v>72.2359</v>
       </c>
       <c r="E21" t="n">
-        <v>15.6172</v>
+        <v>15.7509</v>
       </c>
       <c r="F21" t="n">
-        <v>44.0984</v>
+        <v>45.0413</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>22.1939</v>
+        <v>22.2826</v>
       </c>
       <c r="C22" t="n">
-        <v>51.1193</v>
+        <v>41.5558</v>
       </c>
       <c r="D22" t="n">
-        <v>69.20480000000001</v>
+        <v>71.1246</v>
       </c>
       <c r="E22" t="n">
-        <v>15.5785</v>
+        <v>15.6654</v>
       </c>
       <c r="F22" t="n">
-        <v>44.1752</v>
+        <v>44.8309</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>22.12</v>
+        <v>22.1506</v>
       </c>
       <c r="C23" t="n">
-        <v>51.1983</v>
+        <v>40.883</v>
       </c>
       <c r="D23" t="n">
-        <v>68.1622</v>
+        <v>69.9248</v>
       </c>
       <c r="E23" t="n">
-        <v>27.7587</v>
+        <v>27.6752</v>
       </c>
       <c r="F23" t="n">
-        <v>51.4474</v>
+        <v>52.8508</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>42.2258</v>
+        <v>37.9308</v>
       </c>
       <c r="C24" t="n">
-        <v>61.819</v>
+        <v>39.7646</v>
       </c>
       <c r="D24" t="n">
-        <v>67.2872</v>
+        <v>69.2216</v>
       </c>
       <c r="E24" t="n">
-        <v>26.8127</v>
+        <v>26.7596</v>
       </c>
       <c r="F24" t="n">
-        <v>50.5009</v>
+        <v>52.4769</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>38.5141</v>
+        <v>36.9023</v>
       </c>
       <c r="C25" t="n">
-        <v>58.6288</v>
+        <v>39.011</v>
       </c>
       <c r="D25" t="n">
-        <v>65.5097</v>
+        <v>68.3822</v>
       </c>
       <c r="E25" t="n">
-        <v>25.8611</v>
+        <v>25.8812</v>
       </c>
       <c r="F25" t="n">
-        <v>49.1684</v>
+        <v>51.4639</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>37.6964</v>
+        <v>41.4845</v>
       </c>
       <c r="C26" t="n">
-        <v>57.1865</v>
+        <v>38.1593</v>
       </c>
       <c r="D26" t="n">
-        <v>64.5575</v>
+        <v>67.6454</v>
       </c>
       <c r="E26" t="n">
-        <v>25.0794</v>
+        <v>24.96</v>
       </c>
       <c r="F26" t="n">
-        <v>48.6451</v>
+        <v>50.4417</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>34.7561</v>
+        <v>34.9069</v>
       </c>
       <c r="C27" t="n">
-        <v>56.4514</v>
+        <v>37.3502</v>
       </c>
       <c r="D27" t="n">
-        <v>63.844</v>
+        <v>66.5959</v>
       </c>
       <c r="E27" t="n">
-        <v>24.2366</v>
+        <v>24.1618</v>
       </c>
       <c r="F27" t="n">
-        <v>47.7515</v>
+        <v>50.1981</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>36.2256</v>
+        <v>33.9521</v>
       </c>
       <c r="C28" t="n">
-        <v>55.945</v>
+        <v>36.6268</v>
       </c>
       <c r="D28" t="n">
-        <v>63.2269</v>
+        <v>66.0164</v>
       </c>
       <c r="E28" t="n">
-        <v>23.3974</v>
+        <v>23.3321</v>
       </c>
       <c r="F28" t="n">
-        <v>47.2877</v>
+        <v>49.4006</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>34.6728</v>
+        <v>36.4219</v>
       </c>
       <c r="C29" t="n">
-        <v>55.3104</v>
+        <v>35.9321</v>
       </c>
       <c r="D29" t="n">
-        <v>62.6624</v>
+        <v>65.51220000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>22.7018</v>
+        <v>22.5895</v>
       </c>
       <c r="F29" t="n">
-        <v>46.7878</v>
+        <v>48.7142</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>33.8378</v>
+        <v>31.9347</v>
       </c>
       <c r="C30" t="n">
-        <v>54.8732</v>
+        <v>35.2307</v>
       </c>
       <c r="D30" t="n">
-        <v>62.0873</v>
+        <v>64.4216</v>
       </c>
       <c r="E30" t="n">
-        <v>21.9766</v>
+        <v>21.8967</v>
       </c>
       <c r="F30" t="n">
-        <v>46.1921</v>
+        <v>47.3842</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>30.9681</v>
+        <v>34.5142</v>
       </c>
       <c r="C31" t="n">
-        <v>54.0647</v>
+        <v>34.6168</v>
       </c>
       <c r="D31" t="n">
-        <v>61.5746</v>
+        <v>63.946</v>
       </c>
       <c r="E31" t="n">
-        <v>21.3265</v>
+        <v>21.2286</v>
       </c>
       <c r="F31" t="n">
-        <v>45.6566</v>
+        <v>47.0661</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>30.1173</v>
+        <v>33.5515</v>
       </c>
       <c r="C32" t="n">
-        <v>53.607</v>
+        <v>33.9647</v>
       </c>
       <c r="D32" t="n">
-        <v>61.1384</v>
+        <v>63.3422</v>
       </c>
       <c r="E32" t="n">
-        <v>20.7489</v>
+        <v>20.6563</v>
       </c>
       <c r="F32" t="n">
-        <v>45.2344</v>
+        <v>46.5556</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>29.7547</v>
+        <v>34.1421</v>
       </c>
       <c r="C33" t="n">
-        <v>53.5822</v>
+        <v>33.3605</v>
       </c>
       <c r="D33" t="n">
-        <v>61.4912</v>
+        <v>62.9243</v>
       </c>
       <c r="E33" t="n">
-        <v>20.2299</v>
+        <v>20.0794</v>
       </c>
       <c r="F33" t="n">
-        <v>45.3094</v>
+        <v>46.0407</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>28.8882</v>
+        <v>31.879</v>
       </c>
       <c r="C34" t="n">
-        <v>53.1001</v>
+        <v>32.8243</v>
       </c>
       <c r="D34" t="n">
-        <v>61.0236</v>
+        <v>62.2496</v>
       </c>
       <c r="E34" t="n">
-        <v>19.7485</v>
+        <v>19.6236</v>
       </c>
       <c r="F34" t="n">
-        <v>44.9777</v>
+        <v>45.7429</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>28.1991</v>
+        <v>29.5561</v>
       </c>
       <c r="C35" t="n">
-        <v>52.8223</v>
+        <v>32.2636</v>
       </c>
       <c r="D35" t="n">
-        <v>73.9119</v>
+        <v>75.4863</v>
       </c>
       <c r="E35" t="n">
-        <v>19.3621</v>
+        <v>19.3247</v>
       </c>
       <c r="F35" t="n">
-        <v>44.649</v>
+        <v>45.3819</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>27.6332</v>
+        <v>27.6856</v>
       </c>
       <c r="C36" t="n">
-        <v>52.7434</v>
+        <v>31.767</v>
       </c>
       <c r="D36" t="n">
-        <v>72.9616</v>
+        <v>74.68680000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>19.17</v>
+        <v>19.1117</v>
       </c>
       <c r="F36" t="n">
-        <v>44.6622</v>
+        <v>45.3928</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>30.4605</v>
+        <v>30.1975</v>
       </c>
       <c r="C37" t="n">
-        <v>52.7036</v>
+        <v>43.9057</v>
       </c>
       <c r="D37" t="n">
-        <v>71.53740000000001</v>
+        <v>73.4191</v>
       </c>
       <c r="E37" t="n">
-        <v>31.6584</v>
+        <v>31.3113</v>
       </c>
       <c r="F37" t="n">
-        <v>55.1527</v>
+        <v>55.6792</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>52.6891</v>
+        <v>47.436</v>
       </c>
       <c r="C38" t="n">
-        <v>67.392</v>
+        <v>42.7832</v>
       </c>
       <c r="D38" t="n">
-        <v>70.6319</v>
+        <v>72.1399</v>
       </c>
       <c r="E38" t="n">
-        <v>30.4127</v>
+        <v>30.3033</v>
       </c>
       <c r="F38" t="n">
-        <v>54.2768</v>
+        <v>54.6556</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>51.4279</v>
+        <v>43.5495</v>
       </c>
       <c r="C39" t="n">
-        <v>65.43689999999999</v>
+        <v>41.8611</v>
       </c>
       <c r="D39" t="n">
-        <v>69.48220000000001</v>
+        <v>71.04130000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>29.4092</v>
+        <v>29.225</v>
       </c>
       <c r="F39" t="n">
-        <v>53.3968</v>
+        <v>53.8455</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>47.053</v>
+        <v>44.7571</v>
       </c>
       <c r="C40" t="n">
-        <v>64.456</v>
+        <v>40.7027</v>
       </c>
       <c r="D40" t="n">
-        <v>68.6117</v>
+        <v>70.1259</v>
       </c>
       <c r="E40" t="n">
-        <v>28.3514</v>
+        <v>27.9832</v>
       </c>
       <c r="F40" t="n">
-        <v>52.6866</v>
+        <v>53.2704</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>45.5662</v>
+        <v>43.2178</v>
       </c>
       <c r="C41" t="n">
-        <v>63.2529</v>
+        <v>39.7878</v>
       </c>
       <c r="D41" t="n">
-        <v>67.6247</v>
+        <v>69.3511</v>
       </c>
       <c r="E41" t="n">
-        <v>27.4292</v>
+        <v>27.2534</v>
       </c>
       <c r="F41" t="n">
-        <v>51.8775</v>
+        <v>52.305</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>46.7354</v>
+        <v>40.0823</v>
       </c>
       <c r="C42" t="n">
-        <v>64.02070000000001</v>
+        <v>38.9112</v>
       </c>
       <c r="D42" t="n">
-        <v>67.0787</v>
+        <v>68.34059999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>26.4418</v>
+        <v>26.281</v>
       </c>
       <c r="F42" t="n">
-        <v>51.2541</v>
+        <v>51.7278</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>44.7448</v>
+        <v>39.1344</v>
       </c>
       <c r="C43" t="n">
-        <v>62.9053</v>
+        <v>38.4206</v>
       </c>
       <c r="D43" t="n">
-        <v>66.12520000000001</v>
+        <v>67.7697</v>
       </c>
       <c r="E43" t="n">
-        <v>25.5728</v>
+        <v>25.5304</v>
       </c>
       <c r="F43" t="n">
-        <v>50.3858</v>
+        <v>50.9291</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>43.4463</v>
+        <v>39.7747</v>
       </c>
       <c r="C44" t="n">
-        <v>62.4756</v>
+        <v>37.5532</v>
       </c>
       <c r="D44" t="n">
-        <v>65.5457</v>
+        <v>67.43689999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>24.7479</v>
+        <v>24.5324</v>
       </c>
       <c r="F44" t="n">
-        <v>49.7732</v>
+        <v>52.3939</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>42.8921</v>
+        <v>36.7948</v>
       </c>
       <c r="C45" t="n">
-        <v>61.4822</v>
+        <v>36.6241</v>
       </c>
       <c r="D45" t="n">
-        <v>64.9932</v>
+        <v>67.34099999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>23.9619</v>
+        <v>23.8933</v>
       </c>
       <c r="F45" t="n">
-        <v>49.0879</v>
+        <v>49.871</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>40.966</v>
+        <v>37.4976</v>
       </c>
       <c r="C46" t="n">
-        <v>60.0714</v>
+        <v>35.8754</v>
       </c>
       <c r="D46" t="n">
-        <v>64.49339999999999</v>
+        <v>67.0919</v>
       </c>
       <c r="E46" t="n">
-        <v>23.3893</v>
+        <v>23.0863</v>
       </c>
       <c r="F46" t="n">
-        <v>48.4774</v>
+        <v>49.9434</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>38.3629</v>
+        <v>36.2207</v>
       </c>
       <c r="C47" t="n">
-        <v>59.5853</v>
+        <v>35.1744</v>
       </c>
       <c r="D47" t="n">
-        <v>64.01900000000001</v>
+        <v>65.712</v>
       </c>
       <c r="E47" t="n">
-        <v>22.6689</v>
+        <v>22.4472</v>
       </c>
       <c r="F47" t="n">
-        <v>48.0627</v>
+        <v>48.7417</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>38.5339</v>
+        <v>33.9899</v>
       </c>
       <c r="C48" t="n">
-        <v>58.4835</v>
+        <v>34.6933</v>
       </c>
       <c r="D48" t="n">
-        <v>63.26</v>
+        <v>65.4465</v>
       </c>
       <c r="E48" t="n">
-        <v>22.0937</v>
+        <v>21.8348</v>
       </c>
       <c r="F48" t="n">
-        <v>47.354</v>
+        <v>48.1538</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>37.8059</v>
+        <v>34.5399</v>
       </c>
       <c r="C49" t="n">
-        <v>58.5057</v>
+        <v>33.9153</v>
       </c>
       <c r="D49" t="n">
-        <v>62.9908</v>
+        <v>66.504</v>
       </c>
       <c r="E49" t="n">
-        <v>21.5994</v>
+        <v>21.3386</v>
       </c>
       <c r="F49" t="n">
-        <v>47.193</v>
+        <v>47.8763</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>36.7279</v>
+        <v>32.6201</v>
       </c>
       <c r="C50" t="n">
-        <v>58.149</v>
+        <v>33.4305</v>
       </c>
       <c r="D50" t="n">
-        <v>77.3185</v>
+        <v>79.14449999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>21.3396</v>
+        <v>21.2298</v>
       </c>
       <c r="F50" t="n">
-        <v>47.085</v>
+        <v>47.6625</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>35.8701</v>
+        <v>32.6359</v>
       </c>
       <c r="C51" t="n">
-        <v>57.7166</v>
+        <v>45.2569</v>
       </c>
       <c r="D51" t="n">
-        <v>76.22709999999999</v>
+        <v>77.7929</v>
       </c>
       <c r="E51" t="n">
-        <v>33.5203</v>
+        <v>33.2682</v>
       </c>
       <c r="F51" t="n">
-        <v>57.9101</v>
+        <v>58.5627</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>35.293</v>
+        <v>32.4132</v>
       </c>
       <c r="C52" t="n">
-        <v>57.2462</v>
+        <v>44.1792</v>
       </c>
       <c r="D52" t="n">
-        <v>74.8753</v>
+        <v>76.80880000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>32.3633</v>
+        <v>32.323</v>
       </c>
       <c r="F52" t="n">
-        <v>56.7728</v>
+        <v>57.582</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>56.2669</v>
+        <v>51.85</v>
       </c>
       <c r="C53" t="n">
-        <v>71.5337</v>
+        <v>43.3049</v>
       </c>
       <c r="D53" t="n">
-        <v>73.9289</v>
+        <v>75.4271</v>
       </c>
       <c r="E53" t="n">
-        <v>31.3877</v>
+        <v>31.0723</v>
       </c>
       <c r="F53" t="n">
-        <v>56.5521</v>
+        <v>56.8002</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>55.182</v>
+        <v>51.9658</v>
       </c>
       <c r="C54" t="n">
-        <v>70.886</v>
+        <v>42.1788</v>
       </c>
       <c r="D54" t="n">
-        <v>72.75530000000001</v>
+        <v>74.1815</v>
       </c>
       <c r="E54" t="n">
-        <v>30.288</v>
+        <v>30.3678</v>
       </c>
       <c r="F54" t="n">
-        <v>55.3321</v>
+        <v>56.0882</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>53.7694</v>
+        <v>49.0402</v>
       </c>
       <c r="C55" t="n">
-        <v>70.2881</v>
+        <v>41.6051</v>
       </c>
       <c r="D55" t="n">
-        <v>71.6486</v>
+        <v>73.7158</v>
       </c>
       <c r="E55" t="n">
-        <v>29.1204</v>
+        <v>29.3702</v>
       </c>
       <c r="F55" t="n">
-        <v>54.4215</v>
+        <v>54.9692</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>51.0724</v>
+        <v>47.6157</v>
       </c>
       <c r="C56" t="n">
-        <v>68.66970000000001</v>
+        <v>40.1784</v>
       </c>
       <c r="D56" t="n">
-        <v>70.8173</v>
+        <v>72.5778</v>
       </c>
       <c r="E56" t="n">
-        <v>28.2108</v>
+        <v>28.276</v>
       </c>
       <c r="F56" t="n">
-        <v>53.6554</v>
+        <v>54.3526</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>50.5247</v>
+        <v>46.0293</v>
       </c>
       <c r="C57" t="n">
-        <v>67.2261</v>
+        <v>39.426</v>
       </c>
       <c r="D57" t="n">
-        <v>72.9271</v>
+        <v>71.4927</v>
       </c>
       <c r="E57" t="n">
-        <v>27.3475</v>
+        <v>27.2182</v>
       </c>
       <c r="F57" t="n">
-        <v>54.5937</v>
+        <v>53.3876</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>48.9732</v>
+        <v>44.3906</v>
       </c>
       <c r="C58" t="n">
-        <v>67.01439999999999</v>
+        <v>38.673</v>
       </c>
       <c r="D58" t="n">
-        <v>69.47029999999999</v>
+        <v>71.06100000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>26.5185</v>
+        <v>26.36</v>
       </c>
       <c r="F58" t="n">
-        <v>52.6479</v>
+        <v>53.0191</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>46.539</v>
+        <v>43.6412</v>
       </c>
       <c r="C59" t="n">
-        <v>65.1981</v>
+        <v>38.0165</v>
       </c>
       <c r="D59" t="n">
-        <v>68.80370000000001</v>
+        <v>69.7885</v>
       </c>
       <c r="E59" t="n">
-        <v>25.7349</v>
+        <v>25.7132</v>
       </c>
       <c r="F59" t="n">
-        <v>51.8239</v>
+        <v>52.4605</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>46.0028</v>
+        <v>42.2657</v>
       </c>
       <c r="C60" t="n">
-        <v>64.6082</v>
+        <v>37.1278</v>
       </c>
       <c r="D60" t="n">
-        <v>68.0986</v>
+        <v>69.4207</v>
       </c>
       <c r="E60" t="n">
-        <v>24.7485</v>
+        <v>24.867</v>
       </c>
       <c r="F60" t="n">
-        <v>51.2294</v>
+        <v>53.359</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>44.0637</v>
+        <v>41.1141</v>
       </c>
       <c r="C61" t="n">
-        <v>63.5275</v>
+        <v>36.5517</v>
       </c>
       <c r="D61" t="n">
-        <v>67.5527</v>
+        <v>69.1037</v>
       </c>
       <c r="E61" t="n">
-        <v>24.1303</v>
+        <v>24.2663</v>
       </c>
       <c r="F61" t="n">
-        <v>50.5867</v>
+        <v>51.3562</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>42.7706</v>
+        <v>40.0283</v>
       </c>
       <c r="C62" t="n">
-        <v>62.8423</v>
+        <v>35.8121</v>
       </c>
       <c r="D62" t="n">
-        <v>67.1181</v>
+        <v>69.0106</v>
       </c>
       <c r="E62" t="n">
-        <v>23.91</v>
+        <v>23.6595</v>
       </c>
       <c r="F62" t="n">
-        <v>50.1543</v>
+        <v>50.9638</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>42.3395</v>
+        <v>39.0722</v>
       </c>
       <c r="C63" t="n">
-        <v>62.1854</v>
+        <v>35.4007</v>
       </c>
       <c r="D63" t="n">
-        <v>67.02119999999999</v>
+        <v>69.0022</v>
       </c>
       <c r="E63" t="n">
-        <v>23.0579</v>
+        <v>23.12</v>
       </c>
       <c r="F63" t="n">
-        <v>49.8842</v>
+        <v>50.4052</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>40.4691</v>
+        <v>39.48</v>
       </c>
       <c r="C64" t="n">
-        <v>61.6545</v>
+        <v>34.8874</v>
       </c>
       <c r="D64" t="n">
-        <v>83.2505</v>
+        <v>85.4684</v>
       </c>
       <c r="E64" t="n">
-        <v>22.7219</v>
+        <v>22.6495</v>
       </c>
       <c r="F64" t="n">
-        <v>49.6369</v>
+        <v>50.7496</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>40.0262</v>
+        <v>37.9696</v>
       </c>
       <c r="C65" t="n">
-        <v>61.3025</v>
+        <v>47.0105</v>
       </c>
       <c r="D65" t="n">
-        <v>81.6157</v>
+        <v>83.88760000000001</v>
       </c>
       <c r="E65" t="n">
-        <v>22.4126</v>
+        <v>22.3956</v>
       </c>
       <c r="F65" t="n">
-        <v>49.5131</v>
+        <v>50.1145</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>38.9534</v>
+        <v>37.9266</v>
       </c>
       <c r="C66" t="n">
-        <v>60.5854</v>
+        <v>45.9858</v>
       </c>
       <c r="D66" t="n">
-        <v>81.0188</v>
+        <v>82.40479999999999</v>
       </c>
       <c r="E66" t="n">
-        <v>34.4241</v>
+        <v>34.6336</v>
       </c>
       <c r="F66" t="n">
-        <v>60.6938</v>
+        <v>60.7249</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>61.1302</v>
+        <v>60.5372</v>
       </c>
       <c r="C67" t="n">
-        <v>79.3917</v>
+        <v>44.5814</v>
       </c>
       <c r="D67" t="n">
-        <v>79.2364</v>
+        <v>80.3278</v>
       </c>
       <c r="E67" t="n">
-        <v>33.2445</v>
+        <v>32.7828</v>
       </c>
       <c r="F67" t="n">
-        <v>60.3673</v>
+        <v>60.0094</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>60.4935</v>
+        <v>59.5361</v>
       </c>
       <c r="C68" t="n">
-        <v>77.68689999999999</v>
+        <v>43.8768</v>
       </c>
       <c r="D68" t="n">
-        <v>77.2756</v>
+        <v>79.126</v>
       </c>
       <c r="E68" t="n">
-        <v>32.0106</v>
+        <v>32.4067</v>
       </c>
       <c r="F68" t="n">
-        <v>58.7459</v>
+        <v>59.5155</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>58.2353</v>
+        <v>57.2464</v>
       </c>
       <c r="C69" t="n">
-        <v>77.0391</v>
+        <v>42.6588</v>
       </c>
       <c r="D69" t="n">
-        <v>76.63509999999999</v>
+        <v>77.6413</v>
       </c>
       <c r="E69" t="n">
-        <v>31.2028</v>
+        <v>30.8413</v>
       </c>
       <c r="F69" t="n">
-        <v>57.9345</v>
+        <v>58.152</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>56.6439</v>
+        <v>55.3798</v>
       </c>
       <c r="C70" t="n">
-        <v>76.11620000000001</v>
+        <v>41.9701</v>
       </c>
       <c r="D70" t="n">
-        <v>76.5304</v>
+        <v>76.6356</v>
       </c>
       <c r="E70" t="n">
-        <v>29.9529</v>
+        <v>29.9569</v>
       </c>
       <c r="F70" t="n">
-        <v>57.5091</v>
+        <v>58.3858</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>55.42</v>
+        <v>55.0947</v>
       </c>
       <c r="C71" t="n">
-        <v>74.9915</v>
+        <v>40.9788</v>
       </c>
       <c r="D71" t="n">
-        <v>74.9753</v>
+        <v>76.51560000000001</v>
       </c>
       <c r="E71" t="n">
-        <v>29.4756</v>
+        <v>28.8377</v>
       </c>
       <c r="F71" t="n">
-        <v>57.0258</v>
+        <v>57.0186</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>53.808</v>
+        <v>52.812</v>
       </c>
       <c r="C72" t="n">
-        <v>73.6919</v>
+        <v>40.6928</v>
       </c>
       <c r="D72" t="n">
-        <v>74.0072</v>
+        <v>74.81019999999999</v>
       </c>
       <c r="E72" t="n">
-        <v>28.3366</v>
+        <v>28.2966</v>
       </c>
       <c r="F72" t="n">
-        <v>57.1517</v>
+        <v>56.341</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>52.4475</v>
+        <v>51.6995</v>
       </c>
       <c r="C73" t="n">
-        <v>73.196</v>
+        <v>39.4623</v>
       </c>
       <c r="D73" t="n">
-        <v>74.82259999999999</v>
+        <v>74.9988</v>
       </c>
       <c r="E73" t="n">
-        <v>27.4952</v>
+        <v>27.5593</v>
       </c>
       <c r="F73" t="n">
-        <v>56.0832</v>
+        <v>55.5457</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>50.9972</v>
+        <v>49.6363</v>
       </c>
       <c r="C74" t="n">
-        <v>72.4131</v>
+        <v>39.0311</v>
       </c>
       <c r="D74" t="n">
-        <v>72.8348</v>
+        <v>75.0222</v>
       </c>
       <c r="E74" t="n">
-        <v>26.9136</v>
+        <v>26.8658</v>
       </c>
       <c r="F74" t="n">
-        <v>55.3174</v>
+        <v>55.7039</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>49.8534</v>
+        <v>48.5591</v>
       </c>
       <c r="C75" t="n">
-        <v>71.7341</v>
+        <v>37.9504</v>
       </c>
       <c r="D75" t="n">
-        <v>72.48739999999999</v>
+        <v>74.24590000000001</v>
       </c>
       <c r="E75" t="n">
-        <v>25.7092</v>
+        <v>25.796</v>
       </c>
       <c r="F75" t="n">
-        <v>54.9313</v>
+        <v>54.689</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>48.5749</v>
+        <v>47.3725</v>
       </c>
       <c r="C76" t="n">
-        <v>69.9524</v>
+        <v>37.6504</v>
       </c>
       <c r="D76" t="n">
-        <v>73.3673</v>
+        <v>73.23269999999999</v>
       </c>
       <c r="E76" t="n">
-        <v>25.0864</v>
+        <v>25.3884</v>
       </c>
       <c r="F76" t="n">
-        <v>55.1644</v>
+        <v>54.7003</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>47.7536</v>
+        <v>46.7771</v>
       </c>
       <c r="C77" t="n">
-        <v>69.1772</v>
+        <v>36.6915</v>
       </c>
       <c r="D77" t="n">
-        <v>72.89530000000001</v>
+        <v>74.505</v>
       </c>
       <c r="E77" t="n">
-        <v>24.7012</v>
+        <v>24.383</v>
       </c>
       <c r="F77" t="n">
-        <v>53.212</v>
+        <v>54.4787</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>43.7041</v>
+        <v>45.4</v>
       </c>
       <c r="C78" t="n">
-        <v>68.47029999999999</v>
+        <v>36.5282</v>
       </c>
       <c r="D78" t="n">
-        <v>107.305</v>
+        <v>110.543</v>
       </c>
       <c r="E78" t="n">
-        <v>23.8605</v>
+        <v>23.8988</v>
       </c>
       <c r="F78" t="n">
-        <v>53.4727</v>
+        <v>53.5625</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>42.9685</v>
+        <v>43.8318</v>
       </c>
       <c r="C79" t="n">
-        <v>67.97029999999999</v>
+        <v>49.3737</v>
       </c>
       <c r="D79" t="n">
-        <v>105.771</v>
+        <v>107.82</v>
       </c>
       <c r="E79" t="n">
-        <v>23.8336</v>
+        <v>23.5048</v>
       </c>
       <c r="F79" t="n">
-        <v>53.1291</v>
+        <v>54.7999</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>42.2781</v>
+        <v>43.0671</v>
       </c>
       <c r="C80" t="n">
-        <v>68.0424</v>
+        <v>48.9512</v>
       </c>
       <c r="D80" t="n">
-        <v>105.253</v>
+        <v>105.229</v>
       </c>
       <c r="E80" t="n">
-        <v>36.9827</v>
+        <v>36.1773</v>
       </c>
       <c r="F80" t="n">
-        <v>78.76519999999999</v>
+        <v>79.3284</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>66.4692</v>
+        <v>63.4948</v>
       </c>
       <c r="C81" t="n">
-        <v>99.7193</v>
+        <v>49.1118</v>
       </c>
       <c r="D81" t="n">
-        <v>104.986</v>
+        <v>105.66</v>
       </c>
       <c r="E81" t="n">
-        <v>35.2868</v>
+        <v>36.1078</v>
       </c>
       <c r="F81" t="n">
-        <v>79.00190000000001</v>
+        <v>80.74509999999999</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>65.47539999999999</v>
+        <v>62.98</v>
       </c>
       <c r="C82" t="n">
-        <v>100.747</v>
+        <v>48.2734</v>
       </c>
       <c r="D82" t="n">
-        <v>103.535</v>
+        <v>104.541</v>
       </c>
       <c r="E82" t="n">
-        <v>34.8578</v>
+        <v>34.2429</v>
       </c>
       <c r="F82" t="n">
-        <v>78.7794</v>
+        <v>78.7871</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>65.0985</v>
+        <v>62.314</v>
       </c>
       <c r="C83" t="n">
-        <v>100.698</v>
+        <v>48.2693</v>
       </c>
       <c r="D83" t="n">
-        <v>103.31</v>
+        <v>102.63</v>
       </c>
       <c r="E83" t="n">
-        <v>33.4008</v>
+        <v>33.3058</v>
       </c>
       <c r="F83" t="n">
-        <v>77.8185</v>
+        <v>78.0369</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>64.7189</v>
+        <v>61.4324</v>
       </c>
       <c r="C84" t="n">
-        <v>99.0552</v>
+        <v>47.4458</v>
       </c>
       <c r="D84" t="n">
-        <v>102.883</v>
+        <v>102.126</v>
       </c>
       <c r="E84" t="n">
-        <v>32.8256</v>
+        <v>32.7213</v>
       </c>
       <c r="F84" t="n">
-        <v>76.4969</v>
+        <v>77.0188</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>62.7811</v>
+        <v>60.956</v>
       </c>
       <c r="C85" t="n">
-        <v>97.6236</v>
+        <v>47.2043</v>
       </c>
       <c r="D85" t="n">
-        <v>102.524</v>
+        <v>102.658</v>
       </c>
       <c r="E85" t="n">
-        <v>31.6492</v>
+        <v>31.6678</v>
       </c>
       <c r="F85" t="n">
-        <v>75.7332</v>
+        <v>76.5711</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>62.4056</v>
+        <v>59.9657</v>
       </c>
       <c r="C86" t="n">
-        <v>97.2022</v>
+        <v>46.5115</v>
       </c>
       <c r="D86" t="n">
-        <v>102.286</v>
+        <v>103.596</v>
       </c>
       <c r="E86" t="n">
-        <v>30.7998</v>
+        <v>31.5805</v>
       </c>
       <c r="F86" t="n">
-        <v>75.4057</v>
+        <v>74.4637</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>61.2603</v>
+        <v>58.656</v>
       </c>
       <c r="C87" t="n">
-        <v>95.5839</v>
+        <v>45.9236</v>
       </c>
       <c r="D87" t="n">
-        <v>102.33</v>
+        <v>102.871</v>
       </c>
       <c r="E87" t="n">
-        <v>30.3211</v>
+        <v>30.3381</v>
       </c>
       <c r="F87" t="n">
-        <v>73.35720000000001</v>
+        <v>73.6705</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>59.7199</v>
+        <v>58.1822</v>
       </c>
       <c r="C88" t="n">
-        <v>93.4349</v>
+        <v>45.5233</v>
       </c>
       <c r="D88" t="n">
-        <v>102.506</v>
+        <v>102.496</v>
       </c>
       <c r="E88" t="n">
-        <v>29.4258</v>
+        <v>29.1739</v>
       </c>
       <c r="F88" t="n">
-        <v>72.04170000000001</v>
+        <v>72.9584</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>58.7261</v>
+        <v>56.5808</v>
       </c>
       <c r="C89" t="n">
-        <v>92.92449999999999</v>
+        <v>44.7474</v>
       </c>
       <c r="D89" t="n">
-        <v>102.736</v>
+        <v>105.257</v>
       </c>
       <c r="E89" t="n">
-        <v>28.7965</v>
+        <v>28.4489</v>
       </c>
       <c r="F89" t="n">
-        <v>72.3445</v>
+        <v>71.45610000000001</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>58.1036</v>
+        <v>56.0429</v>
       </c>
       <c r="C90" t="n">
-        <v>91.1645</v>
+        <v>44.4131</v>
       </c>
       <c r="D90" t="n">
-        <v>103.713</v>
+        <v>104.861</v>
       </c>
       <c r="E90" t="n">
-        <v>28.3357</v>
+        <v>27.8077</v>
       </c>
       <c r="F90" t="n">
-        <v>70.3061</v>
+        <v>70.8652</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>56.3314</v>
+        <v>55.0523</v>
       </c>
       <c r="C91" t="n">
-        <v>89.9003</v>
+        <v>43.6763</v>
       </c>
       <c r="D91" t="n">
-        <v>105.041</v>
+        <v>105.342</v>
       </c>
       <c r="E91" t="n">
-        <v>27.5141</v>
+        <v>27.1061</v>
       </c>
       <c r="F91" t="n">
-        <v>69.3785</v>
+        <v>70.1431</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>55.0951</v>
+        <v>53.8156</v>
       </c>
       <c r="C92" t="n">
-        <v>89.09229999999999</v>
+        <v>43.1074</v>
       </c>
       <c r="D92" t="n">
-        <v>147.717</v>
+        <v>147.459</v>
       </c>
       <c r="E92" t="n">
-        <v>26.8607</v>
+        <v>27.0312</v>
       </c>
       <c r="F92" t="n">
-        <v>68.7765</v>
+        <v>68.9919</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>53.9405</v>
+        <v>53.8774</v>
       </c>
       <c r="C93" t="n">
-        <v>88.6319</v>
+        <v>42.71</v>
       </c>
       <c r="D93" t="n">
-        <v>147.066</v>
+        <v>147.521</v>
       </c>
       <c r="E93" t="n">
-        <v>26.5868</v>
+        <v>26.5153</v>
       </c>
       <c r="F93" t="n">
-        <v>68.29810000000001</v>
+        <v>67.7478</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>53.1176</v>
+        <v>52.6038</v>
       </c>
       <c r="C94" t="n">
-        <v>87.4663</v>
+        <v>57.0718</v>
       </c>
       <c r="D94" t="n">
-        <v>146.819</v>
+        <v>145.658</v>
       </c>
       <c r="E94" t="n">
-        <v>39.9134</v>
+        <v>39.0144</v>
       </c>
       <c r="F94" t="n">
-        <v>99.1601</v>
+        <v>98.4911</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>71.8338</v>
+        <v>76.098</v>
       </c>
       <c r="C95" t="n">
-        <v>123.6</v>
+        <v>55.862</v>
       </c>
       <c r="D95" t="n">
-        <v>145.888</v>
+        <v>146.342</v>
       </c>
       <c r="E95" t="n">
-        <v>38.5093</v>
+        <v>37.9072</v>
       </c>
       <c r="F95" t="n">
-        <v>98.8777</v>
+        <v>98.4926</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>71.7949</v>
+        <v>75.5184</v>
       </c>
       <c r="C96" t="n">
-        <v>124.243</v>
+        <v>55.2441</v>
       </c>
       <c r="D96" t="n">
-        <v>144.789</v>
+        <v>143.685</v>
       </c>
       <c r="E96" t="n">
-        <v>37.8312</v>
+        <v>38.1964</v>
       </c>
       <c r="F96" t="n">
-        <v>98.2979</v>
+        <v>97.3402</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>70.6931</v>
+        <v>75.03189999999999</v>
       </c>
       <c r="C97" t="n">
-        <v>122.947</v>
+        <v>55.714</v>
       </c>
       <c r="D97" t="n">
-        <v>144.221</v>
+        <v>143.776</v>
       </c>
       <c r="E97" t="n">
-        <v>37.2358</v>
+        <v>36.9259</v>
       </c>
       <c r="F97" t="n">
-        <v>97.51949999999999</v>
+        <v>96.86709999999999</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>70.53879999999999</v>
+        <v>73.4175</v>
       </c>
       <c r="C98" t="n">
-        <v>121.863</v>
+        <v>54.9935</v>
       </c>
       <c r="D98" t="n">
-        <v>144.146</v>
+        <v>144.389</v>
       </c>
       <c r="E98" t="n">
-        <v>36.1223</v>
+        <v>36.1052</v>
       </c>
       <c r="F98" t="n">
-        <v>95.7169</v>
+        <v>95.5857</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>69.3797</v>
+        <v>73.0981</v>
       </c>
       <c r="C99" t="n">
-        <v>119.532</v>
+        <v>55.2848</v>
       </c>
       <c r="D99" t="n">
-        <v>143.906</v>
+        <v>144.251</v>
       </c>
       <c r="E99" t="n">
-        <v>35.2031</v>
+        <v>34.9375</v>
       </c>
       <c r="F99" t="n">
-        <v>94.7924</v>
+        <v>94.809</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>69.4962</v>
+        <v>71.5003</v>
       </c>
       <c r="C100" t="n">
-        <v>118.403</v>
+        <v>54.8705</v>
       </c>
       <c r="D100" t="n">
-        <v>144.599</v>
+        <v>145.099</v>
       </c>
       <c r="E100" t="n">
-        <v>34.0529</v>
+        <v>33.978</v>
       </c>
       <c r="F100" t="n">
-        <v>93.75</v>
+        <v>94.33240000000001</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>68.1657</v>
+        <v>70.9337</v>
       </c>
       <c r="C101" t="n">
-        <v>119.707</v>
+        <v>54.5014</v>
       </c>
       <c r="D101" t="n">
-        <v>145.69</v>
+        <v>145.178</v>
       </c>
       <c r="E101" t="n">
-        <v>33.2525</v>
+        <v>33.583</v>
       </c>
       <c r="F101" t="n">
-        <v>92.2415</v>
+        <v>91.80070000000001</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>69.959</v>
+        <v>70.95820000000001</v>
       </c>
       <c r="C102" t="n">
-        <v>118.227</v>
+        <v>54.3183</v>
       </c>
       <c r="D102" t="n">
-        <v>145.737</v>
+        <v>145.54</v>
       </c>
       <c r="E102" t="n">
-        <v>32.9388</v>
+        <v>32.7867</v>
       </c>
       <c r="F102" t="n">
-        <v>91.32989999999999</v>
+        <v>92.5778</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>68.85809999999999</v>
+        <v>70.56180000000001</v>
       </c>
       <c r="C103" t="n">
-        <v>116.742</v>
+        <v>54.0574</v>
       </c>
       <c r="D103" t="n">
-        <v>146.869</v>
+        <v>148.682</v>
       </c>
       <c r="E103" t="n">
-        <v>32.2009</v>
+        <v>31.7636</v>
       </c>
       <c r="F103" t="n">
-        <v>90.91330000000001</v>
+        <v>89.9325</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>68.2527</v>
+        <v>69.9543</v>
       </c>
       <c r="C104" t="n">
-        <v>116.271</v>
+        <v>53.9655</v>
       </c>
       <c r="D104" t="n">
-        <v>147.194</v>
+        <v>146.922</v>
       </c>
       <c r="E104" t="n">
-        <v>31.4144</v>
+        <v>31.3609</v>
       </c>
       <c r="F104" t="n">
-        <v>89.6968</v>
+        <v>89.6986</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>68.15560000000001</v>
+        <v>69.11660000000001</v>
       </c>
       <c r="C105" t="n">
-        <v>115.877</v>
+        <v>53.809</v>
       </c>
       <c r="D105" t="n">
-        <v>148.034</v>
+        <v>148.876</v>
       </c>
       <c r="E105" t="n">
-        <v>31.3563</v>
+        <v>31.3567</v>
       </c>
       <c r="F105" t="n">
-        <v>89.3143</v>
+        <v>88.4623</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>66.1934</v>
+        <v>68.1936</v>
       </c>
       <c r="C106" t="n">
-        <v>114.801</v>
+        <v>53.8213</v>
       </c>
       <c r="D106" t="n">
-        <v>149.024</v>
+        <v>151.671</v>
       </c>
       <c r="E106" t="n">
-        <v>30.3869</v>
+        <v>31.0661</v>
       </c>
       <c r="F106" t="n">
-        <v>87.92019999999999</v>
+        <v>88.4273</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>66.11579999999999</v>
+        <v>66.9449</v>
       </c>
       <c r="C107" t="n">
-        <v>113.279</v>
+        <v>54.0371</v>
       </c>
       <c r="D107" t="n">
-        <v>193.43</v>
+        <v>194.338</v>
       </c>
       <c r="E107" t="n">
-        <v>30.442</v>
+        <v>30.3236</v>
       </c>
       <c r="F107" t="n">
-        <v>86.8793</v>
+        <v>87.3272</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>66.8441</v>
+        <v>66.66419999999999</v>
       </c>
       <c r="C108" t="n">
-        <v>112.971</v>
+        <v>66.3218</v>
       </c>
       <c r="D108" t="n">
-        <v>191.452</v>
+        <v>192.237</v>
       </c>
       <c r="E108" t="n">
-        <v>43.2856</v>
+        <v>42.899</v>
       </c>
       <c r="F108" t="n">
-        <v>119.711</v>
+        <v>119.377</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>66.7193</v>
+        <v>65.7192</v>
       </c>
       <c r="C109" t="n">
-        <v>112.368</v>
+        <v>66.40940000000001</v>
       </c>
       <c r="D109" t="n">
-        <v>190.262</v>
+        <v>190.586</v>
       </c>
       <c r="E109" t="n">
-        <v>42.8516</v>
+        <v>42.8208</v>
       </c>
       <c r="F109" t="n">
-        <v>119.893</v>
+        <v>119.122</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>90.26009999999999</v>
+        <v>84.5102</v>
       </c>
       <c r="C110" t="n">
-        <v>152.584</v>
+        <v>66.62139999999999</v>
       </c>
       <c r="D110" t="n">
-        <v>189.102</v>
+        <v>189.427</v>
       </c>
       <c r="E110" t="n">
-        <v>42.2346</v>
+        <v>41.3308</v>
       </c>
       <c r="F110" t="n">
-        <v>119.305</v>
+        <v>117.937</v>
       </c>
     </row>
     <row r="111">
@@ -7259,16 +7259,16 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>89.03449999999999</v>
+        <v>84.6147</v>
       </c>
       <c r="C111" t="n">
-        <v>151.707</v>
+        <v>66.8356</v>
       </c>
       <c r="D111" t="n">
-        <v>188.666</v>
+        <v>188.66</v>
       </c>
       <c r="E111" t="n">
-        <v>40.8407</v>
+        <v>40.9573</v>
       </c>
       <c r="F111" t="n">
         <v>117.949</v>
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>88.3515</v>
+        <v>84.0294</v>
       </c>
       <c r="C112" t="n">
-        <v>150.661</v>
+        <v>66.67019999999999</v>
       </c>
       <c r="D112" t="n">
-        <v>188.008</v>
+        <v>187.329</v>
       </c>
       <c r="E112" t="n">
-        <v>40.0581</v>
+        <v>39.8264</v>
       </c>
       <c r="F112" t="n">
-        <v>117.575</v>
+        <v>116.592</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>82.35599999999999</v>
+        <v>81.4855</v>
       </c>
       <c r="C113" t="n">
-        <v>149.561</v>
+        <v>66.30889999999999</v>
       </c>
       <c r="D113" t="n">
-        <v>187.121</v>
+        <v>187.694</v>
       </c>
       <c r="E113" t="n">
-        <v>39.5659</v>
+        <v>39.2406</v>
       </c>
       <c r="F113" t="n">
-        <v>117.262</v>
+        <v>116.237</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>82.319</v>
+        <v>80.9123</v>
       </c>
       <c r="C114" t="n">
-        <v>147.908</v>
+        <v>66.4015</v>
       </c>
       <c r="D114" t="n">
-        <v>186.079</v>
+        <v>186.629</v>
       </c>
       <c r="E114" t="n">
-        <v>38.4966</v>
+        <v>38.8796</v>
       </c>
       <c r="F114" t="n">
-        <v>116.094</v>
+        <v>115.979</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>80.9004</v>
+        <v>80.0487</v>
       </c>
       <c r="C115" t="n">
-        <v>146.475</v>
+        <v>66.51779999999999</v>
       </c>
       <c r="D115" t="n">
-        <v>185.729</v>
+        <v>187.639</v>
       </c>
       <c r="E115" t="n">
-        <v>38.1442</v>
+        <v>38.1756</v>
       </c>
       <c r="F115" t="n">
-        <v>115.364</v>
+        <v>115.492</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>80.3417</v>
+        <v>80.1356</v>
       </c>
       <c r="C116" t="n">
-        <v>147.329</v>
+        <v>66.1596</v>
       </c>
       <c r="D116" t="n">
-        <v>186.492</v>
+        <v>187.374</v>
       </c>
       <c r="E116" t="n">
-        <v>38.1556</v>
+        <v>38.1612</v>
       </c>
       <c r="F116" t="n">
-        <v>114.796</v>
+        <v>114.595</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>80.2308</v>
+        <v>81.2777</v>
       </c>
       <c r="C117" t="n">
-        <v>145.396</v>
+        <v>66.66970000000001</v>
       </c>
       <c r="D117" t="n">
-        <v>187</v>
+        <v>187.395</v>
       </c>
       <c r="E117" t="n">
-        <v>37.1035</v>
+        <v>37.0049</v>
       </c>
       <c r="F117" t="n">
-        <v>114.76</v>
+        <v>114.293</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>79.26349999999999</v>
+        <v>80.07980000000001</v>
       </c>
       <c r="C118" t="n">
-        <v>144.299</v>
+        <v>66.41379999999999</v>
       </c>
       <c r="D118" t="n">
-        <v>186.922</v>
+        <v>187.755</v>
       </c>
       <c r="E118" t="n">
-        <v>35.9889</v>
+        <v>36.1902</v>
       </c>
       <c r="F118" t="n">
-        <v>113.818</v>
+        <v>113.932</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>78.5384</v>
+        <v>79.7645</v>
       </c>
       <c r="C119" t="n">
-        <v>143.275</v>
+        <v>66.13720000000001</v>
       </c>
       <c r="D119" t="n">
-        <v>188.066</v>
+        <v>189.126</v>
       </c>
       <c r="E119" t="n">
-        <v>35.6427</v>
+        <v>35.7418</v>
       </c>
       <c r="F119" t="n">
-        <v>113.272</v>
+        <v>113.055</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>77.9134</v>
+        <v>77.3032</v>
       </c>
       <c r="C120" t="n">
-        <v>142.834</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="D120" t="n">
-        <v>188.664</v>
+        <v>189.743</v>
       </c>
       <c r="E120" t="n">
-        <v>35.3737</v>
+        <v>35.4305</v>
       </c>
       <c r="F120" t="n">
-        <v>112.985</v>
+        <v>112.891</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>77.206</v>
+        <v>76.6005</v>
       </c>
       <c r="C121" t="n">
-        <v>141.616</v>
+        <v>65.4248</v>
       </c>
       <c r="D121" t="n">
-        <v>235.952</v>
+        <v>236.759</v>
       </c>
       <c r="E121" t="n">
-        <v>35.2057</v>
+        <v>34.9768</v>
       </c>
       <c r="F121" t="n">
-        <v>112.708</v>
+        <v>112.504</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>76.0485</v>
+        <v>75.5917</v>
       </c>
       <c r="C122" t="n">
-        <v>141.094</v>
+        <v>78.68640000000001</v>
       </c>
       <c r="D122" t="n">
-        <v>233.449</v>
+        <v>234.492</v>
       </c>
       <c r="E122" t="n">
-        <v>35.285</v>
+        <v>34.8551</v>
       </c>
       <c r="F122" t="n">
-        <v>111.782</v>
+        <v>112.196</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>77.6087</v>
+        <v>77.4105</v>
       </c>
       <c r="C123" t="n">
-        <v>141.371</v>
+        <v>78.4464</v>
       </c>
       <c r="D123" t="n">
-        <v>230.713</v>
+        <v>231.478</v>
       </c>
       <c r="E123" t="n">
-        <v>47.9181</v>
+        <v>48.0309</v>
       </c>
       <c r="F123" t="n">
-        <v>144.763</v>
+        <v>145.741</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>96.77719999999999</v>
+        <v>97.9611</v>
       </c>
       <c r="C124" t="n">
-        <v>183.397</v>
+        <v>78.52200000000001</v>
       </c>
       <c r="D124" t="n">
-        <v>229.255</v>
+        <v>229.412</v>
       </c>
       <c r="E124" t="n">
-        <v>47.6251</v>
+        <v>47.7181</v>
       </c>
       <c r="F124" t="n">
-        <v>143.862</v>
+        <v>144.822</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>98.60720000000001</v>
+        <v>96.2709</v>
       </c>
       <c r="C125" t="n">
-        <v>181.049</v>
+        <v>78.49460000000001</v>
       </c>
       <c r="D125" t="n">
-        <v>227.469</v>
+        <v>227.365</v>
       </c>
       <c r="E125" t="n">
-        <v>48.8485</v>
+        <v>47.7912</v>
       </c>
       <c r="F125" t="n">
-        <v>143.419</v>
+        <v>142.642</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>97.5158</v>
+        <v>96.8937</v>
       </c>
       <c r="C126" t="n">
-        <v>180.048</v>
+        <v>79.1981</v>
       </c>
       <c r="D126" t="n">
-        <v>226.18</v>
+        <v>226.679</v>
       </c>
       <c r="E126" t="n">
-        <v>47.1132</v>
+        <v>47.3118</v>
       </c>
       <c r="F126" t="n">
-        <v>143.647</v>
+        <v>142.844</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>96.5789</v>
+        <v>96.63120000000001</v>
       </c>
       <c r="C127" t="n">
-        <v>178.788</v>
+        <v>79.46810000000001</v>
       </c>
       <c r="D127" t="n">
-        <v>224.65</v>
+        <v>224.963</v>
       </c>
       <c r="E127" t="n">
-        <v>46.6655</v>
+        <v>46.0613</v>
       </c>
       <c r="F127" t="n">
-        <v>142.79</v>
+        <v>142.098</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>94.1268</v>
+        <v>92.95189999999999</v>
       </c>
       <c r="C128" t="n">
-        <v>177.259</v>
+        <v>79.5181</v>
       </c>
       <c r="D128" t="n">
-        <v>223.591</v>
+        <v>223.91</v>
       </c>
       <c r="E128" t="n">
-        <v>45.0182</v>
+        <v>44.4302</v>
       </c>
       <c r="F128" t="n">
-        <v>142.152</v>
+        <v>141.54</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>95.44629999999999</v>
+        <v>92.26139999999999</v>
       </c>
       <c r="C129" t="n">
-        <v>176.248</v>
+        <v>79.76300000000001</v>
       </c>
       <c r="D129" t="n">
-        <v>222.489</v>
+        <v>222.89</v>
       </c>
       <c r="E129" t="n">
-        <v>44.5898</v>
+        <v>44.8652</v>
       </c>
       <c r="F129" t="n">
-        <v>141.612</v>
+        <v>141.035</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>95.2158</v>
+        <v>95.1619</v>
       </c>
       <c r="C130" t="n">
-        <v>173.269</v>
+        <v>79.7512</v>
       </c>
       <c r="D130" t="n">
-        <v>222.239</v>
+        <v>222.383</v>
       </c>
       <c r="E130" t="n">
-        <v>43.8765</v>
+        <v>43.812</v>
       </c>
       <c r="F130" t="n">
-        <v>140.876</v>
+        <v>141.18</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>91.499</v>
+        <v>93.7499</v>
       </c>
       <c r="C131" t="n">
-        <v>172.725</v>
+        <v>79.56910000000001</v>
       </c>
       <c r="D131" t="n">
-        <v>221.403</v>
+        <v>222.225</v>
       </c>
       <c r="E131" t="n">
-        <v>43.6855</v>
+        <v>43.6914</v>
       </c>
       <c r="F131" t="n">
-        <v>140.659</v>
+        <v>140.491</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>90.982</v>
+        <v>92.6611</v>
       </c>
       <c r="C132" t="n">
-        <v>171.683</v>
+        <v>79.8571</v>
       </c>
       <c r="D132" t="n">
-        <v>221.36</v>
+        <v>222.303</v>
       </c>
       <c r="E132" t="n">
-        <v>43.7327</v>
+        <v>43.3475</v>
       </c>
       <c r="F132" t="n">
-        <v>140.194</v>
+        <v>139.701</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>93.2277</v>
+        <v>92.09739999999999</v>
       </c>
       <c r="C133" t="n">
-        <v>171.412</v>
+        <v>79.9374</v>
       </c>
       <c r="D133" t="n">
-        <v>221.367</v>
+        <v>222.18</v>
       </c>
       <c r="E133" t="n">
-        <v>43.4777</v>
+        <v>43.1493</v>
       </c>
       <c r="F133" t="n">
-        <v>140.018</v>
+        <v>139.761</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>91.5247</v>
+        <v>92.56829999999999</v>
       </c>
       <c r="C134" t="n">
-        <v>169.945</v>
+        <v>80.28619999999999</v>
       </c>
       <c r="D134" t="n">
-        <v>221.856</v>
+        <v>222.91</v>
       </c>
       <c r="E134" t="n">
-        <v>43.2594</v>
+        <v>42.9665</v>
       </c>
       <c r="F134" t="n">
-        <v>139.915</v>
+        <v>139.048</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>91.2427</v>
+        <v>92.3262</v>
       </c>
       <c r="C135" t="n">
-        <v>169.882</v>
+        <v>80.31829999999999</v>
       </c>
       <c r="D135" t="n">
-        <v>271.262</v>
+        <v>271.045</v>
       </c>
       <c r="E135" t="n">
-        <v>42.9335</v>
+        <v>43.0154</v>
       </c>
       <c r="F135" t="n">
-        <v>139.757</v>
+        <v>138.899</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>90.6974</v>
+        <v>92.11669999999999</v>
       </c>
       <c r="C136" t="n">
-        <v>168.206</v>
+        <v>92.96250000000001</v>
       </c>
       <c r="D136" t="n">
-        <v>268.213</v>
+        <v>267.811</v>
       </c>
       <c r="E136" t="n">
-        <v>42.8909</v>
+        <v>42.391</v>
       </c>
       <c r="F136" t="n">
-        <v>139.598</v>
+        <v>138.789</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>90.7349</v>
+        <v>90.72620000000001</v>
       </c>
       <c r="C137" t="n">
-        <v>167.988</v>
+        <v>93.52379999999999</v>
       </c>
       <c r="D137" t="n">
-        <v>264.407</v>
+        <v>264.19</v>
       </c>
       <c r="E137" t="n">
-        <v>56.21</v>
+        <v>55.7631</v>
       </c>
       <c r="F137" t="n">
-        <v>173.781</v>
+        <v>172.784</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>109.616</v>
+        <v>112.204</v>
       </c>
       <c r="C138" t="n">
-        <v>211.597</v>
+        <v>94.038</v>
       </c>
       <c r="D138" t="n">
-        <v>261.874</v>
+        <v>261.51</v>
       </c>
       <c r="E138" t="n">
-        <v>54.9942</v>
+        <v>55.2695</v>
       </c>
       <c r="F138" t="n">
-        <v>172.201</v>
+        <v>170.73</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>109.135</v>
+        <v>108.211</v>
       </c>
       <c r="C139" t="n">
-        <v>209.213</v>
+        <v>94.0498</v>
       </c>
       <c r="D139" t="n">
-        <v>259.165</v>
+        <v>259.044</v>
       </c>
       <c r="E139" t="n">
-        <v>55.5366</v>
+        <v>55.1932</v>
       </c>
       <c r="F139" t="n">
-        <v>170.543</v>
+        <v>169.679</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>107.297</v>
+        <v>111.112</v>
       </c>
       <c r="C140" t="n">
-        <v>206.649</v>
+        <v>93.953</v>
       </c>
       <c r="D140" t="n">
-        <v>256.895</v>
+        <v>256.32</v>
       </c>
       <c r="E140" t="n">
-        <v>54.5123</v>
+        <v>54.8054</v>
       </c>
       <c r="F140" t="n">
-        <v>170.341</v>
+        <v>168.741</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>108.439</v>
+        <v>108.556</v>
       </c>
       <c r="C141" t="n">
-        <v>204.495</v>
+        <v>94.4727</v>
       </c>
       <c r="D141" t="n">
-        <v>253.985</v>
+        <v>254.43</v>
       </c>
       <c r="E141" t="n">
-        <v>55.7027</v>
+        <v>54.7408</v>
       </c>
       <c r="F141" t="n">
-        <v>168.428</v>
+        <v>167.532</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>110.476</v>
+        <v>107.746</v>
       </c>
       <c r="C142" t="n">
-        <v>203.158</v>
+        <v>94.44840000000001</v>
       </c>
       <c r="D142" t="n">
-        <v>252.476</v>
+        <v>252.49</v>
       </c>
       <c r="E142" t="n">
-        <v>54.1596</v>
+        <v>53.9346</v>
       </c>
       <c r="F142" t="n">
-        <v>167.349</v>
+        <v>166.767</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>107.398</v>
+        <v>107.123</v>
       </c>
       <c r="C143" t="n">
-        <v>202.146</v>
+        <v>94.59520000000001</v>
       </c>
       <c r="D143" t="n">
-        <v>251.344</v>
+        <v>250.835</v>
       </c>
       <c r="E143" t="n">
-        <v>54.1262</v>
+        <v>53.6957</v>
       </c>
       <c r="F143" t="n">
-        <v>166.741</v>
+        <v>165.753</v>
       </c>
     </row>
   </sheetData>

--- a/vs-x64/Running insertion.xlsx
+++ b/vs-x64/Running insertion.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>24.5466</v>
+        <v>23.792</v>
       </c>
       <c r="C2" t="n">
-        <v>30.6861</v>
+        <v>30.6511</v>
       </c>
       <c r="D2" t="n">
-        <v>59.1464</v>
+        <v>59.0695</v>
       </c>
       <c r="E2" t="n">
-        <v>15.761</v>
+        <v>14.6379</v>
       </c>
       <c r="F2" t="n">
-        <v>52.7497</v>
+        <v>51.5501</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>23.4207</v>
+        <v>22.5944</v>
       </c>
       <c r="C3" t="n">
-        <v>30.1487</v>
+        <v>30.1208</v>
       </c>
       <c r="D3" t="n">
-        <v>58.905</v>
+        <v>59.1033</v>
       </c>
       <c r="E3" t="n">
-        <v>15.2776</v>
+        <v>14.2385</v>
       </c>
       <c r="F3" t="n">
-        <v>51.9377</v>
+        <v>50.6251</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>22.7703</v>
+        <v>22.5357</v>
       </c>
       <c r="C4" t="n">
-        <v>29.7167</v>
+        <v>29.7606</v>
       </c>
       <c r="D4" t="n">
-        <v>58.3881</v>
+        <v>57.7973</v>
       </c>
       <c r="E4" t="n">
-        <v>14.9592</v>
+        <v>13.8104</v>
       </c>
       <c r="F4" t="n">
-        <v>52.1419</v>
+        <v>50.3904</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>21.8644</v>
+        <v>21.7467</v>
       </c>
       <c r="C5" t="n">
-        <v>29.4496</v>
+        <v>29.3448</v>
       </c>
       <c r="D5" t="n">
-        <v>57.5927</v>
+        <v>57.8255</v>
       </c>
       <c r="E5" t="n">
-        <v>14.628</v>
+        <v>13.572</v>
       </c>
       <c r="F5" t="n">
-        <v>51.5029</v>
+        <v>49.9085</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>21.6686</v>
+        <v>21.3877</v>
       </c>
       <c r="C6" t="n">
-        <v>28.9093</v>
+        <v>28.9364</v>
       </c>
       <c r="D6" t="n">
-        <v>56.8279</v>
+        <v>57.0179</v>
       </c>
       <c r="E6" t="n">
-        <v>14.3335</v>
+        <v>13.3088</v>
       </c>
       <c r="F6" t="n">
-        <v>50.7924</v>
+        <v>49.5245</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>21.44</v>
+        <v>21.327</v>
       </c>
       <c r="C7" t="n">
-        <v>28.6355</v>
+        <v>28.6459</v>
       </c>
       <c r="D7" t="n">
-        <v>68.1803</v>
+        <v>68.8613</v>
       </c>
       <c r="E7" t="n">
-        <v>14.1862</v>
+        <v>20.2434</v>
       </c>
       <c r="F7" t="n">
-        <v>50.3238</v>
+        <v>56.0629</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>21.3649</v>
+        <v>21.1249</v>
       </c>
       <c r="C8" t="n">
-        <v>35.402</v>
+        <v>35.41</v>
       </c>
       <c r="D8" t="n">
-        <v>67.3819</v>
+        <v>67.5214</v>
       </c>
       <c r="E8" t="n">
-        <v>14.2217</v>
+        <v>19.5386</v>
       </c>
       <c r="F8" t="n">
-        <v>50.7701</v>
+        <v>55.9654</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>21.2732</v>
+        <v>21.4553</v>
       </c>
       <c r="C9" t="n">
-        <v>34.744</v>
+        <v>34.7543</v>
       </c>
       <c r="D9" t="n">
-        <v>66.3351</v>
+        <v>66.19119999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>21.185</v>
+        <v>18.9009</v>
       </c>
       <c r="F9" t="n">
-        <v>57.4497</v>
+        <v>54.9898</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>27.8324</v>
+        <v>27.9463</v>
       </c>
       <c r="C10" t="n">
-        <v>34.1023</v>
+        <v>34.1351</v>
       </c>
       <c r="D10" t="n">
-        <v>65.1845</v>
+        <v>65.23820000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>20.4728</v>
+        <v>18.2863</v>
       </c>
       <c r="F10" t="n">
-        <v>56.3341</v>
+        <v>54.24</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>27.3068</v>
+        <v>27.2427</v>
       </c>
       <c r="C11" t="n">
-        <v>33.5462</v>
+        <v>33.5307</v>
       </c>
       <c r="D11" t="n">
-        <v>64.56059999999999</v>
+        <v>64.44029999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>19.8075</v>
+        <v>17.7187</v>
       </c>
       <c r="F11" t="n">
-        <v>56.1112</v>
+        <v>54.0777</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>26.3498</v>
+        <v>26.3179</v>
       </c>
       <c r="C12" t="n">
-        <v>32.9717</v>
+        <v>32.9493</v>
       </c>
       <c r="D12" t="n">
-        <v>63.3926</v>
+        <v>63.6434</v>
       </c>
       <c r="E12" t="n">
-        <v>19.1163</v>
+        <v>17.1516</v>
       </c>
       <c r="F12" t="n">
-        <v>55.2178</v>
+        <v>52.9656</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>26.0418</v>
+        <v>25.6913</v>
       </c>
       <c r="C13" t="n">
-        <v>32.4394</v>
+        <v>32.4343</v>
       </c>
       <c r="D13" t="n">
-        <v>62.9254</v>
+        <v>62.767</v>
       </c>
       <c r="E13" t="n">
-        <v>18.4479</v>
+        <v>16.5999</v>
       </c>
       <c r="F13" t="n">
-        <v>54.5676</v>
+        <v>52.2197</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>25.4703</v>
+        <v>25.2711</v>
       </c>
       <c r="C14" t="n">
-        <v>31.8895</v>
+        <v>31.8694</v>
       </c>
       <c r="D14" t="n">
-        <v>61.9436</v>
+        <v>61.9972</v>
       </c>
       <c r="E14" t="n">
-        <v>17.8591</v>
+        <v>16.1144</v>
       </c>
       <c r="F14" t="n">
-        <v>53.7186</v>
+        <v>51.739</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>25.133</v>
+        <v>24.718</v>
       </c>
       <c r="C15" t="n">
-        <v>31.414</v>
+        <v>31.4138</v>
       </c>
       <c r="D15" t="n">
-        <v>61.0354</v>
+        <v>61.2638</v>
       </c>
       <c r="E15" t="n">
-        <v>17.2947</v>
+        <v>15.625</v>
       </c>
       <c r="F15" t="n">
-        <v>52.8834</v>
+        <v>51.0826</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>24.4095</v>
+        <v>24.0888</v>
       </c>
       <c r="C16" t="n">
-        <v>30.9279</v>
+        <v>30.9443</v>
       </c>
       <c r="D16" t="n">
-        <v>61.0622</v>
+        <v>60.8845</v>
       </c>
       <c r="E16" t="n">
-        <v>16.769</v>
+        <v>15.2191</v>
       </c>
       <c r="F16" t="n">
-        <v>52.6983</v>
+        <v>50.9546</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>23.7549</v>
+        <v>23.5079</v>
       </c>
       <c r="C17" t="n">
-        <v>30.4496</v>
+        <v>30.4842</v>
       </c>
       <c r="D17" t="n">
-        <v>60.3501</v>
+        <v>60.1291</v>
       </c>
       <c r="E17" t="n">
-        <v>16.2864</v>
+        <v>14.7989</v>
       </c>
       <c r="F17" t="n">
-        <v>52.0695</v>
+        <v>50.3394</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>23.6309</v>
+        <v>23.3227</v>
       </c>
       <c r="C18" t="n">
-        <v>30.0384</v>
+        <v>30.0523</v>
       </c>
       <c r="D18" t="n">
-        <v>60.0462</v>
+        <v>59.9335</v>
       </c>
       <c r="E18" t="n">
-        <v>15.8484</v>
+        <v>14.4698</v>
       </c>
       <c r="F18" t="n">
-        <v>51.6225</v>
+        <v>50.4028</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>22.9537</v>
+        <v>22.7501</v>
       </c>
       <c r="C19" t="n">
-        <v>29.6425</v>
+        <v>29.6693</v>
       </c>
       <c r="D19" t="n">
-        <v>59.4008</v>
+        <v>59.5374</v>
       </c>
       <c r="E19" t="n">
-        <v>15.4805</v>
+        <v>14.148</v>
       </c>
       <c r="F19" t="n">
-        <v>51.322</v>
+        <v>49.6654</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>22.8484</v>
+        <v>22.6029</v>
       </c>
       <c r="C20" t="n">
-        <v>29.2779</v>
+        <v>29.3009</v>
       </c>
       <c r="D20" t="n">
-        <v>59.1939</v>
+        <v>59.3718</v>
       </c>
       <c r="E20" t="n">
-        <v>15.2557</v>
+        <v>13.8563</v>
       </c>
       <c r="F20" t="n">
-        <v>50.6864</v>
+        <v>49.3375</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>22.4412</v>
+        <v>22.5539</v>
       </c>
       <c r="C21" t="n">
-        <v>28.8986</v>
+        <v>28.9069</v>
       </c>
       <c r="D21" t="n">
-        <v>72.35120000000001</v>
+        <v>72.01600000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>15.0787</v>
+        <v>27.0711</v>
       </c>
       <c r="F21" t="n">
-        <v>50.5081</v>
+        <v>57.1597</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>22.4172</v>
+        <v>22.3226</v>
       </c>
       <c r="C22" t="n">
-        <v>41.8135</v>
+        <v>40.5954</v>
       </c>
       <c r="D22" t="n">
-        <v>71.0577</v>
+        <v>70.9224</v>
       </c>
       <c r="E22" t="n">
-        <v>15.0736</v>
+        <v>26.0785</v>
       </c>
       <c r="F22" t="n">
-        <v>50.4451</v>
+        <v>56.2859</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>22.3372</v>
+        <v>22.3631</v>
       </c>
       <c r="C23" t="n">
-        <v>40.9554</v>
+        <v>39.6964</v>
       </c>
       <c r="D23" t="n">
-        <v>69.97669999999999</v>
+        <v>69.64700000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>28.1667</v>
+        <v>25.118</v>
       </c>
       <c r="F23" t="n">
-        <v>58.1529</v>
+        <v>55.4099</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>42.3873</v>
+        <v>41.6333</v>
       </c>
       <c r="C24" t="n">
-        <v>40.1017</v>
+        <v>38.9501</v>
       </c>
       <c r="D24" t="n">
-        <v>69.17740000000001</v>
+        <v>69.0107</v>
       </c>
       <c r="E24" t="n">
-        <v>27.1933</v>
+        <v>24.2582</v>
       </c>
       <c r="F24" t="n">
-        <v>57.1652</v>
+        <v>54.9331</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>38.5858</v>
+        <v>39.8796</v>
       </c>
       <c r="C25" t="n">
-        <v>39.2032</v>
+        <v>38.1253</v>
       </c>
       <c r="D25" t="n">
-        <v>67.90430000000001</v>
+        <v>68.14579999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>26.1814</v>
+        <v>23.3915</v>
       </c>
       <c r="F25" t="n">
-        <v>56.3716</v>
+        <v>54.1515</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>39.6505</v>
+        <v>35.0578</v>
       </c>
       <c r="C26" t="n">
-        <v>38.371</v>
+        <v>37.3577</v>
       </c>
       <c r="D26" t="n">
-        <v>67.3831</v>
+        <v>67.1814</v>
       </c>
       <c r="E26" t="n">
-        <v>25.2428</v>
+        <v>22.6498</v>
       </c>
       <c r="F26" t="n">
-        <v>55.9908</v>
+        <v>53.4779</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>38.0797</v>
+        <v>34.0118</v>
       </c>
       <c r="C27" t="n">
-        <v>37.5769</v>
+        <v>36.6149</v>
       </c>
       <c r="D27" t="n">
-        <v>66.0796</v>
+        <v>66.1134</v>
       </c>
       <c r="E27" t="n">
-        <v>24.3721</v>
+        <v>21.8496</v>
       </c>
       <c r="F27" t="n">
-        <v>53.1338</v>
+        <v>50.9564</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>39.1051</v>
+        <v>33.1043</v>
       </c>
       <c r="C28" t="n">
-        <v>36.8548</v>
+        <v>35.9368</v>
       </c>
       <c r="D28" t="n">
-        <v>64.6811</v>
+        <v>64.8382</v>
       </c>
       <c r="E28" t="n">
-        <v>23.4932</v>
+        <v>21.1327</v>
       </c>
       <c r="F28" t="n">
-        <v>52.563</v>
+        <v>50.6976</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>32.2763</v>
+        <v>32.4139</v>
       </c>
       <c r="C29" t="n">
-        <v>36.1834</v>
+        <v>35.2072</v>
       </c>
       <c r="D29" t="n">
-        <v>64.11069999999999</v>
+        <v>64.4973</v>
       </c>
       <c r="E29" t="n">
-        <v>22.6979</v>
+        <v>20.4843</v>
       </c>
       <c r="F29" t="n">
-        <v>51.9635</v>
+        <v>51.9684</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>31.3941</v>
+        <v>32.6999</v>
       </c>
       <c r="C30" t="n">
-        <v>35.464</v>
+        <v>34.7036</v>
       </c>
       <c r="D30" t="n">
-        <v>63.6707</v>
+        <v>63.5723</v>
       </c>
       <c r="E30" t="n">
-        <v>21.9674</v>
+        <v>19.8394</v>
       </c>
       <c r="F30" t="n">
-        <v>51.1081</v>
+        <v>49.3507</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>35.7557</v>
+        <v>31.0298</v>
       </c>
       <c r="C31" t="n">
-        <v>34.8165</v>
+        <v>33.9626</v>
       </c>
       <c r="D31" t="n">
-        <v>63.3747</v>
+        <v>63.3923</v>
       </c>
       <c r="E31" t="n">
-        <v>21.2619</v>
+        <v>19.2032</v>
       </c>
       <c r="F31" t="n">
-        <v>50.9654</v>
+        <v>49.1513</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>34.5526</v>
+        <v>30.2611</v>
       </c>
       <c r="C32" t="n">
-        <v>34.207</v>
+        <v>33.3889</v>
       </c>
       <c r="D32" t="n">
-        <v>62.9031</v>
+        <v>63.0498</v>
       </c>
       <c r="E32" t="n">
-        <v>20.6219</v>
+        <v>18.6645</v>
       </c>
       <c r="F32" t="n">
-        <v>50.3968</v>
+        <v>48.8425</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>29.1959</v>
+        <v>27.1269</v>
       </c>
       <c r="C33" t="n">
-        <v>33.5871</v>
+        <v>32.8555</v>
       </c>
       <c r="D33" t="n">
-        <v>62.4656</v>
+        <v>62.6735</v>
       </c>
       <c r="E33" t="n">
-        <v>20.0491</v>
+        <v>18.1801</v>
       </c>
       <c r="F33" t="n">
-        <v>49.7405</v>
+        <v>48.6467</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>28.6512</v>
+        <v>28.5416</v>
       </c>
       <c r="C34" t="n">
-        <v>32.9632</v>
+        <v>32.362</v>
       </c>
       <c r="D34" t="n">
-        <v>62.1137</v>
+        <v>62.4359</v>
       </c>
       <c r="E34" t="n">
-        <v>19.5349</v>
+        <v>17.7701</v>
       </c>
       <c r="F34" t="n">
-        <v>49.5641</v>
+        <v>48.2279</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>28.1127</v>
+        <v>28.1467</v>
       </c>
       <c r="C35" t="n">
-        <v>32.4707</v>
+        <v>31.8226</v>
       </c>
       <c r="D35" t="n">
-        <v>78.20229999999999</v>
+        <v>76.8279</v>
       </c>
       <c r="E35" t="n">
-        <v>19.123</v>
+        <v>31.1008</v>
       </c>
       <c r="F35" t="n">
-        <v>49.5847</v>
+        <v>58.7539</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>27.4579</v>
+        <v>27.5158</v>
       </c>
       <c r="C36" t="n">
-        <v>31.9897</v>
+        <v>31.45</v>
       </c>
       <c r="D36" t="n">
-        <v>75.1902</v>
+        <v>75.3663</v>
       </c>
       <c r="E36" t="n">
-        <v>18.8381</v>
+        <v>29.8067</v>
       </c>
       <c r="F36" t="n">
-        <v>50.2055</v>
+        <v>58.0599</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>30.1812</v>
+        <v>26.9393</v>
       </c>
       <c r="C37" t="n">
-        <v>44.8091</v>
+        <v>42.6492</v>
       </c>
       <c r="D37" t="n">
-        <v>73.4366</v>
+        <v>74.46080000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>32.4944</v>
+        <v>28.7266</v>
       </c>
       <c r="F37" t="n">
-        <v>60.1746</v>
+        <v>57.1638</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>44.6371</v>
+        <v>48.3696</v>
       </c>
       <c r="C38" t="n">
-        <v>43.7505</v>
+        <v>41.6174</v>
       </c>
       <c r="D38" t="n">
-        <v>72.4237</v>
+        <v>72.83199999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>31.3203</v>
+        <v>27.8332</v>
       </c>
       <c r="F38" t="n">
-        <v>59.2819</v>
+        <v>56.4651</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>43.3945</v>
+        <v>46.8925</v>
       </c>
       <c r="C39" t="n">
-        <v>42.7038</v>
+        <v>40.6979</v>
       </c>
       <c r="D39" t="n">
-        <v>71.70820000000001</v>
+        <v>71.3386</v>
       </c>
       <c r="E39" t="n">
-        <v>30.1977</v>
+        <v>26.7723</v>
       </c>
       <c r="F39" t="n">
-        <v>58.6646</v>
+        <v>55.8812</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>45.2683</v>
+        <v>45.4182</v>
       </c>
       <c r="C40" t="n">
-        <v>41.7267</v>
+        <v>39.7745</v>
       </c>
       <c r="D40" t="n">
-        <v>70.5324</v>
+        <v>71.0192</v>
       </c>
       <c r="E40" t="n">
-        <v>29.0972</v>
+        <v>25.7564</v>
       </c>
       <c r="F40" t="n">
-        <v>57.5449</v>
+        <v>54.289</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>40.8369</v>
+        <v>43.8631</v>
       </c>
       <c r="C41" t="n">
-        <v>40.7223</v>
+        <v>38.9367</v>
       </c>
       <c r="D41" t="n">
-        <v>69.6664</v>
+        <v>69.5254</v>
       </c>
       <c r="E41" t="n">
-        <v>28.0051</v>
+        <v>24.874</v>
       </c>
       <c r="F41" t="n">
-        <v>56.9307</v>
+        <v>53.5934</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>39.5814</v>
+        <v>42.7653</v>
       </c>
       <c r="C42" t="n">
-        <v>39.8872</v>
+        <v>38.1095</v>
       </c>
       <c r="D42" t="n">
-        <v>69.0046</v>
+        <v>68.54819999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>27.0331</v>
+        <v>24.1248</v>
       </c>
       <c r="F42" t="n">
-        <v>55.9652</v>
+        <v>53.2645</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>38.5985</v>
+        <v>41.2689</v>
       </c>
       <c r="C43" t="n">
-        <v>38.9706</v>
+        <v>37.3143</v>
       </c>
       <c r="D43" t="n">
-        <v>67.9361</v>
+        <v>68.096</v>
       </c>
       <c r="E43" t="n">
-        <v>26.0578</v>
+        <v>23.2951</v>
       </c>
       <c r="F43" t="n">
-        <v>55.2895</v>
+        <v>52.4485</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>39.9983</v>
+        <v>42.4378</v>
       </c>
       <c r="C44" t="n">
-        <v>38.156</v>
+        <v>36.5779</v>
       </c>
       <c r="D44" t="n">
-        <v>67.5363</v>
+        <v>67.5423</v>
       </c>
       <c r="E44" t="n">
-        <v>25.1835</v>
+        <v>22.4983</v>
       </c>
       <c r="F44" t="n">
-        <v>54.4818</v>
+        <v>51.8661</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>36.1866</v>
+        <v>41.937</v>
       </c>
       <c r="C45" t="n">
-        <v>37.4511</v>
+        <v>35.9159</v>
       </c>
       <c r="D45" t="n">
-        <v>66.6212</v>
+        <v>66.7833</v>
       </c>
       <c r="E45" t="n">
-        <v>24.3772</v>
+        <v>21.7882</v>
       </c>
       <c r="F45" t="n">
-        <v>53.932</v>
+        <v>51.3965</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>37.2428</v>
+        <v>37.8173</v>
       </c>
       <c r="C46" t="n">
-        <v>36.6558</v>
+        <v>35.2427</v>
       </c>
       <c r="D46" t="n">
-        <v>66.5509</v>
+        <v>66.7567</v>
       </c>
       <c r="E46" t="n">
-        <v>23.5754</v>
+        <v>21.1565</v>
       </c>
       <c r="F46" t="n">
-        <v>53.2334</v>
+        <v>50.957</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>36.0878</v>
+        <v>38.2267</v>
       </c>
       <c r="C47" t="n">
-        <v>35.9915</v>
+        <v>34.5889</v>
       </c>
       <c r="D47" t="n">
-        <v>65.84439999999999</v>
+        <v>65.8539</v>
       </c>
       <c r="E47" t="n">
-        <v>22.8944</v>
+        <v>20.5184</v>
       </c>
       <c r="F47" t="n">
-        <v>52.8849</v>
+        <v>50.4924</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>35.3613</v>
+        <v>35.8115</v>
       </c>
       <c r="C48" t="n">
-        <v>35.2944</v>
+        <v>33.9818</v>
       </c>
       <c r="D48" t="n">
-        <v>65.2794</v>
+        <v>65.4915</v>
       </c>
       <c r="E48" t="n">
-        <v>22.2603</v>
+        <v>20.0666</v>
       </c>
       <c r="F48" t="n">
-        <v>52.4368</v>
+        <v>50.0276</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>34.3787</v>
+        <v>36.7077</v>
       </c>
       <c r="C49" t="n">
-        <v>34.7177</v>
+        <v>33.3945</v>
       </c>
       <c r="D49" t="n">
-        <v>65.09180000000001</v>
+        <v>64.89190000000001</v>
       </c>
       <c r="E49" t="n">
-        <v>21.7038</v>
+        <v>19.6742</v>
       </c>
       <c r="F49" t="n">
-        <v>52.2167</v>
+        <v>49.8242</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>33.6456</v>
+        <v>35.2715</v>
       </c>
       <c r="C50" t="n">
-        <v>34.0638</v>
+        <v>32.8598</v>
       </c>
       <c r="D50" t="n">
-        <v>80.9404</v>
+        <v>79.9965</v>
       </c>
       <c r="E50" t="n">
-        <v>21.2944</v>
+        <v>32.0415</v>
       </c>
       <c r="F50" t="n">
-        <v>51.6289</v>
+        <v>59.581</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>33.2813</v>
+        <v>33.6203</v>
       </c>
       <c r="C51" t="n">
-        <v>46.784</v>
+        <v>43.5769</v>
       </c>
       <c r="D51" t="n">
-        <v>79.7727</v>
+        <v>78.8623</v>
       </c>
       <c r="E51" t="n">
-        <v>34.9211</v>
+        <v>30.9797</v>
       </c>
       <c r="F51" t="n">
-        <v>62.819</v>
+        <v>58.6866</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>31.3769</v>
+        <v>34.1898</v>
       </c>
       <c r="C52" t="n">
-        <v>45.6085</v>
+        <v>42.5205</v>
       </c>
       <c r="D52" t="n">
-        <v>78.0793</v>
+        <v>77.20829999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>33.6268</v>
+        <v>29.8694</v>
       </c>
       <c r="F52" t="n">
-        <v>61.6073</v>
+        <v>57.8582</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>53.8148</v>
+        <v>56.3091</v>
       </c>
       <c r="C53" t="n">
-        <v>44.4742</v>
+        <v>41.7083</v>
       </c>
       <c r="D53" t="n">
-        <v>76.82559999999999</v>
+        <v>75.92919999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>32.4279</v>
+        <v>28.8446</v>
       </c>
       <c r="F53" t="n">
-        <v>60.7851</v>
+        <v>57.0398</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>50.2436</v>
+        <v>54.4439</v>
       </c>
       <c r="C54" t="n">
-        <v>43.4064</v>
+        <v>41.0448</v>
       </c>
       <c r="D54" t="n">
-        <v>76.82640000000001</v>
+        <v>75.2979</v>
       </c>
       <c r="E54" t="n">
-        <v>31.2924</v>
+        <v>27.5989</v>
       </c>
       <c r="F54" t="n">
-        <v>60.0163</v>
+        <v>56.1266</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>49.8302</v>
+        <v>52.6946</v>
       </c>
       <c r="C55" t="n">
-        <v>42.4048</v>
+        <v>39.9268</v>
       </c>
       <c r="D55" t="n">
-        <v>74.9589</v>
+        <v>73.9254</v>
       </c>
       <c r="E55" t="n">
-        <v>30.1878</v>
+        <v>26.6809</v>
       </c>
       <c r="F55" t="n">
-        <v>58.7571</v>
+        <v>55.4978</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>47.4636</v>
+        <v>49.6603</v>
       </c>
       <c r="C56" t="n">
-        <v>41.4243</v>
+        <v>39.0007</v>
       </c>
       <c r="D56" t="n">
-        <v>74.0299</v>
+        <v>72.9162</v>
       </c>
       <c r="E56" t="n">
-        <v>29.1189</v>
+        <v>25.7488</v>
       </c>
       <c r="F56" t="n">
-        <v>57.9443</v>
+        <v>54.7033</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>46.2321</v>
+        <v>49.3352</v>
       </c>
       <c r="C57" t="n">
-        <v>40.5283</v>
+        <v>38.2179</v>
       </c>
       <c r="D57" t="n">
-        <v>73.31310000000001</v>
+        <v>74.1661</v>
       </c>
       <c r="E57" t="n">
-        <v>28.1279</v>
+        <v>25.1261</v>
       </c>
       <c r="F57" t="n">
-        <v>57.3144</v>
+        <v>54.1892</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>46.0344</v>
+        <v>47.0954</v>
       </c>
       <c r="C58" t="n">
-        <v>39.6181</v>
+        <v>37.5814</v>
       </c>
       <c r="D58" t="n">
-        <v>71.9723</v>
+        <v>71.322</v>
       </c>
       <c r="E58" t="n">
-        <v>27.1742</v>
+        <v>24.4897</v>
       </c>
       <c r="F58" t="n">
-        <v>56.2964</v>
+        <v>53.6777</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>43.2113</v>
+        <v>46.7737</v>
       </c>
       <c r="C59" t="n">
-        <v>38.7782</v>
+        <v>36.9339</v>
       </c>
       <c r="D59" t="n">
-        <v>71.3746</v>
+        <v>70.5224</v>
       </c>
       <c r="E59" t="n">
-        <v>26.29</v>
+        <v>23.5147</v>
       </c>
       <c r="F59" t="n">
-        <v>55.6885</v>
+        <v>53.0313</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>42.171</v>
+        <v>45.4142</v>
       </c>
       <c r="C60" t="n">
-        <v>37.9855</v>
+        <v>36.1838</v>
       </c>
       <c r="D60" t="n">
-        <v>70.9224</v>
+        <v>69.883</v>
       </c>
       <c r="E60" t="n">
-        <v>25.4898</v>
+        <v>22.7613</v>
       </c>
       <c r="F60" t="n">
-        <v>55.0959</v>
+        <v>52.6682</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>41.0919</v>
+        <v>43.2179</v>
       </c>
       <c r="C61" t="n">
-        <v>37.2139</v>
+        <v>35.4331</v>
       </c>
       <c r="D61" t="n">
-        <v>70.4301</v>
+        <v>72.40430000000001</v>
       </c>
       <c r="E61" t="n">
-        <v>24.7291</v>
+        <v>22.1014</v>
       </c>
       <c r="F61" t="n">
-        <v>54.74</v>
+        <v>52.2634</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>40.377</v>
+        <v>42.1249</v>
       </c>
       <c r="C62" t="n">
-        <v>36.4957</v>
+        <v>34.9662</v>
       </c>
       <c r="D62" t="n">
-        <v>69.7929</v>
+        <v>71.3378</v>
       </c>
       <c r="E62" t="n">
-        <v>24.0497</v>
+        <v>21.6614</v>
       </c>
       <c r="F62" t="n">
-        <v>53.9991</v>
+        <v>52.6991</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>40.4688</v>
+        <v>39.1439</v>
       </c>
       <c r="C63" t="n">
-        <v>35.8518</v>
+        <v>34.3136</v>
       </c>
       <c r="D63" t="n">
-        <v>68.79940000000001</v>
+        <v>69.4359</v>
       </c>
       <c r="E63" t="n">
-        <v>23.4474</v>
+        <v>21.1476</v>
       </c>
       <c r="F63" t="n">
-        <v>53.6961</v>
+        <v>51.4079</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>38.6622</v>
+        <v>37.8625</v>
       </c>
       <c r="C64" t="n">
-        <v>35.2313</v>
+        <v>33.8061</v>
       </c>
       <c r="D64" t="n">
-        <v>85.90560000000001</v>
+        <v>86.0017</v>
       </c>
       <c r="E64" t="n">
-        <v>22.9534</v>
+        <v>33.5783</v>
       </c>
       <c r="F64" t="n">
-        <v>53.4834</v>
+        <v>62.1252</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>38.4287</v>
+        <v>37.5138</v>
       </c>
       <c r="C65" t="n">
-        <v>48.0856</v>
+        <v>45.0325</v>
       </c>
       <c r="D65" t="n">
-        <v>85.7555</v>
+        <v>85.4258</v>
       </c>
       <c r="E65" t="n">
-        <v>22.6144</v>
+        <v>32.9629</v>
       </c>
       <c r="F65" t="n">
-        <v>53.6058</v>
+        <v>61.6338</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>37.1395</v>
+        <v>36.3886</v>
       </c>
       <c r="C66" t="n">
-        <v>47.0583</v>
+        <v>43.93</v>
       </c>
       <c r="D66" t="n">
-        <v>84.3699</v>
+        <v>83.4714</v>
       </c>
       <c r="E66" t="n">
-        <v>35.5556</v>
+        <v>32.3241</v>
       </c>
       <c r="F66" t="n">
-        <v>64.9363</v>
+        <v>60.245</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>59.9008</v>
+        <v>58.6887</v>
       </c>
       <c r="C67" t="n">
-        <v>46.0366</v>
+        <v>42.9675</v>
       </c>
       <c r="D67" t="n">
-        <v>82.15779999999999</v>
+        <v>80.3506</v>
       </c>
       <c r="E67" t="n">
-        <v>34.3295</v>
+        <v>30.6064</v>
       </c>
       <c r="F67" t="n">
-        <v>64.18859999999999</v>
+        <v>59.8852</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>58.0564</v>
+        <v>56.642</v>
       </c>
       <c r="C68" t="n">
-        <v>45.1875</v>
+        <v>42.0409</v>
       </c>
       <c r="D68" t="n">
-        <v>81.6279</v>
+        <v>79.39830000000001</v>
       </c>
       <c r="E68" t="n">
-        <v>33.1813</v>
+        <v>29.7345</v>
       </c>
       <c r="F68" t="n">
-        <v>62.5625</v>
+        <v>58.4936</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>57.0031</v>
+        <v>56.0424</v>
       </c>
       <c r="C69" t="n">
-        <v>44.0953</v>
+        <v>41.2612</v>
       </c>
       <c r="D69" t="n">
-        <v>80.27509999999999</v>
+        <v>78.90389999999999</v>
       </c>
       <c r="E69" t="n">
-        <v>32.1497</v>
+        <v>28.9318</v>
       </c>
       <c r="F69" t="n">
-        <v>61.7425</v>
+        <v>58.3647</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>55.6118</v>
+        <v>53.5874</v>
       </c>
       <c r="C70" t="n">
-        <v>43.446</v>
+        <v>40.5804</v>
       </c>
       <c r="D70" t="n">
-        <v>79.82680000000001</v>
+        <v>78.1858</v>
       </c>
       <c r="E70" t="n">
-        <v>31.091</v>
+        <v>28.0216</v>
       </c>
       <c r="F70" t="n">
-        <v>61.935</v>
+        <v>57.8598</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>53.7817</v>
+        <v>52.7071</v>
       </c>
       <c r="C71" t="n">
-        <v>42.6256</v>
+        <v>39.3889</v>
       </c>
       <c r="D71" t="n">
-        <v>78.47410000000001</v>
+        <v>76.76260000000001</v>
       </c>
       <c r="E71" t="n">
-        <v>30.0719</v>
+        <v>26.6094</v>
       </c>
       <c r="F71" t="n">
-        <v>60.8208</v>
+        <v>56.7476</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>52.5537</v>
+        <v>51.4848</v>
       </c>
       <c r="C72" t="n">
-        <v>41.7931</v>
+        <v>39.0463</v>
       </c>
       <c r="D72" t="n">
-        <v>77.4413</v>
+        <v>75.77719999999999</v>
       </c>
       <c r="E72" t="n">
-        <v>29.1025</v>
+        <v>26.4305</v>
       </c>
       <c r="F72" t="n">
-        <v>59.8153</v>
+        <v>55.8953</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>51.5795</v>
+        <v>49.7716</v>
       </c>
       <c r="C73" t="n">
-        <v>40.9607</v>
+        <v>38.3888</v>
       </c>
       <c r="D73" t="n">
-        <v>77.6657</v>
+        <v>75.621</v>
       </c>
       <c r="E73" t="n">
-        <v>28.1922</v>
+        <v>25.2797</v>
       </c>
       <c r="F73" t="n">
-        <v>60.8397</v>
+        <v>55.491</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>49.031</v>
+        <v>48.4091</v>
       </c>
       <c r="C74" t="n">
-        <v>39.9232</v>
+        <v>37.4599</v>
       </c>
       <c r="D74" t="n">
-        <v>77.1078</v>
+        <v>74.6707</v>
       </c>
       <c r="E74" t="n">
-        <v>27.3127</v>
+        <v>24.9037</v>
       </c>
       <c r="F74" t="n">
-        <v>58.1428</v>
+        <v>54.84</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>48.205</v>
+        <v>46.8903</v>
       </c>
       <c r="C75" t="n">
-        <v>39.3783</v>
+        <v>36.7097</v>
       </c>
       <c r="D75" t="n">
-        <v>76.7628</v>
+        <v>75.5595</v>
       </c>
       <c r="E75" t="n">
-        <v>26.5613</v>
+        <v>24.3599</v>
       </c>
       <c r="F75" t="n">
-        <v>57.658</v>
+        <v>54.5218</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>47.3056</v>
+        <v>46.6521</v>
       </c>
       <c r="C76" t="n">
-        <v>38.4786</v>
+        <v>36.0968</v>
       </c>
       <c r="D76" t="n">
-        <v>76.6673</v>
+        <v>74.521</v>
       </c>
       <c r="E76" t="n">
-        <v>25.8455</v>
+        <v>23.4138</v>
       </c>
       <c r="F76" t="n">
-        <v>58.075</v>
+        <v>54.061</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>46.7216</v>
+        <v>45.3344</v>
       </c>
       <c r="C77" t="n">
-        <v>38.0685</v>
+        <v>35.5244</v>
       </c>
       <c r="D77" t="n">
-        <v>75.6382</v>
+        <v>74.50449999999999</v>
       </c>
       <c r="E77" t="n">
-        <v>25.1684</v>
+        <v>22.5365</v>
       </c>
       <c r="F77" t="n">
-        <v>56.9675</v>
+        <v>53.8773</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>44.933</v>
+        <v>45.2564</v>
       </c>
       <c r="C78" t="n">
-        <v>37.2122</v>
+        <v>35.0386</v>
       </c>
       <c r="D78" t="n">
-        <v>109.795</v>
+        <v>109.534</v>
       </c>
       <c r="E78" t="n">
-        <v>24.7281</v>
+        <v>36.8757</v>
       </c>
       <c r="F78" t="n">
-        <v>56.5132</v>
+        <v>77.9734</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>43.6875</v>
+        <v>44.1094</v>
       </c>
       <c r="C79" t="n">
-        <v>50.2547</v>
+        <v>47.2666</v>
       </c>
       <c r="D79" t="n">
-        <v>109.701</v>
+        <v>107.896</v>
       </c>
       <c r="E79" t="n">
-        <v>24.3543</v>
+        <v>34.946</v>
       </c>
       <c r="F79" t="n">
-        <v>57.1052</v>
+        <v>78.8558</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>42.1627</v>
+        <v>43.2682</v>
       </c>
       <c r="C80" t="n">
-        <v>50.108</v>
+        <v>46.5729</v>
       </c>
       <c r="D80" t="n">
-        <v>107.94</v>
+        <v>107.103</v>
       </c>
       <c r="E80" t="n">
-        <v>37.7877</v>
+        <v>34.4481</v>
       </c>
       <c r="F80" t="n">
-        <v>82.05459999999999</v>
+        <v>78.0046</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>62.9804</v>
+        <v>63.5519</v>
       </c>
       <c r="C81" t="n">
-        <v>49.8614</v>
+        <v>47.2279</v>
       </c>
       <c r="D81" t="n">
-        <v>107.103</v>
+        <v>106.28</v>
       </c>
       <c r="E81" t="n">
-        <v>36.8837</v>
+        <v>33.7394</v>
       </c>
       <c r="F81" t="n">
-        <v>82.7418</v>
+        <v>78.0898</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>62.5996</v>
+        <v>63.1173</v>
       </c>
       <c r="C82" t="n">
-        <v>49.6867</v>
+        <v>46.127</v>
       </c>
       <c r="D82" t="n">
-        <v>106.076</v>
+        <v>105.316</v>
       </c>
       <c r="E82" t="n">
-        <v>35.9338</v>
+        <v>32.1119</v>
       </c>
       <c r="F82" t="n">
-        <v>82.214</v>
+        <v>76.9419</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>61.6889</v>
+        <v>62.156</v>
       </c>
       <c r="C83" t="n">
-        <v>49.3761</v>
+        <v>45.7158</v>
       </c>
       <c r="D83" t="n">
-        <v>106.193</v>
+        <v>103.875</v>
       </c>
       <c r="E83" t="n">
-        <v>35.0386</v>
+        <v>31.2994</v>
       </c>
       <c r="F83" t="n">
-        <v>81.8639</v>
+        <v>76.0432</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>60.9289</v>
+        <v>61.5289</v>
       </c>
       <c r="C84" t="n">
-        <v>49.0924</v>
+        <v>45.1251</v>
       </c>
       <c r="D84" t="n">
-        <v>106.294</v>
+        <v>103.902</v>
       </c>
       <c r="E84" t="n">
-        <v>34.0774</v>
+        <v>30.3722</v>
       </c>
       <c r="F84" t="n">
-        <v>80.01909999999999</v>
+        <v>75.2503</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>59.9843</v>
+        <v>60.0568</v>
       </c>
       <c r="C85" t="n">
-        <v>48.983</v>
+        <v>44.8646</v>
       </c>
       <c r="D85" t="n">
-        <v>104.97</v>
+        <v>103.992</v>
       </c>
       <c r="E85" t="n">
-        <v>33.214</v>
+        <v>29.5333</v>
       </c>
       <c r="F85" t="n">
-        <v>79.3306</v>
+        <v>73.04559999999999</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>59.1072</v>
+        <v>59.2215</v>
       </c>
       <c r="C86" t="n">
-        <v>48.4072</v>
+        <v>44.7479</v>
       </c>
       <c r="D86" t="n">
-        <v>105.073</v>
+        <v>103.151</v>
       </c>
       <c r="E86" t="n">
-        <v>32.2919</v>
+        <v>28.7893</v>
       </c>
       <c r="F86" t="n">
-        <v>77.37350000000001</v>
+        <v>71.4414</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>58.107</v>
+        <v>58.2869</v>
       </c>
       <c r="C87" t="n">
-        <v>47.9975</v>
+        <v>44.0994</v>
       </c>
       <c r="D87" t="n">
-        <v>105.361</v>
+        <v>103.267</v>
       </c>
       <c r="E87" t="n">
-        <v>31.4768</v>
+        <v>27.7248</v>
       </c>
       <c r="F87" t="n">
-        <v>77.7234</v>
+        <v>71.58540000000001</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>57.2062</v>
+        <v>57.3551</v>
       </c>
       <c r="C88" t="n">
-        <v>47.7075</v>
+        <v>43.424</v>
       </c>
       <c r="D88" t="n">
-        <v>106.346</v>
+        <v>104.533</v>
       </c>
       <c r="E88" t="n">
-        <v>30.6997</v>
+        <v>27.6671</v>
       </c>
       <c r="F88" t="n">
-        <v>76.7359</v>
+        <v>70.4813</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>55.9541</v>
+        <v>56.0674</v>
       </c>
       <c r="C89" t="n">
-        <v>47.2212</v>
+        <v>42.847</v>
       </c>
       <c r="D89" t="n">
-        <v>108.432</v>
+        <v>104.507</v>
       </c>
       <c r="E89" t="n">
-        <v>29.9555</v>
+        <v>26.4926</v>
       </c>
       <c r="F89" t="n">
-        <v>76.23180000000001</v>
+        <v>68.4615</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>55.2202</v>
+        <v>55.3149</v>
       </c>
       <c r="C90" t="n">
-        <v>46.7063</v>
+        <v>42.408</v>
       </c>
       <c r="D90" t="n">
-        <v>107.221</v>
+        <v>104.781</v>
       </c>
       <c r="E90" t="n">
-        <v>29.2674</v>
+        <v>26.3345</v>
       </c>
       <c r="F90" t="n">
-        <v>74.65519999999999</v>
+        <v>70.00790000000001</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>53.9369</v>
+        <v>54.29</v>
       </c>
       <c r="C91" t="n">
-        <v>46.4369</v>
+        <v>42.3738</v>
       </c>
       <c r="D91" t="n">
-        <v>109.647</v>
+        <v>107.368</v>
       </c>
       <c r="E91" t="n">
-        <v>28.596</v>
+        <v>25.1791</v>
       </c>
       <c r="F91" t="n">
-        <v>73.59610000000001</v>
+        <v>67.1728</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>52.496</v>
+        <v>52.7114</v>
       </c>
       <c r="C92" t="n">
-        <v>46.1357</v>
+        <v>41.601</v>
       </c>
       <c r="D92" t="n">
-        <v>149.972</v>
+        <v>148.224</v>
       </c>
       <c r="E92" t="n">
-        <v>28.1023</v>
+        <v>38.6773</v>
       </c>
       <c r="F92" t="n">
-        <v>71.1841</v>
+        <v>98.8065</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>52.9293</v>
+        <v>49.0302</v>
       </c>
       <c r="C93" t="n">
-        <v>45.6441</v>
+        <v>41.295</v>
       </c>
       <c r="D93" t="n">
-        <v>150.26</v>
+        <v>148.436</v>
       </c>
       <c r="E93" t="n">
-        <v>27.6258</v>
+        <v>38.9182</v>
       </c>
       <c r="F93" t="n">
-        <v>71.0915</v>
+        <v>98.25539999999999</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>52.2091</v>
+        <v>48.3997</v>
       </c>
       <c r="C94" t="n">
-        <v>59.3965</v>
+        <v>54.0952</v>
       </c>
       <c r="D94" t="n">
-        <v>147.813</v>
+        <v>146.789</v>
       </c>
       <c r="E94" t="n">
-        <v>41.3912</v>
+        <v>37.3089</v>
       </c>
       <c r="F94" t="n">
-        <v>102.638</v>
+        <v>98.2242</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>74.7452</v>
+        <v>71.7152</v>
       </c>
       <c r="C95" t="n">
-        <v>59.142</v>
+        <v>53.8786</v>
       </c>
       <c r="D95" t="n">
-        <v>146.112</v>
+        <v>146.282</v>
       </c>
       <c r="E95" t="n">
-        <v>40.7216</v>
+        <v>37.1364</v>
       </c>
       <c r="F95" t="n">
-        <v>101.789</v>
+        <v>96.9787</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>74.88420000000001</v>
+        <v>70.8416</v>
       </c>
       <c r="C96" t="n">
-        <v>58.89</v>
+        <v>53.001</v>
       </c>
       <c r="D96" t="n">
-        <v>145.786</v>
+        <v>145.953</v>
       </c>
       <c r="E96" t="n">
-        <v>39.6711</v>
+        <v>35.6797</v>
       </c>
       <c r="F96" t="n">
-        <v>101.366</v>
+        <v>95.1474</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>73.9186</v>
+        <v>70.7713</v>
       </c>
       <c r="C97" t="n">
-        <v>58.4227</v>
+        <v>52.8003</v>
       </c>
       <c r="D97" t="n">
-        <v>145.84</v>
+        <v>145.273</v>
       </c>
       <c r="E97" t="n">
-        <v>38.6621</v>
+        <v>34.9548</v>
       </c>
       <c r="F97" t="n">
-        <v>101.811</v>
+        <v>94.2105</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>73.15600000000001</v>
+        <v>69.96080000000001</v>
       </c>
       <c r="C98" t="n">
-        <v>58.2548</v>
+        <v>52.752</v>
       </c>
       <c r="D98" t="n">
-        <v>145.232</v>
+        <v>145.083</v>
       </c>
       <c r="E98" t="n">
-        <v>37.7805</v>
+        <v>33.9595</v>
       </c>
       <c r="F98" t="n">
-        <v>99.9229</v>
+        <v>93.5228</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>72.65309999999999</v>
+        <v>68.5283</v>
       </c>
       <c r="C99" t="n">
-        <v>57.7412</v>
+        <v>52.8714</v>
       </c>
       <c r="D99" t="n">
-        <v>146.427</v>
+        <v>145.431</v>
       </c>
       <c r="E99" t="n">
-        <v>36.8044</v>
+        <v>33.0165</v>
       </c>
       <c r="F99" t="n">
-        <v>99.4406</v>
+        <v>92.8728</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>71.2236</v>
+        <v>68.497</v>
       </c>
       <c r="C100" t="n">
-        <v>57.1902</v>
+        <v>52.4271</v>
       </c>
       <c r="D100" t="n">
-        <v>146.631</v>
+        <v>145.657</v>
       </c>
       <c r="E100" t="n">
-        <v>35.7849</v>
+        <v>32.0604</v>
       </c>
       <c r="F100" t="n">
-        <v>99.2169</v>
+        <v>91.1771</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>70.2734</v>
+        <v>67.1737</v>
       </c>
       <c r="C101" t="n">
-        <v>56.8781</v>
+        <v>52.8585</v>
       </c>
       <c r="D101" t="n">
-        <v>147.818</v>
+        <v>145.613</v>
       </c>
       <c r="E101" t="n">
-        <v>34.9707</v>
+        <v>31.2815</v>
       </c>
       <c r="F101" t="n">
-        <v>97.488</v>
+        <v>89.5437</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>70.236</v>
+        <v>66.9654</v>
       </c>
       <c r="C102" t="n">
-        <v>56.5416</v>
+        <v>52.4421</v>
       </c>
       <c r="D102" t="n">
-        <v>147.963</v>
+        <v>145.629</v>
       </c>
       <c r="E102" t="n">
-        <v>34.1729</v>
+        <v>30.8589</v>
       </c>
       <c r="F102" t="n">
-        <v>96.7672</v>
+        <v>89.7432</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>70.509</v>
+        <v>65.9782</v>
       </c>
       <c r="C103" t="n">
-        <v>56.289</v>
+        <v>52.127</v>
       </c>
       <c r="D103" t="n">
-        <v>148.725</v>
+        <v>146.464</v>
       </c>
       <c r="E103" t="n">
-        <v>33.4444</v>
+        <v>29.9221</v>
       </c>
       <c r="F103" t="n">
-        <v>95.13420000000001</v>
+        <v>88.23999999999999</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>69.0522</v>
+        <v>65.4144</v>
       </c>
       <c r="C104" t="n">
-        <v>56.0111</v>
+        <v>52.646</v>
       </c>
       <c r="D104" t="n">
-        <v>148.722</v>
+        <v>147.518</v>
       </c>
       <c r="E104" t="n">
-        <v>32.6998</v>
+        <v>29.3997</v>
       </c>
       <c r="F104" t="n">
-        <v>94.3767</v>
+        <v>87.9987</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>68.733</v>
+        <v>64.87560000000001</v>
       </c>
       <c r="C105" t="n">
-        <v>55.6345</v>
+        <v>51.8659</v>
       </c>
       <c r="D105" t="n">
-        <v>150.564</v>
+        <v>149.194</v>
       </c>
       <c r="E105" t="n">
-        <v>32.0521</v>
+        <v>29.0008</v>
       </c>
       <c r="F105" t="n">
-        <v>94.2226</v>
+        <v>87.5973</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>67.51819999999999</v>
+        <v>64.9752</v>
       </c>
       <c r="C106" t="n">
-        <v>55.4183</v>
+        <v>52.0529</v>
       </c>
       <c r="D106" t="n">
-        <v>151.79</v>
+        <v>150.718</v>
       </c>
       <c r="E106" t="n">
-        <v>31.5291</v>
+        <v>28.5002</v>
       </c>
       <c r="F106" t="n">
-        <v>93.4267</v>
+        <v>86.3891</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>67.00449999999999</v>
+        <v>64.33880000000001</v>
       </c>
       <c r="C107" t="n">
-        <v>55.1243</v>
+        <v>51.5561</v>
       </c>
       <c r="D107" t="n">
-        <v>194.105</v>
+        <v>194.399</v>
       </c>
       <c r="E107" t="n">
-        <v>31.0852</v>
+        <v>41.5747</v>
       </c>
       <c r="F107" t="n">
-        <v>93.2139</v>
+        <v>120.877</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>66.7991</v>
+        <v>64.7955</v>
       </c>
       <c r="C108" t="n">
-        <v>69.31010000000001</v>
+        <v>63.9105</v>
       </c>
       <c r="D108" t="n">
-        <v>192.572</v>
+        <v>193.405</v>
       </c>
       <c r="E108" t="n">
-        <v>44.8627</v>
+        <v>41.8764</v>
       </c>
       <c r="F108" t="n">
-        <v>127.399</v>
+        <v>119.652</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>66.3768</v>
+        <v>64.61109999999999</v>
       </c>
       <c r="C109" t="n">
-        <v>68.90819999999999</v>
+        <v>64.2428</v>
       </c>
       <c r="D109" t="n">
-        <v>191.147</v>
+        <v>191.3</v>
       </c>
       <c r="E109" t="n">
-        <v>44.33</v>
+        <v>40.1143</v>
       </c>
       <c r="F109" t="n">
-        <v>126.64</v>
+        <v>118.915</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>84.5915</v>
+        <v>83.3556</v>
       </c>
       <c r="C110" t="n">
-        <v>68.6369</v>
+        <v>63.5294</v>
       </c>
       <c r="D110" t="n">
-        <v>189.965</v>
+        <v>189.994</v>
       </c>
       <c r="E110" t="n">
-        <v>43.3996</v>
+        <v>39.625</v>
       </c>
       <c r="F110" t="n">
-        <v>125.192</v>
+        <v>117.836</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>84.36239999999999</v>
+        <v>82.7817</v>
       </c>
       <c r="C111" t="n">
-        <v>68.4164</v>
+        <v>63.5096</v>
       </c>
       <c r="D111" t="n">
-        <v>189.08</v>
+        <v>189.217</v>
       </c>
       <c r="E111" t="n">
-        <v>42.509</v>
+        <v>39.1027</v>
       </c>
       <c r="F111" t="n">
-        <v>125.347</v>
+        <v>117.521</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>83.4336</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="C112" t="n">
-        <v>68.11960000000001</v>
+        <v>63.8984</v>
       </c>
       <c r="D112" t="n">
-        <v>187.759</v>
+        <v>188.973</v>
       </c>
       <c r="E112" t="n">
-        <v>41.4857</v>
+        <v>37.6343</v>
       </c>
       <c r="F112" t="n">
-        <v>123.561</v>
+        <v>116.536</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>82.9877</v>
+        <v>85.30880000000001</v>
       </c>
       <c r="C113" t="n">
-        <v>67.8737</v>
+        <v>63.7033</v>
       </c>
       <c r="D113" t="n">
-        <v>186.662</v>
+        <v>188.42</v>
       </c>
       <c r="E113" t="n">
-        <v>40.6374</v>
+        <v>36.7191</v>
       </c>
       <c r="F113" t="n">
-        <v>122.487</v>
+        <v>115.917</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>81.84010000000001</v>
+        <v>84.8038</v>
       </c>
       <c r="C114" t="n">
-        <v>67.54689999999999</v>
+        <v>63.6988</v>
       </c>
       <c r="D114" t="n">
-        <v>186.284</v>
+        <v>187.188</v>
       </c>
       <c r="E114" t="n">
-        <v>39.8815</v>
+        <v>36.2654</v>
       </c>
       <c r="F114" t="n">
-        <v>121.317</v>
+        <v>116.119</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>81.95569999999999</v>
+        <v>83.54300000000001</v>
       </c>
       <c r="C115" t="n">
-        <v>67.2137</v>
+        <v>63.8198</v>
       </c>
       <c r="D115" t="n">
-        <v>186.465</v>
+        <v>187.012</v>
       </c>
       <c r="E115" t="n">
-        <v>39.0372</v>
+        <v>36.1917</v>
       </c>
       <c r="F115" t="n">
-        <v>120.414</v>
+        <v>115.114</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>80.0382</v>
+        <v>82.164</v>
       </c>
       <c r="C116" t="n">
-        <v>66.95820000000001</v>
+        <v>63.9696</v>
       </c>
       <c r="D116" t="n">
-        <v>186.201</v>
+        <v>187.31</v>
       </c>
       <c r="E116" t="n">
-        <v>38.3412</v>
+        <v>34.7674</v>
       </c>
       <c r="F116" t="n">
-        <v>119.862</v>
+        <v>114.792</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>81.5488</v>
+        <v>77.8326</v>
       </c>
       <c r="C117" t="n">
-        <v>66.81999999999999</v>
+        <v>64.00660000000001</v>
       </c>
       <c r="D117" t="n">
-        <v>186.321</v>
+        <v>187.94</v>
       </c>
       <c r="E117" t="n">
-        <v>37.6791</v>
+        <v>34.464</v>
       </c>
       <c r="F117" t="n">
-        <v>119.45</v>
+        <v>114.222</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>80.9974</v>
+        <v>77.6451</v>
       </c>
       <c r="C118" t="n">
-        <v>66.56</v>
+        <v>63.8602</v>
       </c>
       <c r="D118" t="n">
-        <v>187.262</v>
+        <v>188.273</v>
       </c>
       <c r="E118" t="n">
-        <v>36.9691</v>
+        <v>34.1875</v>
       </c>
       <c r="F118" t="n">
-        <v>118.122</v>
+        <v>113.67</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>79.2677</v>
+        <v>76.8698</v>
       </c>
       <c r="C119" t="n">
-        <v>66.3578</v>
+        <v>63.6804</v>
       </c>
       <c r="D119" t="n">
-        <v>188.659</v>
+        <v>188.535</v>
       </c>
       <c r="E119" t="n">
-        <v>36.396</v>
+        <v>33.6846</v>
       </c>
       <c r="F119" t="n">
-        <v>118.681</v>
+        <v>113.4</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>79.3035</v>
+        <v>78.0254</v>
       </c>
       <c r="C120" t="n">
-        <v>66.1598</v>
+        <v>64.0676</v>
       </c>
       <c r="D120" t="n">
-        <v>188.361</v>
+        <v>189.328</v>
       </c>
       <c r="E120" t="n">
-        <v>35.732</v>
+        <v>32.7864</v>
       </c>
       <c r="F120" t="n">
-        <v>117.666</v>
+        <v>113.261</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>77.81440000000001</v>
+        <v>77.93519999999999</v>
       </c>
       <c r="C121" t="n">
-        <v>66.0127</v>
+        <v>63.1793</v>
       </c>
       <c r="D121" t="n">
-        <v>236.715</v>
+        <v>236.869</v>
       </c>
       <c r="E121" t="n">
-        <v>35.3648</v>
+        <v>46.8787</v>
       </c>
       <c r="F121" t="n">
-        <v>117.444</v>
+        <v>147.968</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>77.9303</v>
+        <v>76.7736</v>
       </c>
       <c r="C122" t="n">
-        <v>77.9862</v>
+        <v>75.3109</v>
       </c>
       <c r="D122" t="n">
-        <v>233.763</v>
+        <v>234.568</v>
       </c>
       <c r="E122" t="n">
-        <v>34.9643</v>
+        <v>45.252</v>
       </c>
       <c r="F122" t="n">
-        <v>116.467</v>
+        <v>147.032</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>77.3951</v>
+        <v>75.6275</v>
       </c>
       <c r="C123" t="n">
-        <v>78.258</v>
+        <v>75.27</v>
       </c>
       <c r="D123" t="n">
-        <v>231.265</v>
+        <v>232.002</v>
       </c>
       <c r="E123" t="n">
-        <v>47.1598</v>
+        <v>45.4791</v>
       </c>
       <c r="F123" t="n">
-        <v>154.908</v>
+        <v>146.843</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>96.6015</v>
+        <v>99.9173</v>
       </c>
       <c r="C124" t="n">
-        <v>78.49460000000001</v>
+        <v>75.50879999999999</v>
       </c>
       <c r="D124" t="n">
-        <v>229.283</v>
+        <v>230.04</v>
       </c>
       <c r="E124" t="n">
-        <v>46.7715</v>
+        <v>46.1641</v>
       </c>
       <c r="F124" t="n">
-        <v>153.148</v>
+        <v>145.82</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>97.164</v>
+        <v>98.6327</v>
       </c>
       <c r="C125" t="n">
-        <v>78.30970000000001</v>
+        <v>76.2576</v>
       </c>
       <c r="D125" t="n">
-        <v>228.592</v>
+        <v>228.46</v>
       </c>
       <c r="E125" t="n">
-        <v>46.1107</v>
+        <v>43.8857</v>
       </c>
       <c r="F125" t="n">
-        <v>148.908</v>
+        <v>145.46</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>96.7668</v>
+        <v>94.79219999999999</v>
       </c>
       <c r="C126" t="n">
-        <v>78.37179999999999</v>
+        <v>76.59050000000001</v>
       </c>
       <c r="D126" t="n">
-        <v>225.758</v>
+        <v>226.283</v>
       </c>
       <c r="E126" t="n">
-        <v>45.68</v>
+        <v>44.2586</v>
       </c>
       <c r="F126" t="n">
-        <v>148.697</v>
+        <v>144.04</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>97.50530000000001</v>
+        <v>93.8685</v>
       </c>
       <c r="C127" t="n">
-        <v>78.46040000000001</v>
+        <v>76.916</v>
       </c>
       <c r="D127" t="n">
-        <v>224.917</v>
+        <v>225.504</v>
       </c>
       <c r="E127" t="n">
-        <v>44.8758</v>
+        <v>43.2434</v>
       </c>
       <c r="F127" t="n">
-        <v>148.642</v>
+        <v>143.317</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>96.1177</v>
+        <v>95.5647</v>
       </c>
       <c r="C128" t="n">
-        <v>78.4808</v>
+        <v>76.9808</v>
       </c>
       <c r="D128" t="n">
-        <v>223.357</v>
+        <v>223.899</v>
       </c>
       <c r="E128" t="n">
-        <v>44.4159</v>
+        <v>43.1658</v>
       </c>
       <c r="F128" t="n">
-        <v>148.251</v>
+        <v>143.3</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>96.2127</v>
+        <v>95.4589</v>
       </c>
       <c r="C129" t="n">
-        <v>78.6682</v>
+        <v>76.7646</v>
       </c>
       <c r="D129" t="n">
-        <v>223.035</v>
+        <v>222.762</v>
       </c>
       <c r="E129" t="n">
-        <v>43.9732</v>
+        <v>41.9904</v>
       </c>
       <c r="F129" t="n">
-        <v>147.455</v>
+        <v>142.271</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>95.9667</v>
+        <v>92.9372</v>
       </c>
       <c r="C130" t="n">
-        <v>78.7196</v>
+        <v>77.27030000000001</v>
       </c>
       <c r="D130" t="n">
-        <v>221.568</v>
+        <v>222.651</v>
       </c>
       <c r="E130" t="n">
-        <v>43.4679</v>
+        <v>41.8843</v>
       </c>
       <c r="F130" t="n">
-        <v>146.306</v>
+        <v>141.953</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>97.2734</v>
+        <v>91.44750000000001</v>
       </c>
       <c r="C131" t="n">
-        <v>78.8331</v>
+        <v>77.34050000000001</v>
       </c>
       <c r="D131" t="n">
-        <v>220.865</v>
+        <v>221.339</v>
       </c>
       <c r="E131" t="n">
-        <v>43.0401</v>
+        <v>41.7308</v>
       </c>
       <c r="F131" t="n">
-        <v>145.778</v>
+        <v>142.568</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>94.05119999999999</v>
+        <v>93.3181</v>
       </c>
       <c r="C132" t="n">
-        <v>79.1584</v>
+        <v>77.34139999999999</v>
       </c>
       <c r="D132" t="n">
-        <v>221.403</v>
+        <v>221.962</v>
       </c>
       <c r="E132" t="n">
-        <v>42.765</v>
+        <v>41.2924</v>
       </c>
       <c r="F132" t="n">
-        <v>144.472</v>
+        <v>141.25</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>93.5033</v>
+        <v>91.4198</v>
       </c>
       <c r="C133" t="n">
-        <v>78.7081</v>
+        <v>77.3861</v>
       </c>
       <c r="D133" t="n">
-        <v>222.334</v>
+        <v>222.073</v>
       </c>
       <c r="E133" t="n">
-        <v>42.689</v>
+        <v>40.6956</v>
       </c>
       <c r="F133" t="n">
-        <v>143.872</v>
+        <v>140.729</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>93.31</v>
+        <v>91.324</v>
       </c>
       <c r="C134" t="n">
-        <v>78.33329999999999</v>
+        <v>77.6507</v>
       </c>
       <c r="D134" t="n">
-        <v>221.572</v>
+        <v>222.226</v>
       </c>
       <c r="E134" t="n">
-        <v>42.0834</v>
+        <v>40.7</v>
       </c>
       <c r="F134" t="n">
-        <v>143.99</v>
+        <v>140.568</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>92.5622</v>
+        <v>90.3794</v>
       </c>
       <c r="C135" t="n">
-        <v>78.3262</v>
+        <v>77.669</v>
       </c>
       <c r="D135" t="n">
-        <v>270.89</v>
+        <v>271.777</v>
       </c>
       <c r="E135" t="n">
-        <v>41.567</v>
+        <v>54.4033</v>
       </c>
       <c r="F135" t="n">
-        <v>143.42</v>
+        <v>176.894</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>97.1572</v>
+        <v>89.9867</v>
       </c>
       <c r="C136" t="n">
-        <v>91.1581</v>
+        <v>90.0188</v>
       </c>
       <c r="D136" t="n">
-        <v>267.144</v>
+        <v>269.301</v>
       </c>
       <c r="E136" t="n">
-        <v>41.2908</v>
+        <v>54.0267</v>
       </c>
       <c r="F136" t="n">
-        <v>143.294</v>
+        <v>174.922</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>90.6431</v>
+        <v>89.26819999999999</v>
       </c>
       <c r="C137" t="n">
-        <v>90.919</v>
+        <v>90.783</v>
       </c>
       <c r="D137" t="n">
-        <v>264.479</v>
+        <v>265.078</v>
       </c>
       <c r="E137" t="n">
-        <v>53.6721</v>
+        <v>53.4806</v>
       </c>
       <c r="F137" t="n">
-        <v>176.992</v>
+        <v>173.345</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>111.093</v>
+        <v>108.642</v>
       </c>
       <c r="C138" t="n">
-        <v>91.32559999999999</v>
+        <v>91.2294</v>
       </c>
       <c r="D138" t="n">
-        <v>260.293</v>
+        <v>262.948</v>
       </c>
       <c r="E138" t="n">
-        <v>53.3925</v>
+        <v>53.2702</v>
       </c>
       <c r="F138" t="n">
-        <v>174.974</v>
+        <v>172.304</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>117.283</v>
+        <v>108.906</v>
       </c>
       <c r="C139" t="n">
-        <v>91.60769999999999</v>
+        <v>91.242</v>
       </c>
       <c r="D139" t="n">
-        <v>257.453</v>
+        <v>259.422</v>
       </c>
       <c r="E139" t="n">
-        <v>53.2905</v>
+        <v>52.9818</v>
       </c>
       <c r="F139" t="n">
-        <v>173.602</v>
+        <v>170.784</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>111.186</v>
+        <v>108.993</v>
       </c>
       <c r="C140" t="n">
-        <v>91.7855</v>
+        <v>91.5805</v>
       </c>
       <c r="D140" t="n">
-        <v>254.732</v>
+        <v>257.07</v>
       </c>
       <c r="E140" t="n">
-        <v>52.8965</v>
+        <v>52.7628</v>
       </c>
       <c r="F140" t="n">
-        <v>172.138</v>
+        <v>170.197</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>106.707</v>
+        <v>109.26</v>
       </c>
       <c r="C141" t="n">
-        <v>91.9075</v>
+        <v>91.66800000000001</v>
       </c>
       <c r="D141" t="n">
-        <v>252.928</v>
+        <v>254.399</v>
       </c>
       <c r="E141" t="n">
-        <v>52.8227</v>
+        <v>52.7578</v>
       </c>
       <c r="F141" t="n">
-        <v>170.895</v>
+        <v>169.975</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>110.058</v>
+        <v>107.459</v>
       </c>
       <c r="C142" t="n">
-        <v>92.3704</v>
+        <v>92.1417</v>
       </c>
       <c r="D142" t="n">
-        <v>250.704</v>
+        <v>253.142</v>
       </c>
       <c r="E142" t="n">
-        <v>52.5558</v>
+        <v>52.892</v>
       </c>
       <c r="F142" t="n">
-        <v>169.837</v>
+        <v>168.111</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>106.465</v>
+        <v>109.72</v>
       </c>
       <c r="C143" t="n">
-        <v>92.5205</v>
+        <v>92.3129</v>
       </c>
       <c r="D143" t="n">
-        <v>249.532</v>
+        <v>251.527</v>
       </c>
       <c r="E143" t="n">
-        <v>52.7814</v>
+        <v>52.1572</v>
       </c>
       <c r="F143" t="n">
-        <v>169.076</v>
+        <v>166.93</v>
       </c>
     </row>
   </sheetData>

--- a/vs-x64/Running insertion.xlsx
+++ b/vs-x64/Running insertion.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>23.792</v>
+        <v>24.2499</v>
       </c>
       <c r="C2" t="n">
-        <v>30.6511</v>
+        <v>31.2784</v>
       </c>
       <c r="D2" t="n">
-        <v>59.0695</v>
+        <v>63.436</v>
       </c>
       <c r="E2" t="n">
-        <v>14.6379</v>
+        <v>15.2311</v>
       </c>
       <c r="F2" t="n">
-        <v>51.5501</v>
+        <v>49.5178</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>22.5944</v>
+        <v>22.866</v>
       </c>
       <c r="C3" t="n">
-        <v>30.1208</v>
+        <v>30.6872</v>
       </c>
       <c r="D3" t="n">
-        <v>59.1033</v>
+        <v>63.3277</v>
       </c>
       <c r="E3" t="n">
-        <v>14.2385</v>
+        <v>14.8254</v>
       </c>
       <c r="F3" t="n">
-        <v>50.6251</v>
+        <v>48.8058</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>22.5357</v>
+        <v>22.2377</v>
       </c>
       <c r="C4" t="n">
-        <v>29.7606</v>
+        <v>30.2956</v>
       </c>
       <c r="D4" t="n">
-        <v>57.7973</v>
+        <v>62.6798</v>
       </c>
       <c r="E4" t="n">
-        <v>13.8104</v>
+        <v>14.4575</v>
       </c>
       <c r="F4" t="n">
-        <v>50.3904</v>
+        <v>48.3763</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>21.7467</v>
+        <v>22.0611</v>
       </c>
       <c r="C5" t="n">
-        <v>29.3448</v>
+        <v>29.8981</v>
       </c>
       <c r="D5" t="n">
-        <v>57.8255</v>
+        <v>61.8299</v>
       </c>
       <c r="E5" t="n">
-        <v>13.572</v>
+        <v>14.127</v>
       </c>
       <c r="F5" t="n">
-        <v>49.9085</v>
+        <v>48.1462</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>21.3877</v>
+        <v>21.7007</v>
       </c>
       <c r="C6" t="n">
-        <v>28.9364</v>
+        <v>29.5744</v>
       </c>
       <c r="D6" t="n">
-        <v>57.0179</v>
+        <v>61.2344</v>
       </c>
       <c r="E6" t="n">
-        <v>13.3088</v>
+        <v>13.9869</v>
       </c>
       <c r="F6" t="n">
-        <v>49.5245</v>
+        <v>47.699</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>21.327</v>
+        <v>21.6112</v>
       </c>
       <c r="C7" t="n">
-        <v>28.6459</v>
+        <v>29.1553</v>
       </c>
       <c r="D7" t="n">
-        <v>68.8613</v>
+        <v>73.1819</v>
       </c>
       <c r="E7" t="n">
-        <v>20.2434</v>
+        <v>20.9236</v>
       </c>
       <c r="F7" t="n">
-        <v>56.0629</v>
+        <v>54.2598</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>21.1249</v>
+        <v>21.0581</v>
       </c>
       <c r="C8" t="n">
-        <v>35.41</v>
+        <v>35.9508</v>
       </c>
       <c r="D8" t="n">
-        <v>67.5214</v>
+        <v>71.5145</v>
       </c>
       <c r="E8" t="n">
-        <v>19.5386</v>
+        <v>20.2245</v>
       </c>
       <c r="F8" t="n">
-        <v>55.9654</v>
+        <v>54.1473</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>21.4553</v>
+        <v>21.2412</v>
       </c>
       <c r="C9" t="n">
-        <v>34.7543</v>
+        <v>35.2691</v>
       </c>
       <c r="D9" t="n">
-        <v>66.19119999999999</v>
+        <v>70.3022</v>
       </c>
       <c r="E9" t="n">
-        <v>18.9009</v>
+        <v>19.5587</v>
       </c>
       <c r="F9" t="n">
-        <v>54.9898</v>
+        <v>53.1431</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>27.9463</v>
+        <v>27.7245</v>
       </c>
       <c r="C10" t="n">
-        <v>34.1351</v>
+        <v>34.6585</v>
       </c>
       <c r="D10" t="n">
-        <v>65.23820000000001</v>
+        <v>69.0819</v>
       </c>
       <c r="E10" t="n">
-        <v>18.2863</v>
+        <v>18.9435</v>
       </c>
       <c r="F10" t="n">
-        <v>54.24</v>
+        <v>52.3917</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>27.2427</v>
+        <v>27.4199</v>
       </c>
       <c r="C11" t="n">
-        <v>33.5307</v>
+        <v>34.0546</v>
       </c>
       <c r="D11" t="n">
-        <v>64.44029999999999</v>
+        <v>68.4739</v>
       </c>
       <c r="E11" t="n">
-        <v>17.7187</v>
+        <v>18.3815</v>
       </c>
       <c r="F11" t="n">
-        <v>54.0777</v>
+        <v>51.9889</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>26.3179</v>
+        <v>26.638</v>
       </c>
       <c r="C12" t="n">
-        <v>32.9493</v>
+        <v>33.5116</v>
       </c>
       <c r="D12" t="n">
-        <v>63.6434</v>
+        <v>67.4327</v>
       </c>
       <c r="E12" t="n">
-        <v>17.1516</v>
+        <v>17.787</v>
       </c>
       <c r="F12" t="n">
-        <v>52.9656</v>
+        <v>51.1143</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>25.6913</v>
+        <v>25.9886</v>
       </c>
       <c r="C13" t="n">
-        <v>32.4343</v>
+        <v>32.9631</v>
       </c>
       <c r="D13" t="n">
-        <v>62.767</v>
+        <v>66.69840000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>16.5999</v>
+        <v>17.2541</v>
       </c>
       <c r="F13" t="n">
-        <v>52.2197</v>
+        <v>50.9439</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>25.2711</v>
+        <v>25.4212</v>
       </c>
       <c r="C14" t="n">
-        <v>31.8694</v>
+        <v>32.515</v>
       </c>
       <c r="D14" t="n">
-        <v>61.9972</v>
+        <v>65.92270000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>16.1144</v>
+        <v>16.7412</v>
       </c>
       <c r="F14" t="n">
-        <v>51.739</v>
+        <v>50.0373</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>24.718</v>
+        <v>25.0098</v>
       </c>
       <c r="C15" t="n">
-        <v>31.4138</v>
+        <v>31.9608</v>
       </c>
       <c r="D15" t="n">
-        <v>61.2638</v>
+        <v>65.1465</v>
       </c>
       <c r="E15" t="n">
-        <v>15.625</v>
+        <v>16.2502</v>
       </c>
       <c r="F15" t="n">
-        <v>51.0826</v>
+        <v>49.2175</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>24.0888</v>
+        <v>24.2996</v>
       </c>
       <c r="C16" t="n">
-        <v>30.9443</v>
+        <v>31.5529</v>
       </c>
       <c r="D16" t="n">
-        <v>60.8845</v>
+        <v>65.0642</v>
       </c>
       <c r="E16" t="n">
-        <v>15.2191</v>
+        <v>15.822</v>
       </c>
       <c r="F16" t="n">
-        <v>50.9546</v>
+        <v>49.0967</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>23.5079</v>
+        <v>24.0691</v>
       </c>
       <c r="C17" t="n">
-        <v>30.4842</v>
+        <v>31.0698</v>
       </c>
       <c r="D17" t="n">
-        <v>60.1291</v>
+        <v>64.0801</v>
       </c>
       <c r="E17" t="n">
-        <v>14.7989</v>
+        <v>15.4218</v>
       </c>
       <c r="F17" t="n">
-        <v>50.3394</v>
+        <v>48.421</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>23.3227</v>
+        <v>23.234</v>
       </c>
       <c r="C18" t="n">
-        <v>30.0523</v>
+        <v>30.671</v>
       </c>
       <c r="D18" t="n">
-        <v>59.9335</v>
+        <v>63.4628</v>
       </c>
       <c r="E18" t="n">
-        <v>14.4698</v>
+        <v>15.0576</v>
       </c>
       <c r="F18" t="n">
-        <v>50.4028</v>
+        <v>48.0855</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>22.7501</v>
+        <v>23.3111</v>
       </c>
       <c r="C19" t="n">
-        <v>29.6693</v>
+        <v>30.2144</v>
       </c>
       <c r="D19" t="n">
-        <v>59.5374</v>
+        <v>62.8456</v>
       </c>
       <c r="E19" t="n">
-        <v>14.148</v>
+        <v>14.7555</v>
       </c>
       <c r="F19" t="n">
-        <v>49.6654</v>
+        <v>47.604</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>22.6029</v>
+        <v>22.6165</v>
       </c>
       <c r="C20" t="n">
-        <v>29.3009</v>
+        <v>29.8655</v>
       </c>
       <c r="D20" t="n">
-        <v>59.3718</v>
+        <v>62.854</v>
       </c>
       <c r="E20" t="n">
-        <v>13.8563</v>
+        <v>14.533</v>
       </c>
       <c r="F20" t="n">
-        <v>49.3375</v>
+        <v>47.4879</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>22.5539</v>
+        <v>22.2289</v>
       </c>
       <c r="C21" t="n">
-        <v>28.9069</v>
+        <v>29.5267</v>
       </c>
       <c r="D21" t="n">
-        <v>72.01600000000001</v>
+        <v>75.7277</v>
       </c>
       <c r="E21" t="n">
-        <v>27.0711</v>
+        <v>27.4927</v>
       </c>
       <c r="F21" t="n">
-        <v>57.1597</v>
+        <v>55.1836</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>22.3226</v>
+        <v>22.1039</v>
       </c>
       <c r="C22" t="n">
-        <v>40.5954</v>
+        <v>40.8676</v>
       </c>
       <c r="D22" t="n">
-        <v>70.9224</v>
+        <v>74.65560000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>26.0785</v>
+        <v>26.4431</v>
       </c>
       <c r="F22" t="n">
-        <v>56.2859</v>
+        <v>54.4959</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>22.3631</v>
+        <v>22.0412</v>
       </c>
       <c r="C23" t="n">
-        <v>39.6964</v>
+        <v>39.9959</v>
       </c>
       <c r="D23" t="n">
-        <v>69.64700000000001</v>
+        <v>72.9982</v>
       </c>
       <c r="E23" t="n">
-        <v>25.118</v>
+        <v>25.6008</v>
       </c>
       <c r="F23" t="n">
-        <v>55.4099</v>
+        <v>53.6943</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>41.6333</v>
+        <v>39.0142</v>
       </c>
       <c r="C24" t="n">
-        <v>38.9501</v>
+        <v>39.288</v>
       </c>
       <c r="D24" t="n">
-        <v>69.0107</v>
+        <v>72.2009</v>
       </c>
       <c r="E24" t="n">
-        <v>24.2582</v>
+        <v>24.669</v>
       </c>
       <c r="F24" t="n">
-        <v>54.9331</v>
+        <v>53.12</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>39.8796</v>
+        <v>38.2255</v>
       </c>
       <c r="C25" t="n">
-        <v>38.1253</v>
+        <v>38.4695</v>
       </c>
       <c r="D25" t="n">
-        <v>68.14579999999999</v>
+        <v>71.79640000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>23.3915</v>
+        <v>23.7678</v>
       </c>
       <c r="F25" t="n">
-        <v>54.1515</v>
+        <v>52.5884</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>35.0578</v>
+        <v>38.4353</v>
       </c>
       <c r="C26" t="n">
-        <v>37.3577</v>
+        <v>37.641</v>
       </c>
       <c r="D26" t="n">
-        <v>67.1814</v>
+        <v>70.39279999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>22.6498</v>
+        <v>23.0653</v>
       </c>
       <c r="F26" t="n">
-        <v>53.4779</v>
+        <v>51.6037</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>34.0118</v>
+        <v>38.3599</v>
       </c>
       <c r="C27" t="n">
-        <v>36.6149</v>
+        <v>36.9466</v>
       </c>
       <c r="D27" t="n">
-        <v>66.1134</v>
+        <v>69.0466</v>
       </c>
       <c r="E27" t="n">
-        <v>21.8496</v>
+        <v>22.3246</v>
       </c>
       <c r="F27" t="n">
-        <v>50.9564</v>
+        <v>49.8127</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>33.1043</v>
+        <v>32.3647</v>
       </c>
       <c r="C28" t="n">
-        <v>35.9368</v>
+        <v>36.3026</v>
       </c>
       <c r="D28" t="n">
-        <v>64.8382</v>
+        <v>67.8205</v>
       </c>
       <c r="E28" t="n">
-        <v>21.1327</v>
+        <v>21.4989</v>
       </c>
       <c r="F28" t="n">
-        <v>50.6976</v>
+        <v>48.9589</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>32.4139</v>
+        <v>33.7889</v>
       </c>
       <c r="C29" t="n">
-        <v>35.2072</v>
+        <v>35.6698</v>
       </c>
       <c r="D29" t="n">
-        <v>64.4973</v>
+        <v>66.9247</v>
       </c>
       <c r="E29" t="n">
-        <v>20.4843</v>
+        <v>20.8329</v>
       </c>
       <c r="F29" t="n">
-        <v>51.9684</v>
+        <v>48.5445</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>32.6999</v>
+        <v>33.0916</v>
       </c>
       <c r="C30" t="n">
-        <v>34.7036</v>
+        <v>35.0459</v>
       </c>
       <c r="D30" t="n">
-        <v>63.5723</v>
+        <v>65.9585</v>
       </c>
       <c r="E30" t="n">
-        <v>19.8394</v>
+        <v>20.2612</v>
       </c>
       <c r="F30" t="n">
-        <v>49.3507</v>
+        <v>48.2539</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>31.0298</v>
+        <v>33.5067</v>
       </c>
       <c r="C31" t="n">
-        <v>33.9626</v>
+        <v>34.4039</v>
       </c>
       <c r="D31" t="n">
-        <v>63.3923</v>
+        <v>65.3532</v>
       </c>
       <c r="E31" t="n">
-        <v>19.2032</v>
+        <v>19.6294</v>
       </c>
       <c r="F31" t="n">
-        <v>49.1513</v>
+        <v>47.9349</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>30.2611</v>
+        <v>32.4133</v>
       </c>
       <c r="C32" t="n">
-        <v>33.3889</v>
+        <v>33.8968</v>
       </c>
       <c r="D32" t="n">
-        <v>63.0498</v>
+        <v>64.9228</v>
       </c>
       <c r="E32" t="n">
-        <v>18.6645</v>
+        <v>19.0757</v>
       </c>
       <c r="F32" t="n">
-        <v>48.8425</v>
+        <v>47.3509</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>27.1269</v>
+        <v>31.7322</v>
       </c>
       <c r="C33" t="n">
-        <v>32.8555</v>
+        <v>33.3398</v>
       </c>
       <c r="D33" t="n">
-        <v>62.6735</v>
+        <v>64.6671</v>
       </c>
       <c r="E33" t="n">
-        <v>18.1801</v>
+        <v>18.5821</v>
       </c>
       <c r="F33" t="n">
-        <v>48.6467</v>
+        <v>47.4135</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>28.5416</v>
+        <v>28.1375</v>
       </c>
       <c r="C34" t="n">
-        <v>32.362</v>
+        <v>32.9131</v>
       </c>
       <c r="D34" t="n">
-        <v>62.4359</v>
+        <v>64.148</v>
       </c>
       <c r="E34" t="n">
-        <v>17.7701</v>
+        <v>18.2386</v>
       </c>
       <c r="F34" t="n">
-        <v>48.2279</v>
+        <v>47.1665</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>28.1467</v>
+        <v>28.8046</v>
       </c>
       <c r="C35" t="n">
-        <v>31.8226</v>
+        <v>32.3376</v>
       </c>
       <c r="D35" t="n">
-        <v>76.8279</v>
+        <v>77.7508</v>
       </c>
       <c r="E35" t="n">
-        <v>31.1008</v>
+        <v>31.4409</v>
       </c>
       <c r="F35" t="n">
-        <v>58.7539</v>
+        <v>57.024</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>27.5158</v>
+        <v>32.1219</v>
       </c>
       <c r="C36" t="n">
-        <v>31.45</v>
+        <v>31.9287</v>
       </c>
       <c r="D36" t="n">
-        <v>75.3663</v>
+        <v>77.5723</v>
       </c>
       <c r="E36" t="n">
-        <v>29.8067</v>
+        <v>30.2158</v>
       </c>
       <c r="F36" t="n">
-        <v>58.0599</v>
+        <v>56.4814</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>26.9393</v>
+        <v>28.0157</v>
       </c>
       <c r="C37" t="n">
-        <v>42.6492</v>
+        <v>42.84</v>
       </c>
       <c r="D37" t="n">
-        <v>74.46080000000001</v>
+        <v>75.8305</v>
       </c>
       <c r="E37" t="n">
-        <v>28.7266</v>
+        <v>29.1915</v>
       </c>
       <c r="F37" t="n">
-        <v>57.1638</v>
+        <v>55.5975</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>48.3696</v>
+        <v>51.4468</v>
       </c>
       <c r="C38" t="n">
-        <v>41.6174</v>
+        <v>41.7965</v>
       </c>
       <c r="D38" t="n">
-        <v>72.83199999999999</v>
+        <v>74.85599999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>27.8332</v>
+        <v>28.1707</v>
       </c>
       <c r="F38" t="n">
-        <v>56.4651</v>
+        <v>54.6724</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>46.8925</v>
+        <v>49.334</v>
       </c>
       <c r="C39" t="n">
-        <v>40.6979</v>
+        <v>40.9147</v>
       </c>
       <c r="D39" t="n">
-        <v>71.3386</v>
+        <v>74.06489999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>26.7723</v>
+        <v>27.1889</v>
       </c>
       <c r="F39" t="n">
-        <v>55.8812</v>
+        <v>54.0572</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>45.4182</v>
+        <v>47.8606</v>
       </c>
       <c r="C40" t="n">
-        <v>39.7745</v>
+        <v>40.0609</v>
       </c>
       <c r="D40" t="n">
-        <v>71.0192</v>
+        <v>72.70399999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>25.7564</v>
+        <v>26.2718</v>
       </c>
       <c r="F40" t="n">
-        <v>54.289</v>
+        <v>53.3818</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>43.8631</v>
+        <v>46.2279</v>
       </c>
       <c r="C41" t="n">
-        <v>38.9367</v>
+        <v>39.2765</v>
       </c>
       <c r="D41" t="n">
-        <v>69.5254</v>
+        <v>71.6086</v>
       </c>
       <c r="E41" t="n">
-        <v>24.874</v>
+        <v>25.4208</v>
       </c>
       <c r="F41" t="n">
-        <v>53.5934</v>
+        <v>52.4433</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>42.7653</v>
+        <v>45.7411</v>
       </c>
       <c r="C42" t="n">
-        <v>38.1095</v>
+        <v>38.4928</v>
       </c>
       <c r="D42" t="n">
-        <v>68.54819999999999</v>
+        <v>70.6823</v>
       </c>
       <c r="E42" t="n">
-        <v>24.1248</v>
+        <v>24.5768</v>
       </c>
       <c r="F42" t="n">
-        <v>53.2645</v>
+        <v>52.0764</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>41.2689</v>
+        <v>44.1368</v>
       </c>
       <c r="C43" t="n">
-        <v>37.3143</v>
+        <v>37.6477</v>
       </c>
       <c r="D43" t="n">
-        <v>68.096</v>
+        <v>70.4226</v>
       </c>
       <c r="E43" t="n">
-        <v>23.2951</v>
+        <v>23.6466</v>
       </c>
       <c r="F43" t="n">
-        <v>52.4485</v>
+        <v>51.263</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>42.4378</v>
+        <v>43.3314</v>
       </c>
       <c r="C44" t="n">
-        <v>36.5779</v>
+        <v>36.9678</v>
       </c>
       <c r="D44" t="n">
-        <v>67.5423</v>
+        <v>69.5829</v>
       </c>
       <c r="E44" t="n">
-        <v>22.4983</v>
+        <v>22.8416</v>
       </c>
       <c r="F44" t="n">
-        <v>51.8661</v>
+        <v>50.8327</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>41.937</v>
+        <v>43.7468</v>
       </c>
       <c r="C45" t="n">
-        <v>35.9159</v>
+        <v>36.4159</v>
       </c>
       <c r="D45" t="n">
-        <v>66.7833</v>
+        <v>68.9731</v>
       </c>
       <c r="E45" t="n">
-        <v>21.7882</v>
+        <v>22.1594</v>
       </c>
       <c r="F45" t="n">
-        <v>51.3965</v>
+        <v>50.2387</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>37.8173</v>
+        <v>42.1493</v>
       </c>
       <c r="C46" t="n">
-        <v>35.2427</v>
+        <v>35.7855</v>
       </c>
       <c r="D46" t="n">
-        <v>66.7567</v>
+        <v>68.20740000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>21.1565</v>
+        <v>21.7251</v>
       </c>
       <c r="F46" t="n">
-        <v>50.957</v>
+        <v>49.8673</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>38.2267</v>
+        <v>41.1754</v>
       </c>
       <c r="C47" t="n">
-        <v>34.5889</v>
+        <v>35.0826</v>
       </c>
       <c r="D47" t="n">
-        <v>65.8539</v>
+        <v>67.77419999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>20.5184</v>
+        <v>21.0009</v>
       </c>
       <c r="F47" t="n">
-        <v>50.4924</v>
+        <v>49.4729</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>35.8115</v>
+        <v>40.1355</v>
       </c>
       <c r="C48" t="n">
-        <v>33.9818</v>
+        <v>34.5467</v>
       </c>
       <c r="D48" t="n">
-        <v>65.4915</v>
+        <v>67.339</v>
       </c>
       <c r="E48" t="n">
-        <v>20.0666</v>
+        <v>20.651</v>
       </c>
       <c r="F48" t="n">
-        <v>50.0276</v>
+        <v>49.054</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>36.7077</v>
+        <v>37.3863</v>
       </c>
       <c r="C49" t="n">
-        <v>33.3945</v>
+        <v>33.8195</v>
       </c>
       <c r="D49" t="n">
-        <v>64.89190000000001</v>
+        <v>67.0262</v>
       </c>
       <c r="E49" t="n">
-        <v>19.6742</v>
+        <v>20.0452</v>
       </c>
       <c r="F49" t="n">
-        <v>49.8242</v>
+        <v>48.808</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>35.2715</v>
+        <v>37.5808</v>
       </c>
       <c r="C50" t="n">
-        <v>32.8598</v>
+        <v>33.2803</v>
       </c>
       <c r="D50" t="n">
-        <v>79.9965</v>
+        <v>81.76519999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>32.0415</v>
+        <v>32.5237</v>
       </c>
       <c r="F50" t="n">
-        <v>59.581</v>
+        <v>58.8088</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>33.6203</v>
+        <v>37.06</v>
       </c>
       <c r="C51" t="n">
-        <v>43.5769</v>
+        <v>44.0656</v>
       </c>
       <c r="D51" t="n">
-        <v>78.8623</v>
+        <v>80.866</v>
       </c>
       <c r="E51" t="n">
-        <v>30.9797</v>
+        <v>31.3667</v>
       </c>
       <c r="F51" t="n">
-        <v>58.6866</v>
+        <v>57.8895</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>34.1898</v>
+        <v>36.1994</v>
       </c>
       <c r="C52" t="n">
-        <v>42.5205</v>
+        <v>43.1018</v>
       </c>
       <c r="D52" t="n">
-        <v>77.20829999999999</v>
+        <v>78.9833</v>
       </c>
       <c r="E52" t="n">
-        <v>29.8694</v>
+        <v>30.0309</v>
       </c>
       <c r="F52" t="n">
-        <v>57.8582</v>
+        <v>56.7673</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>56.3091</v>
+        <v>56.85</v>
       </c>
       <c r="C53" t="n">
-        <v>41.7083</v>
+        <v>42.4669</v>
       </c>
       <c r="D53" t="n">
-        <v>75.92919999999999</v>
+        <v>77.6234</v>
       </c>
       <c r="E53" t="n">
-        <v>28.8446</v>
+        <v>29.1549</v>
       </c>
       <c r="F53" t="n">
-        <v>57.0398</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>54.4439</v>
+        <v>55.2271</v>
       </c>
       <c r="C54" t="n">
-        <v>41.0448</v>
+        <v>41.2195</v>
       </c>
       <c r="D54" t="n">
-        <v>75.2979</v>
+        <v>76.6782</v>
       </c>
       <c r="E54" t="n">
-        <v>27.5989</v>
+        <v>28.2197</v>
       </c>
       <c r="F54" t="n">
-        <v>56.1266</v>
+        <v>55.4633</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>52.6946</v>
+        <v>53.5514</v>
       </c>
       <c r="C55" t="n">
-        <v>39.9268</v>
+        <v>40.5397</v>
       </c>
       <c r="D55" t="n">
-        <v>73.9254</v>
+        <v>75.60420000000001</v>
       </c>
       <c r="E55" t="n">
-        <v>26.6809</v>
+        <v>27.3923</v>
       </c>
       <c r="F55" t="n">
-        <v>55.4978</v>
+        <v>55.2308</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>49.6603</v>
+        <v>50.2252</v>
       </c>
       <c r="C56" t="n">
-        <v>39.0007</v>
+        <v>39.4189</v>
       </c>
       <c r="D56" t="n">
-        <v>72.9162</v>
+        <v>74.36360000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>25.7488</v>
+        <v>26.5008</v>
       </c>
       <c r="F56" t="n">
-        <v>54.7033</v>
+        <v>53.8379</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>49.3352</v>
+        <v>49.0454</v>
       </c>
       <c r="C57" t="n">
-        <v>38.2179</v>
+        <v>38.9174</v>
       </c>
       <c r="D57" t="n">
-        <v>74.1661</v>
+        <v>73.88939999999999</v>
       </c>
       <c r="E57" t="n">
-        <v>25.1261</v>
+        <v>25.9884</v>
       </c>
       <c r="F57" t="n">
-        <v>54.1892</v>
+        <v>53.3069</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>47.0954</v>
+        <v>48.4244</v>
       </c>
       <c r="C58" t="n">
-        <v>37.5814</v>
+        <v>37.9412</v>
       </c>
       <c r="D58" t="n">
-        <v>71.322</v>
+        <v>72.7332</v>
       </c>
       <c r="E58" t="n">
-        <v>24.4897</v>
+        <v>24.9561</v>
       </c>
       <c r="F58" t="n">
-        <v>53.6777</v>
+        <v>52.8852</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>46.7737</v>
+        <v>47.0989</v>
       </c>
       <c r="C59" t="n">
-        <v>36.9339</v>
+        <v>37.2288</v>
       </c>
       <c r="D59" t="n">
-        <v>70.5224</v>
+        <v>72.05880000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>23.5147</v>
+        <v>24.073</v>
       </c>
       <c r="F59" t="n">
-        <v>53.0313</v>
+        <v>52.434</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>45.4142</v>
+        <v>44.608</v>
       </c>
       <c r="C60" t="n">
-        <v>36.1838</v>
+        <v>36.5187</v>
       </c>
       <c r="D60" t="n">
-        <v>69.883</v>
+        <v>71.2619</v>
       </c>
       <c r="E60" t="n">
-        <v>22.7613</v>
+        <v>23.3113</v>
       </c>
       <c r="F60" t="n">
-        <v>52.6682</v>
+        <v>51.6611</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>43.2179</v>
+        <v>43.249</v>
       </c>
       <c r="C61" t="n">
-        <v>35.4331</v>
+        <v>35.9128</v>
       </c>
       <c r="D61" t="n">
-        <v>72.40430000000001</v>
+        <v>71.41070000000001</v>
       </c>
       <c r="E61" t="n">
-        <v>22.1014</v>
+        <v>23.0785</v>
       </c>
       <c r="F61" t="n">
-        <v>52.2634</v>
+        <v>51.3933</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>42.1249</v>
+        <v>43.3886</v>
       </c>
       <c r="C62" t="n">
-        <v>34.9662</v>
+        <v>35.4173</v>
       </c>
       <c r="D62" t="n">
-        <v>71.3378</v>
+        <v>70.3113</v>
       </c>
       <c r="E62" t="n">
-        <v>21.6614</v>
+        <v>22.4028</v>
       </c>
       <c r="F62" t="n">
-        <v>52.6991</v>
+        <v>51.2142</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>39.1439</v>
+        <v>40.9612</v>
       </c>
       <c r="C63" t="n">
-        <v>34.3136</v>
+        <v>34.7983</v>
       </c>
       <c r="D63" t="n">
-        <v>69.4359</v>
+        <v>69.4588</v>
       </c>
       <c r="E63" t="n">
-        <v>21.1476</v>
+        <v>21.8097</v>
       </c>
       <c r="F63" t="n">
-        <v>51.4079</v>
+        <v>50.2651</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>37.8625</v>
+        <v>40.072</v>
       </c>
       <c r="C64" t="n">
-        <v>33.8061</v>
+        <v>34.2999</v>
       </c>
       <c r="D64" t="n">
-        <v>86.0017</v>
+        <v>86.074</v>
       </c>
       <c r="E64" t="n">
-        <v>33.5783</v>
+        <v>35.1808</v>
       </c>
       <c r="F64" t="n">
-        <v>62.1252</v>
+        <v>60.7458</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>37.5138</v>
+        <v>38.9229</v>
       </c>
       <c r="C65" t="n">
-        <v>45.0325</v>
+        <v>45.7495</v>
       </c>
       <c r="D65" t="n">
-        <v>85.4258</v>
+        <v>84.6254</v>
       </c>
       <c r="E65" t="n">
-        <v>32.9629</v>
+        <v>34.0475</v>
       </c>
       <c r="F65" t="n">
-        <v>61.6338</v>
+        <v>59.7091</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>36.3886</v>
+        <v>38.19</v>
       </c>
       <c r="C66" t="n">
-        <v>43.93</v>
+        <v>44.0658</v>
       </c>
       <c r="D66" t="n">
-        <v>83.4714</v>
+        <v>83.0652</v>
       </c>
       <c r="E66" t="n">
-        <v>32.3241</v>
+        <v>32.3293</v>
       </c>
       <c r="F66" t="n">
-        <v>60.245</v>
+        <v>59.0306</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>58.6887</v>
+        <v>60.3617</v>
       </c>
       <c r="C67" t="n">
-        <v>42.9675</v>
+        <v>43.4681</v>
       </c>
       <c r="D67" t="n">
-        <v>80.3506</v>
+        <v>85.023</v>
       </c>
       <c r="E67" t="n">
-        <v>30.6064</v>
+        <v>31.6691</v>
       </c>
       <c r="F67" t="n">
-        <v>59.8852</v>
+        <v>60.3803</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>56.642</v>
+        <v>59.5122</v>
       </c>
       <c r="C68" t="n">
-        <v>42.0409</v>
+        <v>43.1286</v>
       </c>
       <c r="D68" t="n">
-        <v>79.39830000000001</v>
+        <v>82.3051</v>
       </c>
       <c r="E68" t="n">
-        <v>29.7345</v>
+        <v>30.9553</v>
       </c>
       <c r="F68" t="n">
-        <v>58.4936</v>
+        <v>58.7294</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>56.0424</v>
+        <v>56.4691</v>
       </c>
       <c r="C69" t="n">
-        <v>41.2612</v>
+        <v>41.8781</v>
       </c>
       <c r="D69" t="n">
-        <v>78.90389999999999</v>
+        <v>79.76690000000001</v>
       </c>
       <c r="E69" t="n">
-        <v>28.9318</v>
+        <v>29.3925</v>
       </c>
       <c r="F69" t="n">
-        <v>58.3647</v>
+        <v>57.6262</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>53.5874</v>
+        <v>55.8694</v>
       </c>
       <c r="C70" t="n">
-        <v>40.5804</v>
+        <v>41.5199</v>
       </c>
       <c r="D70" t="n">
-        <v>78.1858</v>
+        <v>80.3639</v>
       </c>
       <c r="E70" t="n">
-        <v>28.0216</v>
+        <v>28.7916</v>
       </c>
       <c r="F70" t="n">
-        <v>57.8598</v>
+        <v>58.2251</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>52.7071</v>
+        <v>54.0203</v>
       </c>
       <c r="C71" t="n">
-        <v>39.3889</v>
+        <v>40.024</v>
       </c>
       <c r="D71" t="n">
-        <v>76.76260000000001</v>
+        <v>79.0368</v>
       </c>
       <c r="E71" t="n">
-        <v>26.6094</v>
+        <v>27.7604</v>
       </c>
       <c r="F71" t="n">
-        <v>56.7476</v>
+        <v>56.3345</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>51.4848</v>
+        <v>52.8866</v>
       </c>
       <c r="C72" t="n">
-        <v>39.0463</v>
+        <v>39.1778</v>
       </c>
       <c r="D72" t="n">
-        <v>75.77719999999999</v>
+        <v>78.79170000000001</v>
       </c>
       <c r="E72" t="n">
-        <v>26.4305</v>
+        <v>26.7789</v>
       </c>
       <c r="F72" t="n">
-        <v>55.8953</v>
+        <v>55.3557</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>49.7716</v>
+        <v>51.6058</v>
       </c>
       <c r="C73" t="n">
-        <v>38.3888</v>
+        <v>38.8621</v>
       </c>
       <c r="D73" t="n">
-        <v>75.621</v>
+        <v>76.9156</v>
       </c>
       <c r="E73" t="n">
-        <v>25.2797</v>
+        <v>25.9928</v>
       </c>
       <c r="F73" t="n">
-        <v>55.491</v>
+        <v>55.5531</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>48.4091</v>
+        <v>50.2216</v>
       </c>
       <c r="C74" t="n">
-        <v>37.4599</v>
+        <v>38.1165</v>
       </c>
       <c r="D74" t="n">
-        <v>74.6707</v>
+        <v>76.60590000000001</v>
       </c>
       <c r="E74" t="n">
-        <v>24.9037</v>
+        <v>25.2143</v>
       </c>
       <c r="F74" t="n">
-        <v>54.84</v>
+        <v>54.2901</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>46.8903</v>
+        <v>48.6111</v>
       </c>
       <c r="C75" t="n">
-        <v>36.7097</v>
+        <v>37.4416</v>
       </c>
       <c r="D75" t="n">
-        <v>75.5595</v>
+        <v>77.0438</v>
       </c>
       <c r="E75" t="n">
-        <v>24.3599</v>
+        <v>24.5859</v>
       </c>
       <c r="F75" t="n">
-        <v>54.5218</v>
+        <v>54.7715</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>46.6521</v>
+        <v>47.4948</v>
       </c>
       <c r="C76" t="n">
-        <v>36.0968</v>
+        <v>36.562</v>
       </c>
       <c r="D76" t="n">
-        <v>74.521</v>
+        <v>76.7658</v>
       </c>
       <c r="E76" t="n">
-        <v>23.4138</v>
+        <v>24.1495</v>
       </c>
       <c r="F76" t="n">
-        <v>54.061</v>
+        <v>54.7909</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>45.3344</v>
+        <v>46.3363</v>
       </c>
       <c r="C77" t="n">
-        <v>35.5244</v>
+        <v>35.9148</v>
       </c>
       <c r="D77" t="n">
-        <v>74.50449999999999</v>
+        <v>77.1895</v>
       </c>
       <c r="E77" t="n">
-        <v>22.5365</v>
+        <v>23.6117</v>
       </c>
       <c r="F77" t="n">
-        <v>53.8773</v>
+        <v>53.1186</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>45.2564</v>
+        <v>45.2296</v>
       </c>
       <c r="C78" t="n">
-        <v>35.0386</v>
+        <v>35.3852</v>
       </c>
       <c r="D78" t="n">
-        <v>109.534</v>
+        <v>110.255</v>
       </c>
       <c r="E78" t="n">
-        <v>36.8757</v>
+        <v>36.6259</v>
       </c>
       <c r="F78" t="n">
-        <v>77.9734</v>
+        <v>77.7522</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>44.1094</v>
+        <v>44.2993</v>
       </c>
       <c r="C79" t="n">
-        <v>47.2666</v>
+        <v>47.0998</v>
       </c>
       <c r="D79" t="n">
-        <v>107.896</v>
+        <v>109.281</v>
       </c>
       <c r="E79" t="n">
-        <v>34.946</v>
+        <v>36.9009</v>
       </c>
       <c r="F79" t="n">
-        <v>78.8558</v>
+        <v>78.4303</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>43.2682</v>
+        <v>44.071</v>
       </c>
       <c r="C80" t="n">
-        <v>46.5729</v>
+        <v>47.8483</v>
       </c>
       <c r="D80" t="n">
-        <v>107.103</v>
+        <v>109.901</v>
       </c>
       <c r="E80" t="n">
-        <v>34.4481</v>
+        <v>35.8792</v>
       </c>
       <c r="F80" t="n">
-        <v>78.0046</v>
+        <v>77.94889999999999</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>63.5519</v>
+        <v>66.9713</v>
       </c>
       <c r="C81" t="n">
-        <v>47.2279</v>
+        <v>47.6595</v>
       </c>
       <c r="D81" t="n">
-        <v>106.28</v>
+        <v>107.366</v>
       </c>
       <c r="E81" t="n">
-        <v>33.7394</v>
+        <v>34.462</v>
       </c>
       <c r="F81" t="n">
-        <v>78.0898</v>
+        <v>78.59229999999999</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>63.1173</v>
+        <v>66.4633</v>
       </c>
       <c r="C82" t="n">
-        <v>46.127</v>
+        <v>47.158</v>
       </c>
       <c r="D82" t="n">
-        <v>105.316</v>
+        <v>107.153</v>
       </c>
       <c r="E82" t="n">
-        <v>32.1119</v>
+        <v>33.1277</v>
       </c>
       <c r="F82" t="n">
-        <v>76.9419</v>
+        <v>78.3811</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>62.156</v>
+        <v>65.8507</v>
       </c>
       <c r="C83" t="n">
-        <v>45.7158</v>
+        <v>46.866</v>
       </c>
       <c r="D83" t="n">
-        <v>103.875</v>
+        <v>106.182</v>
       </c>
       <c r="E83" t="n">
-        <v>31.2994</v>
+        <v>32.2611</v>
       </c>
       <c r="F83" t="n">
-        <v>76.0432</v>
+        <v>76.07640000000001</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>61.5289</v>
+        <v>65.04600000000001</v>
       </c>
       <c r="C84" t="n">
-        <v>45.1251</v>
+        <v>45.9733</v>
       </c>
       <c r="D84" t="n">
-        <v>103.902</v>
+        <v>105.692</v>
       </c>
       <c r="E84" t="n">
-        <v>30.3722</v>
+        <v>32.0134</v>
       </c>
       <c r="F84" t="n">
-        <v>75.2503</v>
+        <v>75.2711</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>60.0568</v>
+        <v>63.5941</v>
       </c>
       <c r="C85" t="n">
-        <v>44.8646</v>
+        <v>45.3356</v>
       </c>
       <c r="D85" t="n">
-        <v>103.992</v>
+        <v>105.762</v>
       </c>
       <c r="E85" t="n">
-        <v>29.5333</v>
+        <v>30.3143</v>
       </c>
       <c r="F85" t="n">
-        <v>73.04559999999999</v>
+        <v>73.13420000000001</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>59.2215</v>
+        <v>63.1745</v>
       </c>
       <c r="C86" t="n">
-        <v>44.7479</v>
+        <v>44.9641</v>
       </c>
       <c r="D86" t="n">
-        <v>103.151</v>
+        <v>105.033</v>
       </c>
       <c r="E86" t="n">
-        <v>28.7893</v>
+        <v>29.7637</v>
       </c>
       <c r="F86" t="n">
-        <v>71.4414</v>
+        <v>73.3287</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>58.2869</v>
+        <v>61.7997</v>
       </c>
       <c r="C87" t="n">
-        <v>44.0994</v>
+        <v>44.4362</v>
       </c>
       <c r="D87" t="n">
-        <v>103.267</v>
+        <v>106.521</v>
       </c>
       <c r="E87" t="n">
-        <v>27.7248</v>
+        <v>29.266</v>
       </c>
       <c r="F87" t="n">
-        <v>71.58540000000001</v>
+        <v>72.4799</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>57.3551</v>
+        <v>60.2108</v>
       </c>
       <c r="C88" t="n">
-        <v>43.424</v>
+        <v>43.9125</v>
       </c>
       <c r="D88" t="n">
-        <v>104.533</v>
+        <v>106.109</v>
       </c>
       <c r="E88" t="n">
-        <v>27.6671</v>
+        <v>28.2345</v>
       </c>
       <c r="F88" t="n">
-        <v>70.4813</v>
+        <v>71.2619</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>56.0674</v>
+        <v>59.2178</v>
       </c>
       <c r="C89" t="n">
-        <v>42.847</v>
+        <v>43.3434</v>
       </c>
       <c r="D89" t="n">
-        <v>104.507</v>
+        <v>106.747</v>
       </c>
       <c r="E89" t="n">
-        <v>26.4926</v>
+        <v>27.5875</v>
       </c>
       <c r="F89" t="n">
-        <v>68.4615</v>
+        <v>70.6079</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>55.3149</v>
+        <v>58.4704</v>
       </c>
       <c r="C90" t="n">
-        <v>42.408</v>
+        <v>42.7497</v>
       </c>
       <c r="D90" t="n">
-        <v>104.781</v>
+        <v>107.352</v>
       </c>
       <c r="E90" t="n">
-        <v>26.3345</v>
+        <v>26.8776</v>
       </c>
       <c r="F90" t="n">
-        <v>70.00790000000001</v>
+        <v>68.66240000000001</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>54.29</v>
+        <v>56.384</v>
       </c>
       <c r="C91" t="n">
-        <v>42.3738</v>
+        <v>42.8357</v>
       </c>
       <c r="D91" t="n">
-        <v>107.368</v>
+        <v>107.573</v>
       </c>
       <c r="E91" t="n">
-        <v>25.1791</v>
+        <v>25.8981</v>
       </c>
       <c r="F91" t="n">
-        <v>67.1728</v>
+        <v>68.09950000000001</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>52.7114</v>
+        <v>55.4475</v>
       </c>
       <c r="C92" t="n">
-        <v>41.601</v>
+        <v>41.9161</v>
       </c>
       <c r="D92" t="n">
-        <v>148.224</v>
+        <v>148.92</v>
       </c>
       <c r="E92" t="n">
-        <v>38.6773</v>
+        <v>39.828</v>
       </c>
       <c r="F92" t="n">
-        <v>98.8065</v>
+        <v>97.5585</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>49.0302</v>
+        <v>48.9778</v>
       </c>
       <c r="C93" t="n">
-        <v>41.295</v>
+        <v>41.2448</v>
       </c>
       <c r="D93" t="n">
-        <v>148.436</v>
+        <v>149.198</v>
       </c>
       <c r="E93" t="n">
-        <v>38.9182</v>
+        <v>38.9577</v>
       </c>
       <c r="F93" t="n">
-        <v>98.25539999999999</v>
+        <v>99.48699999999999</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>48.3997</v>
+        <v>47.9936</v>
       </c>
       <c r="C94" t="n">
-        <v>54.0952</v>
+        <v>53.9634</v>
       </c>
       <c r="D94" t="n">
-        <v>146.789</v>
+        <v>148.36</v>
       </c>
       <c r="E94" t="n">
-        <v>37.3089</v>
+        <v>39.4461</v>
       </c>
       <c r="F94" t="n">
-        <v>98.2242</v>
+        <v>98.81999999999999</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>71.7152</v>
+        <v>66.5005</v>
       </c>
       <c r="C95" t="n">
-        <v>53.8786</v>
+        <v>54.1527</v>
       </c>
       <c r="D95" t="n">
-        <v>146.282</v>
+        <v>147.214</v>
       </c>
       <c r="E95" t="n">
-        <v>37.1364</v>
+        <v>37.1167</v>
       </c>
       <c r="F95" t="n">
-        <v>96.9787</v>
+        <v>96.38890000000001</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>70.8416</v>
+        <v>66.9316</v>
       </c>
       <c r="C96" t="n">
-        <v>53.001</v>
+        <v>53.2153</v>
       </c>
       <c r="D96" t="n">
-        <v>145.953</v>
+        <v>146.686</v>
       </c>
       <c r="E96" t="n">
-        <v>35.6797</v>
+        <v>36.7207</v>
       </c>
       <c r="F96" t="n">
-        <v>95.1474</v>
+        <v>95.5399</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>70.7713</v>
+        <v>66.7379</v>
       </c>
       <c r="C97" t="n">
-        <v>52.8003</v>
+        <v>53.4169</v>
       </c>
       <c r="D97" t="n">
-        <v>145.273</v>
+        <v>145.847</v>
       </c>
       <c r="E97" t="n">
-        <v>34.9548</v>
+        <v>36.3706</v>
       </c>
       <c r="F97" t="n">
-        <v>94.2105</v>
+        <v>95.3176</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>69.96080000000001</v>
+        <v>66.88249999999999</v>
       </c>
       <c r="C98" t="n">
-        <v>52.752</v>
+        <v>53.0484</v>
       </c>
       <c r="D98" t="n">
-        <v>145.083</v>
+        <v>145.878</v>
       </c>
       <c r="E98" t="n">
-        <v>33.9595</v>
+        <v>34.892</v>
       </c>
       <c r="F98" t="n">
-        <v>93.5228</v>
+        <v>94.22020000000001</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>68.5283</v>
+        <v>65.53879999999999</v>
       </c>
       <c r="C99" t="n">
-        <v>52.8714</v>
+        <v>52.7723</v>
       </c>
       <c r="D99" t="n">
-        <v>145.431</v>
+        <v>146.436</v>
       </c>
       <c r="E99" t="n">
-        <v>33.0165</v>
+        <v>33.8692</v>
       </c>
       <c r="F99" t="n">
-        <v>92.8728</v>
+        <v>92.2611</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>68.497</v>
+        <v>65.07170000000001</v>
       </c>
       <c r="C100" t="n">
-        <v>52.4271</v>
+        <v>52.5236</v>
       </c>
       <c r="D100" t="n">
-        <v>145.657</v>
+        <v>145.952</v>
       </c>
       <c r="E100" t="n">
-        <v>32.0604</v>
+        <v>32.6326</v>
       </c>
       <c r="F100" t="n">
-        <v>91.1771</v>
+        <v>91.42910000000001</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>67.1737</v>
+        <v>63.3807</v>
       </c>
       <c r="C101" t="n">
-        <v>52.8585</v>
+        <v>53.1103</v>
       </c>
       <c r="D101" t="n">
-        <v>145.613</v>
+        <v>146.185</v>
       </c>
       <c r="E101" t="n">
-        <v>31.2815</v>
+        <v>32.4234</v>
       </c>
       <c r="F101" t="n">
-        <v>89.5437</v>
+        <v>91.01949999999999</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>66.9654</v>
+        <v>70.0748</v>
       </c>
       <c r="C102" t="n">
-        <v>52.4421</v>
+        <v>52.4218</v>
       </c>
       <c r="D102" t="n">
-        <v>145.629</v>
+        <v>147.107</v>
       </c>
       <c r="E102" t="n">
-        <v>30.8589</v>
+        <v>31.455</v>
       </c>
       <c r="F102" t="n">
-        <v>89.7432</v>
+        <v>90.51519999999999</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>65.9782</v>
+        <v>69.3507</v>
       </c>
       <c r="C103" t="n">
-        <v>52.127</v>
+        <v>52.659</v>
       </c>
       <c r="D103" t="n">
-        <v>146.464</v>
+        <v>147.796</v>
       </c>
       <c r="E103" t="n">
-        <v>29.9221</v>
+        <v>31.1857</v>
       </c>
       <c r="F103" t="n">
-        <v>88.23999999999999</v>
+        <v>89.23860000000001</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>65.4144</v>
+        <v>68.6695</v>
       </c>
       <c r="C104" t="n">
-        <v>52.646</v>
+        <v>52.259</v>
       </c>
       <c r="D104" t="n">
-        <v>147.518</v>
+        <v>148.624</v>
       </c>
       <c r="E104" t="n">
-        <v>29.3997</v>
+        <v>30.4146</v>
       </c>
       <c r="F104" t="n">
-        <v>87.9987</v>
+        <v>88.1189</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>64.87560000000001</v>
+        <v>68.1892</v>
       </c>
       <c r="C105" t="n">
-        <v>51.8659</v>
+        <v>52.025</v>
       </c>
       <c r="D105" t="n">
-        <v>149.194</v>
+        <v>150.267</v>
       </c>
       <c r="E105" t="n">
-        <v>29.0008</v>
+        <v>29.9307</v>
       </c>
       <c r="F105" t="n">
-        <v>87.5973</v>
+        <v>87.3485</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>64.9752</v>
+        <v>66.559</v>
       </c>
       <c r="C106" t="n">
-        <v>52.0529</v>
+        <v>52.4884</v>
       </c>
       <c r="D106" t="n">
-        <v>150.718</v>
+        <v>151.517</v>
       </c>
       <c r="E106" t="n">
-        <v>28.5002</v>
+        <v>29.4233</v>
       </c>
       <c r="F106" t="n">
-        <v>86.3891</v>
+        <v>86.7899</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>64.33880000000001</v>
+        <v>66.14449999999999</v>
       </c>
       <c r="C107" t="n">
-        <v>51.5561</v>
+        <v>52.087</v>
       </c>
       <c r="D107" t="n">
-        <v>194.399</v>
+        <v>194.545</v>
       </c>
       <c r="E107" t="n">
-        <v>41.5747</v>
+        <v>43.0602</v>
       </c>
       <c r="F107" t="n">
-        <v>120.877</v>
+        <v>120.121</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>64.7955</v>
+        <v>65.56019999999999</v>
       </c>
       <c r="C108" t="n">
-        <v>63.9105</v>
+        <v>64.2161</v>
       </c>
       <c r="D108" t="n">
-        <v>193.405</v>
+        <v>193.138</v>
       </c>
       <c r="E108" t="n">
-        <v>41.8764</v>
+        <v>42.517</v>
       </c>
       <c r="F108" t="n">
-        <v>119.652</v>
+        <v>120.552</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>64.61109999999999</v>
+        <v>62.0667</v>
       </c>
       <c r="C109" t="n">
-        <v>64.2428</v>
+        <v>64.39530000000001</v>
       </c>
       <c r="D109" t="n">
-        <v>191.3</v>
+        <v>191.95</v>
       </c>
       <c r="E109" t="n">
-        <v>40.1143</v>
+        <v>41.0397</v>
       </c>
       <c r="F109" t="n">
-        <v>118.915</v>
+        <v>118.936</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>83.3556</v>
+        <v>84.9028</v>
       </c>
       <c r="C110" t="n">
-        <v>63.5294</v>
+        <v>64.2482</v>
       </c>
       <c r="D110" t="n">
-        <v>189.994</v>
+        <v>190.648</v>
       </c>
       <c r="E110" t="n">
-        <v>39.625</v>
+        <v>40.8824</v>
       </c>
       <c r="F110" t="n">
-        <v>117.836</v>
+        <v>118.084</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>82.7817</v>
+        <v>83.97669999999999</v>
       </c>
       <c r="C111" t="n">
-        <v>63.5096</v>
+        <v>64.4862</v>
       </c>
       <c r="D111" t="n">
-        <v>189.217</v>
+        <v>190.14</v>
       </c>
       <c r="E111" t="n">
-        <v>39.1027</v>
+        <v>39.083</v>
       </c>
       <c r="F111" t="n">
-        <v>117.521</v>
+        <v>117.814</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>83.23999999999999</v>
+        <v>84.0266</v>
       </c>
       <c r="C112" t="n">
-        <v>63.8984</v>
+        <v>63.7813</v>
       </c>
       <c r="D112" t="n">
-        <v>188.973</v>
+        <v>188.756</v>
       </c>
       <c r="E112" t="n">
-        <v>37.6343</v>
+        <v>38.6594</v>
       </c>
       <c r="F112" t="n">
-        <v>116.536</v>
+        <v>117.245</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>85.30880000000001</v>
+        <v>81.6208</v>
       </c>
       <c r="C113" t="n">
-        <v>63.7033</v>
+        <v>64.3796</v>
       </c>
       <c r="D113" t="n">
-        <v>188.42</v>
+        <v>188.383</v>
       </c>
       <c r="E113" t="n">
-        <v>36.7191</v>
+        <v>38.2056</v>
       </c>
       <c r="F113" t="n">
-        <v>115.917</v>
+        <v>116.055</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>84.8038</v>
+        <v>80.56910000000001</v>
       </c>
       <c r="C114" t="n">
-        <v>63.6988</v>
+        <v>64.31659999999999</v>
       </c>
       <c r="D114" t="n">
-        <v>187.188</v>
+        <v>188.341</v>
       </c>
       <c r="E114" t="n">
-        <v>36.2654</v>
+        <v>37.594</v>
       </c>
       <c r="F114" t="n">
-        <v>116.119</v>
+        <v>115.683</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>83.54300000000001</v>
+        <v>80.31740000000001</v>
       </c>
       <c r="C115" t="n">
-        <v>63.8198</v>
+        <v>64.1554</v>
       </c>
       <c r="D115" t="n">
-        <v>187.012</v>
+        <v>188.245</v>
       </c>
       <c r="E115" t="n">
-        <v>36.1917</v>
+        <v>36.8603</v>
       </c>
       <c r="F115" t="n">
-        <v>115.114</v>
+        <v>115.535</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>82.164</v>
+        <v>79.7307</v>
       </c>
       <c r="C116" t="n">
-        <v>63.9696</v>
+        <v>64.1571</v>
       </c>
       <c r="D116" t="n">
-        <v>187.31</v>
+        <v>188.112</v>
       </c>
       <c r="E116" t="n">
-        <v>34.7674</v>
+        <v>36.822</v>
       </c>
       <c r="F116" t="n">
-        <v>114.792</v>
+        <v>114.864</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>77.8326</v>
+        <v>80.11190000000001</v>
       </c>
       <c r="C117" t="n">
-        <v>64.00660000000001</v>
+        <v>64.3091</v>
       </c>
       <c r="D117" t="n">
-        <v>187.94</v>
+        <v>187.976</v>
       </c>
       <c r="E117" t="n">
-        <v>34.464</v>
+        <v>35.522</v>
       </c>
       <c r="F117" t="n">
-        <v>114.222</v>
+        <v>114.437</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>77.6451</v>
+        <v>79.1311</v>
       </c>
       <c r="C118" t="n">
-        <v>63.8602</v>
+        <v>64.3413</v>
       </c>
       <c r="D118" t="n">
-        <v>188.273</v>
+        <v>188.541</v>
       </c>
       <c r="E118" t="n">
-        <v>34.1875</v>
+        <v>35.3396</v>
       </c>
       <c r="F118" t="n">
-        <v>113.67</v>
+        <v>113.659</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>76.8698</v>
+        <v>77.44799999999999</v>
       </c>
       <c r="C119" t="n">
-        <v>63.6804</v>
+        <v>64.1641</v>
       </c>
       <c r="D119" t="n">
-        <v>188.535</v>
+        <v>189.159</v>
       </c>
       <c r="E119" t="n">
-        <v>33.6846</v>
+        <v>34.5147</v>
       </c>
       <c r="F119" t="n">
-        <v>113.4</v>
+        <v>113.369</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>78.0254</v>
+        <v>74.8683</v>
       </c>
       <c r="C120" t="n">
-        <v>64.0676</v>
+        <v>64.268</v>
       </c>
       <c r="D120" t="n">
-        <v>189.328</v>
+        <v>190.132</v>
       </c>
       <c r="E120" t="n">
-        <v>32.7864</v>
+        <v>34.1365</v>
       </c>
       <c r="F120" t="n">
-        <v>113.261</v>
+        <v>113.212</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>77.93519999999999</v>
+        <v>73.7677</v>
       </c>
       <c r="C121" t="n">
-        <v>63.1793</v>
+        <v>63.7788</v>
       </c>
       <c r="D121" t="n">
-        <v>236.869</v>
+        <v>238.224</v>
       </c>
       <c r="E121" t="n">
-        <v>46.8787</v>
+        <v>48.5088</v>
       </c>
       <c r="F121" t="n">
-        <v>147.968</v>
+        <v>148.786</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>76.7736</v>
+        <v>72.8954</v>
       </c>
       <c r="C122" t="n">
-        <v>75.3109</v>
+        <v>75.3475</v>
       </c>
       <c r="D122" t="n">
-        <v>234.568</v>
+        <v>235.378</v>
       </c>
       <c r="E122" t="n">
-        <v>45.252</v>
+        <v>46.7471</v>
       </c>
       <c r="F122" t="n">
-        <v>147.032</v>
+        <v>147.351</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>75.6275</v>
+        <v>76.7811</v>
       </c>
       <c r="C123" t="n">
-        <v>75.27</v>
+        <v>75.3865</v>
       </c>
       <c r="D123" t="n">
-        <v>232.002</v>
+        <v>233.082</v>
       </c>
       <c r="E123" t="n">
-        <v>45.4791</v>
+        <v>47.5512</v>
       </c>
       <c r="F123" t="n">
-        <v>146.843</v>
+        <v>146.878</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>99.9173</v>
+        <v>96.9395</v>
       </c>
       <c r="C124" t="n">
-        <v>75.50879999999999</v>
+        <v>75.7324</v>
       </c>
       <c r="D124" t="n">
-        <v>230.04</v>
+        <v>230.609</v>
       </c>
       <c r="E124" t="n">
-        <v>46.1641</v>
+        <v>46.7212</v>
       </c>
       <c r="F124" t="n">
-        <v>145.82</v>
+        <v>146.045</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>98.6327</v>
+        <v>96.2718</v>
       </c>
       <c r="C125" t="n">
-        <v>76.2576</v>
+        <v>76.1661</v>
       </c>
       <c r="D125" t="n">
-        <v>228.46</v>
+        <v>229.42</v>
       </c>
       <c r="E125" t="n">
-        <v>43.8857</v>
+        <v>46.9679</v>
       </c>
       <c r="F125" t="n">
-        <v>145.46</v>
+        <v>144.958</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>94.79219999999999</v>
+        <v>94.3857</v>
       </c>
       <c r="C126" t="n">
-        <v>76.59050000000001</v>
+        <v>76.7159</v>
       </c>
       <c r="D126" t="n">
-        <v>226.283</v>
+        <v>227.539</v>
       </c>
       <c r="E126" t="n">
-        <v>44.2586</v>
+        <v>45.9786</v>
       </c>
       <c r="F126" t="n">
-        <v>144.04</v>
+        <v>144.824</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>93.8685</v>
+        <v>93.541</v>
       </c>
       <c r="C127" t="n">
-        <v>76.916</v>
+        <v>76.5123</v>
       </c>
       <c r="D127" t="n">
-        <v>225.504</v>
+        <v>226.055</v>
       </c>
       <c r="E127" t="n">
-        <v>43.2434</v>
+        <v>45.2872</v>
       </c>
       <c r="F127" t="n">
-        <v>143.317</v>
+        <v>144.199</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>95.5647</v>
+        <v>93.687</v>
       </c>
       <c r="C128" t="n">
-        <v>76.9808</v>
+        <v>77.0338</v>
       </c>
       <c r="D128" t="n">
-        <v>223.899</v>
+        <v>225.088</v>
       </c>
       <c r="E128" t="n">
-        <v>43.1658</v>
+        <v>43.9897</v>
       </c>
       <c r="F128" t="n">
-        <v>143.3</v>
+        <v>143.661</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>95.4589</v>
+        <v>94.2718</v>
       </c>
       <c r="C129" t="n">
-        <v>76.7646</v>
+        <v>77.01609999999999</v>
       </c>
       <c r="D129" t="n">
-        <v>222.762</v>
+        <v>224.744</v>
       </c>
       <c r="E129" t="n">
-        <v>41.9904</v>
+        <v>43.6468</v>
       </c>
       <c r="F129" t="n">
-        <v>142.271</v>
+        <v>143.109</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>92.9372</v>
+        <v>93.90309999999999</v>
       </c>
       <c r="C130" t="n">
-        <v>77.27030000000001</v>
+        <v>76.9265</v>
       </c>
       <c r="D130" t="n">
-        <v>222.651</v>
+        <v>222.822</v>
       </c>
       <c r="E130" t="n">
-        <v>41.8843</v>
+        <v>43.4818</v>
       </c>
       <c r="F130" t="n">
-        <v>141.953</v>
+        <v>142.304</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>91.44750000000001</v>
+        <v>92.8747</v>
       </c>
       <c r="C131" t="n">
-        <v>77.34050000000001</v>
+        <v>77.6309</v>
       </c>
       <c r="D131" t="n">
-        <v>221.339</v>
+        <v>222.664</v>
       </c>
       <c r="E131" t="n">
-        <v>41.7308</v>
+        <v>43.4397</v>
       </c>
       <c r="F131" t="n">
-        <v>142.568</v>
+        <v>141.954</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>93.3181</v>
+        <v>92.6544</v>
       </c>
       <c r="C132" t="n">
-        <v>77.34139999999999</v>
+        <v>77.7667</v>
       </c>
       <c r="D132" t="n">
-        <v>221.962</v>
+        <v>222.463</v>
       </c>
       <c r="E132" t="n">
-        <v>41.2924</v>
+        <v>42.9135</v>
       </c>
       <c r="F132" t="n">
-        <v>141.25</v>
+        <v>141.896</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>91.4198</v>
+        <v>93.0245</v>
       </c>
       <c r="C133" t="n">
-        <v>77.3861</v>
+        <v>77.5412</v>
       </c>
       <c r="D133" t="n">
-        <v>222.073</v>
+        <v>223.072</v>
       </c>
       <c r="E133" t="n">
-        <v>40.6956</v>
+        <v>42.8814</v>
       </c>
       <c r="F133" t="n">
-        <v>140.729</v>
+        <v>141.34</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>91.324</v>
+        <v>93.1053</v>
       </c>
       <c r="C134" t="n">
-        <v>77.6507</v>
+        <v>77.8638</v>
       </c>
       <c r="D134" t="n">
-        <v>222.226</v>
+        <v>223.592</v>
       </c>
       <c r="E134" t="n">
-        <v>40.7</v>
+        <v>42.4836</v>
       </c>
       <c r="F134" t="n">
-        <v>140.568</v>
+        <v>141.276</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>90.3794</v>
+        <v>88.8651</v>
       </c>
       <c r="C135" t="n">
-        <v>77.669</v>
+        <v>77.9342</v>
       </c>
       <c r="D135" t="n">
-        <v>271.777</v>
+        <v>272.855</v>
       </c>
       <c r="E135" t="n">
-        <v>54.4033</v>
+        <v>56.5892</v>
       </c>
       <c r="F135" t="n">
-        <v>176.894</v>
+        <v>177.319</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>89.9867</v>
+        <v>89.9194</v>
       </c>
       <c r="C136" t="n">
-        <v>90.0188</v>
+        <v>90.7938</v>
       </c>
       <c r="D136" t="n">
-        <v>269.301</v>
+        <v>269.246</v>
       </c>
       <c r="E136" t="n">
-        <v>54.0267</v>
+        <v>55.9317</v>
       </c>
       <c r="F136" t="n">
-        <v>174.922</v>
+        <v>175.656</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>89.26819999999999</v>
+        <v>91.39230000000001</v>
       </c>
       <c r="C137" t="n">
-        <v>90.783</v>
+        <v>90.52549999999999</v>
       </c>
       <c r="D137" t="n">
-        <v>265.078</v>
+        <v>265.959</v>
       </c>
       <c r="E137" t="n">
-        <v>53.4806</v>
+        <v>56.1324</v>
       </c>
       <c r="F137" t="n">
-        <v>173.345</v>
+        <v>174.068</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>108.642</v>
+        <v>108.978</v>
       </c>
       <c r="C138" t="n">
-        <v>91.2294</v>
+        <v>91.1185</v>
       </c>
       <c r="D138" t="n">
-        <v>262.948</v>
+        <v>262.763</v>
       </c>
       <c r="E138" t="n">
-        <v>53.2702</v>
+        <v>55.4183</v>
       </c>
       <c r="F138" t="n">
-        <v>172.304</v>
+        <v>172.822</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>108.906</v>
+        <v>111.881</v>
       </c>
       <c r="C139" t="n">
-        <v>91.242</v>
+        <v>91.54510000000001</v>
       </c>
       <c r="D139" t="n">
-        <v>259.422</v>
+        <v>260.087</v>
       </c>
       <c r="E139" t="n">
-        <v>52.9818</v>
+        <v>55.9339</v>
       </c>
       <c r="F139" t="n">
-        <v>170.784</v>
+        <v>171.654</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>108.993</v>
+        <v>108.222</v>
       </c>
       <c r="C140" t="n">
-        <v>91.5805</v>
+        <v>91.8719</v>
       </c>
       <c r="D140" t="n">
-        <v>257.07</v>
+        <v>257.511</v>
       </c>
       <c r="E140" t="n">
-        <v>52.7628</v>
+        <v>55.4582</v>
       </c>
       <c r="F140" t="n">
-        <v>170.197</v>
+        <v>170.497</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>109.26</v>
+        <v>111.021</v>
       </c>
       <c r="C141" t="n">
-        <v>91.66800000000001</v>
+        <v>92.1395</v>
       </c>
       <c r="D141" t="n">
-        <v>254.399</v>
+        <v>255.614</v>
       </c>
       <c r="E141" t="n">
-        <v>52.7578</v>
+        <v>55.2059</v>
       </c>
       <c r="F141" t="n">
-        <v>169.975</v>
+        <v>170.152</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>107.459</v>
+        <v>108.515</v>
       </c>
       <c r="C142" t="n">
-        <v>92.1417</v>
+        <v>92.40689999999999</v>
       </c>
       <c r="D142" t="n">
-        <v>253.142</v>
+        <v>254.069</v>
       </c>
       <c r="E142" t="n">
-        <v>52.892</v>
+        <v>54.8279</v>
       </c>
       <c r="F142" t="n">
-        <v>168.111</v>
+        <v>168.765</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>109.72</v>
+        <v>109.918</v>
       </c>
       <c r="C143" t="n">
-        <v>92.3129</v>
+        <v>92.6165</v>
       </c>
       <c r="D143" t="n">
-        <v>251.527</v>
+        <v>252.665</v>
       </c>
       <c r="E143" t="n">
-        <v>52.1572</v>
+        <v>54.8533</v>
       </c>
       <c r="F143" t="n">
-        <v>166.93</v>
+        <v>167.968</v>
       </c>
     </row>
   </sheetData>

--- a/vs-x64/Running insertion.xlsx
+++ b/vs-x64/Running insertion.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>24.2499</v>
+        <v>24.1897</v>
       </c>
       <c r="C2" t="n">
-        <v>31.2784</v>
+        <v>31.1853</v>
       </c>
       <c r="D2" t="n">
-        <v>63.436</v>
+        <v>59.0451</v>
       </c>
       <c r="E2" t="n">
-        <v>15.2311</v>
+        <v>15.0727</v>
       </c>
       <c r="F2" t="n">
-        <v>49.5178</v>
+        <v>51.4417</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>22.866</v>
+        <v>22.7125</v>
       </c>
       <c r="C3" t="n">
-        <v>30.6872</v>
+        <v>30.7151</v>
       </c>
       <c r="D3" t="n">
-        <v>63.3277</v>
+        <v>58.491</v>
       </c>
       <c r="E3" t="n">
-        <v>14.8254</v>
+        <v>14.6297</v>
       </c>
       <c r="F3" t="n">
-        <v>48.8058</v>
+        <v>50.6549</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>22.2377</v>
+        <v>22.6819</v>
       </c>
       <c r="C4" t="n">
-        <v>30.2956</v>
+        <v>30.3007</v>
       </c>
       <c r="D4" t="n">
-        <v>62.6798</v>
+        <v>57.9995</v>
       </c>
       <c r="E4" t="n">
-        <v>14.4575</v>
+        <v>14.2933</v>
       </c>
       <c r="F4" t="n">
-        <v>48.3763</v>
+        <v>50.407</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>22.0611</v>
+        <v>22.1039</v>
       </c>
       <c r="C5" t="n">
-        <v>29.8981</v>
+        <v>29.8982</v>
       </c>
       <c r="D5" t="n">
-        <v>61.8299</v>
+        <v>57.5385</v>
       </c>
       <c r="E5" t="n">
-        <v>14.127</v>
+        <v>13.9826</v>
       </c>
       <c r="F5" t="n">
-        <v>48.1462</v>
+        <v>50.0167</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>21.7007</v>
+        <v>22.1417</v>
       </c>
       <c r="C6" t="n">
-        <v>29.5744</v>
+        <v>29.5168</v>
       </c>
       <c r="D6" t="n">
-        <v>61.2344</v>
+        <v>56.9192</v>
       </c>
       <c r="E6" t="n">
-        <v>13.9869</v>
+        <v>13.7237</v>
       </c>
       <c r="F6" t="n">
-        <v>47.699</v>
+        <v>49.6196</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>21.6112</v>
+        <v>21.6548</v>
       </c>
       <c r="C7" t="n">
-        <v>29.1553</v>
+        <v>29.1779</v>
       </c>
       <c r="D7" t="n">
-        <v>73.1819</v>
+        <v>68.2184</v>
       </c>
       <c r="E7" t="n">
-        <v>20.9236</v>
+        <v>20.6423</v>
       </c>
       <c r="F7" t="n">
-        <v>54.2598</v>
+        <v>56.1001</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>21.0581</v>
+        <v>21.5864</v>
       </c>
       <c r="C8" t="n">
-        <v>35.9508</v>
+        <v>35.9227</v>
       </c>
       <c r="D8" t="n">
-        <v>71.5145</v>
+        <v>67.2996</v>
       </c>
       <c r="E8" t="n">
-        <v>20.2245</v>
+        <v>19.9373</v>
       </c>
       <c r="F8" t="n">
-        <v>54.1473</v>
+        <v>55.878</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>21.2412</v>
+        <v>21.1762</v>
       </c>
       <c r="C9" t="n">
-        <v>35.2691</v>
+        <v>35.2348</v>
       </c>
       <c r="D9" t="n">
-        <v>70.3022</v>
+        <v>66.0121</v>
       </c>
       <c r="E9" t="n">
-        <v>19.5587</v>
+        <v>19.2717</v>
       </c>
       <c r="F9" t="n">
-        <v>53.1431</v>
+        <v>54.9724</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>27.7245</v>
+        <v>27.4703</v>
       </c>
       <c r="C10" t="n">
-        <v>34.6585</v>
+        <v>34.6112</v>
       </c>
       <c r="D10" t="n">
-        <v>69.0819</v>
+        <v>64.7612</v>
       </c>
       <c r="E10" t="n">
-        <v>18.9435</v>
+        <v>18.6217</v>
       </c>
       <c r="F10" t="n">
-        <v>52.3917</v>
+        <v>54.3276</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>27.4199</v>
+        <v>26.9754</v>
       </c>
       <c r="C11" t="n">
-        <v>34.0546</v>
+        <v>34.0048</v>
       </c>
       <c r="D11" t="n">
-        <v>68.4739</v>
+        <v>63.9908</v>
       </c>
       <c r="E11" t="n">
-        <v>18.3815</v>
+        <v>18.0649</v>
       </c>
       <c r="F11" t="n">
-        <v>51.9889</v>
+        <v>53.8141</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>26.638</v>
+        <v>26.4235</v>
       </c>
       <c r="C12" t="n">
-        <v>33.5116</v>
+        <v>33.4763</v>
       </c>
       <c r="D12" t="n">
-        <v>67.4327</v>
+        <v>63.1554</v>
       </c>
       <c r="E12" t="n">
-        <v>17.787</v>
+        <v>17.5124</v>
       </c>
       <c r="F12" t="n">
-        <v>51.1143</v>
+        <v>53.0128</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>25.9886</v>
+        <v>25.6945</v>
       </c>
       <c r="C13" t="n">
-        <v>32.9631</v>
+        <v>32.9547</v>
       </c>
       <c r="D13" t="n">
-        <v>66.69840000000001</v>
+        <v>62.4811</v>
       </c>
       <c r="E13" t="n">
-        <v>17.2541</v>
+        <v>16.9892</v>
       </c>
       <c r="F13" t="n">
-        <v>50.9439</v>
+        <v>52.3646</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>25.4212</v>
+        <v>25.3856</v>
       </c>
       <c r="C14" t="n">
-        <v>32.515</v>
+        <v>32.4578</v>
       </c>
       <c r="D14" t="n">
-        <v>65.92270000000001</v>
+        <v>61.6994</v>
       </c>
       <c r="E14" t="n">
-        <v>16.7412</v>
+        <v>16.4902</v>
       </c>
       <c r="F14" t="n">
-        <v>50.0373</v>
+        <v>51.878</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>25.0098</v>
+        <v>24.7117</v>
       </c>
       <c r="C15" t="n">
-        <v>31.9608</v>
+        <v>31.962</v>
       </c>
       <c r="D15" t="n">
-        <v>65.1465</v>
+        <v>61.1511</v>
       </c>
       <c r="E15" t="n">
-        <v>16.2502</v>
+        <v>16.0185</v>
       </c>
       <c r="F15" t="n">
-        <v>49.2175</v>
+        <v>51.2434</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>24.2996</v>
+        <v>24.0761</v>
       </c>
       <c r="C16" t="n">
-        <v>31.5529</v>
+        <v>31.4754</v>
       </c>
       <c r="D16" t="n">
-        <v>65.0642</v>
+        <v>60.7203</v>
       </c>
       <c r="E16" t="n">
-        <v>15.822</v>
+        <v>15.5762</v>
       </c>
       <c r="F16" t="n">
-        <v>49.0967</v>
+        <v>51.0111</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>24.0691</v>
+        <v>23.6176</v>
       </c>
       <c r="C17" t="n">
-        <v>31.0698</v>
+        <v>31.0447</v>
       </c>
       <c r="D17" t="n">
-        <v>64.0801</v>
+        <v>60.1468</v>
       </c>
       <c r="E17" t="n">
-        <v>15.4218</v>
+        <v>15.1684</v>
       </c>
       <c r="F17" t="n">
-        <v>48.421</v>
+        <v>50.2694</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>23.234</v>
+        <v>23.319</v>
       </c>
       <c r="C18" t="n">
-        <v>30.671</v>
+        <v>30.6308</v>
       </c>
       <c r="D18" t="n">
-        <v>63.4628</v>
+        <v>59.5052</v>
       </c>
       <c r="E18" t="n">
-        <v>15.0576</v>
+        <v>14.8546</v>
       </c>
       <c r="F18" t="n">
-        <v>48.0855</v>
+        <v>50.0076</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>23.3111</v>
+        <v>22.9859</v>
       </c>
       <c r="C19" t="n">
-        <v>30.2144</v>
+        <v>30.2693</v>
       </c>
       <c r="D19" t="n">
-        <v>62.8456</v>
+        <v>59.0864</v>
       </c>
       <c r="E19" t="n">
-        <v>14.7555</v>
+        <v>14.4948</v>
       </c>
       <c r="F19" t="n">
-        <v>47.604</v>
+        <v>49.4947</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>22.6165</v>
+        <v>22.3017</v>
       </c>
       <c r="C20" t="n">
-        <v>29.8655</v>
+        <v>29.8848</v>
       </c>
       <c r="D20" t="n">
-        <v>62.854</v>
+        <v>59.282</v>
       </c>
       <c r="E20" t="n">
-        <v>14.533</v>
+        <v>14.2797</v>
       </c>
       <c r="F20" t="n">
-        <v>47.4879</v>
+        <v>49.3864</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>22.2289</v>
+        <v>21.937</v>
       </c>
       <c r="C21" t="n">
-        <v>29.5267</v>
+        <v>29.5163</v>
       </c>
       <c r="D21" t="n">
-        <v>75.7277</v>
+        <v>71.51730000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>27.4927</v>
+        <v>27.0507</v>
       </c>
       <c r="F21" t="n">
-        <v>55.1836</v>
+        <v>56.6614</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>22.1039</v>
+        <v>21.8696</v>
       </c>
       <c r="C22" t="n">
-        <v>40.8676</v>
+        <v>40.8439</v>
       </c>
       <c r="D22" t="n">
-        <v>74.65560000000001</v>
+        <v>70.4585</v>
       </c>
       <c r="E22" t="n">
-        <v>26.4431</v>
+        <v>26.1314</v>
       </c>
       <c r="F22" t="n">
-        <v>54.4959</v>
+        <v>55.7667</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>22.0412</v>
+        <v>22.1221</v>
       </c>
       <c r="C23" t="n">
-        <v>39.9959</v>
+        <v>39.9233</v>
       </c>
       <c r="D23" t="n">
-        <v>72.9982</v>
+        <v>69.21510000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>25.6008</v>
+        <v>25.2291</v>
       </c>
       <c r="F23" t="n">
-        <v>53.6943</v>
+        <v>55.2037</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>39.0142</v>
+        <v>44.1733</v>
       </c>
       <c r="C24" t="n">
-        <v>39.288</v>
+        <v>39.1629</v>
       </c>
       <c r="D24" t="n">
-        <v>72.2009</v>
+        <v>68.45820000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>24.669</v>
+        <v>24.3177</v>
       </c>
       <c r="F24" t="n">
-        <v>53.12</v>
+        <v>54.5364</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>38.2255</v>
+        <v>40.2106</v>
       </c>
       <c r="C25" t="n">
-        <v>38.4695</v>
+        <v>38.4843</v>
       </c>
       <c r="D25" t="n">
-        <v>71.79640000000001</v>
+        <v>67.4141</v>
       </c>
       <c r="E25" t="n">
-        <v>23.7678</v>
+        <v>23.5266</v>
       </c>
       <c r="F25" t="n">
-        <v>52.5884</v>
+        <v>54.0419</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>38.4353</v>
+        <v>39.6454</v>
       </c>
       <c r="C26" t="n">
-        <v>37.641</v>
+        <v>37.7747</v>
       </c>
       <c r="D26" t="n">
-        <v>70.39279999999999</v>
+        <v>66.6121</v>
       </c>
       <c r="E26" t="n">
-        <v>23.0653</v>
+        <v>22.6982</v>
       </c>
       <c r="F26" t="n">
-        <v>51.6037</v>
+        <v>53.0801</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>38.3599</v>
+        <v>40.265</v>
       </c>
       <c r="C27" t="n">
-        <v>36.9466</v>
+        <v>36.918</v>
       </c>
       <c r="D27" t="n">
-        <v>69.0466</v>
+        <v>65.4864</v>
       </c>
       <c r="E27" t="n">
-        <v>22.3246</v>
+        <v>21.968</v>
       </c>
       <c r="F27" t="n">
-        <v>49.8127</v>
+        <v>50.7859</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>32.3647</v>
+        <v>37.2232</v>
       </c>
       <c r="C28" t="n">
-        <v>36.3026</v>
+        <v>36.4046</v>
       </c>
       <c r="D28" t="n">
-        <v>67.8205</v>
+        <v>64.5364</v>
       </c>
       <c r="E28" t="n">
-        <v>21.4989</v>
+        <v>21.2688</v>
       </c>
       <c r="F28" t="n">
-        <v>48.9589</v>
+        <v>50.4386</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>33.7889</v>
+        <v>36.1192</v>
       </c>
       <c r="C29" t="n">
-        <v>35.6698</v>
+        <v>35.6357</v>
       </c>
       <c r="D29" t="n">
-        <v>66.9247</v>
+        <v>64.1568</v>
       </c>
       <c r="E29" t="n">
-        <v>20.8329</v>
+        <v>20.6233</v>
       </c>
       <c r="F29" t="n">
-        <v>48.5445</v>
+        <v>49.9758</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>33.0916</v>
+        <v>37.3076</v>
       </c>
       <c r="C30" t="n">
-        <v>35.0459</v>
+        <v>35.0179</v>
       </c>
       <c r="D30" t="n">
-        <v>65.9585</v>
+        <v>63.5234</v>
       </c>
       <c r="E30" t="n">
-        <v>20.2612</v>
+        <v>19.9674</v>
       </c>
       <c r="F30" t="n">
-        <v>48.2539</v>
+        <v>49.3635</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>33.5067</v>
+        <v>34.533</v>
       </c>
       <c r="C31" t="n">
-        <v>34.4039</v>
+        <v>34.4094</v>
       </c>
       <c r="D31" t="n">
-        <v>65.3532</v>
+        <v>62.7531</v>
       </c>
       <c r="E31" t="n">
-        <v>19.6294</v>
+        <v>19.3859</v>
       </c>
       <c r="F31" t="n">
-        <v>47.9349</v>
+        <v>49.0387</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>32.4133</v>
+        <v>31.7418</v>
       </c>
       <c r="C32" t="n">
-        <v>33.8968</v>
+        <v>33.9049</v>
       </c>
       <c r="D32" t="n">
-        <v>64.9228</v>
+        <v>62.3972</v>
       </c>
       <c r="E32" t="n">
-        <v>19.0757</v>
+        <v>18.8364</v>
       </c>
       <c r="F32" t="n">
-        <v>47.3509</v>
+        <v>48.4209</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>31.7322</v>
+        <v>32.7961</v>
       </c>
       <c r="C33" t="n">
-        <v>33.3398</v>
+        <v>33.387</v>
       </c>
       <c r="D33" t="n">
-        <v>64.6671</v>
+        <v>62.278</v>
       </c>
       <c r="E33" t="n">
-        <v>18.5821</v>
+        <v>18.3914</v>
       </c>
       <c r="F33" t="n">
-        <v>47.4135</v>
+        <v>48.2933</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>28.1375</v>
+        <v>31.9265</v>
       </c>
       <c r="C34" t="n">
-        <v>32.9131</v>
+        <v>32.7388</v>
       </c>
       <c r="D34" t="n">
-        <v>64.148</v>
+        <v>61.8992</v>
       </c>
       <c r="E34" t="n">
-        <v>18.2386</v>
+        <v>17.9734</v>
       </c>
       <c r="F34" t="n">
-        <v>47.1665</v>
+        <v>48.0855</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>28.8046</v>
+        <v>30.981</v>
       </c>
       <c r="C35" t="n">
-        <v>32.3376</v>
+        <v>32.3369</v>
       </c>
       <c r="D35" t="n">
-        <v>77.7508</v>
+        <v>75.7659</v>
       </c>
       <c r="E35" t="n">
-        <v>31.4409</v>
+        <v>31.2781</v>
       </c>
       <c r="F35" t="n">
-        <v>57.024</v>
+        <v>58.2759</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>32.1219</v>
+        <v>32.0132</v>
       </c>
       <c r="C36" t="n">
-        <v>31.9287</v>
+        <v>31.9446</v>
       </c>
       <c r="D36" t="n">
-        <v>77.5723</v>
+        <v>74.53019999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>30.2158</v>
+        <v>30.116</v>
       </c>
       <c r="F36" t="n">
-        <v>56.4814</v>
+        <v>57.6248</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>28.0157</v>
+        <v>31.1712</v>
       </c>
       <c r="C37" t="n">
-        <v>42.84</v>
+        <v>42.9498</v>
       </c>
       <c r="D37" t="n">
-        <v>75.8305</v>
+        <v>73.3459</v>
       </c>
       <c r="E37" t="n">
-        <v>29.1915</v>
+        <v>28.9766</v>
       </c>
       <c r="F37" t="n">
-        <v>55.5975</v>
+        <v>56.8653</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>51.4468</v>
+        <v>46.4652</v>
       </c>
       <c r="C38" t="n">
-        <v>41.7965</v>
+        <v>42.0295</v>
       </c>
       <c r="D38" t="n">
-        <v>74.85599999999999</v>
+        <v>72.1383</v>
       </c>
       <c r="E38" t="n">
-        <v>28.1707</v>
+        <v>27.8913</v>
       </c>
       <c r="F38" t="n">
-        <v>54.6724</v>
+        <v>55.8774</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>49.334</v>
+        <v>44.8094</v>
       </c>
       <c r="C39" t="n">
-        <v>40.9147</v>
+        <v>41.074</v>
       </c>
       <c r="D39" t="n">
-        <v>74.06489999999999</v>
+        <v>71.4986</v>
       </c>
       <c r="E39" t="n">
-        <v>27.1889</v>
+        <v>26.9957</v>
       </c>
       <c r="F39" t="n">
-        <v>54.0572</v>
+        <v>55.2483</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>47.8606</v>
+        <v>43.5137</v>
       </c>
       <c r="C40" t="n">
-        <v>40.0609</v>
+        <v>40.2078</v>
       </c>
       <c r="D40" t="n">
-        <v>72.70399999999999</v>
+        <v>70.49679999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>26.2718</v>
+        <v>26.0007</v>
       </c>
       <c r="F40" t="n">
-        <v>53.3818</v>
+        <v>54.4353</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>46.2279</v>
+        <v>43.199</v>
       </c>
       <c r="C41" t="n">
-        <v>39.2765</v>
+        <v>39.3561</v>
       </c>
       <c r="D41" t="n">
-        <v>71.6086</v>
+        <v>69.24469999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>25.4208</v>
+        <v>25.2388</v>
       </c>
       <c r="F41" t="n">
-        <v>52.4433</v>
+        <v>53.8554</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>45.7411</v>
+        <v>41.8109</v>
       </c>
       <c r="C42" t="n">
-        <v>38.4928</v>
+        <v>38.6265</v>
       </c>
       <c r="D42" t="n">
-        <v>70.6823</v>
+        <v>68.4126</v>
       </c>
       <c r="E42" t="n">
-        <v>24.5768</v>
+        <v>24.2962</v>
       </c>
       <c r="F42" t="n">
-        <v>52.0764</v>
+        <v>53.3837</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>44.1368</v>
+        <v>39.7595</v>
       </c>
       <c r="C43" t="n">
-        <v>37.6477</v>
+        <v>37.8151</v>
       </c>
       <c r="D43" t="n">
-        <v>70.4226</v>
+        <v>67.8436</v>
       </c>
       <c r="E43" t="n">
-        <v>23.6466</v>
+        <v>23.5365</v>
       </c>
       <c r="F43" t="n">
-        <v>51.263</v>
+        <v>52.71</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>43.3314</v>
+        <v>39.3232</v>
       </c>
       <c r="C44" t="n">
-        <v>36.9678</v>
+        <v>37.07</v>
       </c>
       <c r="D44" t="n">
-        <v>69.5829</v>
+        <v>67.41070000000001</v>
       </c>
       <c r="E44" t="n">
-        <v>22.8416</v>
+        <v>22.8388</v>
       </c>
       <c r="F44" t="n">
-        <v>50.8327</v>
+        <v>52.0174</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>43.7468</v>
+        <v>37.2547</v>
       </c>
       <c r="C45" t="n">
-        <v>36.4159</v>
+        <v>36.3826</v>
       </c>
       <c r="D45" t="n">
-        <v>68.9731</v>
+        <v>66.79219999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>22.1594</v>
+        <v>22.04</v>
       </c>
       <c r="F45" t="n">
-        <v>50.2387</v>
+        <v>51.4428</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>42.1493</v>
+        <v>37.0699</v>
       </c>
       <c r="C46" t="n">
-        <v>35.7855</v>
+        <v>35.7112</v>
       </c>
       <c r="D46" t="n">
-        <v>68.20740000000001</v>
+        <v>66.2649</v>
       </c>
       <c r="E46" t="n">
-        <v>21.7251</v>
+        <v>21.4337</v>
       </c>
       <c r="F46" t="n">
-        <v>49.8673</v>
+        <v>50.9987</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>41.1754</v>
+        <v>35.8395</v>
       </c>
       <c r="C47" t="n">
-        <v>35.0826</v>
+        <v>35.0971</v>
       </c>
       <c r="D47" t="n">
-        <v>67.77419999999999</v>
+        <v>65.6104</v>
       </c>
       <c r="E47" t="n">
-        <v>21.0009</v>
+        <v>20.8749</v>
       </c>
       <c r="F47" t="n">
-        <v>49.4729</v>
+        <v>50.5788</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>40.1355</v>
+        <v>35.1186</v>
       </c>
       <c r="C48" t="n">
-        <v>34.5467</v>
+        <v>34.5021</v>
       </c>
       <c r="D48" t="n">
-        <v>67.339</v>
+        <v>65.1747</v>
       </c>
       <c r="E48" t="n">
-        <v>20.651</v>
+        <v>20.4183</v>
       </c>
       <c r="F48" t="n">
-        <v>49.054</v>
+        <v>50.2482</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>37.3863</v>
+        <v>33.7535</v>
       </c>
       <c r="C49" t="n">
-        <v>33.8195</v>
+        <v>34.0254</v>
       </c>
       <c r="D49" t="n">
-        <v>67.0262</v>
+        <v>64.9269</v>
       </c>
       <c r="E49" t="n">
-        <v>20.0452</v>
+        <v>19.8916</v>
       </c>
       <c r="F49" t="n">
-        <v>48.808</v>
+        <v>50.0996</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>37.5808</v>
+        <v>32.7532</v>
       </c>
       <c r="C50" t="n">
-        <v>33.2803</v>
+        <v>33.4208</v>
       </c>
       <c r="D50" t="n">
-        <v>81.76519999999999</v>
+        <v>79.6897</v>
       </c>
       <c r="E50" t="n">
-        <v>32.5237</v>
+        <v>32.1041</v>
       </c>
       <c r="F50" t="n">
-        <v>58.8088</v>
+        <v>59.6685</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>37.06</v>
+        <v>32.6381</v>
       </c>
       <c r="C51" t="n">
-        <v>44.0656</v>
+        <v>44.3085</v>
       </c>
       <c r="D51" t="n">
-        <v>80.866</v>
+        <v>78.59180000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>31.3667</v>
+        <v>30.9569</v>
       </c>
       <c r="F51" t="n">
-        <v>57.8895</v>
+        <v>59.0874</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>36.1994</v>
+        <v>32.1563</v>
       </c>
       <c r="C52" t="n">
-        <v>43.1018</v>
+        <v>43.2196</v>
       </c>
       <c r="D52" t="n">
-        <v>78.9833</v>
+        <v>77.1203</v>
       </c>
       <c r="E52" t="n">
-        <v>30.0309</v>
+        <v>29.8613</v>
       </c>
       <c r="F52" t="n">
-        <v>56.7673</v>
+        <v>58.2223</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>56.85</v>
+        <v>50.8348</v>
       </c>
       <c r="C53" t="n">
-        <v>42.4669</v>
+        <v>42.3329</v>
       </c>
       <c r="D53" t="n">
-        <v>77.6234</v>
+        <v>75.806</v>
       </c>
       <c r="E53" t="n">
-        <v>29.1549</v>
+        <v>29.0524</v>
       </c>
       <c r="F53" t="n">
-        <v>56.2</v>
+        <v>57.1752</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>55.2271</v>
+        <v>49.235</v>
       </c>
       <c r="C54" t="n">
-        <v>41.2195</v>
+        <v>41.2505</v>
       </c>
       <c r="D54" t="n">
-        <v>76.6782</v>
+        <v>74.6187</v>
       </c>
       <c r="E54" t="n">
-        <v>28.2197</v>
+        <v>28.1538</v>
       </c>
       <c r="F54" t="n">
-        <v>55.4633</v>
+        <v>56.4084</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>53.5514</v>
+        <v>47.1442</v>
       </c>
       <c r="C55" t="n">
-        <v>40.5397</v>
+        <v>40.585</v>
       </c>
       <c r="D55" t="n">
-        <v>75.60420000000001</v>
+        <v>75.3416</v>
       </c>
       <c r="E55" t="n">
-        <v>27.3923</v>
+        <v>27.352</v>
       </c>
       <c r="F55" t="n">
-        <v>55.2308</v>
+        <v>55.6077</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>50.2252</v>
+        <v>46.7301</v>
       </c>
       <c r="C56" t="n">
-        <v>39.4189</v>
+        <v>39.5449</v>
       </c>
       <c r="D56" t="n">
-        <v>74.36360000000001</v>
+        <v>72.9495</v>
       </c>
       <c r="E56" t="n">
-        <v>26.5008</v>
+        <v>26.4763</v>
       </c>
       <c r="F56" t="n">
-        <v>53.8379</v>
+        <v>56.8422</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>49.0454</v>
+        <v>44.6557</v>
       </c>
       <c r="C57" t="n">
-        <v>38.9174</v>
+        <v>38.9734</v>
       </c>
       <c r="D57" t="n">
-        <v>73.88939999999999</v>
+        <v>72.5288</v>
       </c>
       <c r="E57" t="n">
-        <v>25.9884</v>
+        <v>25.5817</v>
       </c>
       <c r="F57" t="n">
-        <v>53.3069</v>
+        <v>54.432</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>48.4244</v>
+        <v>43.6209</v>
       </c>
       <c r="C58" t="n">
-        <v>37.9412</v>
+        <v>38.2909</v>
       </c>
       <c r="D58" t="n">
-        <v>72.7332</v>
+        <v>71.2405</v>
       </c>
       <c r="E58" t="n">
-        <v>24.9561</v>
+        <v>24.4647</v>
       </c>
       <c r="F58" t="n">
-        <v>52.8852</v>
+        <v>53.8601</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>47.0989</v>
+        <v>41.6975</v>
       </c>
       <c r="C59" t="n">
-        <v>37.2288</v>
+        <v>37.6624</v>
       </c>
       <c r="D59" t="n">
-        <v>72.05880000000001</v>
+        <v>70.22620000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>24.073</v>
+        <v>23.7694</v>
       </c>
       <c r="F59" t="n">
-        <v>52.434</v>
+        <v>53.2919</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>44.608</v>
+        <v>41.2835</v>
       </c>
       <c r="C60" t="n">
-        <v>36.5187</v>
+        <v>36.8164</v>
       </c>
       <c r="D60" t="n">
-        <v>71.2619</v>
+        <v>69.5599</v>
       </c>
       <c r="E60" t="n">
-        <v>23.3113</v>
+        <v>23.2569</v>
       </c>
       <c r="F60" t="n">
-        <v>51.6611</v>
+        <v>52.8953</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>43.249</v>
+        <v>40.0247</v>
       </c>
       <c r="C61" t="n">
-        <v>35.9128</v>
+        <v>35.986</v>
       </c>
       <c r="D61" t="n">
-        <v>71.41070000000001</v>
+        <v>69.2603</v>
       </c>
       <c r="E61" t="n">
-        <v>23.0785</v>
+        <v>22.6311</v>
       </c>
       <c r="F61" t="n">
-        <v>51.3933</v>
+        <v>52.376</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>43.3886</v>
+        <v>37.7714</v>
       </c>
       <c r="C62" t="n">
-        <v>35.4173</v>
+        <v>35.6279</v>
       </c>
       <c r="D62" t="n">
-        <v>70.3113</v>
+        <v>68.72110000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>22.4028</v>
+        <v>21.791</v>
       </c>
       <c r="F62" t="n">
-        <v>51.2142</v>
+        <v>51.9576</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>40.9612</v>
+        <v>40.8221</v>
       </c>
       <c r="C63" t="n">
-        <v>34.7983</v>
+        <v>34.843</v>
       </c>
       <c r="D63" t="n">
-        <v>69.4588</v>
+        <v>68.2098</v>
       </c>
       <c r="E63" t="n">
-        <v>21.8097</v>
+        <v>21.4539</v>
       </c>
       <c r="F63" t="n">
-        <v>50.2651</v>
+        <v>52.0421</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>40.072</v>
+        <v>40.0062</v>
       </c>
       <c r="C64" t="n">
-        <v>34.2999</v>
+        <v>34.3388</v>
       </c>
       <c r="D64" t="n">
-        <v>86.074</v>
+        <v>84.63339999999999</v>
       </c>
       <c r="E64" t="n">
-        <v>35.1808</v>
+        <v>34.7531</v>
       </c>
       <c r="F64" t="n">
-        <v>60.7458</v>
+        <v>62.0922</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>38.9229</v>
+        <v>37.9617</v>
       </c>
       <c r="C65" t="n">
-        <v>45.7495</v>
+        <v>45.2106</v>
       </c>
       <c r="D65" t="n">
-        <v>84.6254</v>
+        <v>85.4178</v>
       </c>
       <c r="E65" t="n">
-        <v>34.0475</v>
+        <v>33.4567</v>
       </c>
       <c r="F65" t="n">
-        <v>59.7091</v>
+        <v>62.0908</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>38.19</v>
+        <v>37.2726</v>
       </c>
       <c r="C66" t="n">
-        <v>44.0658</v>
+        <v>44.1535</v>
       </c>
       <c r="D66" t="n">
-        <v>83.0652</v>
+        <v>83.54300000000001</v>
       </c>
       <c r="E66" t="n">
-        <v>32.3293</v>
+        <v>31.761</v>
       </c>
       <c r="F66" t="n">
-        <v>59.0306</v>
+        <v>61.8472</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>60.3617</v>
+        <v>60.663</v>
       </c>
       <c r="C67" t="n">
-        <v>43.4681</v>
+        <v>43.0465</v>
       </c>
       <c r="D67" t="n">
-        <v>85.023</v>
+        <v>82.5998</v>
       </c>
       <c r="E67" t="n">
-        <v>31.6691</v>
+        <v>30.8726</v>
       </c>
       <c r="F67" t="n">
-        <v>60.3803</v>
+        <v>60.0066</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>59.5122</v>
+        <v>59.2313</v>
       </c>
       <c r="C68" t="n">
-        <v>43.1286</v>
+        <v>42.3717</v>
       </c>
       <c r="D68" t="n">
-        <v>82.3051</v>
+        <v>80.2406</v>
       </c>
       <c r="E68" t="n">
-        <v>30.9553</v>
+        <v>30.2904</v>
       </c>
       <c r="F68" t="n">
-        <v>58.7294</v>
+        <v>60.0159</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>56.4691</v>
+        <v>56.912</v>
       </c>
       <c r="C69" t="n">
-        <v>41.8781</v>
+        <v>41.4705</v>
       </c>
       <c r="D69" t="n">
-        <v>79.76690000000001</v>
+        <v>78.6473</v>
       </c>
       <c r="E69" t="n">
-        <v>29.3925</v>
+        <v>28.7875</v>
       </c>
       <c r="F69" t="n">
-        <v>57.6262</v>
+        <v>59.3881</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>55.8694</v>
+        <v>56.0259</v>
       </c>
       <c r="C70" t="n">
-        <v>41.5199</v>
+        <v>41.0584</v>
       </c>
       <c r="D70" t="n">
-        <v>80.3639</v>
+        <v>78.74120000000001</v>
       </c>
       <c r="E70" t="n">
-        <v>28.7916</v>
+        <v>28.5148</v>
       </c>
       <c r="F70" t="n">
-        <v>58.2251</v>
+        <v>59.6667</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>54.0203</v>
+        <v>53.0929</v>
       </c>
       <c r="C71" t="n">
-        <v>40.024</v>
+        <v>40.0539</v>
       </c>
       <c r="D71" t="n">
-        <v>79.0368</v>
+        <v>77.7598</v>
       </c>
       <c r="E71" t="n">
-        <v>27.7604</v>
+        <v>27.3932</v>
       </c>
       <c r="F71" t="n">
-        <v>56.3345</v>
+        <v>56.7928</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>52.8866</v>
+        <v>52.2883</v>
       </c>
       <c r="C72" t="n">
-        <v>39.1778</v>
+        <v>39.0529</v>
       </c>
       <c r="D72" t="n">
-        <v>78.79170000000001</v>
+        <v>76.4263</v>
       </c>
       <c r="E72" t="n">
-        <v>26.7789</v>
+        <v>26.1449</v>
       </c>
       <c r="F72" t="n">
-        <v>55.3557</v>
+        <v>56.4312</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>51.6058</v>
+        <v>51.3099</v>
       </c>
       <c r="C73" t="n">
-        <v>38.8621</v>
+        <v>38.5495</v>
       </c>
       <c r="D73" t="n">
-        <v>76.9156</v>
+        <v>75.79170000000001</v>
       </c>
       <c r="E73" t="n">
-        <v>25.9928</v>
+        <v>25.7396</v>
       </c>
       <c r="F73" t="n">
-        <v>55.5531</v>
+        <v>57.6725</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>50.2216</v>
+        <v>50.1675</v>
       </c>
       <c r="C74" t="n">
-        <v>38.1165</v>
+        <v>37.8805</v>
       </c>
       <c r="D74" t="n">
-        <v>76.60590000000001</v>
+        <v>76.52370000000001</v>
       </c>
       <c r="E74" t="n">
-        <v>25.2143</v>
+        <v>24.9334</v>
       </c>
       <c r="F74" t="n">
-        <v>54.2901</v>
+        <v>55.6515</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>48.6111</v>
+        <v>48.759</v>
       </c>
       <c r="C75" t="n">
-        <v>37.4416</v>
+        <v>37.154</v>
       </c>
       <c r="D75" t="n">
-        <v>77.0438</v>
+        <v>75.2072</v>
       </c>
       <c r="E75" t="n">
-        <v>24.5859</v>
+        <v>24.3628</v>
       </c>
       <c r="F75" t="n">
-        <v>54.7715</v>
+        <v>54.4963</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>47.4948</v>
+        <v>47.8351</v>
       </c>
       <c r="C76" t="n">
-        <v>36.562</v>
+        <v>36.701</v>
       </c>
       <c r="D76" t="n">
-        <v>76.7658</v>
+        <v>75.12990000000001</v>
       </c>
       <c r="E76" t="n">
-        <v>24.1495</v>
+        <v>23.4172</v>
       </c>
       <c r="F76" t="n">
-        <v>54.7909</v>
+        <v>54.7161</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>46.3363</v>
+        <v>46.0282</v>
       </c>
       <c r="C77" t="n">
-        <v>35.9148</v>
+        <v>35.8191</v>
       </c>
       <c r="D77" t="n">
-        <v>77.1895</v>
+        <v>74.6116</v>
       </c>
       <c r="E77" t="n">
-        <v>23.6117</v>
+        <v>23.1717</v>
       </c>
       <c r="F77" t="n">
-        <v>53.1186</v>
+        <v>54.6391</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>45.2296</v>
+        <v>44.845</v>
       </c>
       <c r="C78" t="n">
-        <v>35.3852</v>
+        <v>35.3805</v>
       </c>
       <c r="D78" t="n">
-        <v>110.255</v>
+        <v>108.576</v>
       </c>
       <c r="E78" t="n">
-        <v>36.6259</v>
+        <v>36.5328</v>
       </c>
       <c r="F78" t="n">
-        <v>77.7522</v>
+        <v>77.756</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>44.2993</v>
+        <v>42.8447</v>
       </c>
       <c r="C79" t="n">
-        <v>47.0998</v>
+        <v>47.7426</v>
       </c>
       <c r="D79" t="n">
-        <v>109.281</v>
+        <v>107.714</v>
       </c>
       <c r="E79" t="n">
-        <v>36.9009</v>
+        <v>35.5086</v>
       </c>
       <c r="F79" t="n">
-        <v>78.4303</v>
+        <v>79.58280000000001</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>44.071</v>
+        <v>41.8283</v>
       </c>
       <c r="C80" t="n">
-        <v>47.8483</v>
+        <v>47.0634</v>
       </c>
       <c r="D80" t="n">
-        <v>109.901</v>
+        <v>105.679</v>
       </c>
       <c r="E80" t="n">
-        <v>35.8792</v>
+        <v>34.9289</v>
       </c>
       <c r="F80" t="n">
-        <v>77.94889999999999</v>
+        <v>78.2388</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>66.9713</v>
+        <v>60.7431</v>
       </c>
       <c r="C81" t="n">
-        <v>47.6595</v>
+        <v>47.218</v>
       </c>
       <c r="D81" t="n">
-        <v>107.366</v>
+        <v>105.959</v>
       </c>
       <c r="E81" t="n">
-        <v>34.462</v>
+        <v>34.3424</v>
       </c>
       <c r="F81" t="n">
-        <v>78.59229999999999</v>
+        <v>78.57680000000001</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>66.4633</v>
+        <v>60.8882</v>
       </c>
       <c r="C82" t="n">
-        <v>47.158</v>
+        <v>46.5848</v>
       </c>
       <c r="D82" t="n">
-        <v>107.153</v>
+        <v>104.706</v>
       </c>
       <c r="E82" t="n">
-        <v>33.1277</v>
+        <v>32.7329</v>
       </c>
       <c r="F82" t="n">
-        <v>78.3811</v>
+        <v>76.4396</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>65.8507</v>
+        <v>60.1345</v>
       </c>
       <c r="C83" t="n">
-        <v>46.866</v>
+        <v>46.612</v>
       </c>
       <c r="D83" t="n">
-        <v>106.182</v>
+        <v>104.111</v>
       </c>
       <c r="E83" t="n">
-        <v>32.2611</v>
+        <v>31.5005</v>
       </c>
       <c r="F83" t="n">
-        <v>76.07640000000001</v>
+        <v>76.3502</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>65.04600000000001</v>
+        <v>59.0964</v>
       </c>
       <c r="C84" t="n">
-        <v>45.9733</v>
+        <v>45.9737</v>
       </c>
       <c r="D84" t="n">
-        <v>105.692</v>
+        <v>103.728</v>
       </c>
       <c r="E84" t="n">
-        <v>32.0134</v>
+        <v>30.9852</v>
       </c>
       <c r="F84" t="n">
-        <v>75.2711</v>
+        <v>75.4618</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>63.5941</v>
+        <v>58.4806</v>
       </c>
       <c r="C85" t="n">
-        <v>45.3356</v>
+        <v>45.2481</v>
       </c>
       <c r="D85" t="n">
-        <v>105.762</v>
+        <v>102.82</v>
       </c>
       <c r="E85" t="n">
-        <v>30.3143</v>
+        <v>30.1278</v>
       </c>
       <c r="F85" t="n">
-        <v>73.13420000000001</v>
+        <v>73.8296</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>63.1745</v>
+        <v>57.8069</v>
       </c>
       <c r="C86" t="n">
-        <v>44.9641</v>
+        <v>44.876</v>
       </c>
       <c r="D86" t="n">
-        <v>105.033</v>
+        <v>103.489</v>
       </c>
       <c r="E86" t="n">
-        <v>29.7637</v>
+        <v>29.6275</v>
       </c>
       <c r="F86" t="n">
-        <v>73.3287</v>
+        <v>73.0504</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>61.7997</v>
+        <v>56.389</v>
       </c>
       <c r="C87" t="n">
-        <v>44.4362</v>
+        <v>44.3674</v>
       </c>
       <c r="D87" t="n">
-        <v>106.521</v>
+        <v>102.742</v>
       </c>
       <c r="E87" t="n">
-        <v>29.266</v>
+        <v>28.5543</v>
       </c>
       <c r="F87" t="n">
-        <v>72.4799</v>
+        <v>71.5093</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>60.2108</v>
+        <v>55.7102</v>
       </c>
       <c r="C88" t="n">
-        <v>43.9125</v>
+        <v>43.8013</v>
       </c>
       <c r="D88" t="n">
-        <v>106.109</v>
+        <v>103.227</v>
       </c>
       <c r="E88" t="n">
-        <v>28.2345</v>
+        <v>28.3965</v>
       </c>
       <c r="F88" t="n">
-        <v>71.2619</v>
+        <v>69.9743</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>59.2178</v>
+        <v>55.1179</v>
       </c>
       <c r="C89" t="n">
-        <v>43.3434</v>
+        <v>43.3859</v>
       </c>
       <c r="D89" t="n">
-        <v>106.747</v>
+        <v>103.421</v>
       </c>
       <c r="E89" t="n">
-        <v>27.5875</v>
+        <v>27.3639</v>
       </c>
       <c r="F89" t="n">
-        <v>70.6079</v>
+        <v>68.0204</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>58.4704</v>
+        <v>53.7239</v>
       </c>
       <c r="C90" t="n">
-        <v>42.7497</v>
+        <v>42.6803</v>
       </c>
       <c r="D90" t="n">
-        <v>107.352</v>
+        <v>104.834</v>
       </c>
       <c r="E90" t="n">
-        <v>26.8776</v>
+        <v>26.4093</v>
       </c>
       <c r="F90" t="n">
-        <v>68.66240000000001</v>
+        <v>68.24209999999999</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>56.384</v>
+        <v>52.8237</v>
       </c>
       <c r="C91" t="n">
-        <v>42.8357</v>
+        <v>42.2931</v>
       </c>
       <c r="D91" t="n">
-        <v>107.573</v>
+        <v>106.017</v>
       </c>
       <c r="E91" t="n">
-        <v>25.8981</v>
+        <v>26.0008</v>
       </c>
       <c r="F91" t="n">
-        <v>68.09950000000001</v>
+        <v>67.5585</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>55.4475</v>
+        <v>51.3926</v>
       </c>
       <c r="C92" t="n">
-        <v>41.9161</v>
+        <v>41.6197</v>
       </c>
       <c r="D92" t="n">
-        <v>148.92</v>
+        <v>148.363</v>
       </c>
       <c r="E92" t="n">
-        <v>39.828</v>
+        <v>39.0438</v>
       </c>
       <c r="F92" t="n">
-        <v>97.5585</v>
+        <v>98.378</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>48.9778</v>
+        <v>50.9286</v>
       </c>
       <c r="C93" t="n">
-        <v>41.2448</v>
+        <v>41.0599</v>
       </c>
       <c r="D93" t="n">
-        <v>149.198</v>
+        <v>148.203</v>
       </c>
       <c r="E93" t="n">
-        <v>38.9577</v>
+        <v>38.5192</v>
       </c>
       <c r="F93" t="n">
-        <v>99.48699999999999</v>
+        <v>98.7881</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>47.9936</v>
+        <v>52.1476</v>
       </c>
       <c r="C94" t="n">
-        <v>53.9634</v>
+        <v>53.9314</v>
       </c>
       <c r="D94" t="n">
-        <v>148.36</v>
+        <v>147.533</v>
       </c>
       <c r="E94" t="n">
-        <v>39.4461</v>
+        <v>37.5124</v>
       </c>
       <c r="F94" t="n">
-        <v>98.81999999999999</v>
+        <v>98.3845</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>66.5005</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="C95" t="n">
-        <v>54.1527</v>
+        <v>54.6216</v>
       </c>
       <c r="D95" t="n">
-        <v>147.214</v>
+        <v>145.214</v>
       </c>
       <c r="E95" t="n">
-        <v>37.1167</v>
+        <v>37.2194</v>
       </c>
       <c r="F95" t="n">
-        <v>96.38890000000001</v>
+        <v>97.3169</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>66.9316</v>
+        <v>74.59820000000001</v>
       </c>
       <c r="C96" t="n">
-        <v>53.2153</v>
+        <v>53.0635</v>
       </c>
       <c r="D96" t="n">
-        <v>146.686</v>
+        <v>145.162</v>
       </c>
       <c r="E96" t="n">
-        <v>36.7207</v>
+        <v>36.5686</v>
       </c>
       <c r="F96" t="n">
-        <v>95.5399</v>
+        <v>94.72709999999999</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>66.7379</v>
+        <v>73.7234</v>
       </c>
       <c r="C97" t="n">
-        <v>53.4169</v>
+        <v>53.3785</v>
       </c>
       <c r="D97" t="n">
-        <v>145.847</v>
+        <v>143.99</v>
       </c>
       <c r="E97" t="n">
-        <v>36.3706</v>
+        <v>35.3249</v>
       </c>
       <c r="F97" t="n">
-        <v>95.3176</v>
+        <v>94.42140000000001</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>66.88249999999999</v>
+        <v>73.3103</v>
       </c>
       <c r="C98" t="n">
-        <v>53.0484</v>
+        <v>52.9298</v>
       </c>
       <c r="D98" t="n">
-        <v>145.878</v>
+        <v>145.123</v>
       </c>
       <c r="E98" t="n">
-        <v>34.892</v>
+        <v>34.3331</v>
       </c>
       <c r="F98" t="n">
-        <v>94.22020000000001</v>
+        <v>93.2064</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>65.53879999999999</v>
+        <v>72.1743</v>
       </c>
       <c r="C99" t="n">
-        <v>52.7723</v>
+        <v>52.7544</v>
       </c>
       <c r="D99" t="n">
-        <v>146.436</v>
+        <v>144.668</v>
       </c>
       <c r="E99" t="n">
-        <v>33.8692</v>
+        <v>33.743</v>
       </c>
       <c r="F99" t="n">
-        <v>92.2611</v>
+        <v>92.5149</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>65.07170000000001</v>
+        <v>71.488</v>
       </c>
       <c r="C100" t="n">
-        <v>52.5236</v>
+        <v>52.5626</v>
       </c>
       <c r="D100" t="n">
-        <v>145.952</v>
+        <v>145.092</v>
       </c>
       <c r="E100" t="n">
-        <v>32.6326</v>
+        <v>32.7761</v>
       </c>
       <c r="F100" t="n">
-        <v>91.42910000000001</v>
+        <v>91.2996</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>63.3807</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="C101" t="n">
-        <v>53.1103</v>
+        <v>52.8128</v>
       </c>
       <c r="D101" t="n">
-        <v>146.185</v>
+        <v>145.004</v>
       </c>
       <c r="E101" t="n">
-        <v>32.4234</v>
+        <v>31.478</v>
       </c>
       <c r="F101" t="n">
-        <v>91.01949999999999</v>
+        <v>90.4487</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>70.0748</v>
+        <v>66.21720000000001</v>
       </c>
       <c r="C102" t="n">
-        <v>52.4218</v>
+        <v>52.3644</v>
       </c>
       <c r="D102" t="n">
-        <v>147.107</v>
+        <v>145.562</v>
       </c>
       <c r="E102" t="n">
-        <v>31.455</v>
+        <v>31.3911</v>
       </c>
       <c r="F102" t="n">
-        <v>90.51519999999999</v>
+        <v>88.75149999999999</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>69.3507</v>
+        <v>65.8027</v>
       </c>
       <c r="C103" t="n">
-        <v>52.659</v>
+        <v>52.4892</v>
       </c>
       <c r="D103" t="n">
-        <v>147.796</v>
+        <v>146.071</v>
       </c>
       <c r="E103" t="n">
-        <v>31.1857</v>
+        <v>30.5424</v>
       </c>
       <c r="F103" t="n">
-        <v>89.23860000000001</v>
+        <v>88.7414</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>68.6695</v>
+        <v>64.8738</v>
       </c>
       <c r="C104" t="n">
-        <v>52.259</v>
+        <v>52.1091</v>
       </c>
       <c r="D104" t="n">
-        <v>148.624</v>
+        <v>147.579</v>
       </c>
       <c r="E104" t="n">
-        <v>30.4146</v>
+        <v>29.8645</v>
       </c>
       <c r="F104" t="n">
-        <v>88.1189</v>
+        <v>87.8151</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>68.1892</v>
+        <v>64.69459999999999</v>
       </c>
       <c r="C105" t="n">
-        <v>52.025</v>
+        <v>52.4153</v>
       </c>
       <c r="D105" t="n">
-        <v>150.267</v>
+        <v>148.801</v>
       </c>
       <c r="E105" t="n">
-        <v>29.9307</v>
+        <v>29.3629</v>
       </c>
       <c r="F105" t="n">
-        <v>87.3485</v>
+        <v>86.9661</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>66.559</v>
+        <v>64.0097</v>
       </c>
       <c r="C106" t="n">
-        <v>52.4884</v>
+        <v>52.1873</v>
       </c>
       <c r="D106" t="n">
-        <v>151.517</v>
+        <v>149.649</v>
       </c>
       <c r="E106" t="n">
-        <v>29.4233</v>
+        <v>28.9417</v>
       </c>
       <c r="F106" t="n">
-        <v>86.7899</v>
+        <v>86.6347</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>66.14449999999999</v>
+        <v>63.3637</v>
       </c>
       <c r="C107" t="n">
-        <v>52.087</v>
+        <v>51.9431</v>
       </c>
       <c r="D107" t="n">
-        <v>194.545</v>
+        <v>194.132</v>
       </c>
       <c r="E107" t="n">
-        <v>43.0602</v>
+        <v>41.9858</v>
       </c>
       <c r="F107" t="n">
-        <v>120.121</v>
+        <v>120.867</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>65.56019999999999</v>
+        <v>62.9879</v>
       </c>
       <c r="C108" t="n">
-        <v>64.2161</v>
+        <v>63.6709</v>
       </c>
       <c r="D108" t="n">
-        <v>193.138</v>
+        <v>191.937</v>
       </c>
       <c r="E108" t="n">
-        <v>42.517</v>
+        <v>41.8155</v>
       </c>
       <c r="F108" t="n">
-        <v>120.552</v>
+        <v>120.58</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>62.0667</v>
+        <v>63.9723</v>
       </c>
       <c r="C109" t="n">
-        <v>64.39530000000001</v>
+        <v>63.7745</v>
       </c>
       <c r="D109" t="n">
-        <v>191.95</v>
+        <v>190.353</v>
       </c>
       <c r="E109" t="n">
-        <v>41.0397</v>
+        <v>40.0904</v>
       </c>
       <c r="F109" t="n">
-        <v>118.936</v>
+        <v>118.482</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>84.9028</v>
+        <v>84.69</v>
       </c>
       <c r="C110" t="n">
-        <v>64.2482</v>
+        <v>63.6313</v>
       </c>
       <c r="D110" t="n">
-        <v>190.648</v>
+        <v>189.109</v>
       </c>
       <c r="E110" t="n">
-        <v>40.8824</v>
+        <v>39.705</v>
       </c>
       <c r="F110" t="n">
-        <v>118.084</v>
+        <v>117.773</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>83.97669999999999</v>
+        <v>83.30119999999999</v>
       </c>
       <c r="C111" t="n">
-        <v>64.4862</v>
+        <v>63.849</v>
       </c>
       <c r="D111" t="n">
-        <v>190.14</v>
+        <v>187.899</v>
       </c>
       <c r="E111" t="n">
-        <v>39.083</v>
+        <v>38.8372</v>
       </c>
       <c r="F111" t="n">
-        <v>117.814</v>
+        <v>116.939</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>84.0266</v>
+        <v>81.6495</v>
       </c>
       <c r="C112" t="n">
-        <v>63.7813</v>
+        <v>64.5896</v>
       </c>
       <c r="D112" t="n">
-        <v>188.756</v>
+        <v>187.695</v>
       </c>
       <c r="E112" t="n">
-        <v>38.6594</v>
+        <v>38.6152</v>
       </c>
       <c r="F112" t="n">
-        <v>117.245</v>
+        <v>116.457</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>81.6208</v>
+        <v>81.16679999999999</v>
       </c>
       <c r="C113" t="n">
-        <v>64.3796</v>
+        <v>63.9047</v>
       </c>
       <c r="D113" t="n">
-        <v>188.383</v>
+        <v>186.673</v>
       </c>
       <c r="E113" t="n">
-        <v>38.2056</v>
+        <v>37.2138</v>
       </c>
       <c r="F113" t="n">
-        <v>116.055</v>
+        <v>116.781</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>80.56910000000001</v>
+        <v>84.0668</v>
       </c>
       <c r="C114" t="n">
-        <v>64.31659999999999</v>
+        <v>63.9939</v>
       </c>
       <c r="D114" t="n">
-        <v>188.341</v>
+        <v>187.135</v>
       </c>
       <c r="E114" t="n">
-        <v>37.594</v>
+        <v>37.0866</v>
       </c>
       <c r="F114" t="n">
-        <v>115.683</v>
+        <v>115.574</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>80.31740000000001</v>
+        <v>81.9982</v>
       </c>
       <c r="C115" t="n">
-        <v>64.1554</v>
+        <v>64.22450000000001</v>
       </c>
       <c r="D115" t="n">
-        <v>188.245</v>
+        <v>186.976</v>
       </c>
       <c r="E115" t="n">
-        <v>36.8603</v>
+        <v>36.6621</v>
       </c>
       <c r="F115" t="n">
-        <v>115.535</v>
+        <v>115.399</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>79.7307</v>
+        <v>82.61969999999999</v>
       </c>
       <c r="C116" t="n">
-        <v>64.1571</v>
+        <v>64.01819999999999</v>
       </c>
       <c r="D116" t="n">
-        <v>188.112</v>
+        <v>186.791</v>
       </c>
       <c r="E116" t="n">
-        <v>36.822</v>
+        <v>35.4346</v>
       </c>
       <c r="F116" t="n">
-        <v>114.864</v>
+        <v>114.929</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>80.11190000000001</v>
+        <v>79.4075</v>
       </c>
       <c r="C117" t="n">
-        <v>64.3091</v>
+        <v>63.716</v>
       </c>
       <c r="D117" t="n">
-        <v>187.976</v>
+        <v>187.499</v>
       </c>
       <c r="E117" t="n">
-        <v>35.522</v>
+        <v>35.4288</v>
       </c>
       <c r="F117" t="n">
-        <v>114.437</v>
+        <v>114.901</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>79.1311</v>
+        <v>78.3984</v>
       </c>
       <c r="C118" t="n">
-        <v>64.3413</v>
+        <v>63.5948</v>
       </c>
       <c r="D118" t="n">
-        <v>188.541</v>
+        <v>187.526</v>
       </c>
       <c r="E118" t="n">
-        <v>35.3396</v>
+        <v>34.6976</v>
       </c>
       <c r="F118" t="n">
-        <v>113.659</v>
+        <v>113.895</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>77.44799999999999</v>
+        <v>77.5292</v>
       </c>
       <c r="C119" t="n">
-        <v>64.1641</v>
+        <v>63.9466</v>
       </c>
       <c r="D119" t="n">
-        <v>189.159</v>
+        <v>188.439</v>
       </c>
       <c r="E119" t="n">
-        <v>34.5147</v>
+        <v>34.1104</v>
       </c>
       <c r="F119" t="n">
-        <v>113.369</v>
+        <v>114.292</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>74.8683</v>
+        <v>76.1966</v>
       </c>
       <c r="C120" t="n">
-        <v>64.268</v>
+        <v>64.3561</v>
       </c>
       <c r="D120" t="n">
-        <v>190.132</v>
+        <v>190.06</v>
       </c>
       <c r="E120" t="n">
-        <v>34.1365</v>
+        <v>33.8264</v>
       </c>
       <c r="F120" t="n">
-        <v>113.212</v>
+        <v>113.495</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>73.7677</v>
+        <v>77.7813</v>
       </c>
       <c r="C121" t="n">
-        <v>63.7788</v>
+        <v>63.1098</v>
       </c>
       <c r="D121" t="n">
-        <v>238.224</v>
+        <v>236.726</v>
       </c>
       <c r="E121" t="n">
-        <v>48.5088</v>
+        <v>46.8088</v>
       </c>
       <c r="F121" t="n">
-        <v>148.786</v>
+        <v>148.56</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>72.8954</v>
+        <v>76.7754</v>
       </c>
       <c r="C122" t="n">
-        <v>75.3475</v>
+        <v>75.5705</v>
       </c>
       <c r="D122" t="n">
-        <v>235.378</v>
+        <v>233.566</v>
       </c>
       <c r="E122" t="n">
-        <v>46.7471</v>
+        <v>47.3845</v>
       </c>
       <c r="F122" t="n">
-        <v>147.351</v>
+        <v>147.271</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>76.7811</v>
+        <v>74.7307</v>
       </c>
       <c r="C123" t="n">
-        <v>75.3865</v>
+        <v>75.691</v>
       </c>
       <c r="D123" t="n">
-        <v>233.082</v>
+        <v>232.065</v>
       </c>
       <c r="E123" t="n">
-        <v>47.5512</v>
+        <v>46.3152</v>
       </c>
       <c r="F123" t="n">
-        <v>146.878</v>
+        <v>146.387</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>96.9395</v>
+        <v>98.1545</v>
       </c>
       <c r="C124" t="n">
-        <v>75.7324</v>
+        <v>75.47029999999999</v>
       </c>
       <c r="D124" t="n">
-        <v>230.609</v>
+        <v>230.254</v>
       </c>
       <c r="E124" t="n">
-        <v>46.7212</v>
+        <v>45.4366</v>
       </c>
       <c r="F124" t="n">
-        <v>146.045</v>
+        <v>146.024</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>96.2718</v>
+        <v>96.9071</v>
       </c>
       <c r="C125" t="n">
-        <v>76.1661</v>
+        <v>76.16459999999999</v>
       </c>
       <c r="D125" t="n">
-        <v>229.42</v>
+        <v>228.108</v>
       </c>
       <c r="E125" t="n">
-        <v>46.9679</v>
+        <v>45.2978</v>
       </c>
       <c r="F125" t="n">
-        <v>144.958</v>
+        <v>146.031</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>94.3857</v>
+        <v>94.2921</v>
       </c>
       <c r="C126" t="n">
-        <v>76.7159</v>
+        <v>76.14</v>
       </c>
       <c r="D126" t="n">
-        <v>227.539</v>
+        <v>226.221</v>
       </c>
       <c r="E126" t="n">
-        <v>45.9786</v>
+        <v>44.9102</v>
       </c>
       <c r="F126" t="n">
-        <v>144.824</v>
+        <v>144.608</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>93.541</v>
+        <v>93.5557</v>
       </c>
       <c r="C127" t="n">
-        <v>76.5123</v>
+        <v>76.39700000000001</v>
       </c>
       <c r="D127" t="n">
-        <v>226.055</v>
+        <v>225.089</v>
       </c>
       <c r="E127" t="n">
-        <v>45.2872</v>
+        <v>44.8065</v>
       </c>
       <c r="F127" t="n">
-        <v>144.199</v>
+        <v>143.586</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>93.687</v>
+        <v>96.09910000000001</v>
       </c>
       <c r="C128" t="n">
-        <v>77.0338</v>
+        <v>76.5373</v>
       </c>
       <c r="D128" t="n">
-        <v>225.088</v>
+        <v>223.252</v>
       </c>
       <c r="E128" t="n">
-        <v>43.9897</v>
+        <v>44.4401</v>
       </c>
       <c r="F128" t="n">
-        <v>143.661</v>
+        <v>143.205</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>94.2718</v>
+        <v>95.08920000000001</v>
       </c>
       <c r="C129" t="n">
-        <v>77.01609999999999</v>
+        <v>76.85769999999999</v>
       </c>
       <c r="D129" t="n">
-        <v>224.744</v>
+        <v>222.403</v>
       </c>
       <c r="E129" t="n">
-        <v>43.6468</v>
+        <v>43.1643</v>
       </c>
       <c r="F129" t="n">
-        <v>143.109</v>
+        <v>142.755</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>93.90309999999999</v>
+        <v>91.48220000000001</v>
       </c>
       <c r="C130" t="n">
-        <v>76.9265</v>
+        <v>77.0795</v>
       </c>
       <c r="D130" t="n">
-        <v>222.822</v>
+        <v>222.205</v>
       </c>
       <c r="E130" t="n">
-        <v>43.4818</v>
+        <v>43.1553</v>
       </c>
       <c r="F130" t="n">
-        <v>142.304</v>
+        <v>142.104</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>92.8747</v>
+        <v>90.7146</v>
       </c>
       <c r="C131" t="n">
-        <v>77.6309</v>
+        <v>77.1032</v>
       </c>
       <c r="D131" t="n">
-        <v>222.664</v>
+        <v>221.089</v>
       </c>
       <c r="E131" t="n">
-        <v>43.4397</v>
+        <v>42.4219</v>
       </c>
       <c r="F131" t="n">
-        <v>141.954</v>
+        <v>142.025</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>92.6544</v>
+        <v>94.07389999999999</v>
       </c>
       <c r="C132" t="n">
-        <v>77.7667</v>
+        <v>77.34739999999999</v>
       </c>
       <c r="D132" t="n">
-        <v>222.463</v>
+        <v>221.868</v>
       </c>
       <c r="E132" t="n">
-        <v>42.9135</v>
+        <v>42.3744</v>
       </c>
       <c r="F132" t="n">
-        <v>141.896</v>
+        <v>141.295</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>93.0245</v>
+        <v>91.5326</v>
       </c>
       <c r="C133" t="n">
-        <v>77.5412</v>
+        <v>77.58669999999999</v>
       </c>
       <c r="D133" t="n">
-        <v>223.072</v>
+        <v>221.887</v>
       </c>
       <c r="E133" t="n">
-        <v>42.8814</v>
+        <v>42.2658</v>
       </c>
       <c r="F133" t="n">
-        <v>141.34</v>
+        <v>140.888</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>93.1053</v>
+        <v>92.1648</v>
       </c>
       <c r="C134" t="n">
-        <v>77.8638</v>
+        <v>77.5776</v>
       </c>
       <c r="D134" t="n">
-        <v>223.592</v>
+        <v>222.173</v>
       </c>
       <c r="E134" t="n">
-        <v>42.4836</v>
+        <v>41.7989</v>
       </c>
       <c r="F134" t="n">
-        <v>141.276</v>
+        <v>141.032</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>88.8651</v>
+        <v>92.3626</v>
       </c>
       <c r="C135" t="n">
-        <v>77.9342</v>
+        <v>77.8623</v>
       </c>
       <c r="D135" t="n">
-        <v>272.855</v>
+        <v>271.659</v>
       </c>
       <c r="E135" t="n">
-        <v>56.5892</v>
+        <v>55.5401</v>
       </c>
       <c r="F135" t="n">
-        <v>177.319</v>
+        <v>176.92</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>89.9194</v>
+        <v>92.4153</v>
       </c>
       <c r="C136" t="n">
-        <v>90.7938</v>
+        <v>90.0701</v>
       </c>
       <c r="D136" t="n">
-        <v>269.246</v>
+        <v>268.266</v>
       </c>
       <c r="E136" t="n">
-        <v>55.9317</v>
+        <v>55.2642</v>
       </c>
       <c r="F136" t="n">
-        <v>175.656</v>
+        <v>175.475</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>91.39230000000001</v>
+        <v>90.67100000000001</v>
       </c>
       <c r="C137" t="n">
-        <v>90.52549999999999</v>
+        <v>90.37009999999999</v>
       </c>
       <c r="D137" t="n">
-        <v>265.959</v>
+        <v>264.606</v>
       </c>
       <c r="E137" t="n">
-        <v>56.1324</v>
+        <v>55.0696</v>
       </c>
       <c r="F137" t="n">
-        <v>174.068</v>
+        <v>173.891</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>108.978</v>
+        <v>110.848</v>
       </c>
       <c r="C138" t="n">
-        <v>91.1185</v>
+        <v>90.7859</v>
       </c>
       <c r="D138" t="n">
-        <v>262.763</v>
+        <v>261.455</v>
       </c>
       <c r="E138" t="n">
-        <v>55.4183</v>
+        <v>54.6606</v>
       </c>
       <c r="F138" t="n">
-        <v>172.822</v>
+        <v>172.338</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>111.881</v>
+        <v>109.316</v>
       </c>
       <c r="C139" t="n">
-        <v>91.54510000000001</v>
+        <v>90.99379999999999</v>
       </c>
       <c r="D139" t="n">
-        <v>260.087</v>
+        <v>259.546</v>
       </c>
       <c r="E139" t="n">
-        <v>55.9339</v>
+        <v>54.9712</v>
       </c>
       <c r="F139" t="n">
-        <v>171.654</v>
+        <v>171.235</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>108.222</v>
+        <v>108.038</v>
       </c>
       <c r="C140" t="n">
-        <v>91.8719</v>
+        <v>91.3579</v>
       </c>
       <c r="D140" t="n">
-        <v>257.511</v>
+        <v>256.554</v>
       </c>
       <c r="E140" t="n">
-        <v>55.4582</v>
+        <v>54.8644</v>
       </c>
       <c r="F140" t="n">
-        <v>170.497</v>
+        <v>170.185</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>111.021</v>
+        <v>108.971</v>
       </c>
       <c r="C141" t="n">
-        <v>92.1395</v>
+        <v>92.15130000000001</v>
       </c>
       <c r="D141" t="n">
-        <v>255.614</v>
+        <v>254.728</v>
       </c>
       <c r="E141" t="n">
-        <v>55.2059</v>
+        <v>54.5381</v>
       </c>
       <c r="F141" t="n">
-        <v>170.152</v>
+        <v>169.352</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>108.515</v>
+        <v>109.286</v>
       </c>
       <c r="C142" t="n">
-        <v>92.40689999999999</v>
+        <v>92.0069</v>
       </c>
       <c r="D142" t="n">
-        <v>254.069</v>
+        <v>253.144</v>
       </c>
       <c r="E142" t="n">
-        <v>54.8279</v>
+        <v>54.569</v>
       </c>
       <c r="F142" t="n">
-        <v>168.765</v>
+        <v>168.299</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>109.918</v>
+        <v>107.235</v>
       </c>
       <c r="C143" t="n">
-        <v>92.6165</v>
+        <v>92.30329999999999</v>
       </c>
       <c r="D143" t="n">
-        <v>252.665</v>
+        <v>251.348</v>
       </c>
       <c r="E143" t="n">
-        <v>54.8533</v>
+        <v>54.3192</v>
       </c>
       <c r="F143" t="n">
-        <v>167.968</v>
+        <v>167.315</v>
       </c>
     </row>
   </sheetData>

--- a/vs-x64/Running insertion.xlsx
+++ b/vs-x64/Running insertion.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>24.1897</v>
+        <v>23.7256</v>
       </c>
       <c r="C2" t="n">
-        <v>31.1853</v>
+        <v>31.1953</v>
       </c>
       <c r="D2" t="n">
-        <v>59.0451</v>
+        <v>59.0636</v>
       </c>
       <c r="E2" t="n">
-        <v>15.0727</v>
+        <v>15.0458</v>
       </c>
       <c r="F2" t="n">
-        <v>51.4417</v>
+        <v>58.3808</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>22.7125</v>
+        <v>23.1683</v>
       </c>
       <c r="C3" t="n">
-        <v>30.7151</v>
+        <v>30.7307</v>
       </c>
       <c r="D3" t="n">
-        <v>58.491</v>
+        <v>58.8885</v>
       </c>
       <c r="E3" t="n">
-        <v>14.6297</v>
+        <v>14.5758</v>
       </c>
       <c r="F3" t="n">
-        <v>50.6549</v>
+        <v>57.6481</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>22.6819</v>
+        <v>22.2554</v>
       </c>
       <c r="C4" t="n">
-        <v>30.3007</v>
+        <v>30.2423</v>
       </c>
       <c r="D4" t="n">
-        <v>57.9995</v>
+        <v>58.2569</v>
       </c>
       <c r="E4" t="n">
-        <v>14.2933</v>
+        <v>14.2421</v>
       </c>
       <c r="F4" t="n">
-        <v>50.407</v>
+        <v>57.4084</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>22.1039</v>
+        <v>22.0105</v>
       </c>
       <c r="C5" t="n">
-        <v>29.8982</v>
+        <v>29.899</v>
       </c>
       <c r="D5" t="n">
-        <v>57.5385</v>
+        <v>57.6999</v>
       </c>
       <c r="E5" t="n">
-        <v>13.9826</v>
+        <v>14.0118</v>
       </c>
       <c r="F5" t="n">
-        <v>50.0167</v>
+        <v>57.0324</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>22.1417</v>
+        <v>21.6726</v>
       </c>
       <c r="C6" t="n">
-        <v>29.5168</v>
+        <v>29.5354</v>
       </c>
       <c r="D6" t="n">
-        <v>56.9192</v>
+        <v>57.0853</v>
       </c>
       <c r="E6" t="n">
-        <v>13.7237</v>
+        <v>13.7115</v>
       </c>
       <c r="F6" t="n">
-        <v>49.6196</v>
+        <v>56.8568</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>21.6548</v>
+        <v>21.3237</v>
       </c>
       <c r="C7" t="n">
-        <v>29.1779</v>
+        <v>29.1883</v>
       </c>
       <c r="D7" t="n">
-        <v>68.2184</v>
+        <v>68.6844</v>
       </c>
       <c r="E7" t="n">
-        <v>20.6423</v>
+        <v>20.682</v>
       </c>
       <c r="F7" t="n">
-        <v>56.1001</v>
+        <v>63.1626</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>21.5864</v>
+        <v>21.1868</v>
       </c>
       <c r="C8" t="n">
-        <v>35.9227</v>
+        <v>35.916</v>
       </c>
       <c r="D8" t="n">
-        <v>67.2996</v>
+        <v>67.264</v>
       </c>
       <c r="E8" t="n">
-        <v>19.9373</v>
+        <v>19.9946</v>
       </c>
       <c r="F8" t="n">
-        <v>55.878</v>
+        <v>63.3625</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>21.1762</v>
+        <v>21.188</v>
       </c>
       <c r="C9" t="n">
-        <v>35.2348</v>
+        <v>35.3177</v>
       </c>
       <c r="D9" t="n">
-        <v>66.0121</v>
+        <v>66.1561</v>
       </c>
       <c r="E9" t="n">
-        <v>19.2717</v>
+        <v>19.3303</v>
       </c>
       <c r="F9" t="n">
-        <v>54.9724</v>
+        <v>62.1964</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>27.4703</v>
+        <v>27.6193</v>
       </c>
       <c r="C10" t="n">
-        <v>34.6112</v>
+        <v>34.7212</v>
       </c>
       <c r="D10" t="n">
-        <v>64.7612</v>
+        <v>65.0262</v>
       </c>
       <c r="E10" t="n">
-        <v>18.6217</v>
+        <v>18.6817</v>
       </c>
       <c r="F10" t="n">
-        <v>54.3276</v>
+        <v>61.2839</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>26.9754</v>
+        <v>26.9277</v>
       </c>
       <c r="C11" t="n">
-        <v>34.0048</v>
+        <v>34.0845</v>
       </c>
       <c r="D11" t="n">
-        <v>63.9908</v>
+        <v>64.47280000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>18.0649</v>
+        <v>18.1158</v>
       </c>
       <c r="F11" t="n">
-        <v>53.8141</v>
+        <v>61.2439</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>26.4235</v>
+        <v>26.277</v>
       </c>
       <c r="C12" t="n">
-        <v>33.4763</v>
+        <v>33.5399</v>
       </c>
       <c r="D12" t="n">
-        <v>63.1554</v>
+        <v>63.1487</v>
       </c>
       <c r="E12" t="n">
-        <v>17.5124</v>
+        <v>17.5429</v>
       </c>
       <c r="F12" t="n">
-        <v>53.0128</v>
+        <v>60.1213</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>25.6945</v>
+        <v>26.1671</v>
       </c>
       <c r="C13" t="n">
-        <v>32.9547</v>
+        <v>33.0402</v>
       </c>
       <c r="D13" t="n">
-        <v>62.4811</v>
+        <v>62.4526</v>
       </c>
       <c r="E13" t="n">
-        <v>16.9892</v>
+        <v>17.0074</v>
       </c>
       <c r="F13" t="n">
-        <v>52.3646</v>
+        <v>59.571</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>25.3856</v>
+        <v>25.456</v>
       </c>
       <c r="C14" t="n">
-        <v>32.4578</v>
+        <v>32.5189</v>
       </c>
       <c r="D14" t="n">
-        <v>61.6994</v>
+        <v>62.1036</v>
       </c>
       <c r="E14" t="n">
-        <v>16.4902</v>
+        <v>16.486</v>
       </c>
       <c r="F14" t="n">
-        <v>51.878</v>
+        <v>59.1623</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>24.7117</v>
+        <v>24.8806</v>
       </c>
       <c r="C15" t="n">
-        <v>31.962</v>
+        <v>32.0149</v>
       </c>
       <c r="D15" t="n">
-        <v>61.1511</v>
+        <v>61.1951</v>
       </c>
       <c r="E15" t="n">
-        <v>16.0185</v>
+        <v>16.0102</v>
       </c>
       <c r="F15" t="n">
-        <v>51.2434</v>
+        <v>58.3988</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>24.0761</v>
+        <v>24.5073</v>
       </c>
       <c r="C16" t="n">
-        <v>31.4754</v>
+        <v>31.5379</v>
       </c>
       <c r="D16" t="n">
-        <v>60.7203</v>
+        <v>61.027</v>
       </c>
       <c r="E16" t="n">
-        <v>15.5762</v>
+        <v>15.6115</v>
       </c>
       <c r="F16" t="n">
-        <v>51.0111</v>
+        <v>58.4448</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>23.6176</v>
+        <v>24.2656</v>
       </c>
       <c r="C17" t="n">
-        <v>31.0447</v>
+        <v>31.0875</v>
       </c>
       <c r="D17" t="n">
-        <v>60.1468</v>
+        <v>60.1909</v>
       </c>
       <c r="E17" t="n">
-        <v>15.1684</v>
+        <v>15.2072</v>
       </c>
       <c r="F17" t="n">
-        <v>50.2694</v>
+        <v>57.5992</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>23.319</v>
+        <v>23.4978</v>
       </c>
       <c r="C18" t="n">
-        <v>30.6308</v>
+        <v>30.6767</v>
       </c>
       <c r="D18" t="n">
-        <v>59.5052</v>
+        <v>60.0816</v>
       </c>
       <c r="E18" t="n">
-        <v>14.8546</v>
+        <v>14.8687</v>
       </c>
       <c r="F18" t="n">
-        <v>50.0076</v>
+        <v>57.5139</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>22.9859</v>
+        <v>23.2338</v>
       </c>
       <c r="C19" t="n">
-        <v>30.2693</v>
+        <v>30.3267</v>
       </c>
       <c r="D19" t="n">
-        <v>59.0864</v>
+        <v>59.4736</v>
       </c>
       <c r="E19" t="n">
-        <v>14.4948</v>
+        <v>14.5449</v>
       </c>
       <c r="F19" t="n">
-        <v>49.4947</v>
+        <v>56.8156</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>22.3017</v>
+        <v>22.5717</v>
       </c>
       <c r="C20" t="n">
-        <v>29.8848</v>
+        <v>29.8996</v>
       </c>
       <c r="D20" t="n">
-        <v>59.282</v>
+        <v>59.3009</v>
       </c>
       <c r="E20" t="n">
-        <v>14.2797</v>
+        <v>14.3173</v>
       </c>
       <c r="F20" t="n">
-        <v>49.3864</v>
+        <v>56.7374</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>21.937</v>
+        <v>22.4276</v>
       </c>
       <c r="C21" t="n">
-        <v>29.5163</v>
+        <v>29.5504</v>
       </c>
       <c r="D21" t="n">
-        <v>71.51730000000001</v>
+        <v>72.05670000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>27.0507</v>
+        <v>27.1103</v>
       </c>
       <c r="F21" t="n">
-        <v>56.6614</v>
+        <v>64.5498</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>21.8696</v>
+        <v>22.469</v>
       </c>
       <c r="C22" t="n">
-        <v>40.8439</v>
+        <v>40.907</v>
       </c>
       <c r="D22" t="n">
-        <v>70.4585</v>
+        <v>70.8643</v>
       </c>
       <c r="E22" t="n">
-        <v>26.1314</v>
+        <v>26.1062</v>
       </c>
       <c r="F22" t="n">
-        <v>55.7667</v>
+        <v>63.7311</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>22.1221</v>
+        <v>21.9586</v>
       </c>
       <c r="C23" t="n">
-        <v>39.9233</v>
+        <v>40.0342</v>
       </c>
       <c r="D23" t="n">
-        <v>69.21510000000001</v>
+        <v>69.44759999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>25.2291</v>
+        <v>25.3187</v>
       </c>
       <c r="F23" t="n">
-        <v>55.2037</v>
+        <v>62.694</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>44.1733</v>
+        <v>38.4282</v>
       </c>
       <c r="C24" t="n">
-        <v>39.1629</v>
+        <v>39.2434</v>
       </c>
       <c r="D24" t="n">
-        <v>68.45820000000001</v>
+        <v>68.93040000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>24.3177</v>
+        <v>24.3677</v>
       </c>
       <c r="F24" t="n">
-        <v>54.5364</v>
+        <v>62.0733</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>40.2106</v>
+        <v>40.5567</v>
       </c>
       <c r="C25" t="n">
-        <v>38.4843</v>
+        <v>38.5985</v>
       </c>
       <c r="D25" t="n">
-        <v>67.4141</v>
+        <v>68.1631</v>
       </c>
       <c r="E25" t="n">
-        <v>23.5266</v>
+        <v>23.506</v>
       </c>
       <c r="F25" t="n">
-        <v>54.0419</v>
+        <v>63.3757</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>39.6454</v>
+        <v>39.0952</v>
       </c>
       <c r="C26" t="n">
-        <v>37.7747</v>
+        <v>37.7441</v>
       </c>
       <c r="D26" t="n">
-        <v>66.6121</v>
+        <v>67.2449</v>
       </c>
       <c r="E26" t="n">
-        <v>22.6982</v>
+        <v>22.75</v>
       </c>
       <c r="F26" t="n">
-        <v>53.0801</v>
+        <v>60.9892</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>40.265</v>
+        <v>34.3439</v>
       </c>
       <c r="C27" t="n">
-        <v>36.918</v>
+        <v>37.0282</v>
       </c>
       <c r="D27" t="n">
-        <v>65.4864</v>
+        <v>66.1764</v>
       </c>
       <c r="E27" t="n">
-        <v>21.968</v>
+        <v>21.9861</v>
       </c>
       <c r="F27" t="n">
-        <v>50.7859</v>
+        <v>59.9115</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>37.2232</v>
+        <v>33.1346</v>
       </c>
       <c r="C28" t="n">
-        <v>36.4046</v>
+        <v>36.2884</v>
       </c>
       <c r="D28" t="n">
-        <v>64.5364</v>
+        <v>65.7229</v>
       </c>
       <c r="E28" t="n">
-        <v>21.2688</v>
+        <v>21.2344</v>
       </c>
       <c r="F28" t="n">
-        <v>50.4386</v>
+        <v>59.6773</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>36.1192</v>
+        <v>32.6514</v>
       </c>
       <c r="C29" t="n">
-        <v>35.6357</v>
+        <v>35.7161</v>
       </c>
       <c r="D29" t="n">
-        <v>64.1568</v>
+        <v>64.9205</v>
       </c>
       <c r="E29" t="n">
-        <v>20.6233</v>
+        <v>20.6977</v>
       </c>
       <c r="F29" t="n">
-        <v>49.9758</v>
+        <v>59.7181</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>37.3076</v>
+        <v>31.5395</v>
       </c>
       <c r="C30" t="n">
-        <v>35.0179</v>
+        <v>35.0275</v>
       </c>
       <c r="D30" t="n">
-        <v>63.5234</v>
+        <v>64.3888</v>
       </c>
       <c r="E30" t="n">
-        <v>19.9674</v>
+        <v>19.97</v>
       </c>
       <c r="F30" t="n">
-        <v>49.3635</v>
+        <v>58.558</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>34.533</v>
+        <v>35.7659</v>
       </c>
       <c r="C31" t="n">
-        <v>34.4094</v>
+        <v>34.4448</v>
       </c>
       <c r="D31" t="n">
-        <v>62.7531</v>
+        <v>63.8605</v>
       </c>
       <c r="E31" t="n">
-        <v>19.3859</v>
+        <v>19.4001</v>
       </c>
       <c r="F31" t="n">
-        <v>49.0387</v>
+        <v>58.4482</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>31.7418</v>
+        <v>34.6568</v>
       </c>
       <c r="C32" t="n">
-        <v>33.9049</v>
+        <v>33.8561</v>
       </c>
       <c r="D32" t="n">
-        <v>62.3972</v>
+        <v>62.998</v>
       </c>
       <c r="E32" t="n">
-        <v>18.8364</v>
+        <v>18.8346</v>
       </c>
       <c r="F32" t="n">
-        <v>48.4209</v>
+        <v>57.1557</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>32.7961</v>
+        <v>33.7412</v>
       </c>
       <c r="C33" t="n">
-        <v>33.387</v>
+        <v>33.3133</v>
       </c>
       <c r="D33" t="n">
-        <v>62.278</v>
+        <v>62.4117</v>
       </c>
       <c r="E33" t="n">
-        <v>18.3914</v>
+        <v>18.3523</v>
       </c>
       <c r="F33" t="n">
-        <v>48.2933</v>
+        <v>56.8192</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>31.9265</v>
+        <v>28.462</v>
       </c>
       <c r="C34" t="n">
-        <v>32.7388</v>
+        <v>32.7529</v>
       </c>
       <c r="D34" t="n">
-        <v>61.8992</v>
+        <v>61.8171</v>
       </c>
       <c r="E34" t="n">
-        <v>17.9734</v>
+        <v>17.9594</v>
       </c>
       <c r="F34" t="n">
-        <v>48.0855</v>
+        <v>56.619</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>30.981</v>
+        <v>27.9691</v>
       </c>
       <c r="C35" t="n">
-        <v>32.3369</v>
+        <v>32.3324</v>
       </c>
       <c r="D35" t="n">
-        <v>75.7659</v>
+        <v>75.6972</v>
       </c>
       <c r="E35" t="n">
-        <v>31.2781</v>
+        <v>31.0225</v>
       </c>
       <c r="F35" t="n">
-        <v>58.2759</v>
+        <v>66.4933</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>32.0132</v>
+        <v>31.6494</v>
       </c>
       <c r="C36" t="n">
-        <v>31.9446</v>
+        <v>31.8315</v>
       </c>
       <c r="D36" t="n">
-        <v>74.53019999999999</v>
+        <v>74.4995</v>
       </c>
       <c r="E36" t="n">
-        <v>30.116</v>
+        <v>30.1937</v>
       </c>
       <c r="F36" t="n">
-        <v>57.6248</v>
+        <v>65.2046</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>31.1712</v>
+        <v>27.194</v>
       </c>
       <c r="C37" t="n">
-        <v>42.9498</v>
+        <v>42.8675</v>
       </c>
       <c r="D37" t="n">
-        <v>73.3459</v>
+        <v>73.1863</v>
       </c>
       <c r="E37" t="n">
-        <v>28.9766</v>
+        <v>28.9449</v>
       </c>
       <c r="F37" t="n">
-        <v>56.8653</v>
+        <v>64.3115</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>46.4652</v>
+        <v>45.4751</v>
       </c>
       <c r="C38" t="n">
-        <v>42.0295</v>
+        <v>42.0049</v>
       </c>
       <c r="D38" t="n">
-        <v>72.1383</v>
+        <v>72.09610000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>27.8913</v>
+        <v>27.8537</v>
       </c>
       <c r="F38" t="n">
-        <v>55.8774</v>
+        <v>63.5009</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>44.8094</v>
+        <v>42.1117</v>
       </c>
       <c r="C39" t="n">
-        <v>41.074</v>
+        <v>41.0434</v>
       </c>
       <c r="D39" t="n">
-        <v>71.4986</v>
+        <v>71.6049</v>
       </c>
       <c r="E39" t="n">
-        <v>26.9957</v>
+        <v>26.93</v>
       </c>
       <c r="F39" t="n">
-        <v>55.2483</v>
+        <v>62.9392</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>43.5137</v>
+        <v>43.6472</v>
       </c>
       <c r="C40" t="n">
-        <v>40.2078</v>
+        <v>40.2864</v>
       </c>
       <c r="D40" t="n">
-        <v>70.49679999999999</v>
+        <v>70.02979999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>26.0007</v>
+        <v>26.012</v>
       </c>
       <c r="F40" t="n">
-        <v>54.4353</v>
+        <v>62.1188</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>43.199</v>
+        <v>42.3715</v>
       </c>
       <c r="C41" t="n">
-        <v>39.3561</v>
+        <v>39.3708</v>
       </c>
       <c r="D41" t="n">
-        <v>69.24469999999999</v>
+        <v>68.92789999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>25.2388</v>
+        <v>25.0549</v>
       </c>
       <c r="F41" t="n">
-        <v>53.8554</v>
+        <v>61.4518</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>41.8109</v>
+        <v>41.2942</v>
       </c>
       <c r="C42" t="n">
-        <v>38.6265</v>
+        <v>38.5249</v>
       </c>
       <c r="D42" t="n">
-        <v>68.4126</v>
+        <v>68.2475</v>
       </c>
       <c r="E42" t="n">
-        <v>24.2962</v>
+        <v>24.2298</v>
       </c>
       <c r="F42" t="n">
-        <v>53.3837</v>
+        <v>60.7958</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>39.7595</v>
+        <v>39.9383</v>
       </c>
       <c r="C43" t="n">
-        <v>37.8151</v>
+        <v>37.8091</v>
       </c>
       <c r="D43" t="n">
-        <v>67.8436</v>
+        <v>67.5097</v>
       </c>
       <c r="E43" t="n">
-        <v>23.5365</v>
+        <v>23.479</v>
       </c>
       <c r="F43" t="n">
-        <v>52.71</v>
+        <v>60.3015</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>39.3232</v>
+        <v>39.0514</v>
       </c>
       <c r="C44" t="n">
-        <v>37.07</v>
+        <v>37.0534</v>
       </c>
       <c r="D44" t="n">
-        <v>67.41070000000001</v>
+        <v>66.9552</v>
       </c>
       <c r="E44" t="n">
-        <v>22.8388</v>
+        <v>22.6868</v>
       </c>
       <c r="F44" t="n">
-        <v>52.0174</v>
+        <v>59.6961</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>37.2547</v>
+        <v>37.3482</v>
       </c>
       <c r="C45" t="n">
-        <v>36.3826</v>
+        <v>36.422</v>
       </c>
       <c r="D45" t="n">
-        <v>66.79219999999999</v>
+        <v>66.2595</v>
       </c>
       <c r="E45" t="n">
-        <v>22.04</v>
+        <v>22.1593</v>
       </c>
       <c r="F45" t="n">
-        <v>51.4428</v>
+        <v>59.1561</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>37.0699</v>
+        <v>36.3444</v>
       </c>
       <c r="C46" t="n">
-        <v>35.7112</v>
+        <v>35.903</v>
       </c>
       <c r="D46" t="n">
-        <v>66.2649</v>
+        <v>65.794</v>
       </c>
       <c r="E46" t="n">
-        <v>21.4337</v>
+        <v>21.3672</v>
       </c>
       <c r="F46" t="n">
-        <v>50.9987</v>
+        <v>58.6662</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>35.8395</v>
+        <v>33.5739</v>
       </c>
       <c r="C47" t="n">
-        <v>35.0971</v>
+        <v>35.0561</v>
       </c>
       <c r="D47" t="n">
-        <v>65.6104</v>
+        <v>65.3672</v>
       </c>
       <c r="E47" t="n">
-        <v>20.8749</v>
+        <v>20.7705</v>
       </c>
       <c r="F47" t="n">
-        <v>50.5788</v>
+        <v>58.1065</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>35.1186</v>
+        <v>32.6644</v>
       </c>
       <c r="C48" t="n">
-        <v>34.5021</v>
+        <v>34.4981</v>
       </c>
       <c r="D48" t="n">
-        <v>65.1747</v>
+        <v>66.0081</v>
       </c>
       <c r="E48" t="n">
-        <v>20.4183</v>
+        <v>20.3314</v>
       </c>
       <c r="F48" t="n">
-        <v>50.2482</v>
+        <v>57.9305</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>33.7535</v>
+        <v>33.6926</v>
       </c>
       <c r="C49" t="n">
-        <v>34.0254</v>
+        <v>33.9234</v>
       </c>
       <c r="D49" t="n">
-        <v>64.9269</v>
+        <v>64.4817</v>
       </c>
       <c r="E49" t="n">
-        <v>19.8916</v>
+        <v>19.7612</v>
       </c>
       <c r="F49" t="n">
-        <v>50.0996</v>
+        <v>57.5885</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>32.7532</v>
+        <v>33.0911</v>
       </c>
       <c r="C50" t="n">
-        <v>33.4208</v>
+        <v>33.3551</v>
       </c>
       <c r="D50" t="n">
-        <v>79.6897</v>
+        <v>79.331</v>
       </c>
       <c r="E50" t="n">
-        <v>32.1041</v>
+        <v>32.3991</v>
       </c>
       <c r="F50" t="n">
-        <v>59.6685</v>
+        <v>67.3189</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>32.6381</v>
+        <v>30.5805</v>
       </c>
       <c r="C51" t="n">
-        <v>44.3085</v>
+        <v>44.6063</v>
       </c>
       <c r="D51" t="n">
-        <v>78.59180000000001</v>
+        <v>78.0052</v>
       </c>
       <c r="E51" t="n">
-        <v>30.9569</v>
+        <v>30.8427</v>
       </c>
       <c r="F51" t="n">
-        <v>59.0874</v>
+        <v>66.6643</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>32.1563</v>
+        <v>30.52</v>
       </c>
       <c r="C52" t="n">
-        <v>43.2196</v>
+        <v>43.4516</v>
       </c>
       <c r="D52" t="n">
-        <v>77.1203</v>
+        <v>76.42789999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>29.8613</v>
+        <v>30.0207</v>
       </c>
       <c r="F52" t="n">
-        <v>58.2223</v>
+        <v>65.3379</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>50.8348</v>
+        <v>51.4175</v>
       </c>
       <c r="C53" t="n">
-        <v>42.3329</v>
+        <v>42.5577</v>
       </c>
       <c r="D53" t="n">
-        <v>75.806</v>
+        <v>75.5578</v>
       </c>
       <c r="E53" t="n">
-        <v>29.0524</v>
+        <v>28.9173</v>
       </c>
       <c r="F53" t="n">
-        <v>57.1752</v>
+        <v>64.7418</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>49.235</v>
+        <v>51.2303</v>
       </c>
       <c r="C54" t="n">
-        <v>41.2505</v>
+        <v>41.522</v>
       </c>
       <c r="D54" t="n">
-        <v>74.6187</v>
+        <v>74.27670000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>28.1538</v>
+        <v>27.8449</v>
       </c>
       <c r="F54" t="n">
-        <v>56.4084</v>
+        <v>63.8966</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>47.1442</v>
+        <v>48.8116</v>
       </c>
       <c r="C55" t="n">
-        <v>40.585</v>
+        <v>40.4759</v>
       </c>
       <c r="D55" t="n">
-        <v>75.3416</v>
+        <v>73.0063</v>
       </c>
       <c r="E55" t="n">
-        <v>27.352</v>
+        <v>26.8069</v>
       </c>
       <c r="F55" t="n">
-        <v>55.6077</v>
+        <v>63.2467</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>46.7301</v>
+        <v>48.4814</v>
       </c>
       <c r="C56" t="n">
-        <v>39.5449</v>
+        <v>39.6083</v>
       </c>
       <c r="D56" t="n">
-        <v>72.9495</v>
+        <v>73.8467</v>
       </c>
       <c r="E56" t="n">
-        <v>26.4763</v>
+        <v>26.1346</v>
       </c>
       <c r="F56" t="n">
-        <v>56.8422</v>
+        <v>62.5738</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>44.6557</v>
+        <v>45.5066</v>
       </c>
       <c r="C57" t="n">
-        <v>38.9734</v>
+        <v>38.868</v>
       </c>
       <c r="D57" t="n">
-        <v>72.5288</v>
+        <v>73.96850000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>25.5817</v>
+        <v>25.3088</v>
       </c>
       <c r="F57" t="n">
-        <v>54.432</v>
+        <v>61.6543</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>43.6209</v>
+        <v>45.3256</v>
       </c>
       <c r="C58" t="n">
-        <v>38.2909</v>
+        <v>38.1947</v>
       </c>
       <c r="D58" t="n">
-        <v>71.2405</v>
+        <v>71.68389999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>24.4647</v>
+        <v>24.623</v>
       </c>
       <c r="F58" t="n">
-        <v>53.8601</v>
+        <v>60.9606</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>41.6975</v>
+        <v>44.0711</v>
       </c>
       <c r="C59" t="n">
-        <v>37.6624</v>
+        <v>37.3383</v>
       </c>
       <c r="D59" t="n">
-        <v>70.22620000000001</v>
+        <v>69.6559</v>
       </c>
       <c r="E59" t="n">
-        <v>23.7694</v>
+        <v>24.0392</v>
       </c>
       <c r="F59" t="n">
-        <v>53.2919</v>
+        <v>60.8134</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>41.2835</v>
+        <v>42.9721</v>
       </c>
       <c r="C60" t="n">
-        <v>36.8164</v>
+        <v>36.7006</v>
       </c>
       <c r="D60" t="n">
-        <v>69.5599</v>
+        <v>69.42149999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>23.2569</v>
+        <v>23.1465</v>
       </c>
       <c r="F60" t="n">
-        <v>52.8953</v>
+        <v>59.7746</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>40.0247</v>
+        <v>41.4203</v>
       </c>
       <c r="C61" t="n">
-        <v>35.986</v>
+        <v>36.058</v>
       </c>
       <c r="D61" t="n">
-        <v>69.2603</v>
+        <v>68.864</v>
       </c>
       <c r="E61" t="n">
-        <v>22.6311</v>
+        <v>22.492</v>
       </c>
       <c r="F61" t="n">
-        <v>52.376</v>
+        <v>59.6455</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>37.7714</v>
+        <v>40.1165</v>
       </c>
       <c r="C62" t="n">
-        <v>35.6279</v>
+        <v>35.4443</v>
       </c>
       <c r="D62" t="n">
-        <v>68.72110000000001</v>
+        <v>68.215</v>
       </c>
       <c r="E62" t="n">
-        <v>21.791</v>
+        <v>22.021</v>
       </c>
       <c r="F62" t="n">
-        <v>51.9576</v>
+        <v>59.3551</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>40.8221</v>
+        <v>39.6367</v>
       </c>
       <c r="C63" t="n">
-        <v>34.843</v>
+        <v>34.9239</v>
       </c>
       <c r="D63" t="n">
-        <v>68.2098</v>
+        <v>67.90009999999999</v>
       </c>
       <c r="E63" t="n">
-        <v>21.4539</v>
+        <v>21.4999</v>
       </c>
       <c r="F63" t="n">
-        <v>52.0421</v>
+        <v>58.8212</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>40.0062</v>
+        <v>38.1311</v>
       </c>
       <c r="C64" t="n">
-        <v>34.3388</v>
+        <v>34.4336</v>
       </c>
       <c r="D64" t="n">
-        <v>84.63339999999999</v>
+        <v>85.6472</v>
       </c>
       <c r="E64" t="n">
-        <v>34.7531</v>
+        <v>34.9801</v>
       </c>
       <c r="F64" t="n">
-        <v>62.0922</v>
+        <v>69.05289999999999</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>37.9617</v>
+        <v>38.0319</v>
       </c>
       <c r="C65" t="n">
-        <v>45.2106</v>
+        <v>45.6501</v>
       </c>
       <c r="D65" t="n">
-        <v>85.4178</v>
+        <v>84.8389</v>
       </c>
       <c r="E65" t="n">
-        <v>33.4567</v>
+        <v>33.4875</v>
       </c>
       <c r="F65" t="n">
-        <v>62.0908</v>
+        <v>68.64149999999999</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>37.2726</v>
+        <v>36.9284</v>
       </c>
       <c r="C66" t="n">
-        <v>44.1535</v>
+        <v>44.1124</v>
       </c>
       <c r="D66" t="n">
-        <v>83.54300000000001</v>
+        <v>81.20350000000001</v>
       </c>
       <c r="E66" t="n">
-        <v>31.761</v>
+        <v>32.1179</v>
       </c>
       <c r="F66" t="n">
-        <v>61.8472</v>
+        <v>67.81619999999999</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>60.663</v>
+        <v>59.4033</v>
       </c>
       <c r="C67" t="n">
-        <v>43.0465</v>
+        <v>43.5311</v>
       </c>
       <c r="D67" t="n">
-        <v>82.5998</v>
+        <v>80.6652</v>
       </c>
       <c r="E67" t="n">
-        <v>30.8726</v>
+        <v>30.9054</v>
       </c>
       <c r="F67" t="n">
-        <v>60.0066</v>
+        <v>67.5842</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>59.2313</v>
+        <v>57.8353</v>
       </c>
       <c r="C68" t="n">
-        <v>42.3717</v>
+        <v>42.638</v>
       </c>
       <c r="D68" t="n">
-        <v>80.2406</v>
+        <v>79.5027</v>
       </c>
       <c r="E68" t="n">
-        <v>30.2904</v>
+        <v>30.3036</v>
       </c>
       <c r="F68" t="n">
-        <v>60.0159</v>
+        <v>66.26990000000001</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>56.912</v>
+        <v>57.1792</v>
       </c>
       <c r="C69" t="n">
-        <v>41.4705</v>
+        <v>41.6757</v>
       </c>
       <c r="D69" t="n">
-        <v>78.6473</v>
+        <v>79.00620000000001</v>
       </c>
       <c r="E69" t="n">
-        <v>28.7875</v>
+        <v>29.2132</v>
       </c>
       <c r="F69" t="n">
-        <v>59.3881</v>
+        <v>66.6079</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>56.0259</v>
+        <v>55.2641</v>
       </c>
       <c r="C70" t="n">
-        <v>41.0584</v>
+        <v>40.6579</v>
       </c>
       <c r="D70" t="n">
-        <v>78.74120000000001</v>
+        <v>77.35469999999999</v>
       </c>
       <c r="E70" t="n">
-        <v>28.5148</v>
+        <v>27.9593</v>
       </c>
       <c r="F70" t="n">
-        <v>59.6667</v>
+        <v>64.8378</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>53.0929</v>
+        <v>54.0904</v>
       </c>
       <c r="C71" t="n">
-        <v>40.0539</v>
+        <v>40.1781</v>
       </c>
       <c r="D71" t="n">
-        <v>77.7598</v>
+        <v>75.82680000000001</v>
       </c>
       <c r="E71" t="n">
-        <v>27.3932</v>
+        <v>27.2355</v>
       </c>
       <c r="F71" t="n">
-        <v>56.7928</v>
+        <v>65.70440000000001</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>52.2883</v>
+        <v>52.932</v>
       </c>
       <c r="C72" t="n">
-        <v>39.0529</v>
+        <v>39.2122</v>
       </c>
       <c r="D72" t="n">
-        <v>76.4263</v>
+        <v>75.6944</v>
       </c>
       <c r="E72" t="n">
-        <v>26.1449</v>
+        <v>26.5803</v>
       </c>
       <c r="F72" t="n">
-        <v>56.4312</v>
+        <v>64.0716</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>51.3099</v>
+        <v>51.2573</v>
       </c>
       <c r="C73" t="n">
-        <v>38.5495</v>
+        <v>38.4568</v>
       </c>
       <c r="D73" t="n">
-        <v>75.79170000000001</v>
+        <v>75.5771</v>
       </c>
       <c r="E73" t="n">
-        <v>25.7396</v>
+        <v>25.6148</v>
       </c>
       <c r="F73" t="n">
-        <v>57.6725</v>
+        <v>64.706</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>50.1675</v>
+        <v>50.0393</v>
       </c>
       <c r="C74" t="n">
-        <v>37.8805</v>
+        <v>38.2304</v>
       </c>
       <c r="D74" t="n">
-        <v>76.52370000000001</v>
+        <v>74.9423</v>
       </c>
       <c r="E74" t="n">
-        <v>24.9334</v>
+        <v>24.7477</v>
       </c>
       <c r="F74" t="n">
-        <v>55.6515</v>
+        <v>62.5929</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>48.759</v>
+        <v>48.645</v>
       </c>
       <c r="C75" t="n">
-        <v>37.154</v>
+        <v>37.7347</v>
       </c>
       <c r="D75" t="n">
-        <v>75.2072</v>
+        <v>74.758</v>
       </c>
       <c r="E75" t="n">
-        <v>24.3628</v>
+        <v>24.169</v>
       </c>
       <c r="F75" t="n">
-        <v>54.4963</v>
+        <v>61.6802</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>47.8351</v>
+        <v>46.8446</v>
       </c>
       <c r="C76" t="n">
-        <v>36.701</v>
+        <v>37.0587</v>
       </c>
       <c r="D76" t="n">
-        <v>75.12990000000001</v>
+        <v>73.9455</v>
       </c>
       <c r="E76" t="n">
-        <v>23.4172</v>
+        <v>23.5369</v>
       </c>
       <c r="F76" t="n">
-        <v>54.7161</v>
+        <v>61.6633</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>46.0282</v>
+        <v>46.5109</v>
       </c>
       <c r="C77" t="n">
-        <v>35.8191</v>
+        <v>36.2143</v>
       </c>
       <c r="D77" t="n">
-        <v>74.6116</v>
+        <v>74.389</v>
       </c>
       <c r="E77" t="n">
-        <v>23.1717</v>
+        <v>23.0207</v>
       </c>
       <c r="F77" t="n">
-        <v>54.6391</v>
+        <v>62.2263</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>44.845</v>
+        <v>44.103</v>
       </c>
       <c r="C78" t="n">
-        <v>35.3805</v>
+        <v>35.6245</v>
       </c>
       <c r="D78" t="n">
-        <v>108.576</v>
+        <v>109.719</v>
       </c>
       <c r="E78" t="n">
-        <v>36.5328</v>
+        <v>37.089</v>
       </c>
       <c r="F78" t="n">
-        <v>77.756</v>
+        <v>87.011</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>42.8447</v>
+        <v>43.3392</v>
       </c>
       <c r="C79" t="n">
-        <v>47.7426</v>
+        <v>46.3813</v>
       </c>
       <c r="D79" t="n">
-        <v>107.714</v>
+        <v>109.3</v>
       </c>
       <c r="E79" t="n">
-        <v>35.5086</v>
+        <v>35.6134</v>
       </c>
       <c r="F79" t="n">
-        <v>79.58280000000001</v>
+        <v>86.1031</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>41.8283</v>
+        <v>42.5235</v>
       </c>
       <c r="C80" t="n">
-        <v>47.0634</v>
+        <v>47.4919</v>
       </c>
       <c r="D80" t="n">
-        <v>105.679</v>
+        <v>105.77</v>
       </c>
       <c r="E80" t="n">
-        <v>34.9289</v>
+        <v>34.6973</v>
       </c>
       <c r="F80" t="n">
-        <v>78.2388</v>
+        <v>84.8002</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>60.7431</v>
+        <v>62.5281</v>
       </c>
       <c r="C81" t="n">
-        <v>47.218</v>
+        <v>47.1432</v>
       </c>
       <c r="D81" t="n">
-        <v>105.959</v>
+        <v>105.508</v>
       </c>
       <c r="E81" t="n">
-        <v>34.3424</v>
+        <v>34.0616</v>
       </c>
       <c r="F81" t="n">
-        <v>78.57680000000001</v>
+        <v>84.4999</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>60.8882</v>
+        <v>62.4651</v>
       </c>
       <c r="C82" t="n">
-        <v>46.5848</v>
+        <v>46.2839</v>
       </c>
       <c r="D82" t="n">
-        <v>104.706</v>
+        <v>103.855</v>
       </c>
       <c r="E82" t="n">
-        <v>32.7329</v>
+        <v>32.5643</v>
       </c>
       <c r="F82" t="n">
-        <v>76.4396</v>
+        <v>83.4342</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>60.1345</v>
+        <v>61.3873</v>
       </c>
       <c r="C83" t="n">
-        <v>46.612</v>
+        <v>46.028</v>
       </c>
       <c r="D83" t="n">
-        <v>104.111</v>
+        <v>102.959</v>
       </c>
       <c r="E83" t="n">
-        <v>31.5005</v>
+        <v>32.3421</v>
       </c>
       <c r="F83" t="n">
-        <v>76.3502</v>
+        <v>81.5988</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>59.0964</v>
+        <v>60.5874</v>
       </c>
       <c r="C84" t="n">
-        <v>45.9737</v>
+        <v>45.9393</v>
       </c>
       <c r="D84" t="n">
-        <v>103.728</v>
+        <v>102.084</v>
       </c>
       <c r="E84" t="n">
-        <v>30.9852</v>
+        <v>31.3347</v>
       </c>
       <c r="F84" t="n">
-        <v>75.4618</v>
+        <v>81.59820000000001</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>58.4806</v>
+        <v>59.4521</v>
       </c>
       <c r="C85" t="n">
-        <v>45.2481</v>
+        <v>45.3233</v>
       </c>
       <c r="D85" t="n">
-        <v>102.82</v>
+        <v>102.458</v>
       </c>
       <c r="E85" t="n">
-        <v>30.1278</v>
+        <v>30.1025</v>
       </c>
       <c r="F85" t="n">
-        <v>73.8296</v>
+        <v>80.19370000000001</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>57.8069</v>
+        <v>59.1583</v>
       </c>
       <c r="C86" t="n">
-        <v>44.876</v>
+        <v>45.0737</v>
       </c>
       <c r="D86" t="n">
-        <v>103.489</v>
+        <v>101.9</v>
       </c>
       <c r="E86" t="n">
-        <v>29.6275</v>
+        <v>29.2839</v>
       </c>
       <c r="F86" t="n">
-        <v>73.0504</v>
+        <v>78.62730000000001</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>56.389</v>
+        <v>57.8586</v>
       </c>
       <c r="C87" t="n">
-        <v>44.3674</v>
+        <v>44.3253</v>
       </c>
       <c r="D87" t="n">
-        <v>102.742</v>
+        <v>102.408</v>
       </c>
       <c r="E87" t="n">
-        <v>28.5543</v>
+        <v>28.5415</v>
       </c>
       <c r="F87" t="n">
-        <v>71.5093</v>
+        <v>77.88379999999999</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>55.7102</v>
+        <v>56.484</v>
       </c>
       <c r="C88" t="n">
-        <v>43.8013</v>
+        <v>44.0905</v>
       </c>
       <c r="D88" t="n">
-        <v>103.227</v>
+        <v>102.841</v>
       </c>
       <c r="E88" t="n">
-        <v>28.3965</v>
+        <v>27.8006</v>
       </c>
       <c r="F88" t="n">
-        <v>69.9743</v>
+        <v>76.6452</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>55.1179</v>
+        <v>55.2619</v>
       </c>
       <c r="C89" t="n">
-        <v>43.3859</v>
+        <v>43.229</v>
       </c>
       <c r="D89" t="n">
-        <v>103.421</v>
+        <v>102.694</v>
       </c>
       <c r="E89" t="n">
-        <v>27.3639</v>
+        <v>26.8653</v>
       </c>
       <c r="F89" t="n">
-        <v>68.0204</v>
+        <v>76.0575</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>53.7239</v>
+        <v>55.153</v>
       </c>
       <c r="C90" t="n">
-        <v>42.6803</v>
+        <v>42.9406</v>
       </c>
       <c r="D90" t="n">
-        <v>104.834</v>
+        <v>104.472</v>
       </c>
       <c r="E90" t="n">
-        <v>26.4093</v>
+        <v>26.2076</v>
       </c>
       <c r="F90" t="n">
-        <v>68.24209999999999</v>
+        <v>74.5805</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>52.8237</v>
+        <v>53.9211</v>
       </c>
       <c r="C91" t="n">
-        <v>42.2931</v>
+        <v>42.2992</v>
       </c>
       <c r="D91" t="n">
-        <v>106.017</v>
+        <v>104.766</v>
       </c>
       <c r="E91" t="n">
-        <v>26.0008</v>
+        <v>25.8121</v>
       </c>
       <c r="F91" t="n">
-        <v>67.5585</v>
+        <v>72.86199999999999</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>51.3926</v>
+        <v>52.5871</v>
       </c>
       <c r="C92" t="n">
-        <v>41.6197</v>
+        <v>41.6999</v>
       </c>
       <c r="D92" t="n">
-        <v>148.363</v>
+        <v>147.217</v>
       </c>
       <c r="E92" t="n">
-        <v>39.0438</v>
+        <v>38.7213</v>
       </c>
       <c r="F92" t="n">
-        <v>98.378</v>
+        <v>104.491</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>50.9286</v>
+        <v>53.3876</v>
       </c>
       <c r="C93" t="n">
-        <v>41.0599</v>
+        <v>41.1502</v>
       </c>
       <c r="D93" t="n">
-        <v>148.203</v>
+        <v>145.947</v>
       </c>
       <c r="E93" t="n">
-        <v>38.5192</v>
+        <v>38.5455</v>
       </c>
       <c r="F93" t="n">
-        <v>98.7881</v>
+        <v>104.79</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>52.1476</v>
+        <v>52.6466</v>
       </c>
       <c r="C94" t="n">
-        <v>53.9314</v>
+        <v>53.9078</v>
       </c>
       <c r="D94" t="n">
-        <v>147.533</v>
+        <v>145.537</v>
       </c>
       <c r="E94" t="n">
-        <v>37.5124</v>
+        <v>37.4974</v>
       </c>
       <c r="F94" t="n">
-        <v>98.3845</v>
+        <v>103.216</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>75.09999999999999</v>
+        <v>75.01439999999999</v>
       </c>
       <c r="C95" t="n">
-        <v>54.6216</v>
+        <v>54.5605</v>
       </c>
       <c r="D95" t="n">
-        <v>145.214</v>
+        <v>144.928</v>
       </c>
       <c r="E95" t="n">
-        <v>37.2194</v>
+        <v>37.178</v>
       </c>
       <c r="F95" t="n">
-        <v>97.3169</v>
+        <v>102.254</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>74.59820000000001</v>
+        <v>74.9427</v>
       </c>
       <c r="C96" t="n">
-        <v>53.0635</v>
+        <v>53.1933</v>
       </c>
       <c r="D96" t="n">
-        <v>145.162</v>
+        <v>144.135</v>
       </c>
       <c r="E96" t="n">
-        <v>36.5686</v>
+        <v>36.2481</v>
       </c>
       <c r="F96" t="n">
-        <v>94.72709999999999</v>
+        <v>101.533</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>73.7234</v>
+        <v>73.5056</v>
       </c>
       <c r="C97" t="n">
-        <v>53.3785</v>
+        <v>53.0684</v>
       </c>
       <c r="D97" t="n">
-        <v>143.99</v>
+        <v>144.447</v>
       </c>
       <c r="E97" t="n">
-        <v>35.3249</v>
+        <v>34.8441</v>
       </c>
       <c r="F97" t="n">
-        <v>94.42140000000001</v>
+        <v>100.5</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>73.3103</v>
+        <v>73.1748</v>
       </c>
       <c r="C98" t="n">
-        <v>52.9298</v>
+        <v>52.9231</v>
       </c>
       <c r="D98" t="n">
-        <v>145.123</v>
+        <v>144.523</v>
       </c>
       <c r="E98" t="n">
-        <v>34.3331</v>
+        <v>34.2347</v>
       </c>
       <c r="F98" t="n">
-        <v>93.2064</v>
+        <v>99.18940000000001</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>72.1743</v>
+        <v>71.8824</v>
       </c>
       <c r="C99" t="n">
-        <v>52.7544</v>
+        <v>53.2794</v>
       </c>
       <c r="D99" t="n">
-        <v>144.668</v>
+        <v>143.764</v>
       </c>
       <c r="E99" t="n">
-        <v>33.743</v>
+        <v>33.2091</v>
       </c>
       <c r="F99" t="n">
-        <v>92.5149</v>
+        <v>98.0659</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>71.488</v>
+        <v>71.3085</v>
       </c>
       <c r="C100" t="n">
-        <v>52.5626</v>
+        <v>52.9035</v>
       </c>
       <c r="D100" t="n">
-        <v>145.092</v>
+        <v>144.766</v>
       </c>
       <c r="E100" t="n">
-        <v>32.7761</v>
+        <v>32.999</v>
       </c>
       <c r="F100" t="n">
-        <v>91.2996</v>
+        <v>97.0008</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>70.45999999999999</v>
+        <v>70.42270000000001</v>
       </c>
       <c r="C101" t="n">
-        <v>52.8128</v>
+        <v>53.0302</v>
       </c>
       <c r="D101" t="n">
-        <v>145.004</v>
+        <v>145.158</v>
       </c>
       <c r="E101" t="n">
-        <v>31.478</v>
+        <v>31.6431</v>
       </c>
       <c r="F101" t="n">
-        <v>90.4487</v>
+        <v>97.23099999999999</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>66.21720000000001</v>
+        <v>67.3439</v>
       </c>
       <c r="C102" t="n">
-        <v>52.3644</v>
+        <v>52.3757</v>
       </c>
       <c r="D102" t="n">
-        <v>145.562</v>
+        <v>146.467</v>
       </c>
       <c r="E102" t="n">
-        <v>31.3911</v>
+        <v>31.4354</v>
       </c>
       <c r="F102" t="n">
-        <v>88.75149999999999</v>
+        <v>96.48309999999999</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>65.8027</v>
+        <v>66.42959999999999</v>
       </c>
       <c r="C103" t="n">
-        <v>52.4892</v>
+        <v>52.5927</v>
       </c>
       <c r="D103" t="n">
-        <v>146.071</v>
+        <v>146.294</v>
       </c>
       <c r="E103" t="n">
-        <v>30.5424</v>
+        <v>30.3034</v>
       </c>
       <c r="F103" t="n">
-        <v>88.7414</v>
+        <v>94.4109</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>64.8738</v>
+        <v>65.37009999999999</v>
       </c>
       <c r="C104" t="n">
-        <v>52.1091</v>
+        <v>52.091</v>
       </c>
       <c r="D104" t="n">
-        <v>147.579</v>
+        <v>146.927</v>
       </c>
       <c r="E104" t="n">
-        <v>29.8645</v>
+        <v>30.0825</v>
       </c>
       <c r="F104" t="n">
-        <v>87.8151</v>
+        <v>93.5497</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>64.69459999999999</v>
+        <v>64.8956</v>
       </c>
       <c r="C105" t="n">
-        <v>52.4153</v>
+        <v>51.7948</v>
       </c>
       <c r="D105" t="n">
-        <v>148.801</v>
+        <v>147.394</v>
       </c>
       <c r="E105" t="n">
-        <v>29.3629</v>
+        <v>29.1805</v>
       </c>
       <c r="F105" t="n">
-        <v>86.9661</v>
+        <v>92.3587</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>64.0097</v>
+        <v>64.9923</v>
       </c>
       <c r="C106" t="n">
-        <v>52.1873</v>
+        <v>51.8931</v>
       </c>
       <c r="D106" t="n">
-        <v>149.649</v>
+        <v>149.317</v>
       </c>
       <c r="E106" t="n">
-        <v>28.9417</v>
+        <v>29.1644</v>
       </c>
       <c r="F106" t="n">
-        <v>86.6347</v>
+        <v>92.3699</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>63.3637</v>
+        <v>63.5048</v>
       </c>
       <c r="C107" t="n">
-        <v>51.9431</v>
+        <v>52.1213</v>
       </c>
       <c r="D107" t="n">
-        <v>194.132</v>
+        <v>193.297</v>
       </c>
       <c r="E107" t="n">
-        <v>41.9858</v>
+        <v>42.4879</v>
       </c>
       <c r="F107" t="n">
-        <v>120.867</v>
+        <v>125.558</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>62.9879</v>
+        <v>63.5839</v>
       </c>
       <c r="C108" t="n">
-        <v>63.6709</v>
+        <v>63.5594</v>
       </c>
       <c r="D108" t="n">
-        <v>191.937</v>
+        <v>193.022</v>
       </c>
       <c r="E108" t="n">
-        <v>41.8155</v>
+        <v>41.8293</v>
       </c>
       <c r="F108" t="n">
-        <v>120.58</v>
+        <v>124.608</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>63.9723</v>
+        <v>62.8306</v>
       </c>
       <c r="C109" t="n">
-        <v>63.7745</v>
+        <v>64.46210000000001</v>
       </c>
       <c r="D109" t="n">
-        <v>190.353</v>
+        <v>190.609</v>
       </c>
       <c r="E109" t="n">
-        <v>40.0904</v>
+        <v>40.7299</v>
       </c>
       <c r="F109" t="n">
-        <v>118.482</v>
+        <v>123.968</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>84.69</v>
+        <v>84.726</v>
       </c>
       <c r="C110" t="n">
-        <v>63.6313</v>
+        <v>64.429</v>
       </c>
       <c r="D110" t="n">
-        <v>189.109</v>
+        <v>189.7</v>
       </c>
       <c r="E110" t="n">
-        <v>39.705</v>
+        <v>40.5106</v>
       </c>
       <c r="F110" t="n">
-        <v>117.773</v>
+        <v>122.84</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>83.30119999999999</v>
+        <v>83.33750000000001</v>
       </c>
       <c r="C111" t="n">
-        <v>63.849</v>
+        <v>63.7514</v>
       </c>
       <c r="D111" t="n">
-        <v>187.899</v>
+        <v>188.343</v>
       </c>
       <c r="E111" t="n">
-        <v>38.8372</v>
+        <v>38.8751</v>
       </c>
       <c r="F111" t="n">
-        <v>116.939</v>
+        <v>122.466</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>81.6495</v>
+        <v>82.1397</v>
       </c>
       <c r="C112" t="n">
-        <v>64.5896</v>
+        <v>64.01900000000001</v>
       </c>
       <c r="D112" t="n">
-        <v>187.695</v>
+        <v>188.594</v>
       </c>
       <c r="E112" t="n">
-        <v>38.6152</v>
+        <v>37.8755</v>
       </c>
       <c r="F112" t="n">
-        <v>116.457</v>
+        <v>121.271</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>81.16679999999999</v>
+        <v>80.1674</v>
       </c>
       <c r="C113" t="n">
-        <v>63.9047</v>
+        <v>64.4984</v>
       </c>
       <c r="D113" t="n">
-        <v>186.673</v>
+        <v>187.755</v>
       </c>
       <c r="E113" t="n">
-        <v>37.2138</v>
+        <v>37.6072</v>
       </c>
       <c r="F113" t="n">
-        <v>116.781</v>
+        <v>120.343</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>84.0668</v>
+        <v>84.19029999999999</v>
       </c>
       <c r="C114" t="n">
-        <v>63.9939</v>
+        <v>64.21169999999999</v>
       </c>
       <c r="D114" t="n">
-        <v>187.135</v>
+        <v>187.37</v>
       </c>
       <c r="E114" t="n">
-        <v>37.0866</v>
+        <v>37.1188</v>
       </c>
       <c r="F114" t="n">
-        <v>115.574</v>
+        <v>119.98</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>81.9982</v>
+        <v>83.23950000000001</v>
       </c>
       <c r="C115" t="n">
-        <v>64.22450000000001</v>
+        <v>63.9321</v>
       </c>
       <c r="D115" t="n">
-        <v>186.976</v>
+        <v>187.242</v>
       </c>
       <c r="E115" t="n">
-        <v>36.6621</v>
+        <v>36.2498</v>
       </c>
       <c r="F115" t="n">
-        <v>115.399</v>
+        <v>120.501</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>82.61969999999999</v>
+        <v>82.4761</v>
       </c>
       <c r="C116" t="n">
-        <v>64.01819999999999</v>
+        <v>64.5986</v>
       </c>
       <c r="D116" t="n">
-        <v>186.791</v>
+        <v>187.192</v>
       </c>
       <c r="E116" t="n">
-        <v>35.4346</v>
+        <v>35.8598</v>
       </c>
       <c r="F116" t="n">
-        <v>114.929</v>
+        <v>118.044</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>79.4075</v>
+        <v>78.76649999999999</v>
       </c>
       <c r="C117" t="n">
-        <v>63.716</v>
+        <v>64.0283</v>
       </c>
       <c r="D117" t="n">
-        <v>187.499</v>
+        <v>187.27</v>
       </c>
       <c r="E117" t="n">
-        <v>35.4288</v>
+        <v>35.4087</v>
       </c>
       <c r="F117" t="n">
-        <v>114.901</v>
+        <v>117.876</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>78.3984</v>
+        <v>77.9081</v>
       </c>
       <c r="C118" t="n">
-        <v>63.5948</v>
+        <v>63.4198</v>
       </c>
       <c r="D118" t="n">
-        <v>187.526</v>
+        <v>187.852</v>
       </c>
       <c r="E118" t="n">
-        <v>34.6976</v>
+        <v>35.2831</v>
       </c>
       <c r="F118" t="n">
-        <v>113.895</v>
+        <v>117.86</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>77.5292</v>
+        <v>77.57989999999999</v>
       </c>
       <c r="C119" t="n">
-        <v>63.9466</v>
+        <v>63.9338</v>
       </c>
       <c r="D119" t="n">
-        <v>188.439</v>
+        <v>188.014</v>
       </c>
       <c r="E119" t="n">
-        <v>34.1104</v>
+        <v>34.2456</v>
       </c>
       <c r="F119" t="n">
-        <v>114.292</v>
+        <v>118.325</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>76.1966</v>
+        <v>77.84650000000001</v>
       </c>
       <c r="C120" t="n">
-        <v>64.3561</v>
+        <v>63.7205</v>
       </c>
       <c r="D120" t="n">
-        <v>190.06</v>
+        <v>189.272</v>
       </c>
       <c r="E120" t="n">
-        <v>33.8264</v>
+        <v>33.6826</v>
       </c>
       <c r="F120" t="n">
-        <v>113.495</v>
+        <v>116.941</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>77.7813</v>
+        <v>77.1922</v>
       </c>
       <c r="C121" t="n">
-        <v>63.1098</v>
+        <v>63.1871</v>
       </c>
       <c r="D121" t="n">
-        <v>236.726</v>
+        <v>236.748</v>
       </c>
       <c r="E121" t="n">
-        <v>46.8088</v>
+        <v>47.622</v>
       </c>
       <c r="F121" t="n">
-        <v>148.56</v>
+        <v>152.798</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>76.7754</v>
+        <v>76.54730000000001</v>
       </c>
       <c r="C122" t="n">
-        <v>75.5705</v>
+        <v>75.5356</v>
       </c>
       <c r="D122" t="n">
-        <v>233.566</v>
+        <v>233.846</v>
       </c>
       <c r="E122" t="n">
-        <v>47.3845</v>
+        <v>46.539</v>
       </c>
       <c r="F122" t="n">
-        <v>147.271</v>
+        <v>150.316</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>74.7307</v>
+        <v>75.0155</v>
       </c>
       <c r="C123" t="n">
-        <v>75.691</v>
+        <v>75.4644</v>
       </c>
       <c r="D123" t="n">
-        <v>232.065</v>
+        <v>230.926</v>
       </c>
       <c r="E123" t="n">
-        <v>46.3152</v>
+        <v>46.3626</v>
       </c>
       <c r="F123" t="n">
-        <v>146.387</v>
+        <v>150.925</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>98.1545</v>
+        <v>98.5401</v>
       </c>
       <c r="C124" t="n">
-        <v>75.47029999999999</v>
+        <v>76.2743</v>
       </c>
       <c r="D124" t="n">
-        <v>230.254</v>
+        <v>229.49</v>
       </c>
       <c r="E124" t="n">
-        <v>45.4366</v>
+        <v>46.7089</v>
       </c>
       <c r="F124" t="n">
-        <v>146.024</v>
+        <v>148.404</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>96.9071</v>
+        <v>97.9187</v>
       </c>
       <c r="C125" t="n">
-        <v>76.16459999999999</v>
+        <v>76.1992</v>
       </c>
       <c r="D125" t="n">
-        <v>228.108</v>
+        <v>227.807</v>
       </c>
       <c r="E125" t="n">
-        <v>45.2978</v>
+        <v>44.9726</v>
       </c>
       <c r="F125" t="n">
-        <v>146.031</v>
+        <v>147.325</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>94.2921</v>
+        <v>94.89570000000001</v>
       </c>
       <c r="C126" t="n">
-        <v>76.14</v>
+        <v>76.9999</v>
       </c>
       <c r="D126" t="n">
-        <v>226.221</v>
+        <v>226.138</v>
       </c>
       <c r="E126" t="n">
-        <v>44.9102</v>
+        <v>45.5775</v>
       </c>
       <c r="F126" t="n">
-        <v>144.608</v>
+        <v>147.328</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>93.5557</v>
+        <v>95.4455</v>
       </c>
       <c r="C127" t="n">
-        <v>76.39700000000001</v>
+        <v>76.6061</v>
       </c>
       <c r="D127" t="n">
-        <v>225.089</v>
+        <v>225.884</v>
       </c>
       <c r="E127" t="n">
-        <v>44.8065</v>
+        <v>45.0646</v>
       </c>
       <c r="F127" t="n">
-        <v>143.586</v>
+        <v>146.386</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>96.09910000000001</v>
+        <v>93.7349</v>
       </c>
       <c r="C128" t="n">
-        <v>76.5373</v>
+        <v>76.8014</v>
       </c>
       <c r="D128" t="n">
-        <v>223.252</v>
+        <v>224.059</v>
       </c>
       <c r="E128" t="n">
-        <v>44.4401</v>
+        <v>44.1274</v>
       </c>
       <c r="F128" t="n">
-        <v>143.205</v>
+        <v>145.931</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>95.08920000000001</v>
+        <v>92.80500000000001</v>
       </c>
       <c r="C129" t="n">
-        <v>76.85769999999999</v>
+        <v>77.0333</v>
       </c>
       <c r="D129" t="n">
-        <v>222.403</v>
+        <v>222.598</v>
       </c>
       <c r="E129" t="n">
-        <v>43.1643</v>
+        <v>43.2704</v>
       </c>
       <c r="F129" t="n">
-        <v>142.755</v>
+        <v>145.133</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>91.48220000000001</v>
+        <v>92.6435</v>
       </c>
       <c r="C130" t="n">
-        <v>77.0795</v>
+        <v>77.0656</v>
       </c>
       <c r="D130" t="n">
-        <v>222.205</v>
+        <v>222.602</v>
       </c>
       <c r="E130" t="n">
-        <v>43.1553</v>
+        <v>42.7758</v>
       </c>
       <c r="F130" t="n">
-        <v>142.104</v>
+        <v>144.585</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>90.7146</v>
+        <v>93.2059</v>
       </c>
       <c r="C131" t="n">
-        <v>77.1032</v>
+        <v>77.345</v>
       </c>
       <c r="D131" t="n">
-        <v>221.089</v>
+        <v>221.431</v>
       </c>
       <c r="E131" t="n">
-        <v>42.4219</v>
+        <v>42.6829</v>
       </c>
       <c r="F131" t="n">
-        <v>142.025</v>
+        <v>143.88</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>94.07389999999999</v>
+        <v>93.7197</v>
       </c>
       <c r="C132" t="n">
-        <v>77.34739999999999</v>
+        <v>76.9885</v>
       </c>
       <c r="D132" t="n">
-        <v>221.868</v>
+        <v>221.827</v>
       </c>
       <c r="E132" t="n">
-        <v>42.3744</v>
+        <v>42.3416</v>
       </c>
       <c r="F132" t="n">
-        <v>141.295</v>
+        <v>144.014</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>91.5326</v>
+        <v>91.4773</v>
       </c>
       <c r="C133" t="n">
-        <v>77.58669999999999</v>
+        <v>77.8626</v>
       </c>
       <c r="D133" t="n">
-        <v>221.887</v>
+        <v>221.709</v>
       </c>
       <c r="E133" t="n">
-        <v>42.2658</v>
+        <v>42.2279</v>
       </c>
       <c r="F133" t="n">
-        <v>140.888</v>
+        <v>143.337</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>92.1648</v>
+        <v>90.95</v>
       </c>
       <c r="C134" t="n">
-        <v>77.5776</v>
+        <v>77.4563</v>
       </c>
       <c r="D134" t="n">
-        <v>222.173</v>
+        <v>222.198</v>
       </c>
       <c r="E134" t="n">
-        <v>41.7989</v>
+        <v>41.8498</v>
       </c>
       <c r="F134" t="n">
-        <v>141.032</v>
+        <v>143.276</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>92.3626</v>
+        <v>92.71380000000001</v>
       </c>
       <c r="C135" t="n">
-        <v>77.8623</v>
+        <v>77.9081</v>
       </c>
       <c r="D135" t="n">
-        <v>271.659</v>
+        <v>271.643</v>
       </c>
       <c r="E135" t="n">
-        <v>55.5401</v>
+        <v>55.7728</v>
       </c>
       <c r="F135" t="n">
-        <v>176.92</v>
+        <v>178.998</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>92.4153</v>
+        <v>89.56780000000001</v>
       </c>
       <c r="C136" t="n">
-        <v>90.0701</v>
+        <v>90.08110000000001</v>
       </c>
       <c r="D136" t="n">
-        <v>268.266</v>
+        <v>267.937</v>
       </c>
       <c r="E136" t="n">
-        <v>55.2642</v>
+        <v>55.3626</v>
       </c>
       <c r="F136" t="n">
-        <v>175.475</v>
+        <v>176.962</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>90.67100000000001</v>
+        <v>90.1421</v>
       </c>
       <c r="C137" t="n">
-        <v>90.37009999999999</v>
+        <v>90.1823</v>
       </c>
       <c r="D137" t="n">
-        <v>264.606</v>
+        <v>265.056</v>
       </c>
       <c r="E137" t="n">
-        <v>55.0696</v>
+        <v>55.1323</v>
       </c>
       <c r="F137" t="n">
-        <v>173.891</v>
+        <v>175.747</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>110.848</v>
+        <v>109.914</v>
       </c>
       <c r="C138" t="n">
-        <v>90.7859</v>
+        <v>91.0192</v>
       </c>
       <c r="D138" t="n">
-        <v>261.455</v>
+        <v>261.856</v>
       </c>
       <c r="E138" t="n">
-        <v>54.6606</v>
+        <v>54.992</v>
       </c>
       <c r="F138" t="n">
-        <v>172.338</v>
+        <v>173.945</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>109.316</v>
+        <v>111.501</v>
       </c>
       <c r="C139" t="n">
-        <v>90.99379999999999</v>
+        <v>91.02030000000001</v>
       </c>
       <c r="D139" t="n">
-        <v>259.546</v>
+        <v>259.091</v>
       </c>
       <c r="E139" t="n">
-        <v>54.9712</v>
+        <v>54.9561</v>
       </c>
       <c r="F139" t="n">
-        <v>171.235</v>
+        <v>173.168</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>108.038</v>
+        <v>107.568</v>
       </c>
       <c r="C140" t="n">
-        <v>91.3579</v>
+        <v>91.33969999999999</v>
       </c>
       <c r="D140" t="n">
-        <v>256.554</v>
+        <v>256.158</v>
       </c>
       <c r="E140" t="n">
-        <v>54.8644</v>
+        <v>54.7707</v>
       </c>
       <c r="F140" t="n">
-        <v>170.185</v>
+        <v>171.793</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>108.971</v>
+        <v>110.922</v>
       </c>
       <c r="C141" t="n">
-        <v>92.15130000000001</v>
+        <v>91.7851</v>
       </c>
       <c r="D141" t="n">
-        <v>254.728</v>
+        <v>254.515</v>
       </c>
       <c r="E141" t="n">
-        <v>54.5381</v>
+        <v>54.4996</v>
       </c>
       <c r="F141" t="n">
-        <v>169.352</v>
+        <v>170.952</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>109.286</v>
+        <v>107.535</v>
       </c>
       <c r="C142" t="n">
-        <v>92.0069</v>
+        <v>92.15260000000001</v>
       </c>
       <c r="D142" t="n">
-        <v>253.144</v>
+        <v>253.107</v>
       </c>
       <c r="E142" t="n">
-        <v>54.569</v>
+        <v>54.106</v>
       </c>
       <c r="F142" t="n">
-        <v>168.299</v>
+        <v>169.715</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>107.235</v>
+        <v>108.084</v>
       </c>
       <c r="C143" t="n">
-        <v>92.30329999999999</v>
+        <v>92.1187</v>
       </c>
       <c r="D143" t="n">
-        <v>251.348</v>
+        <v>251.333</v>
       </c>
       <c r="E143" t="n">
-        <v>54.3192</v>
+        <v>53.693</v>
       </c>
       <c r="F143" t="n">
-        <v>167.315</v>
+        <v>168.837</v>
       </c>
     </row>
   </sheetData>

--- a/vs-x64/Running insertion.xlsx
+++ b/vs-x64/Running insertion.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>23.7256</v>
+        <v>24.3557</v>
       </c>
       <c r="C2" t="n">
-        <v>31.1953</v>
+        <v>31.2631</v>
       </c>
       <c r="D2" t="n">
-        <v>59.0636</v>
+        <v>59.0792</v>
       </c>
       <c r="E2" t="n">
-        <v>15.0458</v>
+        <v>15.0223</v>
       </c>
       <c r="F2" t="n">
-        <v>58.3808</v>
+        <v>51.4542</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>23.1683</v>
+        <v>22.7475</v>
       </c>
       <c r="C3" t="n">
-        <v>30.7307</v>
+        <v>30.6708</v>
       </c>
       <c r="D3" t="n">
-        <v>58.8885</v>
+        <v>58.614</v>
       </c>
       <c r="E3" t="n">
-        <v>14.5758</v>
+        <v>14.6587</v>
       </c>
       <c r="F3" t="n">
-        <v>57.6481</v>
+        <v>50.652</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>22.2554</v>
+        <v>22.369</v>
       </c>
       <c r="C4" t="n">
-        <v>30.2423</v>
+        <v>30.3237</v>
       </c>
       <c r="D4" t="n">
-        <v>58.2569</v>
+        <v>58.073</v>
       </c>
       <c r="E4" t="n">
-        <v>14.2421</v>
+        <v>14.2385</v>
       </c>
       <c r="F4" t="n">
-        <v>57.4084</v>
+        <v>50.3777</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>22.0105</v>
+        <v>21.7221</v>
       </c>
       <c r="C5" t="n">
-        <v>29.899</v>
+        <v>29.8641</v>
       </c>
       <c r="D5" t="n">
-        <v>57.6999</v>
+        <v>57.6457</v>
       </c>
       <c r="E5" t="n">
-        <v>14.0118</v>
+        <v>14.0112</v>
       </c>
       <c r="F5" t="n">
-        <v>57.0324</v>
+        <v>49.9137</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>21.6726</v>
+        <v>21.3324</v>
       </c>
       <c r="C6" t="n">
-        <v>29.5354</v>
+        <v>29.4883</v>
       </c>
       <c r="D6" t="n">
-        <v>57.0853</v>
+        <v>57.0047</v>
       </c>
       <c r="E6" t="n">
-        <v>13.7115</v>
+        <v>13.6632</v>
       </c>
       <c r="F6" t="n">
-        <v>56.8568</v>
+        <v>49.4395</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>21.3237</v>
+        <v>21.4016</v>
       </c>
       <c r="C7" t="n">
-        <v>29.1883</v>
+        <v>29.1308</v>
       </c>
       <c r="D7" t="n">
-        <v>68.6844</v>
+        <v>68.24769999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>20.682</v>
+        <v>20.7011</v>
       </c>
       <c r="F7" t="n">
-        <v>63.1626</v>
+        <v>56.2611</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>21.1868</v>
+        <v>20.9004</v>
       </c>
       <c r="C8" t="n">
-        <v>35.916</v>
+        <v>35.9211</v>
       </c>
       <c r="D8" t="n">
-        <v>67.264</v>
+        <v>67.119</v>
       </c>
       <c r="E8" t="n">
-        <v>19.9946</v>
+        <v>19.9926</v>
       </c>
       <c r="F8" t="n">
-        <v>63.3625</v>
+        <v>55.8907</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>21.188</v>
+        <v>21.1021</v>
       </c>
       <c r="C9" t="n">
-        <v>35.3177</v>
+        <v>35.3655</v>
       </c>
       <c r="D9" t="n">
-        <v>66.1561</v>
+        <v>66.1602</v>
       </c>
       <c r="E9" t="n">
-        <v>19.3303</v>
+        <v>19.331</v>
       </c>
       <c r="F9" t="n">
-        <v>62.1964</v>
+        <v>55.0424</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>27.6193</v>
+        <v>28.5375</v>
       </c>
       <c r="C10" t="n">
-        <v>34.7212</v>
+        <v>34.7023</v>
       </c>
       <c r="D10" t="n">
-        <v>65.0262</v>
+        <v>64.9256</v>
       </c>
       <c r="E10" t="n">
-        <v>18.6817</v>
+        <v>18.6931</v>
       </c>
       <c r="F10" t="n">
-        <v>61.2839</v>
+        <v>54.1279</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>26.9277</v>
+        <v>27.7805</v>
       </c>
       <c r="C11" t="n">
-        <v>34.0845</v>
+        <v>34.0618</v>
       </c>
       <c r="D11" t="n">
-        <v>64.47280000000001</v>
+        <v>64.05589999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>18.1158</v>
+        <v>18.1129</v>
       </c>
       <c r="F11" t="n">
-        <v>61.2439</v>
+        <v>53.8072</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>26.277</v>
+        <v>26.8278</v>
       </c>
       <c r="C12" t="n">
-        <v>33.5399</v>
+        <v>33.5339</v>
       </c>
       <c r="D12" t="n">
-        <v>63.1487</v>
+        <v>63.2388</v>
       </c>
       <c r="E12" t="n">
-        <v>17.5429</v>
+        <v>17.6</v>
       </c>
       <c r="F12" t="n">
-        <v>60.1213</v>
+        <v>53.2845</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>26.1671</v>
+        <v>25.714</v>
       </c>
       <c r="C13" t="n">
-        <v>33.0402</v>
+        <v>33.0054</v>
       </c>
       <c r="D13" t="n">
-        <v>62.4526</v>
+        <v>62.6593</v>
       </c>
       <c r="E13" t="n">
-        <v>17.0074</v>
+        <v>17.0271</v>
       </c>
       <c r="F13" t="n">
-        <v>59.571</v>
+        <v>52.5213</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>25.456</v>
+        <v>25.0175</v>
       </c>
       <c r="C14" t="n">
-        <v>32.5189</v>
+        <v>32.4557</v>
       </c>
       <c r="D14" t="n">
-        <v>62.1036</v>
+        <v>61.8921</v>
       </c>
       <c r="E14" t="n">
-        <v>16.486</v>
+        <v>16.5094</v>
       </c>
       <c r="F14" t="n">
-        <v>59.1623</v>
+        <v>51.9827</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>24.8806</v>
+        <v>24.6904</v>
       </c>
       <c r="C15" t="n">
-        <v>32.0149</v>
+        <v>31.9746</v>
       </c>
       <c r="D15" t="n">
-        <v>61.1951</v>
+        <v>61.1687</v>
       </c>
       <c r="E15" t="n">
-        <v>16.0102</v>
+        <v>16.0501</v>
       </c>
       <c r="F15" t="n">
-        <v>58.3988</v>
+        <v>51.3401</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>24.5073</v>
+        <v>24.1078</v>
       </c>
       <c r="C16" t="n">
-        <v>31.5379</v>
+        <v>31.5187</v>
       </c>
       <c r="D16" t="n">
-        <v>61.027</v>
+        <v>60.8042</v>
       </c>
       <c r="E16" t="n">
-        <v>15.6115</v>
+        <v>15.591</v>
       </c>
       <c r="F16" t="n">
-        <v>58.4448</v>
+        <v>50.9905</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>24.2656</v>
+        <v>23.9832</v>
       </c>
       <c r="C17" t="n">
-        <v>31.0875</v>
+        <v>31.0871</v>
       </c>
       <c r="D17" t="n">
-        <v>60.1909</v>
+        <v>59.9731</v>
       </c>
       <c r="E17" t="n">
-        <v>15.2072</v>
+        <v>15.2018</v>
       </c>
       <c r="F17" t="n">
-        <v>57.5992</v>
+        <v>50.4187</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>23.4978</v>
+        <v>23.548</v>
       </c>
       <c r="C18" t="n">
-        <v>30.6767</v>
+        <v>30.6399</v>
       </c>
       <c r="D18" t="n">
-        <v>60.0816</v>
+        <v>59.7318</v>
       </c>
       <c r="E18" t="n">
-        <v>14.8687</v>
+        <v>14.8388</v>
       </c>
       <c r="F18" t="n">
-        <v>57.5139</v>
+        <v>49.9674</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>23.2338</v>
+        <v>23.2565</v>
       </c>
       <c r="C19" t="n">
-        <v>30.3267</v>
+        <v>30.2551</v>
       </c>
       <c r="D19" t="n">
-        <v>59.4736</v>
+        <v>59.0738</v>
       </c>
       <c r="E19" t="n">
-        <v>14.5449</v>
+        <v>14.5202</v>
       </c>
       <c r="F19" t="n">
-        <v>56.8156</v>
+        <v>49.6366</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>22.5717</v>
+        <v>22.8484</v>
       </c>
       <c r="C20" t="n">
-        <v>29.8996</v>
+        <v>29.8851</v>
       </c>
       <c r="D20" t="n">
-        <v>59.3009</v>
+        <v>59.0241</v>
       </c>
       <c r="E20" t="n">
-        <v>14.3173</v>
+        <v>14.2853</v>
       </c>
       <c r="F20" t="n">
-        <v>56.7374</v>
+        <v>49.619</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>22.4276</v>
+        <v>22.3542</v>
       </c>
       <c r="C21" t="n">
-        <v>29.5504</v>
+        <v>29.5149</v>
       </c>
       <c r="D21" t="n">
-        <v>72.05670000000001</v>
+        <v>71.85939999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>27.1103</v>
+        <v>27.5542</v>
       </c>
       <c r="F21" t="n">
-        <v>64.5498</v>
+        <v>57.1531</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>22.469</v>
+        <v>21.9915</v>
       </c>
       <c r="C22" t="n">
-        <v>40.907</v>
+        <v>41.205</v>
       </c>
       <c r="D22" t="n">
-        <v>70.8643</v>
+        <v>70.5727</v>
       </c>
       <c r="E22" t="n">
-        <v>26.1062</v>
+        <v>26.5772</v>
       </c>
       <c r="F22" t="n">
-        <v>63.7311</v>
+        <v>56.2446</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>21.9586</v>
+        <v>21.9122</v>
       </c>
       <c r="C23" t="n">
-        <v>40.0342</v>
+        <v>40.3364</v>
       </c>
       <c r="D23" t="n">
-        <v>69.44759999999999</v>
+        <v>69.7711</v>
       </c>
       <c r="E23" t="n">
-        <v>25.3187</v>
+        <v>25.6551</v>
       </c>
       <c r="F23" t="n">
-        <v>62.694</v>
+        <v>55.7433</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>38.4282</v>
+        <v>37.2639</v>
       </c>
       <c r="C24" t="n">
-        <v>39.2434</v>
+        <v>39.491</v>
       </c>
       <c r="D24" t="n">
-        <v>68.93040000000001</v>
+        <v>68.4204</v>
       </c>
       <c r="E24" t="n">
-        <v>24.3677</v>
+        <v>24.768</v>
       </c>
       <c r="F24" t="n">
-        <v>62.0733</v>
+        <v>54.9944</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>40.5567</v>
+        <v>36.4023</v>
       </c>
       <c r="C25" t="n">
-        <v>38.5985</v>
+        <v>38.7626</v>
       </c>
       <c r="D25" t="n">
-        <v>68.1631</v>
+        <v>67.50060000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>23.506</v>
+        <v>23.9504</v>
       </c>
       <c r="F25" t="n">
-        <v>63.3757</v>
+        <v>54.2145</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>39.0952</v>
+        <v>35.3842</v>
       </c>
       <c r="C26" t="n">
-        <v>37.7441</v>
+        <v>37.9896</v>
       </c>
       <c r="D26" t="n">
-        <v>67.2449</v>
+        <v>66.9622</v>
       </c>
       <c r="E26" t="n">
-        <v>22.75</v>
+        <v>23.1087</v>
       </c>
       <c r="F26" t="n">
-        <v>60.9892</v>
+        <v>53.546</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>34.3439</v>
+        <v>34.1478</v>
       </c>
       <c r="C27" t="n">
-        <v>37.0282</v>
+        <v>37.2243</v>
       </c>
       <c r="D27" t="n">
-        <v>66.1764</v>
+        <v>65.2989</v>
       </c>
       <c r="E27" t="n">
-        <v>21.9861</v>
+        <v>22.3556</v>
       </c>
       <c r="F27" t="n">
-        <v>59.9115</v>
+        <v>50.5972</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>33.1346</v>
+        <v>38.8346</v>
       </c>
       <c r="C28" t="n">
-        <v>36.2884</v>
+        <v>36.6073</v>
       </c>
       <c r="D28" t="n">
-        <v>65.7229</v>
+        <v>64.4619</v>
       </c>
       <c r="E28" t="n">
-        <v>21.2344</v>
+        <v>21.53</v>
       </c>
       <c r="F28" t="n">
-        <v>59.6773</v>
+        <v>50.1471</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>32.6514</v>
+        <v>32.3454</v>
       </c>
       <c r="C29" t="n">
-        <v>35.7161</v>
+        <v>35.8876</v>
       </c>
       <c r="D29" t="n">
-        <v>64.9205</v>
+        <v>63.8939</v>
       </c>
       <c r="E29" t="n">
-        <v>20.6977</v>
+        <v>20.906</v>
       </c>
       <c r="F29" t="n">
-        <v>59.7181</v>
+        <v>49.6457</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>31.5395</v>
+        <v>31.6227</v>
       </c>
       <c r="C30" t="n">
-        <v>35.0275</v>
+        <v>35.3196</v>
       </c>
       <c r="D30" t="n">
-        <v>64.3888</v>
+        <v>63.1541</v>
       </c>
       <c r="E30" t="n">
-        <v>19.97</v>
+        <v>20.3128</v>
       </c>
       <c r="F30" t="n">
-        <v>58.558</v>
+        <v>49.1588</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>35.7659</v>
+        <v>31.0249</v>
       </c>
       <c r="C31" t="n">
-        <v>34.4448</v>
+        <v>34.6157</v>
       </c>
       <c r="D31" t="n">
-        <v>63.8605</v>
+        <v>62.8061</v>
       </c>
       <c r="E31" t="n">
-        <v>19.4001</v>
+        <v>19.7388</v>
       </c>
       <c r="F31" t="n">
-        <v>58.4482</v>
+        <v>48.8521</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>34.6568</v>
+        <v>32.9486</v>
       </c>
       <c r="C32" t="n">
-        <v>33.8561</v>
+        <v>34.0538</v>
       </c>
       <c r="D32" t="n">
-        <v>62.998</v>
+        <v>62.5989</v>
       </c>
       <c r="E32" t="n">
-        <v>18.8346</v>
+        <v>19.1218</v>
       </c>
       <c r="F32" t="n">
-        <v>57.1557</v>
+        <v>48.2129</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>33.7412</v>
+        <v>32.1105</v>
       </c>
       <c r="C33" t="n">
-        <v>33.3133</v>
+        <v>33.4759</v>
       </c>
       <c r="D33" t="n">
-        <v>62.4117</v>
+        <v>62.1167</v>
       </c>
       <c r="E33" t="n">
-        <v>18.3523</v>
+        <v>18.6192</v>
       </c>
       <c r="F33" t="n">
-        <v>56.8192</v>
+        <v>48.1063</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>28.462</v>
+        <v>31.8021</v>
       </c>
       <c r="C34" t="n">
-        <v>32.7529</v>
+        <v>32.9683</v>
       </c>
       <c r="D34" t="n">
-        <v>61.8171</v>
+        <v>61.6004</v>
       </c>
       <c r="E34" t="n">
-        <v>17.9594</v>
+        <v>18.1967</v>
       </c>
       <c r="F34" t="n">
-        <v>56.619</v>
+        <v>47.6413</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>27.9691</v>
+        <v>27.9672</v>
       </c>
       <c r="C35" t="n">
-        <v>32.3324</v>
+        <v>32.4787</v>
       </c>
       <c r="D35" t="n">
-        <v>75.6972</v>
+        <v>75.43819999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>31.0225</v>
+        <v>31.8191</v>
       </c>
       <c r="F35" t="n">
-        <v>66.4933</v>
+        <v>58.3998</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>31.6494</v>
+        <v>27.4628</v>
       </c>
       <c r="C36" t="n">
-        <v>31.8315</v>
+        <v>32.0749</v>
       </c>
       <c r="D36" t="n">
-        <v>74.4995</v>
+        <v>74.8236</v>
       </c>
       <c r="E36" t="n">
-        <v>30.1937</v>
+        <v>30.6734</v>
       </c>
       <c r="F36" t="n">
-        <v>65.2046</v>
+        <v>57.518</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>27.194</v>
+        <v>28.3167</v>
       </c>
       <c r="C37" t="n">
-        <v>42.8675</v>
+        <v>43.6148</v>
       </c>
       <c r="D37" t="n">
-        <v>73.1863</v>
+        <v>73.5167</v>
       </c>
       <c r="E37" t="n">
-        <v>28.9449</v>
+        <v>29.5074</v>
       </c>
       <c r="F37" t="n">
-        <v>64.3115</v>
+        <v>56.803</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>45.4751</v>
+        <v>49.4356</v>
       </c>
       <c r="C38" t="n">
-        <v>42.0049</v>
+        <v>42.4846</v>
       </c>
       <c r="D38" t="n">
-        <v>72.09610000000001</v>
+        <v>72.3215</v>
       </c>
       <c r="E38" t="n">
-        <v>27.8537</v>
+        <v>28.4954</v>
       </c>
       <c r="F38" t="n">
-        <v>63.5009</v>
+        <v>56.069</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>42.1117</v>
+        <v>48.0426</v>
       </c>
       <c r="C39" t="n">
-        <v>41.0434</v>
+        <v>41.4918</v>
       </c>
       <c r="D39" t="n">
-        <v>71.6049</v>
+        <v>71.3489</v>
       </c>
       <c r="E39" t="n">
-        <v>26.93</v>
+        <v>27.5278</v>
       </c>
       <c r="F39" t="n">
-        <v>62.9392</v>
+        <v>55.3121</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>43.6472</v>
+        <v>45.3474</v>
       </c>
       <c r="C40" t="n">
-        <v>40.2864</v>
+        <v>40.7152</v>
       </c>
       <c r="D40" t="n">
-        <v>70.02979999999999</v>
+        <v>70.18559999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>26.012</v>
+        <v>26.5783</v>
       </c>
       <c r="F40" t="n">
-        <v>62.1188</v>
+        <v>54.561</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>42.3715</v>
+        <v>44.108</v>
       </c>
       <c r="C41" t="n">
-        <v>39.3708</v>
+        <v>39.7697</v>
       </c>
       <c r="D41" t="n">
-        <v>68.92789999999999</v>
+        <v>69.8706</v>
       </c>
       <c r="E41" t="n">
-        <v>25.0549</v>
+        <v>25.6813</v>
       </c>
       <c r="F41" t="n">
-        <v>61.4518</v>
+        <v>53.9704</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>41.2942</v>
+        <v>42.6945</v>
       </c>
       <c r="C42" t="n">
-        <v>38.5249</v>
+        <v>39.0305</v>
       </c>
       <c r="D42" t="n">
-        <v>68.2475</v>
+        <v>68.7059</v>
       </c>
       <c r="E42" t="n">
-        <v>24.2298</v>
+        <v>24.8787</v>
       </c>
       <c r="F42" t="n">
-        <v>60.7958</v>
+        <v>53.1616</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>39.9383</v>
+        <v>41.7016</v>
       </c>
       <c r="C43" t="n">
-        <v>37.8091</v>
+        <v>38.0769</v>
       </c>
       <c r="D43" t="n">
-        <v>67.5097</v>
+        <v>67.90860000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>23.479</v>
+        <v>23.9451</v>
       </c>
       <c r="F43" t="n">
-        <v>60.3015</v>
+        <v>52.5541</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>39.0514</v>
+        <v>40.058</v>
       </c>
       <c r="C44" t="n">
-        <v>37.0534</v>
+        <v>37.6011</v>
       </c>
       <c r="D44" t="n">
-        <v>66.9552</v>
+        <v>67.2475</v>
       </c>
       <c r="E44" t="n">
-        <v>22.6868</v>
+        <v>23.1272</v>
       </c>
       <c r="F44" t="n">
-        <v>59.6961</v>
+        <v>51.9714</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>37.3482</v>
+        <v>39.0783</v>
       </c>
       <c r="C45" t="n">
-        <v>36.422</v>
+        <v>36.7357</v>
       </c>
       <c r="D45" t="n">
-        <v>66.2595</v>
+        <v>66.9556</v>
       </c>
       <c r="E45" t="n">
-        <v>22.1593</v>
+        <v>22.6074</v>
       </c>
       <c r="F45" t="n">
-        <v>59.1561</v>
+        <v>51.5978</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>36.3444</v>
+        <v>39.6368</v>
       </c>
       <c r="C46" t="n">
-        <v>35.903</v>
+        <v>36.0467</v>
       </c>
       <c r="D46" t="n">
-        <v>65.794</v>
+        <v>66.3413</v>
       </c>
       <c r="E46" t="n">
-        <v>21.3672</v>
+        <v>21.8533</v>
       </c>
       <c r="F46" t="n">
-        <v>58.6662</v>
+        <v>51.1564</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>33.5739</v>
+        <v>36.9021</v>
       </c>
       <c r="C47" t="n">
-        <v>35.0561</v>
+        <v>35.37</v>
       </c>
       <c r="D47" t="n">
-        <v>65.3672</v>
+        <v>65.9815</v>
       </c>
       <c r="E47" t="n">
-        <v>20.7705</v>
+        <v>21.2805</v>
       </c>
       <c r="F47" t="n">
-        <v>58.1065</v>
+        <v>50.5391</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>32.6644</v>
+        <v>35.9609</v>
       </c>
       <c r="C48" t="n">
-        <v>34.4981</v>
+        <v>34.9101</v>
       </c>
       <c r="D48" t="n">
-        <v>66.0081</v>
+        <v>65.4003</v>
       </c>
       <c r="E48" t="n">
-        <v>20.3314</v>
+        <v>20.7894</v>
       </c>
       <c r="F48" t="n">
-        <v>57.9305</v>
+        <v>50.2258</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>33.6926</v>
+        <v>35.0592</v>
       </c>
       <c r="C49" t="n">
-        <v>33.9234</v>
+        <v>34.1452</v>
       </c>
       <c r="D49" t="n">
-        <v>64.4817</v>
+        <v>66.3715</v>
       </c>
       <c r="E49" t="n">
-        <v>19.7612</v>
+        <v>20.2536</v>
       </c>
       <c r="F49" t="n">
-        <v>57.5885</v>
+        <v>49.9678</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>33.0911</v>
+        <v>36.5102</v>
       </c>
       <c r="C50" t="n">
-        <v>33.3551</v>
+        <v>33.6812</v>
       </c>
       <c r="D50" t="n">
-        <v>79.331</v>
+        <v>79.7419</v>
       </c>
       <c r="E50" t="n">
-        <v>32.3991</v>
+        <v>32.9187</v>
       </c>
       <c r="F50" t="n">
-        <v>67.3189</v>
+        <v>59.4553</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>30.5805</v>
+        <v>35.7158</v>
       </c>
       <c r="C51" t="n">
-        <v>44.6063</v>
+        <v>44.617</v>
       </c>
       <c r="D51" t="n">
-        <v>78.0052</v>
+        <v>78.3899</v>
       </c>
       <c r="E51" t="n">
-        <v>30.8427</v>
+        <v>31.9029</v>
       </c>
       <c r="F51" t="n">
-        <v>66.6643</v>
+        <v>58.7514</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>30.52</v>
+        <v>34.9006</v>
       </c>
       <c r="C52" t="n">
-        <v>43.4516</v>
+        <v>43.5398</v>
       </c>
       <c r="D52" t="n">
-        <v>76.42789999999999</v>
+        <v>77.2908</v>
       </c>
       <c r="E52" t="n">
-        <v>30.0207</v>
+        <v>30.7594</v>
       </c>
       <c r="F52" t="n">
-        <v>65.3379</v>
+        <v>58.1219</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>51.4175</v>
+        <v>56.5551</v>
       </c>
       <c r="C53" t="n">
-        <v>42.5577</v>
+        <v>42.4251</v>
       </c>
       <c r="D53" t="n">
-        <v>75.5578</v>
+        <v>75.96339999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>28.9173</v>
+        <v>29.4242</v>
       </c>
       <c r="F53" t="n">
-        <v>64.7418</v>
+        <v>57.2529</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>51.2303</v>
+        <v>54.9603</v>
       </c>
       <c r="C54" t="n">
-        <v>41.522</v>
+        <v>41.7974</v>
       </c>
       <c r="D54" t="n">
-        <v>74.27670000000001</v>
+        <v>74.7295</v>
       </c>
       <c r="E54" t="n">
-        <v>27.8449</v>
+        <v>28.5874</v>
       </c>
       <c r="F54" t="n">
-        <v>63.8966</v>
+        <v>56.3745</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>48.8116</v>
+        <v>52.5136</v>
       </c>
       <c r="C55" t="n">
-        <v>40.4759</v>
+        <v>40.7118</v>
       </c>
       <c r="D55" t="n">
-        <v>73.0063</v>
+        <v>73.7397</v>
       </c>
       <c r="E55" t="n">
-        <v>26.8069</v>
+        <v>27.3194</v>
       </c>
       <c r="F55" t="n">
-        <v>63.2467</v>
+        <v>55.7287</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>48.4814</v>
+        <v>50.9799</v>
       </c>
       <c r="C56" t="n">
-        <v>39.6083</v>
+        <v>39.9455</v>
       </c>
       <c r="D56" t="n">
-        <v>73.8467</v>
+        <v>72.7944</v>
       </c>
       <c r="E56" t="n">
-        <v>26.1346</v>
+        <v>26.7508</v>
       </c>
       <c r="F56" t="n">
-        <v>62.5738</v>
+        <v>54.9781</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>45.5066</v>
+        <v>49.531</v>
       </c>
       <c r="C57" t="n">
-        <v>38.868</v>
+        <v>39.0983</v>
       </c>
       <c r="D57" t="n">
-        <v>73.96850000000001</v>
+        <v>72.23180000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>25.3088</v>
+        <v>25.9553</v>
       </c>
       <c r="F57" t="n">
-        <v>61.6543</v>
+        <v>54.3932</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>45.3256</v>
+        <v>46.9108</v>
       </c>
       <c r="C58" t="n">
-        <v>38.1947</v>
+        <v>38.1598</v>
       </c>
       <c r="D58" t="n">
-        <v>71.68389999999999</v>
+        <v>71.13809999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>24.623</v>
+        <v>25.2808</v>
       </c>
       <c r="F58" t="n">
-        <v>60.9606</v>
+        <v>53.9057</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>44.0711</v>
+        <v>47.0803</v>
       </c>
       <c r="C59" t="n">
-        <v>37.3383</v>
+        <v>37.4622</v>
       </c>
       <c r="D59" t="n">
-        <v>69.6559</v>
+        <v>70.17740000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>24.0392</v>
+        <v>24.5445</v>
       </c>
       <c r="F59" t="n">
-        <v>60.8134</v>
+        <v>53.0697</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>42.9721</v>
+        <v>45.0517</v>
       </c>
       <c r="C60" t="n">
-        <v>36.7006</v>
+        <v>36.855</v>
       </c>
       <c r="D60" t="n">
-        <v>69.42149999999999</v>
+        <v>70.625</v>
       </c>
       <c r="E60" t="n">
-        <v>23.1465</v>
+        <v>23.3912</v>
       </c>
       <c r="F60" t="n">
-        <v>59.7746</v>
+        <v>52.6965</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>41.4203</v>
+        <v>42.9617</v>
       </c>
       <c r="C61" t="n">
-        <v>36.058</v>
+        <v>36.4187</v>
       </c>
       <c r="D61" t="n">
-        <v>68.864</v>
+        <v>70.7396</v>
       </c>
       <c r="E61" t="n">
-        <v>22.492</v>
+        <v>22.8129</v>
       </c>
       <c r="F61" t="n">
-        <v>59.6455</v>
+        <v>52.5483</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>40.1165</v>
+        <v>42.7144</v>
       </c>
       <c r="C62" t="n">
-        <v>35.4443</v>
+        <v>35.5471</v>
       </c>
       <c r="D62" t="n">
-        <v>68.215</v>
+        <v>70.1199</v>
       </c>
       <c r="E62" t="n">
-        <v>22.021</v>
+        <v>22.4666</v>
       </c>
       <c r="F62" t="n">
-        <v>59.3551</v>
+        <v>53.1034</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>39.6367</v>
+        <v>38.6815</v>
       </c>
       <c r="C63" t="n">
-        <v>34.9239</v>
+        <v>35.1793</v>
       </c>
       <c r="D63" t="n">
-        <v>67.90009999999999</v>
+        <v>69.2004</v>
       </c>
       <c r="E63" t="n">
-        <v>21.4999</v>
+        <v>21.8351</v>
       </c>
       <c r="F63" t="n">
-        <v>58.8212</v>
+        <v>51.8227</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>38.1311</v>
+        <v>37.2742</v>
       </c>
       <c r="C64" t="n">
-        <v>34.4336</v>
+        <v>34.6681</v>
       </c>
       <c r="D64" t="n">
-        <v>85.6472</v>
+        <v>85.37479999999999</v>
       </c>
       <c r="E64" t="n">
-        <v>34.9801</v>
+        <v>34.667</v>
       </c>
       <c r="F64" t="n">
-        <v>69.05289999999999</v>
+        <v>61.9093</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>38.0319</v>
+        <v>37.0709</v>
       </c>
       <c r="C65" t="n">
-        <v>45.6501</v>
+        <v>45.4978</v>
       </c>
       <c r="D65" t="n">
-        <v>84.8389</v>
+        <v>84.84569999999999</v>
       </c>
       <c r="E65" t="n">
-        <v>33.4875</v>
+        <v>33.7822</v>
       </c>
       <c r="F65" t="n">
-        <v>68.64149999999999</v>
+        <v>61.2465</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>36.9284</v>
+        <v>35.6491</v>
       </c>
       <c r="C66" t="n">
-        <v>44.1124</v>
+        <v>44.9195</v>
       </c>
       <c r="D66" t="n">
-        <v>81.20350000000001</v>
+        <v>82.9927</v>
       </c>
       <c r="E66" t="n">
-        <v>32.1179</v>
+        <v>32.6665</v>
       </c>
       <c r="F66" t="n">
-        <v>67.81619999999999</v>
+        <v>60.7382</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>59.4033</v>
+        <v>58.5094</v>
       </c>
       <c r="C67" t="n">
-        <v>43.5311</v>
+        <v>44.274</v>
       </c>
       <c r="D67" t="n">
-        <v>80.6652</v>
+        <v>81.23099999999999</v>
       </c>
       <c r="E67" t="n">
-        <v>30.9054</v>
+        <v>31.8234</v>
       </c>
       <c r="F67" t="n">
-        <v>67.5842</v>
+        <v>59.3882</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>57.8353</v>
+        <v>56.9024</v>
       </c>
       <c r="C68" t="n">
-        <v>42.638</v>
+        <v>42.8642</v>
       </c>
       <c r="D68" t="n">
-        <v>79.5027</v>
+        <v>79.7564</v>
       </c>
       <c r="E68" t="n">
-        <v>30.3036</v>
+        <v>30.1682</v>
       </c>
       <c r="F68" t="n">
-        <v>66.26990000000001</v>
+        <v>58.8328</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>57.1792</v>
+        <v>55.5213</v>
       </c>
       <c r="C69" t="n">
-        <v>41.6757</v>
+        <v>42.3487</v>
       </c>
       <c r="D69" t="n">
-        <v>79.00620000000001</v>
+        <v>78.0531</v>
       </c>
       <c r="E69" t="n">
-        <v>29.2132</v>
+        <v>30.0895</v>
       </c>
       <c r="F69" t="n">
-        <v>66.6079</v>
+        <v>57.9537</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>55.2641</v>
+        <v>54.0911</v>
       </c>
       <c r="C70" t="n">
-        <v>40.6579</v>
+        <v>40.8673</v>
       </c>
       <c r="D70" t="n">
-        <v>77.35469999999999</v>
+        <v>78.6931</v>
       </c>
       <c r="E70" t="n">
-        <v>27.9593</v>
+        <v>28.3176</v>
       </c>
       <c r="F70" t="n">
-        <v>64.8378</v>
+        <v>57.8927</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>54.0904</v>
+        <v>52.4425</v>
       </c>
       <c r="C71" t="n">
-        <v>40.1781</v>
+        <v>40.7009</v>
       </c>
       <c r="D71" t="n">
-        <v>75.82680000000001</v>
+        <v>76.2397</v>
       </c>
       <c r="E71" t="n">
-        <v>27.2355</v>
+        <v>27.6511</v>
       </c>
       <c r="F71" t="n">
-        <v>65.70440000000001</v>
+        <v>56.7917</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>52.932</v>
+        <v>51.5201</v>
       </c>
       <c r="C72" t="n">
-        <v>39.2122</v>
+        <v>39.2796</v>
       </c>
       <c r="D72" t="n">
-        <v>75.6944</v>
+        <v>77.0517</v>
       </c>
       <c r="E72" t="n">
-        <v>26.5803</v>
+        <v>27.2737</v>
       </c>
       <c r="F72" t="n">
-        <v>64.0716</v>
+        <v>56.3336</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>51.2573</v>
+        <v>49.5552</v>
       </c>
       <c r="C73" t="n">
-        <v>38.4568</v>
+        <v>38.7606</v>
       </c>
       <c r="D73" t="n">
-        <v>75.5771</v>
+        <v>75.4269</v>
       </c>
       <c r="E73" t="n">
-        <v>25.6148</v>
+        <v>26.3445</v>
       </c>
       <c r="F73" t="n">
-        <v>64.706</v>
+        <v>56.9753</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>50.0393</v>
+        <v>48.5306</v>
       </c>
       <c r="C74" t="n">
-        <v>38.2304</v>
+        <v>37.8971</v>
       </c>
       <c r="D74" t="n">
-        <v>74.9423</v>
+        <v>74.8599</v>
       </c>
       <c r="E74" t="n">
-        <v>24.7477</v>
+        <v>25.5829</v>
       </c>
       <c r="F74" t="n">
-        <v>62.5929</v>
+        <v>55.1627</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>48.645</v>
+        <v>46.8462</v>
       </c>
       <c r="C75" t="n">
-        <v>37.7347</v>
+        <v>37.3347</v>
       </c>
       <c r="D75" t="n">
-        <v>74.758</v>
+        <v>74.9659</v>
       </c>
       <c r="E75" t="n">
-        <v>24.169</v>
+        <v>24.6885</v>
       </c>
       <c r="F75" t="n">
-        <v>61.6802</v>
+        <v>54.8422</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>46.8446</v>
+        <v>45.6621</v>
       </c>
       <c r="C76" t="n">
-        <v>37.0587</v>
+        <v>36.827</v>
       </c>
       <c r="D76" t="n">
-        <v>73.9455</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="E76" t="n">
-        <v>23.5369</v>
+        <v>24.299</v>
       </c>
       <c r="F76" t="n">
-        <v>61.6633</v>
+        <v>54.2294</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>46.5109</v>
+        <v>44.8529</v>
       </c>
       <c r="C77" t="n">
-        <v>36.2143</v>
+        <v>36.2186</v>
       </c>
       <c r="D77" t="n">
-        <v>74.389</v>
+        <v>74.59699999999999</v>
       </c>
       <c r="E77" t="n">
-        <v>23.0207</v>
+        <v>23.3012</v>
       </c>
       <c r="F77" t="n">
-        <v>62.2263</v>
+        <v>54.5739</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>44.103</v>
+        <v>44.8371</v>
       </c>
       <c r="C78" t="n">
-        <v>35.6245</v>
+        <v>35.6405</v>
       </c>
       <c r="D78" t="n">
-        <v>109.719</v>
+        <v>108.704</v>
       </c>
       <c r="E78" t="n">
-        <v>37.089</v>
+        <v>36.9575</v>
       </c>
       <c r="F78" t="n">
-        <v>87.011</v>
+        <v>78.143</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>43.3392</v>
+        <v>43.7958</v>
       </c>
       <c r="C79" t="n">
-        <v>46.3813</v>
+        <v>47.4325</v>
       </c>
       <c r="D79" t="n">
-        <v>109.3</v>
+        <v>106.411</v>
       </c>
       <c r="E79" t="n">
-        <v>35.6134</v>
+        <v>36.6362</v>
       </c>
       <c r="F79" t="n">
-        <v>86.1031</v>
+        <v>77.4811</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>42.5235</v>
+        <v>42.9265</v>
       </c>
       <c r="C80" t="n">
-        <v>47.4919</v>
+        <v>48.3283</v>
       </c>
       <c r="D80" t="n">
-        <v>105.77</v>
+        <v>106.814</v>
       </c>
       <c r="E80" t="n">
-        <v>34.6973</v>
+        <v>35.1074</v>
       </c>
       <c r="F80" t="n">
-        <v>84.8002</v>
+        <v>78.74160000000001</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>62.5281</v>
+        <v>63.1849</v>
       </c>
       <c r="C81" t="n">
-        <v>47.1432</v>
+        <v>47.0582</v>
       </c>
       <c r="D81" t="n">
-        <v>105.508</v>
+        <v>105.205</v>
       </c>
       <c r="E81" t="n">
-        <v>34.0616</v>
+        <v>34.4282</v>
       </c>
       <c r="F81" t="n">
-        <v>84.4999</v>
+        <v>77.0583</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>62.4651</v>
+        <v>62.3854</v>
       </c>
       <c r="C82" t="n">
-        <v>46.2839</v>
+        <v>47.182</v>
       </c>
       <c r="D82" t="n">
-        <v>103.855</v>
+        <v>104.322</v>
       </c>
       <c r="E82" t="n">
-        <v>32.5643</v>
+        <v>33.3532</v>
       </c>
       <c r="F82" t="n">
-        <v>83.4342</v>
+        <v>76.1952</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>61.3873</v>
+        <v>61.7989</v>
       </c>
       <c r="C83" t="n">
-        <v>46.028</v>
+        <v>46.4808</v>
       </c>
       <c r="D83" t="n">
-        <v>102.959</v>
+        <v>103.946</v>
       </c>
       <c r="E83" t="n">
-        <v>32.3421</v>
+        <v>32.1156</v>
       </c>
       <c r="F83" t="n">
-        <v>81.5988</v>
+        <v>75.8946</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>60.5874</v>
+        <v>61.4047</v>
       </c>
       <c r="C84" t="n">
-        <v>45.9393</v>
+        <v>46.1447</v>
       </c>
       <c r="D84" t="n">
-        <v>102.084</v>
+        <v>104.055</v>
       </c>
       <c r="E84" t="n">
-        <v>31.3347</v>
+        <v>31.9289</v>
       </c>
       <c r="F84" t="n">
-        <v>81.59820000000001</v>
+        <v>75.46720000000001</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>59.4521</v>
+        <v>60.1118</v>
       </c>
       <c r="C85" t="n">
-        <v>45.3233</v>
+        <v>45.4475</v>
       </c>
       <c r="D85" t="n">
-        <v>102.458</v>
+        <v>103.655</v>
       </c>
       <c r="E85" t="n">
-        <v>30.1025</v>
+        <v>30.3901</v>
       </c>
       <c r="F85" t="n">
-        <v>80.19370000000001</v>
+        <v>73.14490000000001</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>59.1583</v>
+        <v>58.7341</v>
       </c>
       <c r="C86" t="n">
-        <v>45.0737</v>
+        <v>45.2397</v>
       </c>
       <c r="D86" t="n">
-        <v>101.9</v>
+        <v>102.993</v>
       </c>
       <c r="E86" t="n">
-        <v>29.2839</v>
+        <v>29.9414</v>
       </c>
       <c r="F86" t="n">
-        <v>78.62730000000001</v>
+        <v>71.602</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>57.8586</v>
+        <v>57.9094</v>
       </c>
       <c r="C87" t="n">
-        <v>44.3253</v>
+        <v>44.4425</v>
       </c>
       <c r="D87" t="n">
-        <v>102.408</v>
+        <v>103.427</v>
       </c>
       <c r="E87" t="n">
-        <v>28.5415</v>
+        <v>28.7214</v>
       </c>
       <c r="F87" t="n">
-        <v>77.88379999999999</v>
+        <v>71.3644</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>56.484</v>
+        <v>57.2194</v>
       </c>
       <c r="C88" t="n">
-        <v>44.0905</v>
+        <v>43.8415</v>
       </c>
       <c r="D88" t="n">
-        <v>102.841</v>
+        <v>103.831</v>
       </c>
       <c r="E88" t="n">
-        <v>27.8006</v>
+        <v>28.1824</v>
       </c>
       <c r="F88" t="n">
-        <v>76.6452</v>
+        <v>70.9217</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>55.2619</v>
+        <v>55.7679</v>
       </c>
       <c r="C89" t="n">
-        <v>43.229</v>
+        <v>43.8035</v>
       </c>
       <c r="D89" t="n">
-        <v>102.694</v>
+        <v>104.779</v>
       </c>
       <c r="E89" t="n">
-        <v>26.8653</v>
+        <v>27.9538</v>
       </c>
       <c r="F89" t="n">
-        <v>76.0575</v>
+        <v>69.2448</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>55.153</v>
+        <v>55.1232</v>
       </c>
       <c r="C90" t="n">
-        <v>42.9406</v>
+        <v>42.8894</v>
       </c>
       <c r="D90" t="n">
-        <v>104.472</v>
+        <v>104.916</v>
       </c>
       <c r="E90" t="n">
-        <v>26.2076</v>
+        <v>26.6527</v>
       </c>
       <c r="F90" t="n">
-        <v>74.5805</v>
+        <v>69.38339999999999</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>53.9211</v>
+        <v>53.7204</v>
       </c>
       <c r="C91" t="n">
-        <v>42.2992</v>
+        <v>42.6914</v>
       </c>
       <c r="D91" t="n">
-        <v>104.766</v>
+        <v>106.523</v>
       </c>
       <c r="E91" t="n">
-        <v>25.8121</v>
+        <v>26.0605</v>
       </c>
       <c r="F91" t="n">
-        <v>72.86199999999999</v>
+        <v>68.2265</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>52.5871</v>
+        <v>52.8322</v>
       </c>
       <c r="C92" t="n">
-        <v>41.6999</v>
+        <v>41.8336</v>
       </c>
       <c r="D92" t="n">
-        <v>147.217</v>
+        <v>147.065</v>
       </c>
       <c r="E92" t="n">
-        <v>38.7213</v>
+        <v>39.6541</v>
       </c>
       <c r="F92" t="n">
-        <v>104.491</v>
+        <v>99.3698</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>53.3876</v>
+        <v>51.801</v>
       </c>
       <c r="C93" t="n">
-        <v>41.1502</v>
+        <v>41.1229</v>
       </c>
       <c r="D93" t="n">
-        <v>145.947</v>
+        <v>148.693</v>
       </c>
       <c r="E93" t="n">
-        <v>38.5455</v>
+        <v>39.811</v>
       </c>
       <c r="F93" t="n">
-        <v>104.79</v>
+        <v>99.44289999999999</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>52.6466</v>
+        <v>50.6758</v>
       </c>
       <c r="C94" t="n">
-        <v>53.9078</v>
+        <v>53.6894</v>
       </c>
       <c r="D94" t="n">
-        <v>145.537</v>
+        <v>146.541</v>
       </c>
       <c r="E94" t="n">
-        <v>37.4974</v>
+        <v>38.613</v>
       </c>
       <c r="F94" t="n">
-        <v>103.216</v>
+        <v>98.9286</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>75.01439999999999</v>
+        <v>72.9233</v>
       </c>
       <c r="C95" t="n">
-        <v>54.5605</v>
+        <v>53.3535</v>
       </c>
       <c r="D95" t="n">
-        <v>144.928</v>
+        <v>146.01</v>
       </c>
       <c r="E95" t="n">
-        <v>37.178</v>
+        <v>37.6615</v>
       </c>
       <c r="F95" t="n">
-        <v>102.254</v>
+        <v>96.97969999999999</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>74.9427</v>
+        <v>72.5844</v>
       </c>
       <c r="C96" t="n">
-        <v>53.1933</v>
+        <v>53.6355</v>
       </c>
       <c r="D96" t="n">
-        <v>144.135</v>
+        <v>146.841</v>
       </c>
       <c r="E96" t="n">
-        <v>36.2481</v>
+        <v>36.1635</v>
       </c>
       <c r="F96" t="n">
-        <v>101.533</v>
+        <v>95.57550000000001</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>73.5056</v>
+        <v>71.8002</v>
       </c>
       <c r="C97" t="n">
-        <v>53.0684</v>
+        <v>52.9818</v>
       </c>
       <c r="D97" t="n">
-        <v>144.447</v>
+        <v>145.198</v>
       </c>
       <c r="E97" t="n">
-        <v>34.8441</v>
+        <v>35.2471</v>
       </c>
       <c r="F97" t="n">
-        <v>100.5</v>
+        <v>94.7987</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>73.1748</v>
+        <v>70.6781</v>
       </c>
       <c r="C98" t="n">
-        <v>52.9231</v>
+        <v>52.7919</v>
       </c>
       <c r="D98" t="n">
-        <v>144.523</v>
+        <v>144.611</v>
       </c>
       <c r="E98" t="n">
-        <v>34.2347</v>
+        <v>35.1207</v>
       </c>
       <c r="F98" t="n">
-        <v>99.18940000000001</v>
+        <v>93.0112</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>71.8824</v>
+        <v>70.06870000000001</v>
       </c>
       <c r="C99" t="n">
-        <v>53.2794</v>
+        <v>52.9828</v>
       </c>
       <c r="D99" t="n">
-        <v>143.764</v>
+        <v>144.028</v>
       </c>
       <c r="E99" t="n">
-        <v>33.2091</v>
+        <v>33.6012</v>
       </c>
       <c r="F99" t="n">
-        <v>98.0659</v>
+        <v>92.5986</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>71.3085</v>
+        <v>69.81319999999999</v>
       </c>
       <c r="C100" t="n">
-        <v>52.9035</v>
+        <v>52.5142</v>
       </c>
       <c r="D100" t="n">
-        <v>144.766</v>
+        <v>144.175</v>
       </c>
       <c r="E100" t="n">
-        <v>32.999</v>
+        <v>33.2809</v>
       </c>
       <c r="F100" t="n">
-        <v>97.0008</v>
+        <v>90.6302</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>70.42270000000001</v>
+        <v>69.1823</v>
       </c>
       <c r="C101" t="n">
-        <v>53.0302</v>
+        <v>53.1598</v>
       </c>
       <c r="D101" t="n">
-        <v>145.158</v>
+        <v>144.422</v>
       </c>
       <c r="E101" t="n">
-        <v>31.6431</v>
+        <v>32.2207</v>
       </c>
       <c r="F101" t="n">
-        <v>97.23099999999999</v>
+        <v>90.6134</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>67.3439</v>
+        <v>67.2676</v>
       </c>
       <c r="C102" t="n">
-        <v>52.3757</v>
+        <v>52.2283</v>
       </c>
       <c r="D102" t="n">
-        <v>146.467</v>
+        <v>145.588</v>
       </c>
       <c r="E102" t="n">
-        <v>31.4354</v>
+        <v>31.5929</v>
       </c>
       <c r="F102" t="n">
-        <v>96.48309999999999</v>
+        <v>89.5038</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>66.42959999999999</v>
+        <v>66.5273</v>
       </c>
       <c r="C103" t="n">
-        <v>52.5927</v>
+        <v>52.2376</v>
       </c>
       <c r="D103" t="n">
-        <v>146.294</v>
+        <v>147.216</v>
       </c>
       <c r="E103" t="n">
-        <v>30.3034</v>
+        <v>30.4162</v>
       </c>
       <c r="F103" t="n">
-        <v>94.4109</v>
+        <v>88.8235</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>65.37009999999999</v>
+        <v>66.1635</v>
       </c>
       <c r="C104" t="n">
-        <v>52.091</v>
+        <v>52.1445</v>
       </c>
       <c r="D104" t="n">
-        <v>146.927</v>
+        <v>147.155</v>
       </c>
       <c r="E104" t="n">
-        <v>30.0825</v>
+        <v>29.8571</v>
       </c>
       <c r="F104" t="n">
-        <v>93.5497</v>
+        <v>88.0196</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>64.8956</v>
+        <v>66.0681</v>
       </c>
       <c r="C105" t="n">
-        <v>51.7948</v>
+        <v>51.8814</v>
       </c>
       <c r="D105" t="n">
-        <v>147.394</v>
+        <v>150.509</v>
       </c>
       <c r="E105" t="n">
-        <v>29.1805</v>
+        <v>29.3647</v>
       </c>
       <c r="F105" t="n">
-        <v>92.3587</v>
+        <v>87.4739</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>64.9923</v>
+        <v>64.96210000000001</v>
       </c>
       <c r="C106" t="n">
-        <v>51.8931</v>
+        <v>52.1473</v>
       </c>
       <c r="D106" t="n">
-        <v>149.317</v>
+        <v>150.281</v>
       </c>
       <c r="E106" t="n">
-        <v>29.1644</v>
+        <v>28.9561</v>
       </c>
       <c r="F106" t="n">
-        <v>92.3699</v>
+        <v>86.95740000000001</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>63.5048</v>
+        <v>64.3797</v>
       </c>
       <c r="C107" t="n">
-        <v>52.1213</v>
+        <v>51.6847</v>
       </c>
       <c r="D107" t="n">
-        <v>193.297</v>
+        <v>193.864</v>
       </c>
       <c r="E107" t="n">
-        <v>42.4879</v>
+        <v>42.8176</v>
       </c>
       <c r="F107" t="n">
-        <v>125.558</v>
+        <v>121.145</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>63.5839</v>
+        <v>66.27930000000001</v>
       </c>
       <c r="C108" t="n">
-        <v>63.5594</v>
+        <v>64.22499999999999</v>
       </c>
       <c r="D108" t="n">
-        <v>193.022</v>
+        <v>192.083</v>
       </c>
       <c r="E108" t="n">
-        <v>41.8293</v>
+        <v>41.8207</v>
       </c>
       <c r="F108" t="n">
-        <v>124.608</v>
+        <v>119.474</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>62.8306</v>
+        <v>65.9928</v>
       </c>
       <c r="C109" t="n">
-        <v>64.46210000000001</v>
+        <v>63.571</v>
       </c>
       <c r="D109" t="n">
-        <v>190.609</v>
+        <v>190.39</v>
       </c>
       <c r="E109" t="n">
-        <v>40.7299</v>
+        <v>41.7862</v>
       </c>
       <c r="F109" t="n">
-        <v>123.968</v>
+        <v>118.479</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>84.726</v>
+        <v>89.04559999999999</v>
       </c>
       <c r="C110" t="n">
-        <v>64.429</v>
+        <v>63.4987</v>
       </c>
       <c r="D110" t="n">
-        <v>189.7</v>
+        <v>189.279</v>
       </c>
       <c r="E110" t="n">
-        <v>40.5106</v>
+        <v>40.3828</v>
       </c>
       <c r="F110" t="n">
-        <v>122.84</v>
+        <v>118.373</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>83.33750000000001</v>
+        <v>88.18000000000001</v>
       </c>
       <c r="C111" t="n">
-        <v>63.7514</v>
+        <v>63.3481</v>
       </c>
       <c r="D111" t="n">
-        <v>188.343</v>
+        <v>187.92</v>
       </c>
       <c r="E111" t="n">
-        <v>38.8751</v>
+        <v>40.1953</v>
       </c>
       <c r="F111" t="n">
-        <v>122.466</v>
+        <v>118.173</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>82.1397</v>
+        <v>87.2166</v>
       </c>
       <c r="C112" t="n">
-        <v>64.01900000000001</v>
+        <v>63.8063</v>
       </c>
       <c r="D112" t="n">
-        <v>188.594</v>
+        <v>187.713</v>
       </c>
       <c r="E112" t="n">
-        <v>37.8755</v>
+        <v>39.0598</v>
       </c>
       <c r="F112" t="n">
-        <v>121.271</v>
+        <v>117.021</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>80.1674</v>
+        <v>81.8061</v>
       </c>
       <c r="C113" t="n">
-        <v>64.4984</v>
+        <v>63.4393</v>
       </c>
       <c r="D113" t="n">
-        <v>187.755</v>
+        <v>187.578</v>
       </c>
       <c r="E113" t="n">
-        <v>37.6072</v>
+        <v>38.2524</v>
       </c>
       <c r="F113" t="n">
-        <v>120.343</v>
+        <v>116.79</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>84.19029999999999</v>
+        <v>80.4057</v>
       </c>
       <c r="C114" t="n">
-        <v>64.21169999999999</v>
+        <v>63.9362</v>
       </c>
       <c r="D114" t="n">
-        <v>187.37</v>
+        <v>186.877</v>
       </c>
       <c r="E114" t="n">
-        <v>37.1188</v>
+        <v>37.3124</v>
       </c>
       <c r="F114" t="n">
-        <v>119.98</v>
+        <v>115.741</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>83.23950000000001</v>
+        <v>80.2775</v>
       </c>
       <c r="C115" t="n">
-        <v>63.9321</v>
+        <v>63.7311</v>
       </c>
       <c r="D115" t="n">
-        <v>187.242</v>
+        <v>186.986</v>
       </c>
       <c r="E115" t="n">
-        <v>36.2498</v>
+        <v>36.539</v>
       </c>
       <c r="F115" t="n">
-        <v>120.501</v>
+        <v>115.268</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>82.4761</v>
+        <v>79.9177</v>
       </c>
       <c r="C116" t="n">
-        <v>64.5986</v>
+        <v>63.6255</v>
       </c>
       <c r="D116" t="n">
-        <v>187.192</v>
+        <v>187.112</v>
       </c>
       <c r="E116" t="n">
-        <v>35.8598</v>
+        <v>36.8086</v>
       </c>
       <c r="F116" t="n">
-        <v>118.044</v>
+        <v>115.164</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>78.76649999999999</v>
+        <v>78.4148</v>
       </c>
       <c r="C117" t="n">
-        <v>64.0283</v>
+        <v>63.6111</v>
       </c>
       <c r="D117" t="n">
-        <v>187.27</v>
+        <v>187.351</v>
       </c>
       <c r="E117" t="n">
-        <v>35.4087</v>
+        <v>35.5171</v>
       </c>
       <c r="F117" t="n">
-        <v>117.876</v>
+        <v>114.302</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>77.9081</v>
+        <v>77.38760000000001</v>
       </c>
       <c r="C118" t="n">
-        <v>63.4198</v>
+        <v>63.5557</v>
       </c>
       <c r="D118" t="n">
-        <v>187.852</v>
+        <v>188.081</v>
       </c>
       <c r="E118" t="n">
-        <v>35.2831</v>
+        <v>35.2477</v>
       </c>
       <c r="F118" t="n">
-        <v>117.86</v>
+        <v>113.774</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>77.57989999999999</v>
+        <v>77.6863</v>
       </c>
       <c r="C119" t="n">
-        <v>63.9338</v>
+        <v>63.3491</v>
       </c>
       <c r="D119" t="n">
-        <v>188.014</v>
+        <v>188.596</v>
       </c>
       <c r="E119" t="n">
-        <v>34.2456</v>
+        <v>34.1427</v>
       </c>
       <c r="F119" t="n">
-        <v>118.325</v>
+        <v>114.12</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>77.84650000000001</v>
+        <v>75.9879</v>
       </c>
       <c r="C120" t="n">
-        <v>63.7205</v>
+        <v>63.7159</v>
       </c>
       <c r="D120" t="n">
-        <v>189.272</v>
+        <v>189.903</v>
       </c>
       <c r="E120" t="n">
-        <v>33.6826</v>
+        <v>33.6983</v>
       </c>
       <c r="F120" t="n">
-        <v>116.941</v>
+        <v>113.193</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>77.1922</v>
+        <v>76.37909999999999</v>
       </c>
       <c r="C121" t="n">
-        <v>63.1871</v>
+        <v>62.918</v>
       </c>
       <c r="D121" t="n">
-        <v>236.748</v>
+        <v>236.661</v>
       </c>
       <c r="E121" t="n">
-        <v>47.622</v>
+        <v>47.7151</v>
       </c>
       <c r="F121" t="n">
-        <v>152.798</v>
+        <v>147.647</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>76.54730000000001</v>
+        <v>76.2084</v>
       </c>
       <c r="C122" t="n">
-        <v>75.5356</v>
+        <v>74.5658</v>
       </c>
       <c r="D122" t="n">
-        <v>233.846</v>
+        <v>233.481</v>
       </c>
       <c r="E122" t="n">
-        <v>46.539</v>
+        <v>47.5336</v>
       </c>
       <c r="F122" t="n">
-        <v>150.316</v>
+        <v>146.515</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>75.0155</v>
+        <v>74.4308</v>
       </c>
       <c r="C123" t="n">
-        <v>75.4644</v>
+        <v>75.5217</v>
       </c>
       <c r="D123" t="n">
-        <v>230.926</v>
+        <v>231.238</v>
       </c>
       <c r="E123" t="n">
-        <v>46.3626</v>
+        <v>46.8253</v>
       </c>
       <c r="F123" t="n">
-        <v>150.925</v>
+        <v>145.763</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>98.5401</v>
+        <v>99.03360000000001</v>
       </c>
       <c r="C124" t="n">
-        <v>76.2743</v>
+        <v>75.6187</v>
       </c>
       <c r="D124" t="n">
-        <v>229.49</v>
+        <v>229.089</v>
       </c>
       <c r="E124" t="n">
-        <v>46.7089</v>
+        <v>46.1946</v>
       </c>
       <c r="F124" t="n">
-        <v>148.404</v>
+        <v>145.147</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>97.9187</v>
+        <v>93.4567</v>
       </c>
       <c r="C125" t="n">
-        <v>76.1992</v>
+        <v>75.70010000000001</v>
       </c>
       <c r="D125" t="n">
-        <v>227.807</v>
+        <v>227.296</v>
       </c>
       <c r="E125" t="n">
-        <v>44.9726</v>
+        <v>45.8871</v>
       </c>
       <c r="F125" t="n">
-        <v>147.325</v>
+        <v>143.947</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>94.89570000000001</v>
+        <v>93.1061</v>
       </c>
       <c r="C126" t="n">
-        <v>76.9999</v>
+        <v>76.5934</v>
       </c>
       <c r="D126" t="n">
-        <v>226.138</v>
+        <v>225.64</v>
       </c>
       <c r="E126" t="n">
-        <v>45.5775</v>
+        <v>45.3206</v>
       </c>
       <c r="F126" t="n">
-        <v>147.328</v>
+        <v>143.801</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>95.4455</v>
+        <v>95.1961</v>
       </c>
       <c r="C127" t="n">
-        <v>76.6061</v>
+        <v>76.465</v>
       </c>
       <c r="D127" t="n">
-        <v>225.884</v>
+        <v>224.959</v>
       </c>
       <c r="E127" t="n">
-        <v>45.0646</v>
+        <v>45.3732</v>
       </c>
       <c r="F127" t="n">
-        <v>146.386</v>
+        <v>142.858</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>93.7349</v>
+        <v>94.5926</v>
       </c>
       <c r="C128" t="n">
-        <v>76.8014</v>
+        <v>75.9992</v>
       </c>
       <c r="D128" t="n">
-        <v>224.059</v>
+        <v>223.148</v>
       </c>
       <c r="E128" t="n">
-        <v>44.1274</v>
+        <v>44.4803</v>
       </c>
       <c r="F128" t="n">
-        <v>145.931</v>
+        <v>143.391</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>92.80500000000001</v>
+        <v>92.4046</v>
       </c>
       <c r="C129" t="n">
-        <v>77.0333</v>
+        <v>76.471</v>
       </c>
       <c r="D129" t="n">
-        <v>222.598</v>
+        <v>222.213</v>
       </c>
       <c r="E129" t="n">
-        <v>43.2704</v>
+        <v>43.0778</v>
       </c>
       <c r="F129" t="n">
-        <v>145.133</v>
+        <v>142.226</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>92.6435</v>
+        <v>92.8044</v>
       </c>
       <c r="C130" t="n">
-        <v>77.0656</v>
+        <v>76.8694</v>
       </c>
       <c r="D130" t="n">
-        <v>222.602</v>
+        <v>221.492</v>
       </c>
       <c r="E130" t="n">
-        <v>42.7758</v>
+        <v>43.1879</v>
       </c>
       <c r="F130" t="n">
-        <v>144.585</v>
+        <v>141.717</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>93.2059</v>
+        <v>94.37820000000001</v>
       </c>
       <c r="C131" t="n">
-        <v>77.345</v>
+        <v>76.9438</v>
       </c>
       <c r="D131" t="n">
-        <v>221.431</v>
+        <v>221.374</v>
       </c>
       <c r="E131" t="n">
-        <v>42.6829</v>
+        <v>42.2446</v>
       </c>
       <c r="F131" t="n">
-        <v>143.88</v>
+        <v>141.149</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>93.7197</v>
+        <v>93.6129</v>
       </c>
       <c r="C132" t="n">
-        <v>76.9885</v>
+        <v>76.8878</v>
       </c>
       <c r="D132" t="n">
-        <v>221.827</v>
+        <v>221.139</v>
       </c>
       <c r="E132" t="n">
-        <v>42.3416</v>
+        <v>42.234</v>
       </c>
       <c r="F132" t="n">
-        <v>144.014</v>
+        <v>140.933</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>91.4773</v>
+        <v>90.8382</v>
       </c>
       <c r="C133" t="n">
-        <v>77.8626</v>
+        <v>77.3408</v>
       </c>
       <c r="D133" t="n">
-        <v>221.709</v>
+        <v>221.388</v>
       </c>
       <c r="E133" t="n">
-        <v>42.2279</v>
+        <v>41.6107</v>
       </c>
       <c r="F133" t="n">
-        <v>143.337</v>
+        <v>140.709</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>90.95</v>
+        <v>90.2216</v>
       </c>
       <c r="C134" t="n">
-        <v>77.4563</v>
+        <v>77.4388</v>
       </c>
       <c r="D134" t="n">
-        <v>222.198</v>
+        <v>221.298</v>
       </c>
       <c r="E134" t="n">
-        <v>41.8498</v>
+        <v>41.6782</v>
       </c>
       <c r="F134" t="n">
-        <v>143.276</v>
+        <v>140.609</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>92.71380000000001</v>
+        <v>90.8436</v>
       </c>
       <c r="C135" t="n">
-        <v>77.9081</v>
+        <v>77.6793</v>
       </c>
       <c r="D135" t="n">
-        <v>271.643</v>
+        <v>271.277</v>
       </c>
       <c r="E135" t="n">
-        <v>55.7728</v>
+        <v>56.9388</v>
       </c>
       <c r="F135" t="n">
-        <v>178.998</v>
+        <v>176.076</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>89.56780000000001</v>
+        <v>90.1656</v>
       </c>
       <c r="C136" t="n">
-        <v>90.08110000000001</v>
+        <v>89.5736</v>
       </c>
       <c r="D136" t="n">
-        <v>267.937</v>
+        <v>267.138</v>
       </c>
       <c r="E136" t="n">
-        <v>55.3626</v>
+        <v>55.7189</v>
       </c>
       <c r="F136" t="n">
-        <v>176.962</v>
+        <v>174.896</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>90.1421</v>
+        <v>90.6833</v>
       </c>
       <c r="C137" t="n">
-        <v>90.1823</v>
+        <v>90.5411</v>
       </c>
       <c r="D137" t="n">
-        <v>265.056</v>
+        <v>264.125</v>
       </c>
       <c r="E137" t="n">
-        <v>55.1323</v>
+        <v>55.3839</v>
       </c>
       <c r="F137" t="n">
-        <v>175.747</v>
+        <v>173.561</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>109.914</v>
+        <v>109.328</v>
       </c>
       <c r="C138" t="n">
-        <v>91.0192</v>
+        <v>90.4611</v>
       </c>
       <c r="D138" t="n">
-        <v>261.856</v>
+        <v>261.384</v>
       </c>
       <c r="E138" t="n">
-        <v>54.992</v>
+        <v>54.7556</v>
       </c>
       <c r="F138" t="n">
-        <v>173.945</v>
+        <v>172.067</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>111.501</v>
+        <v>109.264</v>
       </c>
       <c r="C139" t="n">
-        <v>91.02030000000001</v>
+        <v>90.9991</v>
       </c>
       <c r="D139" t="n">
-        <v>259.091</v>
+        <v>258.729</v>
       </c>
       <c r="E139" t="n">
-        <v>54.9561</v>
+        <v>54.6492</v>
       </c>
       <c r="F139" t="n">
-        <v>173.168</v>
+        <v>170.886</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>107.568</v>
+        <v>108.017</v>
       </c>
       <c r="C140" t="n">
-        <v>91.33969999999999</v>
+        <v>91.55029999999999</v>
       </c>
       <c r="D140" t="n">
-        <v>256.158</v>
+        <v>256.599</v>
       </c>
       <c r="E140" t="n">
-        <v>54.7707</v>
+        <v>54.4932</v>
       </c>
       <c r="F140" t="n">
-        <v>171.793</v>
+        <v>169.381</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>110.922</v>
+        <v>110.171</v>
       </c>
       <c r="C141" t="n">
-        <v>91.7851</v>
+        <v>91.6776</v>
       </c>
       <c r="D141" t="n">
-        <v>254.515</v>
+        <v>254.125</v>
       </c>
       <c r="E141" t="n">
-        <v>54.4996</v>
+        <v>54.6073</v>
       </c>
       <c r="F141" t="n">
-        <v>170.952</v>
+        <v>168.646</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>107.535</v>
+        <v>106.678</v>
       </c>
       <c r="C142" t="n">
-        <v>92.15260000000001</v>
+        <v>92.1191</v>
       </c>
       <c r="D142" t="n">
-        <v>253.107</v>
+        <v>252.596</v>
       </c>
       <c r="E142" t="n">
-        <v>54.106</v>
+        <v>54.0272</v>
       </c>
       <c r="F142" t="n">
-        <v>169.715</v>
+        <v>167.805</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>108.084</v>
+        <v>109.503</v>
       </c>
       <c r="C143" t="n">
-        <v>92.1187</v>
+        <v>92.2269</v>
       </c>
       <c r="D143" t="n">
-        <v>251.333</v>
+        <v>250.778</v>
       </c>
       <c r="E143" t="n">
-        <v>53.693</v>
+        <v>53.8424</v>
       </c>
       <c r="F143" t="n">
-        <v>168.837</v>
+        <v>167.012</v>
       </c>
     </row>
   </sheetData>

--- a/vs-x64/Running insertion.xlsx
+++ b/vs-x64/Running insertion.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>24.3557</v>
+        <v>24.1324</v>
       </c>
       <c r="C2" t="n">
-        <v>31.2631</v>
+        <v>31.1801</v>
       </c>
       <c r="D2" t="n">
-        <v>59.0792</v>
+        <v>58.8252</v>
       </c>
       <c r="E2" t="n">
-        <v>15.0223</v>
+        <v>14.3322</v>
       </c>
       <c r="F2" t="n">
-        <v>51.4542</v>
+        <v>50.5636</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>22.7475</v>
+        <v>22.4517</v>
       </c>
       <c r="C3" t="n">
-        <v>30.6708</v>
+        <v>30.679</v>
       </c>
       <c r="D3" t="n">
-        <v>58.614</v>
+        <v>58.4708</v>
       </c>
       <c r="E3" t="n">
-        <v>14.6587</v>
+        <v>13.995</v>
       </c>
       <c r="F3" t="n">
-        <v>50.652</v>
+        <v>49.8191</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>22.369</v>
+        <v>22.4103</v>
       </c>
       <c r="C4" t="n">
-        <v>30.3237</v>
+        <v>30.2872</v>
       </c>
       <c r="D4" t="n">
-        <v>58.073</v>
+        <v>57.994</v>
       </c>
       <c r="E4" t="n">
-        <v>14.2385</v>
+        <v>13.6182</v>
       </c>
       <c r="F4" t="n">
-        <v>50.3777</v>
+        <v>49.6799</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>21.7221</v>
+        <v>21.7879</v>
       </c>
       <c r="C5" t="n">
-        <v>29.8641</v>
+        <v>29.8824</v>
       </c>
       <c r="D5" t="n">
-        <v>57.6457</v>
+        <v>57.24</v>
       </c>
       <c r="E5" t="n">
-        <v>14.0112</v>
+        <v>20.8127</v>
       </c>
       <c r="F5" t="n">
-        <v>49.9137</v>
+        <v>56.4616</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>21.3324</v>
+        <v>21.6632</v>
       </c>
       <c r="C6" t="n">
-        <v>29.4883</v>
+        <v>29.5056</v>
       </c>
       <c r="D6" t="n">
-        <v>57.0047</v>
+        <v>56.6517</v>
       </c>
       <c r="E6" t="n">
-        <v>13.6632</v>
+        <v>20.0676</v>
       </c>
       <c r="F6" t="n">
-        <v>49.4395</v>
+        <v>55.5649</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>21.4016</v>
+        <v>21.4911</v>
       </c>
       <c r="C7" t="n">
-        <v>29.1308</v>
+        <v>29.1891</v>
       </c>
       <c r="D7" t="n">
-        <v>68.24769999999999</v>
+        <v>68.04259999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>20.7011</v>
+        <v>19.4905</v>
       </c>
       <c r="F7" t="n">
-        <v>56.2611</v>
+        <v>54.6526</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>20.9004</v>
+        <v>20.896</v>
       </c>
       <c r="C8" t="n">
-        <v>35.9211</v>
+        <v>35.857</v>
       </c>
       <c r="D8" t="n">
-        <v>67.119</v>
+        <v>66.86069999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>19.9926</v>
+        <v>18.8181</v>
       </c>
       <c r="F8" t="n">
-        <v>55.8907</v>
+        <v>54.5351</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>21.1021</v>
+        <v>21.0178</v>
       </c>
       <c r="C9" t="n">
-        <v>35.3655</v>
+        <v>35.1777</v>
       </c>
       <c r="D9" t="n">
-        <v>66.1602</v>
+        <v>65.5998</v>
       </c>
       <c r="E9" t="n">
-        <v>19.331</v>
+        <v>18.2189</v>
       </c>
       <c r="F9" t="n">
-        <v>55.0424</v>
+        <v>53.7144</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>28.5375</v>
+        <v>27.8055</v>
       </c>
       <c r="C10" t="n">
-        <v>34.7023</v>
+        <v>34.6456</v>
       </c>
       <c r="D10" t="n">
-        <v>64.9256</v>
+        <v>64.89360000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>18.6931</v>
+        <v>17.6406</v>
       </c>
       <c r="F10" t="n">
-        <v>54.1279</v>
+        <v>52.9754</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>27.7805</v>
+        <v>27.1702</v>
       </c>
       <c r="C11" t="n">
-        <v>34.0618</v>
+        <v>34.0132</v>
       </c>
       <c r="D11" t="n">
-        <v>64.05589999999999</v>
+        <v>64.01779999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>18.1129</v>
+        <v>17.1037</v>
       </c>
       <c r="F11" t="n">
-        <v>53.8072</v>
+        <v>52.6398</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>26.8278</v>
+        <v>26.6562</v>
       </c>
       <c r="C12" t="n">
-        <v>33.5339</v>
+        <v>33.491</v>
       </c>
       <c r="D12" t="n">
-        <v>63.2388</v>
+        <v>63.1018</v>
       </c>
       <c r="E12" t="n">
-        <v>17.6</v>
+        <v>16.5874</v>
       </c>
       <c r="F12" t="n">
-        <v>53.2845</v>
+        <v>51.7829</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>25.714</v>
+        <v>25.8968</v>
       </c>
       <c r="C13" t="n">
-        <v>33.0054</v>
+        <v>32.9463</v>
       </c>
       <c r="D13" t="n">
-        <v>62.6593</v>
+        <v>62.3595</v>
       </c>
       <c r="E13" t="n">
-        <v>17.0271</v>
+        <v>16.0813</v>
       </c>
       <c r="F13" t="n">
-        <v>52.5213</v>
+        <v>51.1377</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>25.0175</v>
+        <v>25.357</v>
       </c>
       <c r="C14" t="n">
-        <v>32.4557</v>
+        <v>32.4269</v>
       </c>
       <c r="D14" t="n">
-        <v>61.8921</v>
+        <v>61.7376</v>
       </c>
       <c r="E14" t="n">
-        <v>16.5094</v>
+        <v>15.6795</v>
       </c>
       <c r="F14" t="n">
-        <v>51.9827</v>
+        <v>50.8262</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>24.6904</v>
+        <v>24.8903</v>
       </c>
       <c r="C15" t="n">
-        <v>31.9746</v>
+        <v>31.9557</v>
       </c>
       <c r="D15" t="n">
-        <v>61.1687</v>
+        <v>60.9979</v>
       </c>
       <c r="E15" t="n">
-        <v>16.0501</v>
+        <v>15.2515</v>
       </c>
       <c r="F15" t="n">
-        <v>51.3401</v>
+        <v>50.4692</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>24.1078</v>
+        <v>24.6595</v>
       </c>
       <c r="C16" t="n">
-        <v>31.5187</v>
+        <v>31.5076</v>
       </c>
       <c r="D16" t="n">
-        <v>60.8042</v>
+        <v>60.6749</v>
       </c>
       <c r="E16" t="n">
-        <v>15.591</v>
+        <v>14.7907</v>
       </c>
       <c r="F16" t="n">
-        <v>50.9905</v>
+        <v>50.111</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>23.9832</v>
+        <v>23.5938</v>
       </c>
       <c r="C17" t="n">
-        <v>31.0871</v>
+        <v>31.0229</v>
       </c>
       <c r="D17" t="n">
-        <v>59.9731</v>
+        <v>60.0116</v>
       </c>
       <c r="E17" t="n">
-        <v>15.2018</v>
+        <v>14.4548</v>
       </c>
       <c r="F17" t="n">
-        <v>50.4187</v>
+        <v>49.5363</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>23.548</v>
+        <v>23.2195</v>
       </c>
       <c r="C18" t="n">
-        <v>30.6399</v>
+        <v>30.5974</v>
       </c>
       <c r="D18" t="n">
-        <v>59.7318</v>
+        <v>59.6165</v>
       </c>
       <c r="E18" t="n">
-        <v>14.8388</v>
+        <v>14.1074</v>
       </c>
       <c r="F18" t="n">
-        <v>49.9674</v>
+        <v>49.1449</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>23.2565</v>
+        <v>23.049</v>
       </c>
       <c r="C19" t="n">
-        <v>30.2551</v>
+        <v>30.2641</v>
       </c>
       <c r="D19" t="n">
-        <v>59.0738</v>
+        <v>59.018</v>
       </c>
       <c r="E19" t="n">
-        <v>14.5202</v>
+        <v>13.8624</v>
       </c>
       <c r="F19" t="n">
-        <v>49.6366</v>
+        <v>48.9072</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>22.8484</v>
+        <v>22.6531</v>
       </c>
       <c r="C20" t="n">
-        <v>29.8851</v>
+        <v>29.8651</v>
       </c>
       <c r="D20" t="n">
-        <v>59.0241</v>
+        <v>58.8292</v>
       </c>
       <c r="E20" t="n">
-        <v>14.2853</v>
+        <v>27.173</v>
       </c>
       <c r="F20" t="n">
-        <v>49.619</v>
+        <v>56.3604</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>22.3542</v>
+        <v>22.2285</v>
       </c>
       <c r="C21" t="n">
-        <v>29.5149</v>
+        <v>29.4657</v>
       </c>
       <c r="D21" t="n">
-        <v>71.85939999999999</v>
+        <v>71.541</v>
       </c>
       <c r="E21" t="n">
-        <v>27.5542</v>
+        <v>26.3287</v>
       </c>
       <c r="F21" t="n">
-        <v>57.1531</v>
+        <v>55.2826</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>21.9915</v>
+        <v>22.002</v>
       </c>
       <c r="C22" t="n">
-        <v>41.205</v>
+        <v>40.8162</v>
       </c>
       <c r="D22" t="n">
-        <v>70.5727</v>
+        <v>70.3608</v>
       </c>
       <c r="E22" t="n">
-        <v>26.5772</v>
+        <v>25.3449</v>
       </c>
       <c r="F22" t="n">
-        <v>56.2446</v>
+        <v>54.5612</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>21.9122</v>
+        <v>21.9659</v>
       </c>
       <c r="C23" t="n">
-        <v>40.3364</v>
+        <v>39.9276</v>
       </c>
       <c r="D23" t="n">
-        <v>69.7711</v>
+        <v>69.45099999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>25.6551</v>
+        <v>24.4437</v>
       </c>
       <c r="F23" t="n">
-        <v>55.7433</v>
+        <v>53.6598</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>37.2639</v>
+        <v>37.771</v>
       </c>
       <c r="C24" t="n">
-        <v>39.491</v>
+        <v>39.2904</v>
       </c>
       <c r="D24" t="n">
-        <v>68.4204</v>
+        <v>68.50279999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>24.768</v>
+        <v>23.611</v>
       </c>
       <c r="F24" t="n">
-        <v>54.9944</v>
+        <v>53.2714</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>36.4023</v>
+        <v>41.007</v>
       </c>
       <c r="C25" t="n">
-        <v>38.7626</v>
+        <v>38.4173</v>
       </c>
       <c r="D25" t="n">
-        <v>67.50060000000001</v>
+        <v>67.35299999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>23.9504</v>
+        <v>22.7778</v>
       </c>
       <c r="F25" t="n">
-        <v>54.2145</v>
+        <v>52.5852</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>35.3842</v>
+        <v>39.628</v>
       </c>
       <c r="C26" t="n">
-        <v>37.9896</v>
+        <v>37.6683</v>
       </c>
       <c r="D26" t="n">
-        <v>66.9622</v>
+        <v>66.61190000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>23.1087</v>
+        <v>21.9897</v>
       </c>
       <c r="F26" t="n">
-        <v>53.546</v>
+        <v>51.9192</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>34.1478</v>
+        <v>38.5894</v>
       </c>
       <c r="C27" t="n">
-        <v>37.2243</v>
+        <v>37.0208</v>
       </c>
       <c r="D27" t="n">
-        <v>65.2989</v>
+        <v>64.51049999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>22.3556</v>
+        <v>21.2517</v>
       </c>
       <c r="F27" t="n">
-        <v>50.5972</v>
+        <v>50.3964</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>38.8346</v>
+        <v>37.3781</v>
       </c>
       <c r="C28" t="n">
-        <v>36.6073</v>
+        <v>36.3221</v>
       </c>
       <c r="D28" t="n">
-        <v>64.4619</v>
+        <v>63.7333</v>
       </c>
       <c r="E28" t="n">
-        <v>21.53</v>
+        <v>20.6475</v>
       </c>
       <c r="F28" t="n">
-        <v>50.1471</v>
+        <v>49.9688</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>32.3454</v>
+        <v>31.9718</v>
       </c>
       <c r="C29" t="n">
-        <v>35.8876</v>
+        <v>35.6908</v>
       </c>
       <c r="D29" t="n">
-        <v>63.8939</v>
+        <v>63.1972</v>
       </c>
       <c r="E29" t="n">
-        <v>20.906</v>
+        <v>20.0872</v>
       </c>
       <c r="F29" t="n">
-        <v>49.6457</v>
+        <v>49.4579</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>31.6227</v>
+        <v>31.628</v>
       </c>
       <c r="C30" t="n">
-        <v>35.3196</v>
+        <v>35.0472</v>
       </c>
       <c r="D30" t="n">
-        <v>63.1541</v>
+        <v>62.6654</v>
       </c>
       <c r="E30" t="n">
-        <v>20.3128</v>
+        <v>19.5071</v>
       </c>
       <c r="F30" t="n">
-        <v>49.1588</v>
+        <v>48.9781</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>31.0249</v>
+        <v>30.6983</v>
       </c>
       <c r="C31" t="n">
-        <v>34.6157</v>
+        <v>34.4785</v>
       </c>
       <c r="D31" t="n">
-        <v>62.8061</v>
+        <v>62.1631</v>
       </c>
       <c r="E31" t="n">
-        <v>19.7388</v>
+        <v>18.9425</v>
       </c>
       <c r="F31" t="n">
-        <v>48.8521</v>
+        <v>48.5768</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>32.9486</v>
+        <v>29.9394</v>
       </c>
       <c r="C32" t="n">
-        <v>34.0538</v>
+        <v>33.8581</v>
       </c>
       <c r="D32" t="n">
-        <v>62.5989</v>
+        <v>61.7372</v>
       </c>
       <c r="E32" t="n">
-        <v>19.1218</v>
+        <v>18.335</v>
       </c>
       <c r="F32" t="n">
-        <v>48.2129</v>
+        <v>48.3456</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>32.1105</v>
+        <v>29.2943</v>
       </c>
       <c r="C33" t="n">
-        <v>33.4759</v>
+        <v>33.4087</v>
       </c>
       <c r="D33" t="n">
-        <v>62.1167</v>
+        <v>61.5315</v>
       </c>
       <c r="E33" t="n">
-        <v>18.6192</v>
+        <v>17.9064</v>
       </c>
       <c r="F33" t="n">
-        <v>48.1063</v>
+        <v>48.1122</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>31.8021</v>
+        <v>28.3864</v>
       </c>
       <c r="C34" t="n">
-        <v>32.9683</v>
+        <v>32.8166</v>
       </c>
       <c r="D34" t="n">
-        <v>61.6004</v>
+        <v>61.0412</v>
       </c>
       <c r="E34" t="n">
-        <v>18.1967</v>
+        <v>31.8228</v>
       </c>
       <c r="F34" t="n">
-        <v>47.6413</v>
+        <v>58.0294</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>27.9672</v>
+        <v>28.0514</v>
       </c>
       <c r="C35" t="n">
-        <v>32.4787</v>
+        <v>32.3086</v>
       </c>
       <c r="D35" t="n">
-        <v>75.43819999999999</v>
+        <v>74.79649999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>31.8191</v>
+        <v>30.8983</v>
       </c>
       <c r="F35" t="n">
-        <v>58.3998</v>
+        <v>57.816</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>27.4628</v>
+        <v>28.6102</v>
       </c>
       <c r="C36" t="n">
-        <v>32.0749</v>
+        <v>31.8461</v>
       </c>
       <c r="D36" t="n">
-        <v>74.8236</v>
+        <v>74.3128</v>
       </c>
       <c r="E36" t="n">
-        <v>30.6734</v>
+        <v>29.5801</v>
       </c>
       <c r="F36" t="n">
-        <v>57.518</v>
+        <v>56.987</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>28.3167</v>
+        <v>27.0622</v>
       </c>
       <c r="C37" t="n">
-        <v>43.6148</v>
+        <v>42.873</v>
       </c>
       <c r="D37" t="n">
-        <v>73.5167</v>
+        <v>73.0557</v>
       </c>
       <c r="E37" t="n">
-        <v>29.5074</v>
+        <v>28.5511</v>
       </c>
       <c r="F37" t="n">
-        <v>56.803</v>
+        <v>56.3385</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>49.4356</v>
+        <v>45.5946</v>
       </c>
       <c r="C38" t="n">
-        <v>42.4846</v>
+        <v>41.8768</v>
       </c>
       <c r="D38" t="n">
-        <v>72.3215</v>
+        <v>71.6104</v>
       </c>
       <c r="E38" t="n">
-        <v>28.4954</v>
+        <v>27.5424</v>
       </c>
       <c r="F38" t="n">
-        <v>56.069</v>
+        <v>55.3497</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>48.0426</v>
+        <v>44.3757</v>
       </c>
       <c r="C39" t="n">
-        <v>41.4918</v>
+        <v>41.0148</v>
       </c>
       <c r="D39" t="n">
-        <v>71.3489</v>
+        <v>70.9983</v>
       </c>
       <c r="E39" t="n">
-        <v>27.5278</v>
+        <v>26.7429</v>
       </c>
       <c r="F39" t="n">
-        <v>55.3121</v>
+        <v>54.9708</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>45.3474</v>
+        <v>45.7442</v>
       </c>
       <c r="C40" t="n">
-        <v>40.7152</v>
+        <v>40.2589</v>
       </c>
       <c r="D40" t="n">
-        <v>70.18559999999999</v>
+        <v>69.6039</v>
       </c>
       <c r="E40" t="n">
-        <v>26.5783</v>
+        <v>25.8202</v>
       </c>
       <c r="F40" t="n">
-        <v>54.561</v>
+        <v>54.1505</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>44.108</v>
+        <v>42.3073</v>
       </c>
       <c r="C41" t="n">
-        <v>39.7697</v>
+        <v>39.4985</v>
       </c>
       <c r="D41" t="n">
-        <v>69.8706</v>
+        <v>68.8297</v>
       </c>
       <c r="E41" t="n">
-        <v>25.6813</v>
+        <v>24.8376</v>
       </c>
       <c r="F41" t="n">
-        <v>53.9704</v>
+        <v>53.6241</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>42.6945</v>
+        <v>41.039</v>
       </c>
       <c r="C42" t="n">
-        <v>39.0305</v>
+        <v>38.5756</v>
       </c>
       <c r="D42" t="n">
-        <v>68.7059</v>
+        <v>68.5098</v>
       </c>
       <c r="E42" t="n">
-        <v>24.8787</v>
+        <v>24.0585</v>
       </c>
       <c r="F42" t="n">
-        <v>53.1616</v>
+        <v>52.8174</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>41.7016</v>
+        <v>39.4277</v>
       </c>
       <c r="C43" t="n">
-        <v>38.0769</v>
+        <v>37.9168</v>
       </c>
       <c r="D43" t="n">
-        <v>67.90860000000001</v>
+        <v>67.7088</v>
       </c>
       <c r="E43" t="n">
-        <v>23.9451</v>
+        <v>23.3123</v>
       </c>
       <c r="F43" t="n">
-        <v>52.5541</v>
+        <v>52.3807</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>40.058</v>
+        <v>38.5549</v>
       </c>
       <c r="C44" t="n">
-        <v>37.6011</v>
+        <v>37.2412</v>
       </c>
       <c r="D44" t="n">
-        <v>67.2475</v>
+        <v>67.3793</v>
       </c>
       <c r="E44" t="n">
-        <v>23.1272</v>
+        <v>22.6819</v>
       </c>
       <c r="F44" t="n">
-        <v>51.9714</v>
+        <v>51.8296</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>39.0783</v>
+        <v>38.3276</v>
       </c>
       <c r="C45" t="n">
-        <v>36.7357</v>
+        <v>36.4445</v>
       </c>
       <c r="D45" t="n">
-        <v>66.9556</v>
+        <v>66.5318</v>
       </c>
       <c r="E45" t="n">
-        <v>22.6074</v>
+        <v>21.9797</v>
       </c>
       <c r="F45" t="n">
-        <v>51.5978</v>
+        <v>51.468</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>39.6368</v>
+        <v>38.184</v>
       </c>
       <c r="C46" t="n">
-        <v>36.0467</v>
+        <v>35.7391</v>
       </c>
       <c r="D46" t="n">
-        <v>66.3413</v>
+        <v>66.6748</v>
       </c>
       <c r="E46" t="n">
-        <v>21.8533</v>
+        <v>21.3039</v>
       </c>
       <c r="F46" t="n">
-        <v>51.1564</v>
+        <v>51.087</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>36.9021</v>
+        <v>35.2868</v>
       </c>
       <c r="C47" t="n">
-        <v>35.37</v>
+        <v>35.0798</v>
       </c>
       <c r="D47" t="n">
-        <v>65.9815</v>
+        <v>65.58329999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>21.2805</v>
+        <v>20.6512</v>
       </c>
       <c r="F47" t="n">
-        <v>50.5391</v>
+        <v>50.5356</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>35.9609</v>
+        <v>34.2204</v>
       </c>
       <c r="C48" t="n">
-        <v>34.9101</v>
+        <v>34.4936</v>
       </c>
       <c r="D48" t="n">
-        <v>65.4003</v>
+        <v>65.4915</v>
       </c>
       <c r="E48" t="n">
-        <v>20.7894</v>
+        <v>35.0267</v>
       </c>
       <c r="F48" t="n">
-        <v>50.2258</v>
+        <v>60.7958</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>35.0592</v>
+        <v>35.6544</v>
       </c>
       <c r="C49" t="n">
-        <v>34.1452</v>
+        <v>34.0199</v>
       </c>
       <c r="D49" t="n">
-        <v>66.3715</v>
+        <v>64.991</v>
       </c>
       <c r="E49" t="n">
-        <v>20.2536</v>
+        <v>33.8066</v>
       </c>
       <c r="F49" t="n">
-        <v>49.9678</v>
+        <v>59.7309</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>36.5102</v>
+        <v>34.4142</v>
       </c>
       <c r="C50" t="n">
-        <v>33.6812</v>
+        <v>33.52</v>
       </c>
       <c r="D50" t="n">
-        <v>79.7419</v>
+        <v>79.5385</v>
       </c>
       <c r="E50" t="n">
-        <v>32.9187</v>
+        <v>32.4622</v>
       </c>
       <c r="F50" t="n">
-        <v>59.4553</v>
+        <v>59.0916</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>35.7158</v>
+        <v>34.2381</v>
       </c>
       <c r="C51" t="n">
-        <v>44.617</v>
+        <v>44.9656</v>
       </c>
       <c r="D51" t="n">
-        <v>78.3899</v>
+        <v>78.28019999999999</v>
       </c>
       <c r="E51" t="n">
-        <v>31.9029</v>
+        <v>31.3076</v>
       </c>
       <c r="F51" t="n">
-        <v>58.7514</v>
+        <v>58.3717</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>34.9006</v>
+        <v>32.4478</v>
       </c>
       <c r="C52" t="n">
-        <v>43.5398</v>
+        <v>43.9406</v>
       </c>
       <c r="D52" t="n">
-        <v>77.2908</v>
+        <v>76.5485</v>
       </c>
       <c r="E52" t="n">
-        <v>30.7594</v>
+        <v>30.2408</v>
       </c>
       <c r="F52" t="n">
-        <v>58.1219</v>
+        <v>57.5002</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>56.5551</v>
+        <v>53.8284</v>
       </c>
       <c r="C53" t="n">
-        <v>42.4251</v>
+        <v>42.6065</v>
       </c>
       <c r="D53" t="n">
-        <v>75.96339999999999</v>
+        <v>76.0693</v>
       </c>
       <c r="E53" t="n">
-        <v>29.4242</v>
+        <v>29.7494</v>
       </c>
       <c r="F53" t="n">
-        <v>57.2529</v>
+        <v>56.5603</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>54.9603</v>
+        <v>53.0903</v>
       </c>
       <c r="C54" t="n">
-        <v>41.7974</v>
+        <v>41.5934</v>
       </c>
       <c r="D54" t="n">
-        <v>74.7295</v>
+        <v>74.6664</v>
       </c>
       <c r="E54" t="n">
-        <v>28.5874</v>
+        <v>28.56</v>
       </c>
       <c r="F54" t="n">
-        <v>56.3745</v>
+        <v>55.9224</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>52.5136</v>
+        <v>49.5873</v>
       </c>
       <c r="C55" t="n">
-        <v>40.7118</v>
+        <v>40.7415</v>
       </c>
       <c r="D55" t="n">
-        <v>73.7397</v>
+        <v>73.2958</v>
       </c>
       <c r="E55" t="n">
-        <v>27.3194</v>
+        <v>27.6744</v>
       </c>
       <c r="F55" t="n">
-        <v>55.7287</v>
+        <v>55.1003</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>50.9799</v>
+        <v>48.196</v>
       </c>
       <c r="C56" t="n">
-        <v>39.9455</v>
+        <v>39.6823</v>
       </c>
       <c r="D56" t="n">
-        <v>72.7944</v>
+        <v>74.8419</v>
       </c>
       <c r="E56" t="n">
-        <v>26.7508</v>
+        <v>26.4905</v>
       </c>
       <c r="F56" t="n">
-        <v>54.9781</v>
+        <v>56.178</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>49.531</v>
+        <v>46.8344</v>
       </c>
       <c r="C57" t="n">
-        <v>39.0983</v>
+        <v>39.3811</v>
       </c>
       <c r="D57" t="n">
-        <v>72.23180000000001</v>
+        <v>74.1444</v>
       </c>
       <c r="E57" t="n">
-        <v>25.9553</v>
+        <v>25.5311</v>
       </c>
       <c r="F57" t="n">
-        <v>54.3932</v>
+        <v>54.1543</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>46.9108</v>
+        <v>45.2782</v>
       </c>
       <c r="C58" t="n">
-        <v>38.1598</v>
+        <v>38.2451</v>
       </c>
       <c r="D58" t="n">
-        <v>71.13809999999999</v>
+        <v>70.5431</v>
       </c>
       <c r="E58" t="n">
-        <v>25.2808</v>
+        <v>24.652</v>
       </c>
       <c r="F58" t="n">
-        <v>53.9057</v>
+        <v>53.3645</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>47.0803</v>
+        <v>43.7768</v>
       </c>
       <c r="C59" t="n">
-        <v>37.4622</v>
+        <v>37.3529</v>
       </c>
       <c r="D59" t="n">
-        <v>70.17740000000001</v>
+        <v>69.8519</v>
       </c>
       <c r="E59" t="n">
-        <v>24.5445</v>
+        <v>24.1401</v>
       </c>
       <c r="F59" t="n">
-        <v>53.0697</v>
+        <v>53.7278</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>45.0517</v>
+        <v>42.7058</v>
       </c>
       <c r="C60" t="n">
-        <v>36.855</v>
+        <v>37.0379</v>
       </c>
       <c r="D60" t="n">
-        <v>70.625</v>
+        <v>69.5984</v>
       </c>
       <c r="E60" t="n">
-        <v>23.3912</v>
+        <v>23.5521</v>
       </c>
       <c r="F60" t="n">
-        <v>52.6965</v>
+        <v>52.5443</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>42.9617</v>
+        <v>42.4522</v>
       </c>
       <c r="C61" t="n">
-        <v>36.4187</v>
+        <v>36.0022</v>
       </c>
       <c r="D61" t="n">
-        <v>70.7396</v>
+        <v>69.39400000000001</v>
       </c>
       <c r="E61" t="n">
-        <v>22.8129</v>
+        <v>22.521</v>
       </c>
       <c r="F61" t="n">
-        <v>52.5483</v>
+        <v>51.9925</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>42.7144</v>
+        <v>41.197</v>
       </c>
       <c r="C62" t="n">
-        <v>35.5471</v>
+        <v>35.6973</v>
       </c>
       <c r="D62" t="n">
-        <v>70.1199</v>
+        <v>68.49509999999999</v>
       </c>
       <c r="E62" t="n">
-        <v>22.4666</v>
+        <v>22.0021</v>
       </c>
       <c r="F62" t="n">
-        <v>53.1034</v>
+        <v>51.5177</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>38.6815</v>
+        <v>39.4986</v>
       </c>
       <c r="C63" t="n">
-        <v>35.1793</v>
+        <v>35.0756</v>
       </c>
       <c r="D63" t="n">
-        <v>69.2004</v>
+        <v>68.2582</v>
       </c>
       <c r="E63" t="n">
-        <v>21.8351</v>
+        <v>36.444</v>
       </c>
       <c r="F63" t="n">
-        <v>51.8227</v>
+        <v>61.7408</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>37.2742</v>
+        <v>38.7752</v>
       </c>
       <c r="C64" t="n">
-        <v>34.6681</v>
+        <v>34.2969</v>
       </c>
       <c r="D64" t="n">
-        <v>85.37479999999999</v>
+        <v>84.7272</v>
       </c>
       <c r="E64" t="n">
-        <v>34.667</v>
+        <v>35.287</v>
       </c>
       <c r="F64" t="n">
-        <v>61.9093</v>
+        <v>60.8781</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>37.0709</v>
+        <v>37.4054</v>
       </c>
       <c r="C65" t="n">
-        <v>45.4978</v>
+        <v>46.168</v>
       </c>
       <c r="D65" t="n">
-        <v>84.84569999999999</v>
+        <v>82.94</v>
       </c>
       <c r="E65" t="n">
-        <v>33.7822</v>
+        <v>33.3802</v>
       </c>
       <c r="F65" t="n">
-        <v>61.2465</v>
+        <v>60.1257</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>35.6491</v>
+        <v>36.8843</v>
       </c>
       <c r="C66" t="n">
-        <v>44.9195</v>
+        <v>44.8136</v>
       </c>
       <c r="D66" t="n">
-        <v>82.9927</v>
+        <v>82.3142</v>
       </c>
       <c r="E66" t="n">
-        <v>32.6665</v>
+        <v>32.3552</v>
       </c>
       <c r="F66" t="n">
-        <v>60.7382</v>
+        <v>60.9623</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>58.5094</v>
+        <v>60.842</v>
       </c>
       <c r="C67" t="n">
-        <v>44.274</v>
+        <v>44.4645</v>
       </c>
       <c r="D67" t="n">
-        <v>81.23099999999999</v>
+        <v>81.74890000000001</v>
       </c>
       <c r="E67" t="n">
-        <v>31.8234</v>
+        <v>31.6703</v>
       </c>
       <c r="F67" t="n">
-        <v>59.3882</v>
+        <v>60.343</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>56.9024</v>
+        <v>58.2828</v>
       </c>
       <c r="C68" t="n">
-        <v>42.8642</v>
+        <v>43.3856</v>
       </c>
       <c r="D68" t="n">
-        <v>79.7564</v>
+        <v>79.4385</v>
       </c>
       <c r="E68" t="n">
-        <v>30.1682</v>
+        <v>30.2104</v>
       </c>
       <c r="F68" t="n">
-        <v>58.8328</v>
+        <v>57.8946</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>55.5213</v>
+        <v>56.3163</v>
       </c>
       <c r="C69" t="n">
-        <v>42.3487</v>
+        <v>42.4423</v>
       </c>
       <c r="D69" t="n">
-        <v>78.0531</v>
+        <v>77.9273</v>
       </c>
       <c r="E69" t="n">
-        <v>30.0895</v>
+        <v>29.9001</v>
       </c>
       <c r="F69" t="n">
-        <v>57.9537</v>
+        <v>57.8934</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>54.0911</v>
+        <v>55.0301</v>
       </c>
       <c r="C70" t="n">
-        <v>40.8673</v>
+        <v>41.4429</v>
       </c>
       <c r="D70" t="n">
-        <v>78.6931</v>
+        <v>77.2672</v>
       </c>
       <c r="E70" t="n">
-        <v>28.3176</v>
+        <v>28.2539</v>
       </c>
       <c r="F70" t="n">
-        <v>57.8927</v>
+        <v>57.7155</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>52.4425</v>
+        <v>54.4087</v>
       </c>
       <c r="C71" t="n">
-        <v>40.7009</v>
+        <v>41.3055</v>
       </c>
       <c r="D71" t="n">
-        <v>76.2397</v>
+        <v>75.79989999999999</v>
       </c>
       <c r="E71" t="n">
-        <v>27.6511</v>
+        <v>27.8844</v>
       </c>
       <c r="F71" t="n">
-        <v>56.7917</v>
+        <v>55.9589</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>51.5201</v>
+        <v>52.3331</v>
       </c>
       <c r="C72" t="n">
-        <v>39.2796</v>
+        <v>39.6744</v>
       </c>
       <c r="D72" t="n">
-        <v>77.0517</v>
+        <v>75.2351</v>
       </c>
       <c r="E72" t="n">
-        <v>27.2737</v>
+        <v>27.1551</v>
       </c>
       <c r="F72" t="n">
-        <v>56.3336</v>
+        <v>55.4634</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>49.5552</v>
+        <v>51.3561</v>
       </c>
       <c r="C73" t="n">
-        <v>38.7606</v>
+        <v>39.0856</v>
       </c>
       <c r="D73" t="n">
-        <v>75.4269</v>
+        <v>74.9408</v>
       </c>
       <c r="E73" t="n">
-        <v>26.3445</v>
+        <v>26.0556</v>
       </c>
       <c r="F73" t="n">
-        <v>56.9753</v>
+        <v>55.3116</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>48.5306</v>
+        <v>49.2015</v>
       </c>
       <c r="C74" t="n">
-        <v>37.8971</v>
+        <v>38.0985</v>
       </c>
       <c r="D74" t="n">
-        <v>74.8599</v>
+        <v>74.2838</v>
       </c>
       <c r="E74" t="n">
-        <v>25.5829</v>
+        <v>25.384</v>
       </c>
       <c r="F74" t="n">
-        <v>55.1627</v>
+        <v>54.4359</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>46.8462</v>
+        <v>48.4276</v>
       </c>
       <c r="C75" t="n">
-        <v>37.3347</v>
+        <v>37.3531</v>
       </c>
       <c r="D75" t="n">
-        <v>74.9659</v>
+        <v>74.071</v>
       </c>
       <c r="E75" t="n">
-        <v>24.6885</v>
+        <v>25.0131</v>
       </c>
       <c r="F75" t="n">
-        <v>54.8422</v>
+        <v>54.1623</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>45.6621</v>
+        <v>46.9109</v>
       </c>
       <c r="C76" t="n">
-        <v>36.827</v>
+        <v>36.7728</v>
       </c>
       <c r="D76" t="n">
-        <v>73.93000000000001</v>
+        <v>74.73439999999999</v>
       </c>
       <c r="E76" t="n">
-        <v>24.299</v>
+        <v>24.3641</v>
       </c>
       <c r="F76" t="n">
-        <v>54.2294</v>
+        <v>54.0233</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>44.8529</v>
+        <v>46.5296</v>
       </c>
       <c r="C77" t="n">
-        <v>36.2186</v>
+        <v>36.0549</v>
       </c>
       <c r="D77" t="n">
-        <v>74.59699999999999</v>
+        <v>73.4158</v>
       </c>
       <c r="E77" t="n">
-        <v>23.3012</v>
+        <v>38.842</v>
       </c>
       <c r="F77" t="n">
-        <v>54.5739</v>
+        <v>77.5642</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>44.8371</v>
+        <v>44.7618</v>
       </c>
       <c r="C78" t="n">
-        <v>35.6405</v>
+        <v>35.6447</v>
       </c>
       <c r="D78" t="n">
-        <v>108.704</v>
+        <v>108.341</v>
       </c>
       <c r="E78" t="n">
-        <v>36.9575</v>
+        <v>37.905</v>
       </c>
       <c r="F78" t="n">
-        <v>78.143</v>
+        <v>77.851</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>43.7958</v>
+        <v>43.7231</v>
       </c>
       <c r="C79" t="n">
-        <v>47.4325</v>
+        <v>47.4383</v>
       </c>
       <c r="D79" t="n">
-        <v>106.411</v>
+        <v>107.39</v>
       </c>
       <c r="E79" t="n">
-        <v>36.6362</v>
+        <v>36.7929</v>
       </c>
       <c r="F79" t="n">
-        <v>77.4811</v>
+        <v>77.52200000000001</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>42.9265</v>
+        <v>42.675</v>
       </c>
       <c r="C80" t="n">
-        <v>48.3283</v>
+        <v>47.466</v>
       </c>
       <c r="D80" t="n">
-        <v>106.814</v>
+        <v>105.928</v>
       </c>
       <c r="E80" t="n">
-        <v>35.1074</v>
+        <v>35.9979</v>
       </c>
       <c r="F80" t="n">
-        <v>78.74160000000001</v>
+        <v>76.304</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>63.1849</v>
+        <v>63.1886</v>
       </c>
       <c r="C81" t="n">
-        <v>47.0582</v>
+        <v>48.112</v>
       </c>
       <c r="D81" t="n">
-        <v>105.205</v>
+        <v>104.794</v>
       </c>
       <c r="E81" t="n">
-        <v>34.4282</v>
+        <v>34.7763</v>
       </c>
       <c r="F81" t="n">
-        <v>77.0583</v>
+        <v>76.1263</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>62.3854</v>
+        <v>61.7923</v>
       </c>
       <c r="C82" t="n">
-        <v>47.182</v>
+        <v>47.5516</v>
       </c>
       <c r="D82" t="n">
-        <v>104.322</v>
+        <v>104.097</v>
       </c>
       <c r="E82" t="n">
-        <v>33.3532</v>
+        <v>33.528</v>
       </c>
       <c r="F82" t="n">
-        <v>76.1952</v>
+        <v>74.8776</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>61.7989</v>
+        <v>61.416</v>
       </c>
       <c r="C83" t="n">
-        <v>46.4808</v>
+        <v>46.5501</v>
       </c>
       <c r="D83" t="n">
-        <v>103.946</v>
+        <v>103.782</v>
       </c>
       <c r="E83" t="n">
-        <v>32.1156</v>
+        <v>32.1858</v>
       </c>
       <c r="F83" t="n">
-        <v>75.8946</v>
+        <v>73.8085</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>61.4047</v>
+        <v>60.8752</v>
       </c>
       <c r="C84" t="n">
-        <v>46.1447</v>
+        <v>47.0886</v>
       </c>
       <c r="D84" t="n">
-        <v>104.055</v>
+        <v>102.714</v>
       </c>
       <c r="E84" t="n">
-        <v>31.9289</v>
+        <v>31.8281</v>
       </c>
       <c r="F84" t="n">
-        <v>75.46720000000001</v>
+        <v>73.6431</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>60.1118</v>
+        <v>59.9708</v>
       </c>
       <c r="C85" t="n">
-        <v>45.4475</v>
+        <v>45.7917</v>
       </c>
       <c r="D85" t="n">
-        <v>103.655</v>
+        <v>102.924</v>
       </c>
       <c r="E85" t="n">
-        <v>30.3901</v>
+        <v>30.548</v>
       </c>
       <c r="F85" t="n">
-        <v>73.14490000000001</v>
+        <v>72.20480000000001</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>58.7341</v>
+        <v>58.9186</v>
       </c>
       <c r="C86" t="n">
-        <v>45.2397</v>
+        <v>45.0537</v>
       </c>
       <c r="D86" t="n">
-        <v>102.993</v>
+        <v>102.837</v>
       </c>
       <c r="E86" t="n">
-        <v>29.9414</v>
+        <v>30.1826</v>
       </c>
       <c r="F86" t="n">
-        <v>71.602</v>
+        <v>71.41370000000001</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>57.9094</v>
+        <v>58.0145</v>
       </c>
       <c r="C87" t="n">
-        <v>44.4425</v>
+        <v>44.7097</v>
       </c>
       <c r="D87" t="n">
-        <v>103.427</v>
+        <v>103.484</v>
       </c>
       <c r="E87" t="n">
-        <v>28.7214</v>
+        <v>28.754</v>
       </c>
       <c r="F87" t="n">
-        <v>71.3644</v>
+        <v>70.76990000000001</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>57.2194</v>
+        <v>57.9142</v>
       </c>
       <c r="C88" t="n">
-        <v>43.8415</v>
+        <v>43.7248</v>
       </c>
       <c r="D88" t="n">
-        <v>103.831</v>
+        <v>104.115</v>
       </c>
       <c r="E88" t="n">
-        <v>28.1824</v>
+        <v>28.5693</v>
       </c>
       <c r="F88" t="n">
-        <v>70.9217</v>
+        <v>70.0518</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>55.7679</v>
+        <v>56.5716</v>
       </c>
       <c r="C89" t="n">
-        <v>43.8035</v>
+        <v>43.4155</v>
       </c>
       <c r="D89" t="n">
-        <v>104.779</v>
+        <v>103.549</v>
       </c>
       <c r="E89" t="n">
-        <v>27.9538</v>
+        <v>27.0879</v>
       </c>
       <c r="F89" t="n">
-        <v>69.2448</v>
+        <v>68.1159</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>55.1232</v>
+        <v>54.963</v>
       </c>
       <c r="C90" t="n">
-        <v>42.8894</v>
+        <v>42.8454</v>
       </c>
       <c r="D90" t="n">
-        <v>104.916</v>
+        <v>105.444</v>
       </c>
       <c r="E90" t="n">
-        <v>26.6527</v>
+        <v>27.4148</v>
       </c>
       <c r="F90" t="n">
-        <v>69.38339999999999</v>
+        <v>67.4273</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>53.7204</v>
+        <v>53.835</v>
       </c>
       <c r="C91" t="n">
-        <v>42.6914</v>
+        <v>42.1078</v>
       </c>
       <c r="D91" t="n">
-        <v>106.523</v>
+        <v>105.392</v>
       </c>
       <c r="E91" t="n">
-        <v>26.0605</v>
+        <v>42.4423</v>
       </c>
       <c r="F91" t="n">
-        <v>68.2265</v>
+        <v>98.42100000000001</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>52.8322</v>
+        <v>52.3232</v>
       </c>
       <c r="C92" t="n">
-        <v>41.8336</v>
+        <v>41.7251</v>
       </c>
       <c r="D92" t="n">
-        <v>147.065</v>
+        <v>147.768</v>
       </c>
       <c r="E92" t="n">
-        <v>39.6541</v>
+        <v>40.71</v>
       </c>
       <c r="F92" t="n">
-        <v>99.3698</v>
+        <v>97.54640000000001</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>51.801</v>
+        <v>52.7553</v>
       </c>
       <c r="C93" t="n">
-        <v>41.1229</v>
+        <v>41.2827</v>
       </c>
       <c r="D93" t="n">
-        <v>148.693</v>
+        <v>147.766</v>
       </c>
       <c r="E93" t="n">
-        <v>39.811</v>
+        <v>39.9291</v>
       </c>
       <c r="F93" t="n">
-        <v>99.44289999999999</v>
+        <v>96.6533</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>50.6758</v>
+        <v>51.6044</v>
       </c>
       <c r="C94" t="n">
-        <v>53.6894</v>
+        <v>54.6754</v>
       </c>
       <c r="D94" t="n">
-        <v>146.541</v>
+        <v>145.518</v>
       </c>
       <c r="E94" t="n">
-        <v>38.613</v>
+        <v>39.0182</v>
       </c>
       <c r="F94" t="n">
-        <v>98.9286</v>
+        <v>96.2629</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>72.9233</v>
+        <v>71.71250000000001</v>
       </c>
       <c r="C95" t="n">
-        <v>53.3535</v>
+        <v>54.7351</v>
       </c>
       <c r="D95" t="n">
-        <v>146.01</v>
+        <v>144.37</v>
       </c>
       <c r="E95" t="n">
-        <v>37.6615</v>
+        <v>37.2726</v>
       </c>
       <c r="F95" t="n">
-        <v>96.97969999999999</v>
+        <v>95.1255</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>72.5844</v>
+        <v>71.56959999999999</v>
       </c>
       <c r="C96" t="n">
-        <v>53.6355</v>
+        <v>53.5319</v>
       </c>
       <c r="D96" t="n">
-        <v>146.841</v>
+        <v>144.151</v>
       </c>
       <c r="E96" t="n">
-        <v>36.1635</v>
+        <v>37.4356</v>
       </c>
       <c r="F96" t="n">
-        <v>95.57550000000001</v>
+        <v>94.15000000000001</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>71.8002</v>
+        <v>70.2757</v>
       </c>
       <c r="C97" t="n">
-        <v>52.9818</v>
+        <v>53.6789</v>
       </c>
       <c r="D97" t="n">
-        <v>145.198</v>
+        <v>143.844</v>
       </c>
       <c r="E97" t="n">
-        <v>35.2471</v>
+        <v>35.8719</v>
       </c>
       <c r="F97" t="n">
-        <v>94.7987</v>
+        <v>93.1799</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>70.6781</v>
+        <v>69.85590000000001</v>
       </c>
       <c r="C98" t="n">
-        <v>52.7919</v>
+        <v>53.5588</v>
       </c>
       <c r="D98" t="n">
-        <v>144.611</v>
+        <v>143.431</v>
       </c>
       <c r="E98" t="n">
-        <v>35.1207</v>
+        <v>35.3736</v>
       </c>
       <c r="F98" t="n">
-        <v>93.0112</v>
+        <v>92.8751</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>70.06870000000001</v>
+        <v>69.39</v>
       </c>
       <c r="C99" t="n">
-        <v>52.9828</v>
+        <v>52.7564</v>
       </c>
       <c r="D99" t="n">
-        <v>144.028</v>
+        <v>144.178</v>
       </c>
       <c r="E99" t="n">
-        <v>33.6012</v>
+        <v>33.9647</v>
       </c>
       <c r="F99" t="n">
-        <v>92.5986</v>
+        <v>90.9152</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>69.81319999999999</v>
+        <v>68.5014</v>
       </c>
       <c r="C100" t="n">
-        <v>52.5142</v>
+        <v>52.5765</v>
       </c>
       <c r="D100" t="n">
-        <v>144.175</v>
+        <v>145.2</v>
       </c>
       <c r="E100" t="n">
-        <v>33.2809</v>
+        <v>33.5275</v>
       </c>
       <c r="F100" t="n">
-        <v>90.6302</v>
+        <v>90.8259</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>69.1823</v>
+        <v>68.1788</v>
       </c>
       <c r="C101" t="n">
-        <v>53.1598</v>
+        <v>52.5427</v>
       </c>
       <c r="D101" t="n">
-        <v>144.422</v>
+        <v>144.947</v>
       </c>
       <c r="E101" t="n">
-        <v>32.2207</v>
+        <v>32.5149</v>
       </c>
       <c r="F101" t="n">
-        <v>90.6134</v>
+        <v>89.52719999999999</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>67.2676</v>
+        <v>67.53279999999999</v>
       </c>
       <c r="C102" t="n">
-        <v>52.2283</v>
+        <v>52.6376</v>
       </c>
       <c r="D102" t="n">
-        <v>145.588</v>
+        <v>144.753</v>
       </c>
       <c r="E102" t="n">
-        <v>31.5929</v>
+        <v>32.2783</v>
       </c>
       <c r="F102" t="n">
-        <v>89.5038</v>
+        <v>87.9918</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>66.5273</v>
+        <v>66.3699</v>
       </c>
       <c r="C103" t="n">
-        <v>52.2376</v>
+        <v>52.5217</v>
       </c>
       <c r="D103" t="n">
-        <v>147.216</v>
+        <v>146.094</v>
       </c>
       <c r="E103" t="n">
-        <v>30.4162</v>
+        <v>30.9916</v>
       </c>
       <c r="F103" t="n">
-        <v>88.8235</v>
+        <v>87.64570000000001</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>66.1635</v>
+        <v>64.95399999999999</v>
       </c>
       <c r="C104" t="n">
-        <v>52.1445</v>
+        <v>52.0375</v>
       </c>
       <c r="D104" t="n">
-        <v>147.155</v>
+        <v>146.349</v>
       </c>
       <c r="E104" t="n">
-        <v>29.8571</v>
+        <v>30.2172</v>
       </c>
       <c r="F104" t="n">
-        <v>88.0196</v>
+        <v>86.44629999999999</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>66.0681</v>
+        <v>64.855</v>
       </c>
       <c r="C105" t="n">
-        <v>51.8814</v>
+        <v>52.3906</v>
       </c>
       <c r="D105" t="n">
-        <v>150.509</v>
+        <v>147.272</v>
       </c>
       <c r="E105" t="n">
-        <v>29.3647</v>
+        <v>45.944</v>
       </c>
       <c r="F105" t="n">
-        <v>87.4739</v>
+        <v>121.185</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>64.96210000000001</v>
+        <v>64.6703</v>
       </c>
       <c r="C106" t="n">
-        <v>52.1473</v>
+        <v>51.9479</v>
       </c>
       <c r="D106" t="n">
-        <v>150.281</v>
+        <v>148.557</v>
       </c>
       <c r="E106" t="n">
-        <v>28.9561</v>
+        <v>44.0085</v>
       </c>
       <c r="F106" t="n">
-        <v>86.95740000000001</v>
+        <v>119.603</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>64.3797</v>
+        <v>63.6068</v>
       </c>
       <c r="C107" t="n">
-        <v>51.6847</v>
+        <v>51.8819</v>
       </c>
       <c r="D107" t="n">
-        <v>193.864</v>
+        <v>193.828</v>
       </c>
       <c r="E107" t="n">
-        <v>42.8176</v>
+        <v>43.1458</v>
       </c>
       <c r="F107" t="n">
-        <v>121.145</v>
+        <v>119.257</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>66.27930000000001</v>
+        <v>63.7222</v>
       </c>
       <c r="C108" t="n">
-        <v>64.22499999999999</v>
+        <v>63.5936</v>
       </c>
       <c r="D108" t="n">
-        <v>192.083</v>
+        <v>191.364</v>
       </c>
       <c r="E108" t="n">
-        <v>41.8207</v>
+        <v>42.8242</v>
       </c>
       <c r="F108" t="n">
-        <v>119.474</v>
+        <v>118.642</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>65.9928</v>
+        <v>63.5234</v>
       </c>
       <c r="C109" t="n">
-        <v>63.571</v>
+        <v>63.6178</v>
       </c>
       <c r="D109" t="n">
-        <v>190.39</v>
+        <v>190.283</v>
       </c>
       <c r="E109" t="n">
-        <v>41.7862</v>
+        <v>41.1849</v>
       </c>
       <c r="F109" t="n">
-        <v>118.479</v>
+        <v>117.601</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>89.04559999999999</v>
+        <v>82.5239</v>
       </c>
       <c r="C110" t="n">
-        <v>63.4987</v>
+        <v>63.8015</v>
       </c>
       <c r="D110" t="n">
-        <v>189.279</v>
+        <v>190.007</v>
       </c>
       <c r="E110" t="n">
-        <v>40.3828</v>
+        <v>41.1031</v>
       </c>
       <c r="F110" t="n">
-        <v>118.373</v>
+        <v>117.613</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>88.18000000000001</v>
+        <v>81.9773</v>
       </c>
       <c r="C111" t="n">
-        <v>63.3481</v>
+        <v>63.8272</v>
       </c>
       <c r="D111" t="n">
-        <v>187.92</v>
+        <v>188.434</v>
       </c>
       <c r="E111" t="n">
-        <v>40.1953</v>
+        <v>40.2823</v>
       </c>
       <c r="F111" t="n">
-        <v>118.173</v>
+        <v>115.792</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>87.2166</v>
+        <v>80.89570000000001</v>
       </c>
       <c r="C112" t="n">
-        <v>63.8063</v>
+        <v>64.2354</v>
       </c>
       <c r="D112" t="n">
-        <v>187.713</v>
+        <v>187.401</v>
       </c>
       <c r="E112" t="n">
-        <v>39.0598</v>
+        <v>39.4526</v>
       </c>
       <c r="F112" t="n">
-        <v>117.021</v>
+        <v>114.986</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>81.8061</v>
+        <v>85.2115</v>
       </c>
       <c r="C113" t="n">
-        <v>63.4393</v>
+        <v>63.7072</v>
       </c>
       <c r="D113" t="n">
-        <v>187.578</v>
+        <v>187.523</v>
       </c>
       <c r="E113" t="n">
-        <v>38.2524</v>
+        <v>38.8357</v>
       </c>
       <c r="F113" t="n">
-        <v>116.79</v>
+        <v>114.398</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>80.4057</v>
+        <v>84.99339999999999</v>
       </c>
       <c r="C114" t="n">
-        <v>63.9362</v>
+        <v>63.8559</v>
       </c>
       <c r="D114" t="n">
-        <v>186.877</v>
+        <v>186.593</v>
       </c>
       <c r="E114" t="n">
-        <v>37.3124</v>
+        <v>38.2887</v>
       </c>
       <c r="F114" t="n">
-        <v>115.741</v>
+        <v>114.14</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>80.2775</v>
+        <v>83.8336</v>
       </c>
       <c r="C115" t="n">
-        <v>63.7311</v>
+        <v>63.8316</v>
       </c>
       <c r="D115" t="n">
-        <v>186.986</v>
+        <v>187.004</v>
       </c>
       <c r="E115" t="n">
-        <v>36.539</v>
+        <v>37.5447</v>
       </c>
       <c r="F115" t="n">
-        <v>115.268</v>
+        <v>113.945</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>79.9177</v>
+        <v>82.78579999999999</v>
       </c>
       <c r="C116" t="n">
-        <v>63.6255</v>
+        <v>64.0502</v>
       </c>
       <c r="D116" t="n">
-        <v>187.112</v>
+        <v>186.587</v>
       </c>
       <c r="E116" t="n">
-        <v>36.8086</v>
+        <v>36.6713</v>
       </c>
       <c r="F116" t="n">
-        <v>115.164</v>
+        <v>114.315</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>78.4148</v>
+        <v>77.7236</v>
       </c>
       <c r="C117" t="n">
-        <v>63.6111</v>
+        <v>63.5032</v>
       </c>
       <c r="D117" t="n">
-        <v>187.351</v>
+        <v>186.32</v>
       </c>
       <c r="E117" t="n">
-        <v>35.5171</v>
+        <v>35.8106</v>
       </c>
       <c r="F117" t="n">
-        <v>114.302</v>
+        <v>113.844</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>77.38760000000001</v>
+        <v>76.95440000000001</v>
       </c>
       <c r="C118" t="n">
-        <v>63.5557</v>
+        <v>63.9895</v>
       </c>
       <c r="D118" t="n">
-        <v>188.081</v>
+        <v>187.651</v>
       </c>
       <c r="E118" t="n">
-        <v>35.2477</v>
+        <v>35.4062</v>
       </c>
       <c r="F118" t="n">
-        <v>113.774</v>
+        <v>113.247</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>77.6863</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="C119" t="n">
-        <v>63.3491</v>
+        <v>63.4192</v>
       </c>
       <c r="D119" t="n">
-        <v>188.596</v>
+        <v>187.905</v>
       </c>
       <c r="E119" t="n">
-        <v>34.1427</v>
+        <v>51.1254</v>
       </c>
       <c r="F119" t="n">
-        <v>114.12</v>
+        <v>148.342</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>75.9879</v>
+        <v>76.23560000000001</v>
       </c>
       <c r="C120" t="n">
-        <v>63.7159</v>
+        <v>63.8092</v>
       </c>
       <c r="D120" t="n">
-        <v>189.903</v>
+        <v>189.34</v>
       </c>
       <c r="E120" t="n">
-        <v>33.6983</v>
+        <v>50.2352</v>
       </c>
       <c r="F120" t="n">
-        <v>113.193</v>
+        <v>147.683</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>76.37909999999999</v>
+        <v>76.5326</v>
       </c>
       <c r="C121" t="n">
-        <v>62.918</v>
+        <v>63.3845</v>
       </c>
       <c r="D121" t="n">
-        <v>236.661</v>
+        <v>236.308</v>
       </c>
       <c r="E121" t="n">
-        <v>47.7151</v>
+        <v>49.5785</v>
       </c>
       <c r="F121" t="n">
-        <v>147.647</v>
+        <v>146.948</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>76.2084</v>
+        <v>76.1704</v>
       </c>
       <c r="C122" t="n">
-        <v>74.5658</v>
+        <v>75.3548</v>
       </c>
       <c r="D122" t="n">
-        <v>233.481</v>
+        <v>233.455</v>
       </c>
       <c r="E122" t="n">
-        <v>47.5336</v>
+        <v>48.3187</v>
       </c>
       <c r="F122" t="n">
-        <v>146.515</v>
+        <v>145.352</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>74.4308</v>
+        <v>74.923</v>
       </c>
       <c r="C123" t="n">
-        <v>75.5217</v>
+        <v>75.3933</v>
       </c>
       <c r="D123" t="n">
-        <v>231.238</v>
+        <v>230.746</v>
       </c>
       <c r="E123" t="n">
-        <v>46.8253</v>
+        <v>47.2543</v>
       </c>
       <c r="F123" t="n">
-        <v>145.763</v>
+        <v>144.972</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>99.03360000000001</v>
+        <v>95.0181</v>
       </c>
       <c r="C124" t="n">
-        <v>75.6187</v>
+        <v>75.63209999999999</v>
       </c>
       <c r="D124" t="n">
-        <v>229.089</v>
+        <v>229.779</v>
       </c>
       <c r="E124" t="n">
-        <v>46.1946</v>
+        <v>47.564</v>
       </c>
       <c r="F124" t="n">
-        <v>145.147</v>
+        <v>144.43</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>93.4567</v>
+        <v>94.47029999999999</v>
       </c>
       <c r="C125" t="n">
-        <v>75.70010000000001</v>
+        <v>76.12860000000001</v>
       </c>
       <c r="D125" t="n">
-        <v>227.296</v>
+        <v>226.854</v>
       </c>
       <c r="E125" t="n">
-        <v>45.8871</v>
+        <v>49.0306</v>
       </c>
       <c r="F125" t="n">
-        <v>143.947</v>
+        <v>142.861</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>93.1061</v>
+        <v>94.4127</v>
       </c>
       <c r="C126" t="n">
-        <v>76.5934</v>
+        <v>76.4675</v>
       </c>
       <c r="D126" t="n">
-        <v>225.64</v>
+        <v>226.051</v>
       </c>
       <c r="E126" t="n">
-        <v>45.3206</v>
+        <v>47.2719</v>
       </c>
       <c r="F126" t="n">
-        <v>143.801</v>
+        <v>142.551</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>95.1961</v>
+        <v>92.7774</v>
       </c>
       <c r="C127" t="n">
-        <v>76.465</v>
+        <v>76.41800000000001</v>
       </c>
       <c r="D127" t="n">
-        <v>224.959</v>
+        <v>224.545</v>
       </c>
       <c r="E127" t="n">
-        <v>45.3732</v>
+        <v>46.3513</v>
       </c>
       <c r="F127" t="n">
-        <v>142.858</v>
+        <v>142.108</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>94.5926</v>
+        <v>94.5829</v>
       </c>
       <c r="C128" t="n">
-        <v>75.9992</v>
+        <v>76.7962</v>
       </c>
       <c r="D128" t="n">
-        <v>223.148</v>
+        <v>223.113</v>
       </c>
       <c r="E128" t="n">
-        <v>44.4803</v>
+        <v>44.4237</v>
       </c>
       <c r="F128" t="n">
-        <v>143.391</v>
+        <v>141.648</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>92.4046</v>
+        <v>94.62730000000001</v>
       </c>
       <c r="C129" t="n">
-        <v>76.471</v>
+        <v>77.06100000000001</v>
       </c>
       <c r="D129" t="n">
-        <v>222.213</v>
+        <v>222.649</v>
       </c>
       <c r="E129" t="n">
-        <v>43.0778</v>
+        <v>44.5385</v>
       </c>
       <c r="F129" t="n">
-        <v>142.226</v>
+        <v>140.981</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>92.8044</v>
+        <v>92.5633</v>
       </c>
       <c r="C130" t="n">
-        <v>76.8694</v>
+        <v>76.3546</v>
       </c>
       <c r="D130" t="n">
-        <v>221.492</v>
+        <v>221.299</v>
       </c>
       <c r="E130" t="n">
-        <v>43.1879</v>
+        <v>43.3754</v>
       </c>
       <c r="F130" t="n">
-        <v>141.717</v>
+        <v>140.862</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>94.37820000000001</v>
+        <v>92.9211</v>
       </c>
       <c r="C131" t="n">
-        <v>76.9438</v>
+        <v>77.36150000000001</v>
       </c>
       <c r="D131" t="n">
-        <v>221.374</v>
+        <v>221.473</v>
       </c>
       <c r="E131" t="n">
-        <v>42.2446</v>
+        <v>43.0421</v>
       </c>
       <c r="F131" t="n">
-        <v>141.149</v>
+        <v>140.36</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>93.6129</v>
+        <v>93.00579999999999</v>
       </c>
       <c r="C132" t="n">
-        <v>76.8878</v>
+        <v>77.7094</v>
       </c>
       <c r="D132" t="n">
-        <v>221.139</v>
+        <v>221.469</v>
       </c>
       <c r="E132" t="n">
-        <v>42.234</v>
+        <v>42.3503</v>
       </c>
       <c r="F132" t="n">
-        <v>140.933</v>
+        <v>140.263</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>90.8382</v>
+        <v>91.2873</v>
       </c>
       <c r="C133" t="n">
-        <v>77.3408</v>
+        <v>77.6135</v>
       </c>
       <c r="D133" t="n">
-        <v>221.388</v>
+        <v>221.911</v>
       </c>
       <c r="E133" t="n">
-        <v>41.6107</v>
+        <v>42.5105</v>
       </c>
       <c r="F133" t="n">
-        <v>140.709</v>
+        <v>140.065</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>90.2216</v>
+        <v>90.86879999999999</v>
       </c>
       <c r="C134" t="n">
-        <v>77.4388</v>
+        <v>77.89100000000001</v>
       </c>
       <c r="D134" t="n">
-        <v>221.298</v>
+        <v>222.422</v>
       </c>
       <c r="E134" t="n">
-        <v>41.6782</v>
+        <v>58.0387</v>
       </c>
       <c r="F134" t="n">
-        <v>140.609</v>
+        <v>175.639</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>90.8436</v>
+        <v>90.6211</v>
       </c>
       <c r="C135" t="n">
-        <v>77.6793</v>
+        <v>77.6656</v>
       </c>
       <c r="D135" t="n">
-        <v>271.277</v>
+        <v>271.438</v>
       </c>
       <c r="E135" t="n">
-        <v>56.9388</v>
+        <v>57.8446</v>
       </c>
       <c r="F135" t="n">
-        <v>176.076</v>
+        <v>173.586</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>90.1656</v>
+        <v>91.65689999999999</v>
       </c>
       <c r="C136" t="n">
-        <v>89.5736</v>
+        <v>89.8321</v>
       </c>
       <c r="D136" t="n">
-        <v>267.138</v>
+        <v>266.901</v>
       </c>
       <c r="E136" t="n">
-        <v>55.7189</v>
+        <v>56.714</v>
       </c>
       <c r="F136" t="n">
-        <v>174.896</v>
+        <v>172.282</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>90.6833</v>
+        <v>90.1823</v>
       </c>
       <c r="C137" t="n">
-        <v>90.5411</v>
+        <v>90.4846</v>
       </c>
       <c r="D137" t="n">
-        <v>264.125</v>
+        <v>263.885</v>
       </c>
       <c r="E137" t="n">
-        <v>55.3839</v>
+        <v>56.6944</v>
       </c>
       <c r="F137" t="n">
-        <v>173.561</v>
+        <v>170.862</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>109.328</v>
+        <v>111.83</v>
       </c>
       <c r="C138" t="n">
-        <v>90.4611</v>
+        <v>90.9224</v>
       </c>
       <c r="D138" t="n">
-        <v>261.384</v>
+        <v>260.932</v>
       </c>
       <c r="E138" t="n">
-        <v>54.7556</v>
+        <v>56.8205</v>
       </c>
       <c r="F138" t="n">
-        <v>172.067</v>
+        <v>169.551</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>109.264</v>
+        <v>107.951</v>
       </c>
       <c r="C139" t="n">
-        <v>90.9991</v>
+        <v>91.1872</v>
       </c>
       <c r="D139" t="n">
-        <v>258.729</v>
+        <v>258.305</v>
       </c>
       <c r="E139" t="n">
-        <v>54.6492</v>
+        <v>57.0777</v>
       </c>
       <c r="F139" t="n">
-        <v>170.886</v>
+        <v>168.583</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>108.017</v>
+        <v>109.783</v>
       </c>
       <c r="C140" t="n">
-        <v>91.55029999999999</v>
+        <v>91.6644</v>
       </c>
       <c r="D140" t="n">
-        <v>256.599</v>
+        <v>255.734</v>
       </c>
       <c r="E140" t="n">
-        <v>54.4932</v>
+        <v>56.0526</v>
       </c>
       <c r="F140" t="n">
-        <v>169.381</v>
+        <v>167.556</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>110.171</v>
+        <v>107.881</v>
       </c>
       <c r="C141" t="n">
-        <v>91.6776</v>
+        <v>92.0368</v>
       </c>
       <c r="D141" t="n">
-        <v>254.125</v>
+        <v>253.997</v>
       </c>
       <c r="E141" t="n">
-        <v>54.6073</v>
+        <v>55.324</v>
       </c>
       <c r="F141" t="n">
-        <v>168.646</v>
+        <v>166.694</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>106.678</v>
+        <v>106.528</v>
       </c>
       <c r="C142" t="n">
-        <v>92.1191</v>
+        <v>92.3977</v>
       </c>
       <c r="D142" t="n">
-        <v>252.596</v>
+        <v>252.279</v>
       </c>
       <c r="E142" t="n">
-        <v>54.0272</v>
+        <v>55.1524</v>
       </c>
       <c r="F142" t="n">
-        <v>167.805</v>
+        <v>165.791</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>109.503</v>
+        <v>108.994</v>
       </c>
       <c r="C143" t="n">
-        <v>92.2269</v>
+        <v>92.3753</v>
       </c>
       <c r="D143" t="n">
-        <v>250.778</v>
+        <v>250.687</v>
       </c>
       <c r="E143" t="n">
-        <v>53.8424</v>
+        <v>54.6983</v>
       </c>
       <c r="F143" t="n">
-        <v>167.012</v>
+        <v>164.832</v>
       </c>
     </row>
   </sheetData>

--- a/vs-x64/Running insertion.xlsx
+++ b/vs-x64/Running insertion.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>24.1324</v>
+        <v>24.0632</v>
       </c>
       <c r="C2" t="n">
-        <v>31.1801</v>
+        <v>31.2719</v>
       </c>
       <c r="D2" t="n">
-        <v>58.8252</v>
+        <v>59.07</v>
       </c>
       <c r="E2" t="n">
-        <v>14.3322</v>
+        <v>14.3585</v>
       </c>
       <c r="F2" t="n">
-        <v>50.5636</v>
+        <v>50.5942</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>22.4517</v>
+        <v>22.6496</v>
       </c>
       <c r="C3" t="n">
-        <v>30.679</v>
+        <v>30.7715</v>
       </c>
       <c r="D3" t="n">
-        <v>58.4708</v>
+        <v>58.7827</v>
       </c>
       <c r="E3" t="n">
-        <v>13.995</v>
+        <v>14.0403</v>
       </c>
       <c r="F3" t="n">
-        <v>49.8191</v>
+        <v>49.9044</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>22.4103</v>
+        <v>22.2773</v>
       </c>
       <c r="C4" t="n">
-        <v>30.2872</v>
+        <v>30.3061</v>
       </c>
       <c r="D4" t="n">
-        <v>57.994</v>
+        <v>58.056</v>
       </c>
       <c r="E4" t="n">
-        <v>13.6182</v>
+        <v>13.742</v>
       </c>
       <c r="F4" t="n">
-        <v>49.6799</v>
+        <v>49.6152</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>21.7879</v>
+        <v>22.0631</v>
       </c>
       <c r="C5" t="n">
-        <v>29.8824</v>
+        <v>29.9679</v>
       </c>
       <c r="D5" t="n">
-        <v>57.24</v>
+        <v>57.4046</v>
       </c>
       <c r="E5" t="n">
-        <v>20.8127</v>
+        <v>20.8962</v>
       </c>
       <c r="F5" t="n">
-        <v>56.4616</v>
+        <v>56.4513</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>21.6632</v>
+        <v>21.4422</v>
       </c>
       <c r="C6" t="n">
-        <v>29.5056</v>
+        <v>29.5806</v>
       </c>
       <c r="D6" t="n">
-        <v>56.6517</v>
+        <v>56.6921</v>
       </c>
       <c r="E6" t="n">
-        <v>20.0676</v>
+        <v>20.1738</v>
       </c>
       <c r="F6" t="n">
-        <v>55.5649</v>
+        <v>55.5264</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>21.4911</v>
+        <v>21.3059</v>
       </c>
       <c r="C7" t="n">
-        <v>29.1891</v>
+        <v>29.1883</v>
       </c>
       <c r="D7" t="n">
-        <v>68.04259999999999</v>
+        <v>68.0491</v>
       </c>
       <c r="E7" t="n">
-        <v>19.4905</v>
+        <v>19.5491</v>
       </c>
       <c r="F7" t="n">
-        <v>54.6526</v>
+        <v>54.9055</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>20.896</v>
+        <v>21.0854</v>
       </c>
       <c r="C8" t="n">
-        <v>35.857</v>
+        <v>35.9824</v>
       </c>
       <c r="D8" t="n">
-        <v>66.86069999999999</v>
+        <v>67.18429999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>18.8181</v>
+        <v>18.8843</v>
       </c>
       <c r="F8" t="n">
-        <v>54.5351</v>
+        <v>54.8266</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>21.0178</v>
+        <v>21.0017</v>
       </c>
       <c r="C9" t="n">
-        <v>35.1777</v>
+        <v>35.3327</v>
       </c>
       <c r="D9" t="n">
-        <v>65.5998</v>
+        <v>65.928</v>
       </c>
       <c r="E9" t="n">
-        <v>18.2189</v>
+        <v>18.2884</v>
       </c>
       <c r="F9" t="n">
-        <v>53.7144</v>
+        <v>53.9645</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>27.8055</v>
+        <v>27.6424</v>
       </c>
       <c r="C10" t="n">
-        <v>34.6456</v>
+        <v>34.7248</v>
       </c>
       <c r="D10" t="n">
-        <v>64.89360000000001</v>
+        <v>64.7945</v>
       </c>
       <c r="E10" t="n">
-        <v>17.6406</v>
+        <v>17.7093</v>
       </c>
       <c r="F10" t="n">
-        <v>52.9754</v>
+        <v>53.1203</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>27.1702</v>
+        <v>27.1555</v>
       </c>
       <c r="C11" t="n">
-        <v>34.0132</v>
+        <v>34.0901</v>
       </c>
       <c r="D11" t="n">
-        <v>64.01779999999999</v>
+        <v>64.2256</v>
       </c>
       <c r="E11" t="n">
-        <v>17.1037</v>
+        <v>17.1445</v>
       </c>
       <c r="F11" t="n">
-        <v>52.6398</v>
+        <v>52.7174</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>26.6562</v>
+        <v>26.6809</v>
       </c>
       <c r="C12" t="n">
-        <v>33.491</v>
+        <v>33.5508</v>
       </c>
       <c r="D12" t="n">
-        <v>63.1018</v>
+        <v>63.2675</v>
       </c>
       <c r="E12" t="n">
-        <v>16.5874</v>
+        <v>16.6484</v>
       </c>
       <c r="F12" t="n">
-        <v>51.7829</v>
+        <v>51.9638</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>25.8968</v>
+        <v>26.148</v>
       </c>
       <c r="C13" t="n">
-        <v>32.9463</v>
+        <v>33.0585</v>
       </c>
       <c r="D13" t="n">
-        <v>62.3595</v>
+        <v>62.592</v>
       </c>
       <c r="E13" t="n">
-        <v>16.0813</v>
+        <v>16.196</v>
       </c>
       <c r="F13" t="n">
-        <v>51.1377</v>
+        <v>51.4071</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>25.357</v>
+        <v>25.3678</v>
       </c>
       <c r="C14" t="n">
-        <v>32.4269</v>
+        <v>32.5101</v>
       </c>
       <c r="D14" t="n">
-        <v>61.7376</v>
+        <v>61.842</v>
       </c>
       <c r="E14" t="n">
-        <v>15.6795</v>
+        <v>15.7006</v>
       </c>
       <c r="F14" t="n">
-        <v>50.8262</v>
+        <v>50.7714</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>24.8903</v>
+        <v>24.6843</v>
       </c>
       <c r="C15" t="n">
-        <v>31.9557</v>
+        <v>32.0164</v>
       </c>
       <c r="D15" t="n">
-        <v>60.9979</v>
+        <v>61.0538</v>
       </c>
       <c r="E15" t="n">
-        <v>15.2515</v>
+        <v>15.2722</v>
       </c>
       <c r="F15" t="n">
-        <v>50.4692</v>
+        <v>50.3265</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>24.6595</v>
+        <v>24.1844</v>
       </c>
       <c r="C16" t="n">
-        <v>31.5076</v>
+        <v>31.5412</v>
       </c>
       <c r="D16" t="n">
-        <v>60.6749</v>
+        <v>60.6895</v>
       </c>
       <c r="E16" t="n">
-        <v>14.7907</v>
+        <v>14.8748</v>
       </c>
       <c r="F16" t="n">
-        <v>50.111</v>
+        <v>49.9216</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>23.5938</v>
+        <v>23.9171</v>
       </c>
       <c r="C17" t="n">
-        <v>31.0229</v>
+        <v>31.0989</v>
       </c>
       <c r="D17" t="n">
-        <v>60.0116</v>
+        <v>59.9276</v>
       </c>
       <c r="E17" t="n">
-        <v>14.4548</v>
+        <v>14.4809</v>
       </c>
       <c r="F17" t="n">
-        <v>49.5363</v>
+        <v>49.5921</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>23.2195</v>
+        <v>23.5936</v>
       </c>
       <c r="C18" t="n">
-        <v>30.5974</v>
+        <v>30.714</v>
       </c>
       <c r="D18" t="n">
-        <v>59.6165</v>
+        <v>59.7244</v>
       </c>
       <c r="E18" t="n">
-        <v>14.1074</v>
+        <v>14.1662</v>
       </c>
       <c r="F18" t="n">
-        <v>49.1449</v>
+        <v>49.1646</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>23.049</v>
+        <v>22.858</v>
       </c>
       <c r="C19" t="n">
-        <v>30.2641</v>
+        <v>30.2907</v>
       </c>
       <c r="D19" t="n">
-        <v>59.018</v>
+        <v>59.0145</v>
       </c>
       <c r="E19" t="n">
-        <v>13.8624</v>
+        <v>13.8443</v>
       </c>
       <c r="F19" t="n">
-        <v>48.9072</v>
+        <v>48.8818</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>22.6531</v>
+        <v>22.7763</v>
       </c>
       <c r="C20" t="n">
-        <v>29.8651</v>
+        <v>29.9187</v>
       </c>
       <c r="D20" t="n">
-        <v>58.8292</v>
+        <v>59.1149</v>
       </c>
       <c r="E20" t="n">
-        <v>27.173</v>
+        <v>27.2181</v>
       </c>
       <c r="F20" t="n">
-        <v>56.3604</v>
+        <v>56.6428</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>22.2285</v>
+        <v>22.4261</v>
       </c>
       <c r="C21" t="n">
-        <v>29.4657</v>
+        <v>29.5517</v>
       </c>
       <c r="D21" t="n">
-        <v>71.541</v>
+        <v>71.6559</v>
       </c>
       <c r="E21" t="n">
-        <v>26.3287</v>
+        <v>26.2719</v>
       </c>
       <c r="F21" t="n">
-        <v>55.2826</v>
+        <v>55.7218</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>22.002</v>
+        <v>22.1268</v>
       </c>
       <c r="C22" t="n">
-        <v>40.8162</v>
+        <v>40.8698</v>
       </c>
       <c r="D22" t="n">
-        <v>70.3608</v>
+        <v>70.99550000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>25.3449</v>
+        <v>25.2812</v>
       </c>
       <c r="F22" t="n">
-        <v>54.5612</v>
+        <v>55.5228</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>21.9659</v>
+        <v>21.6971</v>
       </c>
       <c r="C23" t="n">
-        <v>39.9276</v>
+        <v>39.9914</v>
       </c>
       <c r="D23" t="n">
-        <v>69.45099999999999</v>
+        <v>69.49630000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>24.4437</v>
+        <v>24.5117</v>
       </c>
       <c r="F23" t="n">
-        <v>53.6598</v>
+        <v>54.2246</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>37.771</v>
+        <v>37.0097</v>
       </c>
       <c r="C24" t="n">
-        <v>39.2904</v>
+        <v>39.2814</v>
       </c>
       <c r="D24" t="n">
-        <v>68.50279999999999</v>
+        <v>68.5598</v>
       </c>
       <c r="E24" t="n">
-        <v>23.611</v>
+        <v>23.557</v>
       </c>
       <c r="F24" t="n">
-        <v>53.2714</v>
+        <v>53.7069</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>41.007</v>
+        <v>40.0761</v>
       </c>
       <c r="C25" t="n">
-        <v>38.4173</v>
+        <v>38.4033</v>
       </c>
       <c r="D25" t="n">
-        <v>67.35299999999999</v>
+        <v>67.4896</v>
       </c>
       <c r="E25" t="n">
-        <v>22.7778</v>
+        <v>22.7394</v>
       </c>
       <c r="F25" t="n">
-        <v>52.5852</v>
+        <v>53.1305</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>39.628</v>
+        <v>37.1187</v>
       </c>
       <c r="C26" t="n">
-        <v>37.6683</v>
+        <v>37.6419</v>
       </c>
       <c r="D26" t="n">
-        <v>66.61190000000001</v>
+        <v>66.91800000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>21.9897</v>
+        <v>22.0038</v>
       </c>
       <c r="F26" t="n">
-        <v>51.9192</v>
+        <v>52.3429</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>38.5894</v>
+        <v>38.8192</v>
       </c>
       <c r="C27" t="n">
-        <v>37.0208</v>
+        <v>36.9363</v>
       </c>
       <c r="D27" t="n">
-        <v>64.51049999999999</v>
+        <v>65.91119999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>21.2517</v>
+        <v>21.2574</v>
       </c>
       <c r="F27" t="n">
-        <v>50.3964</v>
+        <v>50.5184</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>37.3781</v>
+        <v>37.0285</v>
       </c>
       <c r="C28" t="n">
-        <v>36.3221</v>
+        <v>36.2938</v>
       </c>
       <c r="D28" t="n">
-        <v>63.7333</v>
+        <v>65.03319999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>20.6475</v>
+        <v>20.6083</v>
       </c>
       <c r="F28" t="n">
-        <v>49.9688</v>
+        <v>49.8603</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>31.9718</v>
+        <v>32.8374</v>
       </c>
       <c r="C29" t="n">
-        <v>35.6908</v>
+        <v>35.6785</v>
       </c>
       <c r="D29" t="n">
-        <v>63.1972</v>
+        <v>64.2818</v>
       </c>
       <c r="E29" t="n">
-        <v>20.0872</v>
+        <v>19.9989</v>
       </c>
       <c r="F29" t="n">
-        <v>49.4579</v>
+        <v>49.4568</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>31.628</v>
+        <v>36.9616</v>
       </c>
       <c r="C30" t="n">
-        <v>35.0472</v>
+        <v>35.0603</v>
       </c>
       <c r="D30" t="n">
-        <v>62.6654</v>
+        <v>63.9951</v>
       </c>
       <c r="E30" t="n">
-        <v>19.5071</v>
+        <v>19.3923</v>
       </c>
       <c r="F30" t="n">
-        <v>48.9781</v>
+        <v>49.0477</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>30.6983</v>
+        <v>32.0498</v>
       </c>
       <c r="C31" t="n">
-        <v>34.4785</v>
+        <v>34.4747</v>
       </c>
       <c r="D31" t="n">
-        <v>62.1631</v>
+        <v>63.5768</v>
       </c>
       <c r="E31" t="n">
-        <v>18.9425</v>
+        <v>18.8598</v>
       </c>
       <c r="F31" t="n">
-        <v>48.5768</v>
+        <v>48.5247</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>29.9394</v>
+        <v>29.7243</v>
       </c>
       <c r="C32" t="n">
-        <v>33.8581</v>
+        <v>33.9739</v>
       </c>
       <c r="D32" t="n">
-        <v>61.7372</v>
+        <v>62.8162</v>
       </c>
       <c r="E32" t="n">
-        <v>18.335</v>
+        <v>18.3211</v>
       </c>
       <c r="F32" t="n">
-        <v>48.3456</v>
+        <v>48.066</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>29.2943</v>
+        <v>33.4053</v>
       </c>
       <c r="C33" t="n">
-        <v>33.4087</v>
+        <v>33.3733</v>
       </c>
       <c r="D33" t="n">
-        <v>61.5315</v>
+        <v>62.7348</v>
       </c>
       <c r="E33" t="n">
-        <v>17.9064</v>
+        <v>17.8643</v>
       </c>
       <c r="F33" t="n">
-        <v>48.1122</v>
+        <v>47.8915</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>28.3864</v>
+        <v>32.5793</v>
       </c>
       <c r="C34" t="n">
-        <v>32.8166</v>
+        <v>32.7995</v>
       </c>
       <c r="D34" t="n">
-        <v>61.0412</v>
+        <v>62.0026</v>
       </c>
       <c r="E34" t="n">
-        <v>31.8228</v>
+        <v>32.3144</v>
       </c>
       <c r="F34" t="n">
-        <v>58.0294</v>
+        <v>57.6933</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>28.0514</v>
+        <v>30.6998</v>
       </c>
       <c r="C35" t="n">
-        <v>32.3086</v>
+        <v>32.397</v>
       </c>
       <c r="D35" t="n">
-        <v>74.79649999999999</v>
+        <v>75.6538</v>
       </c>
       <c r="E35" t="n">
-        <v>30.8983</v>
+        <v>31.2765</v>
       </c>
       <c r="F35" t="n">
-        <v>57.816</v>
+        <v>56.7108</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>28.6102</v>
+        <v>30.4381</v>
       </c>
       <c r="C36" t="n">
-        <v>31.8461</v>
+        <v>31.8989</v>
       </c>
       <c r="D36" t="n">
-        <v>74.3128</v>
+        <v>74.3583</v>
       </c>
       <c r="E36" t="n">
-        <v>29.5801</v>
+        <v>30.0666</v>
       </c>
       <c r="F36" t="n">
-        <v>56.987</v>
+        <v>56.0275</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>27.0622</v>
+        <v>26.9552</v>
       </c>
       <c r="C37" t="n">
-        <v>42.873</v>
+        <v>43.0741</v>
       </c>
       <c r="D37" t="n">
-        <v>73.0557</v>
+        <v>72.9376</v>
       </c>
       <c r="E37" t="n">
-        <v>28.5511</v>
+        <v>28.9013</v>
       </c>
       <c r="F37" t="n">
-        <v>56.3385</v>
+        <v>55.4409</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>45.5946</v>
+        <v>46.4131</v>
       </c>
       <c r="C38" t="n">
-        <v>41.8768</v>
+        <v>42.2624</v>
       </c>
       <c r="D38" t="n">
-        <v>71.6104</v>
+        <v>71.75230000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>27.5424</v>
+        <v>27.8317</v>
       </c>
       <c r="F38" t="n">
-        <v>55.3497</v>
+        <v>54.4784</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>44.3757</v>
+        <v>44.8599</v>
       </c>
       <c r="C39" t="n">
-        <v>41.0148</v>
+        <v>41.4159</v>
       </c>
       <c r="D39" t="n">
-        <v>70.9983</v>
+        <v>71.5663</v>
       </c>
       <c r="E39" t="n">
-        <v>26.7429</v>
+        <v>26.9084</v>
       </c>
       <c r="F39" t="n">
-        <v>54.9708</v>
+        <v>53.7758</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>45.7442</v>
+        <v>43.8361</v>
       </c>
       <c r="C40" t="n">
-        <v>40.2589</v>
+        <v>40.3539</v>
       </c>
       <c r="D40" t="n">
-        <v>69.6039</v>
+        <v>70.32080000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>25.8202</v>
+        <v>26.1768</v>
       </c>
       <c r="F40" t="n">
-        <v>54.1505</v>
+        <v>53.0292</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>42.3073</v>
+        <v>43.6691</v>
       </c>
       <c r="C41" t="n">
-        <v>39.4985</v>
+        <v>39.2767</v>
       </c>
       <c r="D41" t="n">
-        <v>68.8297</v>
+        <v>69.071</v>
       </c>
       <c r="E41" t="n">
-        <v>24.8376</v>
+        <v>25.1888</v>
       </c>
       <c r="F41" t="n">
-        <v>53.6241</v>
+        <v>52.7211</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>41.039</v>
+        <v>41.0351</v>
       </c>
       <c r="C42" t="n">
-        <v>38.5756</v>
+        <v>38.4521</v>
       </c>
       <c r="D42" t="n">
-        <v>68.5098</v>
+        <v>68.1818</v>
       </c>
       <c r="E42" t="n">
-        <v>24.0585</v>
+        <v>24.3371</v>
       </c>
       <c r="F42" t="n">
-        <v>52.8174</v>
+        <v>51.7974</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>39.4277</v>
+        <v>37.7097</v>
       </c>
       <c r="C43" t="n">
-        <v>37.9168</v>
+        <v>37.7218</v>
       </c>
       <c r="D43" t="n">
-        <v>67.7088</v>
+        <v>68.28270000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>23.3123</v>
+        <v>23.3641</v>
       </c>
       <c r="F43" t="n">
-        <v>52.3807</v>
+        <v>51.4842</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>38.5549</v>
+        <v>38.4033</v>
       </c>
       <c r="C44" t="n">
-        <v>37.2412</v>
+        <v>37.1574</v>
       </c>
       <c r="D44" t="n">
-        <v>67.3793</v>
+        <v>67.0722</v>
       </c>
       <c r="E44" t="n">
-        <v>22.6819</v>
+        <v>22.3816</v>
       </c>
       <c r="F44" t="n">
-        <v>51.8296</v>
+        <v>50.8851</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>38.3276</v>
+        <v>37.2734</v>
       </c>
       <c r="C45" t="n">
-        <v>36.4445</v>
+        <v>36.3675</v>
       </c>
       <c r="D45" t="n">
-        <v>66.5318</v>
+        <v>66.42959999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>21.9797</v>
+        <v>21.7244</v>
       </c>
       <c r="F45" t="n">
-        <v>51.468</v>
+        <v>50.6299</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>38.184</v>
+        <v>34.6308</v>
       </c>
       <c r="C46" t="n">
-        <v>35.7391</v>
+        <v>35.7221</v>
       </c>
       <c r="D46" t="n">
-        <v>66.6748</v>
+        <v>65.79640000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>21.3039</v>
+        <v>21.2237</v>
       </c>
       <c r="F46" t="n">
-        <v>51.087</v>
+        <v>49.8432</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>35.2868</v>
+        <v>35.1235</v>
       </c>
       <c r="C47" t="n">
-        <v>35.0798</v>
+        <v>35.2875</v>
       </c>
       <c r="D47" t="n">
-        <v>65.58329999999999</v>
+        <v>65.6105</v>
       </c>
       <c r="E47" t="n">
-        <v>20.6512</v>
+        <v>20.7091</v>
       </c>
       <c r="F47" t="n">
-        <v>50.5356</v>
+        <v>49.7087</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>34.2204</v>
+        <v>34.2185</v>
       </c>
       <c r="C48" t="n">
-        <v>34.4936</v>
+        <v>34.5532</v>
       </c>
       <c r="D48" t="n">
-        <v>65.4915</v>
+        <v>65.2037</v>
       </c>
       <c r="E48" t="n">
-        <v>35.0267</v>
+        <v>34.8012</v>
       </c>
       <c r="F48" t="n">
-        <v>60.7958</v>
+        <v>59.8361</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>35.6544</v>
+        <v>32.2365</v>
       </c>
       <c r="C49" t="n">
-        <v>34.0199</v>
+        <v>33.8386</v>
       </c>
       <c r="D49" t="n">
-        <v>64.991</v>
+        <v>64.8603</v>
       </c>
       <c r="E49" t="n">
-        <v>33.8066</v>
+        <v>33.3224</v>
       </c>
       <c r="F49" t="n">
-        <v>59.7309</v>
+        <v>59.0085</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>34.4142</v>
+        <v>31.5764</v>
       </c>
       <c r="C50" t="n">
-        <v>33.52</v>
+        <v>33.3171</v>
       </c>
       <c r="D50" t="n">
-        <v>79.5385</v>
+        <v>79.3173</v>
       </c>
       <c r="E50" t="n">
-        <v>32.4622</v>
+        <v>32.4234</v>
       </c>
       <c r="F50" t="n">
-        <v>59.0916</v>
+        <v>58.3939</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>34.2381</v>
+        <v>32.8178</v>
       </c>
       <c r="C51" t="n">
-        <v>44.9656</v>
+        <v>44.6318</v>
       </c>
       <c r="D51" t="n">
-        <v>78.28019999999999</v>
+        <v>78.749</v>
       </c>
       <c r="E51" t="n">
-        <v>31.3076</v>
+        <v>31.4062</v>
       </c>
       <c r="F51" t="n">
-        <v>58.3717</v>
+        <v>57.5696</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>32.4478</v>
+        <v>31.2236</v>
       </c>
       <c r="C52" t="n">
-        <v>43.9406</v>
+        <v>43.6148</v>
       </c>
       <c r="D52" t="n">
-        <v>76.5485</v>
+        <v>76.8434</v>
       </c>
       <c r="E52" t="n">
-        <v>30.2408</v>
+        <v>30.078</v>
       </c>
       <c r="F52" t="n">
-        <v>57.5002</v>
+        <v>56.5778</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>53.8284</v>
+        <v>51.737</v>
       </c>
       <c r="C53" t="n">
-        <v>42.6065</v>
+        <v>42.5181</v>
       </c>
       <c r="D53" t="n">
-        <v>76.0693</v>
+        <v>75.47629999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>29.7494</v>
+        <v>28.8775</v>
       </c>
       <c r="F53" t="n">
-        <v>56.5603</v>
+        <v>55.9564</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>53.0903</v>
+        <v>50.1892</v>
       </c>
       <c r="C54" t="n">
-        <v>41.5934</v>
+        <v>41.4304</v>
       </c>
       <c r="D54" t="n">
-        <v>74.6664</v>
+        <v>74.41759999999999</v>
       </c>
       <c r="E54" t="n">
-        <v>28.56</v>
+        <v>27.8447</v>
       </c>
       <c r="F54" t="n">
-        <v>55.9224</v>
+        <v>55.1345</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>49.5873</v>
+        <v>48.3947</v>
       </c>
       <c r="C55" t="n">
-        <v>40.7415</v>
+        <v>40.7458</v>
       </c>
       <c r="D55" t="n">
-        <v>73.2958</v>
+        <v>73.4516</v>
       </c>
       <c r="E55" t="n">
-        <v>27.6744</v>
+        <v>27.2477</v>
       </c>
       <c r="F55" t="n">
-        <v>55.1003</v>
+        <v>54.9435</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>48.196</v>
+        <v>47.2206</v>
       </c>
       <c r="C56" t="n">
-        <v>39.6823</v>
+        <v>40.0805</v>
       </c>
       <c r="D56" t="n">
-        <v>74.8419</v>
+        <v>72.35250000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>26.4905</v>
+        <v>26.5966</v>
       </c>
       <c r="F56" t="n">
-        <v>56.178</v>
+        <v>55.3205</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>46.8344</v>
+        <v>46.0646</v>
       </c>
       <c r="C57" t="n">
-        <v>39.3811</v>
+        <v>39.0687</v>
       </c>
       <c r="D57" t="n">
-        <v>74.1444</v>
+        <v>72.4555</v>
       </c>
       <c r="E57" t="n">
-        <v>25.5311</v>
+        <v>25.8764</v>
       </c>
       <c r="F57" t="n">
-        <v>54.1543</v>
+        <v>53.3055</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>45.2782</v>
+        <v>45.3104</v>
       </c>
       <c r="C58" t="n">
-        <v>38.2451</v>
+        <v>38.3055</v>
       </c>
       <c r="D58" t="n">
-        <v>70.5431</v>
+        <v>72.6074</v>
       </c>
       <c r="E58" t="n">
-        <v>24.652</v>
+        <v>24.5414</v>
       </c>
       <c r="F58" t="n">
-        <v>53.3645</v>
+        <v>52.6687</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>43.7768</v>
+        <v>43.8598</v>
       </c>
       <c r="C59" t="n">
-        <v>37.3529</v>
+        <v>37.6146</v>
       </c>
       <c r="D59" t="n">
-        <v>69.8519</v>
+        <v>70.0946</v>
       </c>
       <c r="E59" t="n">
-        <v>24.1401</v>
+        <v>23.8317</v>
       </c>
       <c r="F59" t="n">
-        <v>53.7278</v>
+        <v>52.3643</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>42.7058</v>
+        <v>42.2468</v>
       </c>
       <c r="C60" t="n">
-        <v>37.0379</v>
+        <v>36.9004</v>
       </c>
       <c r="D60" t="n">
-        <v>69.5984</v>
+        <v>69.5964</v>
       </c>
       <c r="E60" t="n">
-        <v>23.5521</v>
+        <v>23.2188</v>
       </c>
       <c r="F60" t="n">
-        <v>52.5443</v>
+        <v>51.722</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>42.4522</v>
+        <v>40.8056</v>
       </c>
       <c r="C61" t="n">
-        <v>36.0022</v>
+        <v>36.0831</v>
       </c>
       <c r="D61" t="n">
-        <v>69.39400000000001</v>
+        <v>69.34399999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>22.521</v>
+        <v>22.6873</v>
       </c>
       <c r="F61" t="n">
-        <v>51.9925</v>
+        <v>51.9917</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>41.197</v>
+        <v>41.0912</v>
       </c>
       <c r="C62" t="n">
-        <v>35.6973</v>
+        <v>36.8766</v>
       </c>
       <c r="D62" t="n">
-        <v>68.49509999999999</v>
+        <v>69.8617</v>
       </c>
       <c r="E62" t="n">
-        <v>22.0021</v>
+        <v>23.8486</v>
       </c>
       <c r="F62" t="n">
-        <v>51.5177</v>
+        <v>51.0241</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>39.4986</v>
+        <v>39.3261</v>
       </c>
       <c r="C63" t="n">
-        <v>35.0756</v>
+        <v>36.1458</v>
       </c>
       <c r="D63" t="n">
-        <v>68.2582</v>
+        <v>68.1836</v>
       </c>
       <c r="E63" t="n">
-        <v>36.444</v>
+        <v>37.6654</v>
       </c>
       <c r="F63" t="n">
-        <v>61.7408</v>
+        <v>61.9081</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>38.7752</v>
+        <v>39.0109</v>
       </c>
       <c r="C64" t="n">
-        <v>34.2969</v>
+        <v>34.253</v>
       </c>
       <c r="D64" t="n">
-        <v>84.7272</v>
+        <v>84.9055</v>
       </c>
       <c r="E64" t="n">
-        <v>35.287</v>
+        <v>35.1822</v>
       </c>
       <c r="F64" t="n">
-        <v>60.8781</v>
+        <v>60.8355</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>37.4054</v>
+        <v>37.4636</v>
       </c>
       <c r="C65" t="n">
-        <v>46.168</v>
+        <v>45.6775</v>
       </c>
       <c r="D65" t="n">
-        <v>82.94</v>
+        <v>84.8036</v>
       </c>
       <c r="E65" t="n">
-        <v>33.3802</v>
+        <v>33.5548</v>
       </c>
       <c r="F65" t="n">
-        <v>60.1257</v>
+        <v>59.938</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>36.8843</v>
+        <v>35.9625</v>
       </c>
       <c r="C66" t="n">
-        <v>44.8136</v>
+        <v>44.4984</v>
       </c>
       <c r="D66" t="n">
-        <v>82.3142</v>
+        <v>82.2788</v>
       </c>
       <c r="E66" t="n">
-        <v>32.3552</v>
+        <v>32.1784</v>
       </c>
       <c r="F66" t="n">
-        <v>60.9623</v>
+        <v>59.3355</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>60.842</v>
+        <v>58.7972</v>
       </c>
       <c r="C67" t="n">
-        <v>44.4645</v>
+        <v>43.9234</v>
       </c>
       <c r="D67" t="n">
-        <v>81.74890000000001</v>
+        <v>80.89400000000001</v>
       </c>
       <c r="E67" t="n">
-        <v>31.6703</v>
+        <v>31.5704</v>
       </c>
       <c r="F67" t="n">
-        <v>60.343</v>
+        <v>58.0379</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>58.2828</v>
+        <v>56.837</v>
       </c>
       <c r="C68" t="n">
-        <v>43.3856</v>
+        <v>43.4249</v>
       </c>
       <c r="D68" t="n">
-        <v>79.4385</v>
+        <v>79.12050000000001</v>
       </c>
       <c r="E68" t="n">
-        <v>30.2104</v>
+        <v>30.5606</v>
       </c>
       <c r="F68" t="n">
-        <v>57.8946</v>
+        <v>57.9764</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>56.3163</v>
+        <v>55.0022</v>
       </c>
       <c r="C69" t="n">
-        <v>42.4423</v>
+        <v>42.1133</v>
       </c>
       <c r="D69" t="n">
-        <v>77.9273</v>
+        <v>77.6307</v>
       </c>
       <c r="E69" t="n">
-        <v>29.9001</v>
+        <v>29.1627</v>
       </c>
       <c r="F69" t="n">
-        <v>57.8934</v>
+        <v>57.7639</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>55.0301</v>
+        <v>53.8067</v>
       </c>
       <c r="C70" t="n">
-        <v>41.4429</v>
+        <v>41.8803</v>
       </c>
       <c r="D70" t="n">
-        <v>77.2672</v>
+        <v>78.0911</v>
       </c>
       <c r="E70" t="n">
-        <v>28.2539</v>
+        <v>28.322</v>
       </c>
       <c r="F70" t="n">
-        <v>57.7155</v>
+        <v>55.9574</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>54.4087</v>
+        <v>52.6354</v>
       </c>
       <c r="C71" t="n">
-        <v>41.3055</v>
+        <v>40.5942</v>
       </c>
       <c r="D71" t="n">
-        <v>75.79989999999999</v>
+        <v>77.2375</v>
       </c>
       <c r="E71" t="n">
-        <v>27.8844</v>
+        <v>27.869</v>
       </c>
       <c r="F71" t="n">
-        <v>55.9589</v>
+        <v>55.8607</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>52.3331</v>
+        <v>51.1702</v>
       </c>
       <c r="C72" t="n">
-        <v>39.6744</v>
+        <v>39.5408</v>
       </c>
       <c r="D72" t="n">
-        <v>75.2351</v>
+        <v>75.44799999999999</v>
       </c>
       <c r="E72" t="n">
-        <v>27.1551</v>
+        <v>26.6025</v>
       </c>
       <c r="F72" t="n">
-        <v>55.4634</v>
+        <v>55.366</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>51.3561</v>
+        <v>50.0368</v>
       </c>
       <c r="C73" t="n">
-        <v>39.0856</v>
+        <v>38.7715</v>
       </c>
       <c r="D73" t="n">
-        <v>74.9408</v>
+        <v>76.1018</v>
       </c>
       <c r="E73" t="n">
-        <v>26.0556</v>
+        <v>25.7139</v>
       </c>
       <c r="F73" t="n">
-        <v>55.3116</v>
+        <v>55.6265</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>49.2015</v>
+        <v>48.4871</v>
       </c>
       <c r="C74" t="n">
-        <v>38.0985</v>
+        <v>38.1003</v>
       </c>
       <c r="D74" t="n">
-        <v>74.2838</v>
+        <v>75.05929999999999</v>
       </c>
       <c r="E74" t="n">
-        <v>25.384</v>
+        <v>24.8771</v>
       </c>
       <c r="F74" t="n">
-        <v>54.4359</v>
+        <v>53.8494</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>48.4276</v>
+        <v>47.2781</v>
       </c>
       <c r="C75" t="n">
-        <v>37.3531</v>
+        <v>37.137</v>
       </c>
       <c r="D75" t="n">
-        <v>74.071</v>
+        <v>74.4177</v>
       </c>
       <c r="E75" t="n">
-        <v>25.0131</v>
+        <v>24.3464</v>
       </c>
       <c r="F75" t="n">
-        <v>54.1623</v>
+        <v>53.4479</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>46.9109</v>
+        <v>46.3164</v>
       </c>
       <c r="C76" t="n">
-        <v>36.7728</v>
+        <v>36.571</v>
       </c>
       <c r="D76" t="n">
-        <v>74.73439999999999</v>
+        <v>75.1229</v>
       </c>
       <c r="E76" t="n">
-        <v>24.3641</v>
+        <v>23.9476</v>
       </c>
       <c r="F76" t="n">
-        <v>54.0233</v>
+        <v>53.6598</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>46.5296</v>
+        <v>45.4121</v>
       </c>
       <c r="C77" t="n">
-        <v>36.0549</v>
+        <v>36.2242</v>
       </c>
       <c r="D77" t="n">
-        <v>73.4158</v>
+        <v>74.0346</v>
       </c>
       <c r="E77" t="n">
-        <v>38.842</v>
+        <v>37.9061</v>
       </c>
       <c r="F77" t="n">
-        <v>77.5642</v>
+        <v>77.4881</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>44.7618</v>
+        <v>44.0515</v>
       </c>
       <c r="C78" t="n">
-        <v>35.6447</v>
+        <v>35.5137</v>
       </c>
       <c r="D78" t="n">
-        <v>108.341</v>
+        <v>108.722</v>
       </c>
       <c r="E78" t="n">
-        <v>37.905</v>
+        <v>37.4715</v>
       </c>
       <c r="F78" t="n">
-        <v>77.851</v>
+        <v>77.0352</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>43.7231</v>
+        <v>44.0002</v>
       </c>
       <c r="C79" t="n">
-        <v>47.4383</v>
+        <v>48.7918</v>
       </c>
       <c r="D79" t="n">
-        <v>107.39</v>
+        <v>108.055</v>
       </c>
       <c r="E79" t="n">
-        <v>36.7929</v>
+        <v>36.2597</v>
       </c>
       <c r="F79" t="n">
-        <v>77.52200000000001</v>
+        <v>77.4085</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>42.675</v>
+        <v>42.4871</v>
       </c>
       <c r="C80" t="n">
-        <v>47.466</v>
+        <v>48.0497</v>
       </c>
       <c r="D80" t="n">
-        <v>105.928</v>
+        <v>106.609</v>
       </c>
       <c r="E80" t="n">
-        <v>35.9979</v>
+        <v>35.0978</v>
       </c>
       <c r="F80" t="n">
-        <v>76.304</v>
+        <v>77.1138</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>63.1886</v>
+        <v>62.9881</v>
       </c>
       <c r="C81" t="n">
-        <v>48.112</v>
+        <v>46.9123</v>
       </c>
       <c r="D81" t="n">
-        <v>104.794</v>
+        <v>107.063</v>
       </c>
       <c r="E81" t="n">
-        <v>34.7763</v>
+        <v>34.6168</v>
       </c>
       <c r="F81" t="n">
-        <v>76.1263</v>
+        <v>76.07299999999999</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>61.7923</v>
+        <v>62.6427</v>
       </c>
       <c r="C82" t="n">
-        <v>47.5516</v>
+        <v>46.7146</v>
       </c>
       <c r="D82" t="n">
-        <v>104.097</v>
+        <v>105.745</v>
       </c>
       <c r="E82" t="n">
-        <v>33.528</v>
+        <v>33.2862</v>
       </c>
       <c r="F82" t="n">
-        <v>74.8776</v>
+        <v>74.86499999999999</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>61.416</v>
+        <v>61.2263</v>
       </c>
       <c r="C83" t="n">
-        <v>46.5501</v>
+        <v>47.0103</v>
       </c>
       <c r="D83" t="n">
-        <v>103.782</v>
+        <v>103.425</v>
       </c>
       <c r="E83" t="n">
-        <v>32.1858</v>
+        <v>32.6517</v>
       </c>
       <c r="F83" t="n">
-        <v>73.8085</v>
+        <v>73.44799999999999</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>60.8752</v>
+        <v>61.1127</v>
       </c>
       <c r="C84" t="n">
-        <v>47.0886</v>
+        <v>45.9915</v>
       </c>
       <c r="D84" t="n">
-        <v>102.714</v>
+        <v>103.459</v>
       </c>
       <c r="E84" t="n">
-        <v>31.8281</v>
+        <v>31.6855</v>
       </c>
       <c r="F84" t="n">
-        <v>73.6431</v>
+        <v>72.6123</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>59.9708</v>
+        <v>60.2815</v>
       </c>
       <c r="C85" t="n">
-        <v>45.7917</v>
+        <v>45.948</v>
       </c>
       <c r="D85" t="n">
-        <v>102.924</v>
+        <v>102.881</v>
       </c>
       <c r="E85" t="n">
-        <v>30.548</v>
+        <v>30.98</v>
       </c>
       <c r="F85" t="n">
-        <v>72.20480000000001</v>
+        <v>71.1542</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>58.9186</v>
+        <v>59.0399</v>
       </c>
       <c r="C86" t="n">
-        <v>45.0537</v>
+        <v>45.2542</v>
       </c>
       <c r="D86" t="n">
-        <v>102.837</v>
+        <v>103.029</v>
       </c>
       <c r="E86" t="n">
-        <v>30.1826</v>
+        <v>29.7276</v>
       </c>
       <c r="F86" t="n">
-        <v>71.41370000000001</v>
+        <v>70.91160000000001</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>58.0145</v>
+        <v>58.4015</v>
       </c>
       <c r="C87" t="n">
-        <v>44.7097</v>
+        <v>44.8184</v>
       </c>
       <c r="D87" t="n">
-        <v>103.484</v>
+        <v>102.917</v>
       </c>
       <c r="E87" t="n">
-        <v>28.754</v>
+        <v>28.9571</v>
       </c>
       <c r="F87" t="n">
-        <v>70.76990000000001</v>
+        <v>68.5981</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>57.9142</v>
+        <v>56.9363</v>
       </c>
       <c r="C88" t="n">
-        <v>43.7248</v>
+        <v>43.9688</v>
       </c>
       <c r="D88" t="n">
-        <v>104.115</v>
+        <v>102.807</v>
       </c>
       <c r="E88" t="n">
-        <v>28.5693</v>
+        <v>27.9672</v>
       </c>
       <c r="F88" t="n">
-        <v>70.0518</v>
+        <v>68.10080000000001</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>56.5716</v>
+        <v>55.8186</v>
       </c>
       <c r="C89" t="n">
-        <v>43.4155</v>
+        <v>43.2974</v>
       </c>
       <c r="D89" t="n">
-        <v>103.549</v>
+        <v>104.902</v>
       </c>
       <c r="E89" t="n">
-        <v>27.0879</v>
+        <v>26.9909</v>
       </c>
       <c r="F89" t="n">
-        <v>68.1159</v>
+        <v>66.7903</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>54.963</v>
+        <v>54.7289</v>
       </c>
       <c r="C90" t="n">
-        <v>42.8454</v>
+        <v>42.8104</v>
       </c>
       <c r="D90" t="n">
-        <v>105.444</v>
+        <v>103.744</v>
       </c>
       <c r="E90" t="n">
-        <v>27.4148</v>
+        <v>27.0347</v>
       </c>
       <c r="F90" t="n">
-        <v>67.4273</v>
+        <v>66.56480000000001</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>53.835</v>
+        <v>53.7413</v>
       </c>
       <c r="C91" t="n">
-        <v>42.1078</v>
+        <v>42.2216</v>
       </c>
       <c r="D91" t="n">
-        <v>105.392</v>
+        <v>107.119</v>
       </c>
       <c r="E91" t="n">
-        <v>42.4423</v>
+        <v>42.4348</v>
       </c>
       <c r="F91" t="n">
-        <v>98.42100000000001</v>
+        <v>98.88849999999999</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>52.3232</v>
+        <v>52.2875</v>
       </c>
       <c r="C92" t="n">
-        <v>41.7251</v>
+        <v>41.6248</v>
       </c>
       <c r="D92" t="n">
-        <v>147.768</v>
+        <v>148.835</v>
       </c>
       <c r="E92" t="n">
-        <v>40.71</v>
+        <v>40.4562</v>
       </c>
       <c r="F92" t="n">
-        <v>97.54640000000001</v>
+        <v>98.88079999999999</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>52.7553</v>
+        <v>52.8117</v>
       </c>
       <c r="C93" t="n">
-        <v>41.2827</v>
+        <v>41.071</v>
       </c>
       <c r="D93" t="n">
-        <v>147.766</v>
+        <v>148.469</v>
       </c>
       <c r="E93" t="n">
-        <v>39.9291</v>
+        <v>39.6212</v>
       </c>
       <c r="F93" t="n">
-        <v>96.6533</v>
+        <v>97.0861</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>51.6044</v>
+        <v>51.1743</v>
       </c>
       <c r="C94" t="n">
-        <v>54.6754</v>
+        <v>54.4057</v>
       </c>
       <c r="D94" t="n">
-        <v>145.518</v>
+        <v>147.938</v>
       </c>
       <c r="E94" t="n">
-        <v>39.0182</v>
+        <v>38.9712</v>
       </c>
       <c r="F94" t="n">
-        <v>96.2629</v>
+        <v>96.5231</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>71.71250000000001</v>
+        <v>73.9417</v>
       </c>
       <c r="C95" t="n">
-        <v>54.7351</v>
+        <v>54.6222</v>
       </c>
       <c r="D95" t="n">
-        <v>144.37</v>
+        <v>146.693</v>
       </c>
       <c r="E95" t="n">
-        <v>37.2726</v>
+        <v>37.5516</v>
       </c>
       <c r="F95" t="n">
-        <v>95.1255</v>
+        <v>95.3099</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>71.56959999999999</v>
+        <v>73.5853</v>
       </c>
       <c r="C96" t="n">
-        <v>53.5319</v>
+        <v>54.2581</v>
       </c>
       <c r="D96" t="n">
-        <v>144.151</v>
+        <v>144.996</v>
       </c>
       <c r="E96" t="n">
-        <v>37.4356</v>
+        <v>36.2531</v>
       </c>
       <c r="F96" t="n">
-        <v>94.15000000000001</v>
+        <v>93.86409999999999</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>70.2757</v>
+        <v>73.1088</v>
       </c>
       <c r="C97" t="n">
-        <v>53.6789</v>
+        <v>52.9877</v>
       </c>
       <c r="D97" t="n">
-        <v>143.844</v>
+        <v>144.364</v>
       </c>
       <c r="E97" t="n">
-        <v>35.8719</v>
+        <v>35.3304</v>
       </c>
       <c r="F97" t="n">
-        <v>93.1799</v>
+        <v>92.8402</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>69.85590000000001</v>
+        <v>72.02249999999999</v>
       </c>
       <c r="C98" t="n">
-        <v>53.5588</v>
+        <v>53.0318</v>
       </c>
       <c r="D98" t="n">
-        <v>143.431</v>
+        <v>144.276</v>
       </c>
       <c r="E98" t="n">
-        <v>35.3736</v>
+        <v>34.7012</v>
       </c>
       <c r="F98" t="n">
-        <v>92.8751</v>
+        <v>91.0861</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>69.39</v>
+        <v>71.3056</v>
       </c>
       <c r="C99" t="n">
-        <v>52.7564</v>
+        <v>53.2722</v>
       </c>
       <c r="D99" t="n">
-        <v>144.178</v>
+        <v>145.005</v>
       </c>
       <c r="E99" t="n">
-        <v>33.9647</v>
+        <v>33.7057</v>
       </c>
       <c r="F99" t="n">
-        <v>90.9152</v>
+        <v>91.2559</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>68.5014</v>
+        <v>70.28449999999999</v>
       </c>
       <c r="C100" t="n">
-        <v>52.5765</v>
+        <v>53.1255</v>
       </c>
       <c r="D100" t="n">
-        <v>145.2</v>
+        <v>145.189</v>
       </c>
       <c r="E100" t="n">
-        <v>33.5275</v>
+        <v>33.7024</v>
       </c>
       <c r="F100" t="n">
-        <v>90.8259</v>
+        <v>89.7732</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>68.1788</v>
+        <v>69.6879</v>
       </c>
       <c r="C101" t="n">
-        <v>52.5427</v>
+        <v>52.5683</v>
       </c>
       <c r="D101" t="n">
-        <v>144.947</v>
+        <v>145.426</v>
       </c>
       <c r="E101" t="n">
-        <v>32.5149</v>
+        <v>32.498</v>
       </c>
       <c r="F101" t="n">
-        <v>89.52719999999999</v>
+        <v>88.86369999999999</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>67.53279999999999</v>
+        <v>65.96769999999999</v>
       </c>
       <c r="C102" t="n">
-        <v>52.6376</v>
+        <v>52.4469</v>
       </c>
       <c r="D102" t="n">
-        <v>144.753</v>
+        <v>145.394</v>
       </c>
       <c r="E102" t="n">
-        <v>32.2783</v>
+        <v>31.6992</v>
       </c>
       <c r="F102" t="n">
-        <v>87.9918</v>
+        <v>88.3946</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>66.3699</v>
+        <v>65.49299999999999</v>
       </c>
       <c r="C103" t="n">
-        <v>52.5217</v>
+        <v>52.1939</v>
       </c>
       <c r="D103" t="n">
-        <v>146.094</v>
+        <v>146.369</v>
       </c>
       <c r="E103" t="n">
-        <v>30.9916</v>
+        <v>31.1981</v>
       </c>
       <c r="F103" t="n">
-        <v>87.64570000000001</v>
+        <v>87.68689999999999</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>64.95399999999999</v>
+        <v>65.4269</v>
       </c>
       <c r="C104" t="n">
-        <v>52.0375</v>
+        <v>52.0529</v>
       </c>
       <c r="D104" t="n">
-        <v>146.349</v>
+        <v>148.148</v>
       </c>
       <c r="E104" t="n">
-        <v>30.2172</v>
+        <v>30.1655</v>
       </c>
       <c r="F104" t="n">
-        <v>86.44629999999999</v>
+        <v>87.27379999999999</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>64.855</v>
+        <v>65.2701</v>
       </c>
       <c r="C105" t="n">
-        <v>52.3906</v>
+        <v>52.3356</v>
       </c>
       <c r="D105" t="n">
-        <v>147.272</v>
+        <v>148.825</v>
       </c>
       <c r="E105" t="n">
-        <v>45.944</v>
+        <v>45.7098</v>
       </c>
       <c r="F105" t="n">
-        <v>121.185</v>
+        <v>120.481</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>64.6703</v>
+        <v>63.8481</v>
       </c>
       <c r="C106" t="n">
-        <v>51.9479</v>
+        <v>51.7009</v>
       </c>
       <c r="D106" t="n">
-        <v>148.557</v>
+        <v>149.064</v>
       </c>
       <c r="E106" t="n">
-        <v>44.0085</v>
+        <v>44.2961</v>
       </c>
       <c r="F106" t="n">
-        <v>119.603</v>
+        <v>119.72</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>63.6068</v>
+        <v>63.2942</v>
       </c>
       <c r="C107" t="n">
-        <v>51.8819</v>
+        <v>51.8838</v>
       </c>
       <c r="D107" t="n">
-        <v>193.828</v>
+        <v>193.994</v>
       </c>
       <c r="E107" t="n">
-        <v>43.1458</v>
+        <v>43.5351</v>
       </c>
       <c r="F107" t="n">
-        <v>119.257</v>
+        <v>119.386</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>63.7222</v>
+        <v>64.1748</v>
       </c>
       <c r="C108" t="n">
-        <v>63.5936</v>
+        <v>63.9479</v>
       </c>
       <c r="D108" t="n">
-        <v>191.364</v>
+        <v>192.454</v>
       </c>
       <c r="E108" t="n">
-        <v>42.8242</v>
+        <v>42.6003</v>
       </c>
       <c r="F108" t="n">
-        <v>118.642</v>
+        <v>118.075</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>63.5234</v>
+        <v>63.8202</v>
       </c>
       <c r="C109" t="n">
-        <v>63.6178</v>
+        <v>64.29430000000001</v>
       </c>
       <c r="D109" t="n">
-        <v>190.283</v>
+        <v>191.242</v>
       </c>
       <c r="E109" t="n">
-        <v>41.1849</v>
+        <v>42.267</v>
       </c>
       <c r="F109" t="n">
-        <v>117.601</v>
+        <v>117.684</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>82.5239</v>
+        <v>83.27160000000001</v>
       </c>
       <c r="C110" t="n">
-        <v>63.8015</v>
+        <v>64.319</v>
       </c>
       <c r="D110" t="n">
-        <v>190.007</v>
+        <v>188.845</v>
       </c>
       <c r="E110" t="n">
-        <v>41.1031</v>
+        <v>40.7981</v>
       </c>
       <c r="F110" t="n">
-        <v>117.613</v>
+        <v>116.004</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>81.9773</v>
+        <v>83.95010000000001</v>
       </c>
       <c r="C111" t="n">
-        <v>63.8272</v>
+        <v>63.6036</v>
       </c>
       <c r="D111" t="n">
-        <v>188.434</v>
+        <v>187.956</v>
       </c>
       <c r="E111" t="n">
-        <v>40.2823</v>
+        <v>40.2852</v>
       </c>
       <c r="F111" t="n">
-        <v>115.792</v>
+        <v>115.79</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>80.89570000000001</v>
+        <v>81.5299</v>
       </c>
       <c r="C112" t="n">
-        <v>64.2354</v>
+        <v>64.0879</v>
       </c>
       <c r="D112" t="n">
-        <v>187.401</v>
+        <v>187.585</v>
       </c>
       <c r="E112" t="n">
-        <v>39.4526</v>
+        <v>39.5543</v>
       </c>
       <c r="F112" t="n">
-        <v>114.986</v>
+        <v>114.886</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>85.2115</v>
+        <v>84.36060000000001</v>
       </c>
       <c r="C113" t="n">
-        <v>63.7072</v>
+        <v>63.418</v>
       </c>
       <c r="D113" t="n">
-        <v>187.523</v>
+        <v>186.815</v>
       </c>
       <c r="E113" t="n">
-        <v>38.8357</v>
+        <v>38.2358</v>
       </c>
       <c r="F113" t="n">
-        <v>114.398</v>
+        <v>114.561</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>84.99339999999999</v>
+        <v>83.62690000000001</v>
       </c>
       <c r="C114" t="n">
-        <v>63.8559</v>
+        <v>64.0094</v>
       </c>
       <c r="D114" t="n">
-        <v>186.593</v>
+        <v>187.009</v>
       </c>
       <c r="E114" t="n">
-        <v>38.2887</v>
+        <v>37.61</v>
       </c>
       <c r="F114" t="n">
-        <v>114.14</v>
+        <v>114.727</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>83.8336</v>
+        <v>82.9525</v>
       </c>
       <c r="C115" t="n">
-        <v>63.8316</v>
+        <v>63.8826</v>
       </c>
       <c r="D115" t="n">
-        <v>187.004</v>
+        <v>186.911</v>
       </c>
       <c r="E115" t="n">
-        <v>37.5447</v>
+        <v>37.4781</v>
       </c>
       <c r="F115" t="n">
-        <v>113.945</v>
+        <v>113.531</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>82.78579999999999</v>
+        <v>81.8669</v>
       </c>
       <c r="C116" t="n">
-        <v>64.0502</v>
+        <v>63.7344</v>
       </c>
       <c r="D116" t="n">
-        <v>186.587</v>
+        <v>186.407</v>
       </c>
       <c r="E116" t="n">
-        <v>36.6713</v>
+        <v>36.6115</v>
       </c>
       <c r="F116" t="n">
-        <v>114.315</v>
+        <v>114.719</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>77.7236</v>
+        <v>78.4836</v>
       </c>
       <c r="C117" t="n">
-        <v>63.5032</v>
+        <v>63.7863</v>
       </c>
       <c r="D117" t="n">
-        <v>186.32</v>
+        <v>187.282</v>
       </c>
       <c r="E117" t="n">
-        <v>35.8106</v>
+        <v>36.1568</v>
       </c>
       <c r="F117" t="n">
-        <v>113.844</v>
+        <v>112.976</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>76.95440000000001</v>
+        <v>76.246</v>
       </c>
       <c r="C118" t="n">
-        <v>63.9895</v>
+        <v>63.746</v>
       </c>
       <c r="D118" t="n">
-        <v>187.651</v>
+        <v>187.635</v>
       </c>
       <c r="E118" t="n">
-        <v>35.4062</v>
+        <v>35.789</v>
       </c>
       <c r="F118" t="n">
-        <v>113.247</v>
+        <v>112.827</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>77.09999999999999</v>
+        <v>76.1056</v>
       </c>
       <c r="C119" t="n">
-        <v>63.4192</v>
+        <v>63.723</v>
       </c>
       <c r="D119" t="n">
-        <v>187.905</v>
+        <v>187.967</v>
       </c>
       <c r="E119" t="n">
-        <v>51.1254</v>
+        <v>50.1213</v>
       </c>
       <c r="F119" t="n">
-        <v>148.342</v>
+        <v>148.541</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>76.23560000000001</v>
+        <v>76.02209999999999</v>
       </c>
       <c r="C120" t="n">
-        <v>63.8092</v>
+        <v>63.8204</v>
       </c>
       <c r="D120" t="n">
-        <v>189.34</v>
+        <v>188.854</v>
       </c>
       <c r="E120" t="n">
-        <v>50.2352</v>
+        <v>50.3066</v>
       </c>
       <c r="F120" t="n">
-        <v>147.683</v>
+        <v>146.775</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>76.5326</v>
+        <v>74.5283</v>
       </c>
       <c r="C121" t="n">
-        <v>63.3845</v>
+        <v>63.0068</v>
       </c>
       <c r="D121" t="n">
-        <v>236.308</v>
+        <v>236.654</v>
       </c>
       <c r="E121" t="n">
-        <v>49.5785</v>
+        <v>49.6354</v>
       </c>
       <c r="F121" t="n">
-        <v>146.948</v>
+        <v>146.559</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>76.1704</v>
+        <v>74.6172</v>
       </c>
       <c r="C122" t="n">
-        <v>75.3548</v>
+        <v>74.92700000000001</v>
       </c>
       <c r="D122" t="n">
-        <v>233.455</v>
+        <v>234.208</v>
       </c>
       <c r="E122" t="n">
-        <v>48.3187</v>
+        <v>49.0726</v>
       </c>
       <c r="F122" t="n">
-        <v>145.352</v>
+        <v>145.614</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>74.923</v>
+        <v>74.2178</v>
       </c>
       <c r="C123" t="n">
-        <v>75.3933</v>
+        <v>75.842</v>
       </c>
       <c r="D123" t="n">
-        <v>230.746</v>
+        <v>231.905</v>
       </c>
       <c r="E123" t="n">
-        <v>47.2543</v>
+        <v>48.2971</v>
       </c>
       <c r="F123" t="n">
-        <v>144.972</v>
+        <v>144.686</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>95.0181</v>
+        <v>96.6985</v>
       </c>
       <c r="C124" t="n">
-        <v>75.63209999999999</v>
+        <v>75.9576</v>
       </c>
       <c r="D124" t="n">
-        <v>229.779</v>
+        <v>229.331</v>
       </c>
       <c r="E124" t="n">
-        <v>47.564</v>
+        <v>47.9897</v>
       </c>
       <c r="F124" t="n">
-        <v>144.43</v>
+        <v>143.49</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>94.47029999999999</v>
+        <v>94.1895</v>
       </c>
       <c r="C125" t="n">
-        <v>76.12860000000001</v>
+        <v>76.0072</v>
       </c>
       <c r="D125" t="n">
-        <v>226.854</v>
+        <v>228.152</v>
       </c>
       <c r="E125" t="n">
-        <v>49.0306</v>
+        <v>47.0773</v>
       </c>
       <c r="F125" t="n">
-        <v>142.861</v>
+        <v>142.998</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>94.4127</v>
+        <v>93.8244</v>
       </c>
       <c r="C126" t="n">
-        <v>76.4675</v>
+        <v>76.0294</v>
       </c>
       <c r="D126" t="n">
-        <v>226.051</v>
+        <v>226.249</v>
       </c>
       <c r="E126" t="n">
-        <v>47.2719</v>
+        <v>46.7299</v>
       </c>
       <c r="F126" t="n">
-        <v>142.551</v>
+        <v>143.03</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>92.7774</v>
+        <v>93.2483</v>
       </c>
       <c r="C127" t="n">
-        <v>76.41800000000001</v>
+        <v>76.2021</v>
       </c>
       <c r="D127" t="n">
-        <v>224.545</v>
+        <v>225.988</v>
       </c>
       <c r="E127" t="n">
-        <v>46.3513</v>
+        <v>46.3751</v>
       </c>
       <c r="F127" t="n">
-        <v>142.108</v>
+        <v>142.411</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>94.5829</v>
+        <v>94.5812</v>
       </c>
       <c r="C128" t="n">
-        <v>76.7962</v>
+        <v>76.2843</v>
       </c>
       <c r="D128" t="n">
-        <v>223.113</v>
+        <v>223.941</v>
       </c>
       <c r="E128" t="n">
-        <v>44.4237</v>
+        <v>44.7987</v>
       </c>
       <c r="F128" t="n">
-        <v>141.648</v>
+        <v>142.142</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>94.62730000000001</v>
+        <v>94.7111</v>
       </c>
       <c r="C129" t="n">
-        <v>77.06100000000001</v>
+        <v>77.0475</v>
       </c>
       <c r="D129" t="n">
-        <v>222.649</v>
+        <v>223.553</v>
       </c>
       <c r="E129" t="n">
-        <v>44.5385</v>
+        <v>44.4001</v>
       </c>
       <c r="F129" t="n">
-        <v>140.981</v>
+        <v>141.331</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>92.5633</v>
+        <v>92.65770000000001</v>
       </c>
       <c r="C130" t="n">
-        <v>76.3546</v>
+        <v>76.9902</v>
       </c>
       <c r="D130" t="n">
-        <v>221.299</v>
+        <v>222.2</v>
       </c>
       <c r="E130" t="n">
-        <v>43.3754</v>
+        <v>43.3869</v>
       </c>
       <c r="F130" t="n">
-        <v>140.862</v>
+        <v>140.734</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>92.9211</v>
+        <v>93.4365</v>
       </c>
       <c r="C131" t="n">
-        <v>77.36150000000001</v>
+        <v>77.047</v>
       </c>
       <c r="D131" t="n">
-        <v>221.473</v>
+        <v>222.183</v>
       </c>
       <c r="E131" t="n">
-        <v>43.0421</v>
+        <v>43.1389</v>
       </c>
       <c r="F131" t="n">
-        <v>140.36</v>
+        <v>140.615</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>93.00579999999999</v>
+        <v>93.33320000000001</v>
       </c>
       <c r="C132" t="n">
-        <v>77.7094</v>
+        <v>77.57170000000001</v>
       </c>
       <c r="D132" t="n">
-        <v>221.469</v>
+        <v>221.954</v>
       </c>
       <c r="E132" t="n">
-        <v>42.3503</v>
+        <v>42.6411</v>
       </c>
       <c r="F132" t="n">
-        <v>140.263</v>
+        <v>140.481</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>91.2873</v>
+        <v>91.0849</v>
       </c>
       <c r="C133" t="n">
-        <v>77.6135</v>
+        <v>77.3794</v>
       </c>
       <c r="D133" t="n">
-        <v>221.911</v>
+        <v>221.627</v>
       </c>
       <c r="E133" t="n">
-        <v>42.5105</v>
+        <v>42.1201</v>
       </c>
       <c r="F133" t="n">
-        <v>140.065</v>
+        <v>140.537</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>90.86879999999999</v>
+        <v>91.1904</v>
       </c>
       <c r="C134" t="n">
-        <v>77.89100000000001</v>
+        <v>77.4252</v>
       </c>
       <c r="D134" t="n">
-        <v>222.422</v>
+        <v>222.108</v>
       </c>
       <c r="E134" t="n">
-        <v>58.0387</v>
+        <v>58.2858</v>
       </c>
       <c r="F134" t="n">
-        <v>175.639</v>
+        <v>175.59</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>90.6211</v>
+        <v>89.1434</v>
       </c>
       <c r="C135" t="n">
-        <v>77.6656</v>
+        <v>77.488</v>
       </c>
       <c r="D135" t="n">
-        <v>271.438</v>
+        <v>271.587</v>
       </c>
       <c r="E135" t="n">
-        <v>57.8446</v>
+        <v>56.9989</v>
       </c>
       <c r="F135" t="n">
-        <v>173.586</v>
+        <v>174.002</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>91.65689999999999</v>
+        <v>89.7148</v>
       </c>
       <c r="C136" t="n">
-        <v>89.8321</v>
+        <v>90.0153</v>
       </c>
       <c r="D136" t="n">
-        <v>266.901</v>
+        <v>267.471</v>
       </c>
       <c r="E136" t="n">
-        <v>56.714</v>
+        <v>57.0706</v>
       </c>
       <c r="F136" t="n">
-        <v>172.282</v>
+        <v>172.617</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>90.1823</v>
+        <v>91.2183</v>
       </c>
       <c r="C137" t="n">
-        <v>90.4846</v>
+        <v>90.3544</v>
       </c>
       <c r="D137" t="n">
-        <v>263.885</v>
+        <v>264.718</v>
       </c>
       <c r="E137" t="n">
-        <v>56.6944</v>
+        <v>57.6037</v>
       </c>
       <c r="F137" t="n">
-        <v>170.862</v>
+        <v>171.306</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>111.83</v>
+        <v>109.515</v>
       </c>
       <c r="C138" t="n">
-        <v>90.9224</v>
+        <v>90.8747</v>
       </c>
       <c r="D138" t="n">
-        <v>260.932</v>
+        <v>261.761</v>
       </c>
       <c r="E138" t="n">
-        <v>56.8205</v>
+        <v>55.853</v>
       </c>
       <c r="F138" t="n">
-        <v>169.551</v>
+        <v>169.833</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>107.951</v>
+        <v>109.302</v>
       </c>
       <c r="C139" t="n">
-        <v>91.1872</v>
+        <v>91.1337</v>
       </c>
       <c r="D139" t="n">
-        <v>258.305</v>
+        <v>259.274</v>
       </c>
       <c r="E139" t="n">
-        <v>57.0777</v>
+        <v>56.0101</v>
       </c>
       <c r="F139" t="n">
-        <v>168.583</v>
+        <v>169.001</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>109.783</v>
+        <v>108.374</v>
       </c>
       <c r="C140" t="n">
-        <v>91.6644</v>
+        <v>91.2456</v>
       </c>
       <c r="D140" t="n">
-        <v>255.734</v>
+        <v>256.639</v>
       </c>
       <c r="E140" t="n">
-        <v>56.0526</v>
+        <v>55.818</v>
       </c>
       <c r="F140" t="n">
-        <v>167.556</v>
+        <v>168.154</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>107.881</v>
+        <v>110.409</v>
       </c>
       <c r="C141" t="n">
-        <v>92.0368</v>
+        <v>91.7278</v>
       </c>
       <c r="D141" t="n">
-        <v>253.997</v>
+        <v>254.588</v>
       </c>
       <c r="E141" t="n">
-        <v>55.324</v>
+        <v>55.632</v>
       </c>
       <c r="F141" t="n">
-        <v>166.694</v>
+        <v>168.558</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>106.528</v>
+        <v>107.328</v>
       </c>
       <c r="C142" t="n">
-        <v>92.3977</v>
+        <v>92.2473</v>
       </c>
       <c r="D142" t="n">
-        <v>252.279</v>
+        <v>253.023</v>
       </c>
       <c r="E142" t="n">
-        <v>55.1524</v>
+        <v>54.9856</v>
       </c>
       <c r="F142" t="n">
-        <v>165.791</v>
+        <v>165.918</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>108.994</v>
+        <v>109.85</v>
       </c>
       <c r="C143" t="n">
-        <v>92.3753</v>
+        <v>92.1966</v>
       </c>
       <c r="D143" t="n">
-        <v>250.687</v>
+        <v>251.679</v>
       </c>
       <c r="E143" t="n">
-        <v>54.6983</v>
+        <v>54.8882</v>
       </c>
       <c r="F143" t="n">
-        <v>164.832</v>
+        <v>165.324</v>
       </c>
     </row>
   </sheetData>
